--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -52697,6 +52697,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2276">
+      <c r="A2276" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2276" t="n">
+        <v>32385</v>
+      </c>
+      <c r="C2276" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D2276" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2276" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -52720,6 +52720,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2277" t="n">
+        <v>15835</v>
+      </c>
+      <c r="C2277" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2277" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -52743,6 +52743,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2278">
+      <c r="A2278" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2278" t="n">
+        <v>32092</v>
+      </c>
+      <c r="C2278" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="G2278" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -52766,6 +52766,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2279">
+      <c r="A2279" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2279" t="n">
+        <v>14720</v>
+      </c>
+      <c r="C2279" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="G2279" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -52607,22 +52607,22 @@
     </row>
     <row r="2272">
       <c r="A2272" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2272" t="n">
-        <v>23999</v>
+        <v>5794</v>
       </c>
       <c r="C2272" t="n">
-        <v>5.19999980926514</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="D2272" t="n">
-        <v>5.11999988555908</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="E2272" t="n">
-        <v>5.19999980926514</v>
+        <v>5.23999977111816</v>
       </c>
       <c r="F2272" t="n">
-        <v>5.1399998664856</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="G2272" t="s">
         <v>7</v>
@@ -52630,22 +52630,22 @@
     </row>
     <row r="2273">
       <c r="A2273" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2273" t="n">
-        <v>27775</v>
+        <v>23999</v>
       </c>
       <c r="C2273" t="n">
-        <v>5.21999979019165</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="D2273" t="n">
-        <v>5.05999994277954</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="E2273" t="n">
-        <v>5.15999984741211</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="F2273" t="n">
-        <v>5.17999982833862</v>
+        <v>5.1399998664856</v>
       </c>
       <c r="G2273" t="s">
         <v>7</v>
@@ -52653,22 +52653,22 @@
     </row>
     <row r="2274">
       <c r="A2274" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2274" t="n">
-        <v>12610</v>
+        <v>27775</v>
       </c>
       <c r="C2274" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="D2274" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E2274" t="n">
         <v>5.15999984741211</v>
       </c>
-      <c r="D2274" t="n">
-        <v>5.09999990463257</v>
-      </c>
-      <c r="E2274" t="n">
-        <v>5.1399998664856</v>
-      </c>
       <c r="F2274" t="n">
-        <v>5.15999984741211</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="G2274" t="s">
         <v>7</v>
@@ -52676,22 +52676,22 @@
     </row>
     <row r="2275">
       <c r="A2275" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2275" t="n">
-        <v>13511</v>
+        <v>12610</v>
       </c>
       <c r="C2275" t="n">
-        <v>5.34000015258789</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="D2275" t="n">
         <v>5.09999990463257</v>
       </c>
       <c r="E2275" t="n">
-        <v>5.17999982833862</v>
+        <v>5.1399998664856</v>
       </c>
       <c r="F2275" t="n">
-        <v>5.26000022888184</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="G2275" t="s">
         <v>7</v>
@@ -52699,22 +52699,22 @@
     </row>
     <row r="2276">
       <c r="A2276" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2276" t="n">
-        <v>32385</v>
+        <v>13511</v>
       </c>
       <c r="C2276" t="n">
-        <v>5.3600001335144</v>
+        <v>5.34000015258789</v>
       </c>
       <c r="D2276" t="n">
-        <v>5.28000020980835</v>
+        <v>5.09999990463257</v>
       </c>
       <c r="E2276" t="n">
-        <v>5.28000020980835</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="F2276" t="n">
-        <v>5.3600001335144</v>
+        <v>5.26000022888184</v>
       </c>
       <c r="G2276" t="s">
         <v>7</v>
@@ -52722,19 +52722,19 @@
     </row>
     <row r="2277">
       <c r="A2277" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2277" t="n">
-        <v>15835</v>
+        <v>32385</v>
       </c>
       <c r="C2277" t="n">
-        <v>5.48000001907349</v>
+        <v>5.3600001335144</v>
       </c>
       <c r="D2277" t="n">
-        <v>5.32000017166138</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="E2277" t="n">
-        <v>5.3600001335144</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="F2277" t="n">
         <v>5.3600001335144</v>
@@ -52745,22 +52745,22 @@
     </row>
     <row r="2278">
       <c r="A2278" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2278" t="n">
-        <v>32092</v>
+        <v>15835</v>
       </c>
       <c r="C2278" t="n">
-        <v>5.5</v>
+        <v>5.48000001907349</v>
       </c>
       <c r="D2278" t="n">
-        <v>5.34000015258789</v>
+        <v>5.32000017166138</v>
       </c>
       <c r="E2278" t="n">
-        <v>5.34000015258789</v>
+        <v>5.3600001335144</v>
       </c>
       <c r="F2278" t="n">
-        <v>5.40000009536743</v>
+        <v>5.3600001335144</v>
       </c>
       <c r="G2278" t="s">
         <v>7</v>
@@ -52768,24 +52768,47 @@
     </row>
     <row r="2279">
       <c r="A2279" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2279" t="n">
-        <v>14720</v>
+        <v>32092</v>
       </c>
       <c r="C2279" t="n">
         <v>5.5</v>
       </c>
       <c r="D2279" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F2279" t="n">
         <v>5.40000009536743</v>
       </c>
-      <c r="E2279" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F2279" t="n">
-        <v>5.44000005722046</v>
-      </c>
       <c r="G2279" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2280" t="n">
+        <v>20882</v>
+      </c>
+      <c r="C2280" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="G2280" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417622566223</v>
+        <v>2.91417598724365</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459334373474</v>
+        <v>2.78459358215332</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522269248962</v>
+        <v>2.86522245407104</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85514402389526</v>
+        <v>2.85514378547668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87098169326782</v>
+        <v>2.8709819316864</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818121910095</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522269248962</v>
+        <v>2.86522245407104</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697693824768</v>
+        <v>2.90697741508484</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91561603546143</v>
+        <v>2.91561627388</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841698646545</v>
+        <v>2.90841674804688</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92137503623962</v>
+        <v>2.9213752746582</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.91561603546143</v>
+        <v>2.91561627388</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85226392745972</v>
+        <v>2.8522641658783</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179215431213</v>
+        <v>2.79179239273071</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818121910095</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050992012024</v>
+        <v>2.81050968170166</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770873069763</v>
+        <v>2.81770896911621</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723648071289</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948722839355</v>
+        <v>2.6794867515564</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283862113953</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283862113953</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532513618469</v>
+        <v>2.69532489776611</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723648071289</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723648071289</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.64349174499512</v>
+        <v>2.64349150657654</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G79" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G80" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.6780469417572</v>
+        <v>2.67804741859436</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524646759033</v>
+        <v>2.68524622917175</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59885787963867</v>
+        <v>2.59885764122009</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>2.59885787963867</v>
+        <v>2.59885764122009</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52686738967896</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52686738967896</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767785072327</v>
+        <v>2.44767737388611</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767785072327</v>
+        <v>2.44767737388611</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.5</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51966834068298</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286215782166</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165811538696</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.60605645179749</v>
+        <v>2.60605669021606</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283862113953</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.52686738967896</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.52686738967896</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.52686738967896</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006192207336</v>
+        <v>2.57006120681763</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006192207336</v>
+        <v>2.57006120681763</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165811538696</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165811538696</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165811538696</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.51966834068298</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.5</v>
       </c>
       <c r="G122" t="n">
-        <v>2.51966834068298</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.52686738967896</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286215782166</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165811538696</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165811538696</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445978164673</v>
+        <v>2.58445930480957</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.62765383720398</v>
+        <v>2.62765407562256</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>2.72844076156616</v>
+        <v>2.72844052314758</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.60117435455322</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>2.82605957984924</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G178" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360179901123</v>
+        <v>2.74360203742981</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>2.63865542411804</v>
+        <v>2.63865566253662</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.90102171897888</v>
+        <v>2.9010214805603</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G193" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75</v>
       </c>
       <c r="G215" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109791755676</v>
+        <v>2.75109815597534</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G224" t="n">
-        <v>2.63115954399109</v>
+        <v>2.63115930557251</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618211746216</v>
+        <v>2.58618235588074</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>2.65364766120911</v>
+        <v>2.65364789962769</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.60117435455322</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G232" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.88602948188782</v>
+        <v>2.88602924346924</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>2.82605957984924</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103676795959</v>
+        <v>2.87103700637817</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103676795959</v>
+        <v>2.87103700637817</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.75</v>
       </c>
       <c r="G248" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.75</v>
       </c>
       <c r="G249" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.75</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.75</v>
       </c>
       <c r="G251" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.75</v>
       </c>
       <c r="G252" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G255" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G258" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381629943848</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883863449097</v>
+        <v>2.27883911132812</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.1738920211792</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>2.24135804176331</v>
+        <v>2.24135780334473</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.1514036655426</v>
+        <v>2.15140342712402</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>2.1738920211792</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.1738920211792</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>2.1738920211792</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>2.1738920211792</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398386478424</v>
+        <v>1.99398410320282</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G296" t="n">
-        <v>2.06894564628601</v>
+        <v>2.06894588470459</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390778541565</v>
+        <v>2.14390754699707</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630465507507</v>
+        <v>2.34630441665649</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G322" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G327" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G328" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G330" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874738693237</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381629943848</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381629943848</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>2.28633499145508</v>
+        <v>2.2863347530365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381629943848</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.21137356758118</v>
+        <v>2.2113733291626</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28633499145508</v>
+        <v>2.2863347530365</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383134841919</v>
+        <v>2.29383111000061</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383134841919</v>
+        <v>2.29383111000061</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381629943848</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381629943848</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.4887318611145</v>
+        <v>2.48873209953308</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370928764343</v>
+        <v>2.53370904922485</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>2.48123598098755</v>
+        <v>2.48123550415039</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868576049805</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868576049805</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.54870176315308</v>
+        <v>2.54870128631592</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.54870176315308</v>
+        <v>2.54870128631592</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>2.59367823600769</v>
+        <v>2.59367847442627</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868576049805</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66863989830017</v>
+        <v>2.66864013671875</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>2.82605957984924</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G387" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856369972229</v>
+        <v>2.81856417655945</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G391" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856369972229</v>
+        <v>2.81856417655945</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G408" t="n">
-        <v>2.95349502563477</v>
+        <v>2.95349526405334</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848773956299</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848773956299</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866326332092</v>
+        <v>2.91866302490234</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G418" t="n">
-        <v>2.90305542945862</v>
+        <v>2.90305519104004</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G419" t="n">
-        <v>2.90305542945862</v>
+        <v>2.90305519104004</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G420" t="n">
-        <v>2.90305542945862</v>
+        <v>2.90305519104004</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98109459877014</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.98109459877014</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670171737671</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G436" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G438" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.98109459877014</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.98109459877014</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G441" t="n">
-        <v>2.90305542945862</v>
+        <v>2.90305519104004</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G442" t="n">
-        <v>2.90305542945862</v>
+        <v>2.90305519104004</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G450" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G477" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G478" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G480" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>3.16838836669922</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764296531677</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764296531677</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.90305542945862</v>
+        <v>2.90305519104004</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.98109459877014</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717269897461</v>
+        <v>3.13717246055603</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474112510681</v>
+        <v>3.07474136352539</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183976173401</v>
+        <v>2.87183952331543</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G530" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772201538086</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.79380035400391</v>
+        <v>2.79380011558533</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>2.79380035400391</v>
+        <v>2.79380011558533</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>2.79380035400391</v>
+        <v>2.79380011558533</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.79380035400391</v>
+        <v>2.79380011558533</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G577" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G579" t="n">
-        <v>2.80940818786621</v>
+        <v>2.80940842628479</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>2.80940818786621</v>
+        <v>2.80940842628479</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407525062561</v>
+        <v>2.54407501220703</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772201538086</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772201538086</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51285934448242</v>
+        <v>2.51285982131958</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.4972517490387</v>
+        <v>2.49725198745728</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631097793579</v>
+        <v>2.21631121635437</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>2.31910848617554</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.5</v>
       </c>
       <c r="G628" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.99015688896179</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.5</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.5</v>
       </c>
       <c r="G634" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.5</v>
       </c>
       <c r="G636" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.99015688896179</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3</v>
       </c>
       <c r="G642" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3</v>
       </c>
       <c r="G649" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3</v>
       </c>
       <c r="G650" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3</v>
       </c>
       <c r="G653" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G656" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.61516451835632</v>
+        <v>2.61516427993774</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3</v>
       </c>
       <c r="G663" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G667" t="n">
-        <v>2.35200333595276</v>
+        <v>2.35200309753418</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G670" t="n">
-        <v>2.31910848617554</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G671" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G677" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G690" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G692" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G697" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G699" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G701" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G719" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G722" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G724" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G725" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G729" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G730" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G751" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G759" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.99015688896179</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.9737092256546</v>
+        <v>1.97370898723602</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.03949952125549</v>
+        <v>2.03949928283691</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.03949952125549</v>
+        <v>2.03949928283691</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.80923366546631</v>
+        <v>1.80923354625702</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633845806122</v>
+        <v>1.77633833885193</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G787" t="n">
-        <v>1.80923366546631</v>
+        <v>1.80923354625702</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502372264862</v>
+        <v>1.87502384185791</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502372264862</v>
+        <v>1.87502384185791</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147138595581</v>
+        <v>1.89147126674652</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.99015688896179</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.9737092256546</v>
+        <v>1.97370898723602</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>2.03949952125549</v>
+        <v>2.03949928283691</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G804" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G806" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G823" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G826" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964067459106</v>
+        <v>2.77964043617249</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.6645073890686</v>
+        <v>2.66450762748718</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3</v>
       </c>
       <c r="G842" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3</v>
       </c>
       <c r="G843" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3</v>
       </c>
       <c r="G844" t="n">
-        <v>2.46713638305664</v>
+        <v>2.46713662147522</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>2.6645073890686</v>
+        <v>2.66450762748718</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G856" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G858" t="n">
-        <v>2.76319265365601</v>
+        <v>2.76319289207458</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="n">
-        <v>2.82898330688477</v>
+        <v>2.82898354530334</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>2.86187815666199</v>
+        <v>2.86187863349915</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G872" t="n">
-        <v>2.86187815666199</v>
+        <v>2.86187863349915</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766833305359</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411587715149</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411587715149</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411587715149</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766833305359</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635431289673</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G892" t="n">
-        <v>3.00168299674988</v>
+        <v>3.00168251991272</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635431289673</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102562904358</v>
+        <v>3.051025390625</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280161857605</v>
+        <v>3.04280185699463</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G907" t="n">
-        <v>3.12503933906555</v>
+        <v>3.12503957748413</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>3.14971089363098</v>
+        <v>3.14971113204956</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.14971089363098</v>
+        <v>3.14971113204956</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727753639221</v>
+        <v>3.20727729797363</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G919" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438197135925</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438197135925</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G921" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G922" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>3.09018111228943</v>
+        <v>3.09018135070801</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>3.09018111228943</v>
+        <v>3.09018135070801</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.1491219997406</v>
+        <v>3.14912176132202</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276660919189</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434685707092</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644728660583</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>3.52802729606628</v>
+        <v>3.52802705764771</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434685707092</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>3.57012724876404</v>
+        <v>3.57012748718262</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G968" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752419471741</v>
+        <v>3.31752443313599</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G984" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>3.35120463371277</v>
+        <v>3.35120439529419</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.65432858467102</v>
+        <v>3.6543288230896</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.58696794509888</v>
+        <v>3.5869677066803</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481365203857</v>
+        <v>4.02481412887573</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007457733154</v>
+        <v>4.05007362365723</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059452056885</v>
+        <v>4.10059404373169</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.99113321304321</v>
+        <v>3.99113297462463</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.76378989219666</v>
+        <v>3.76378965377808</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.94061255455017</v>
+        <v>3.94061231613159</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.92377209663391</v>
+        <v>3.92377233505249</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.86483216285706</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.92377209663391</v>
+        <v>3.92377233505249</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.86483216285706</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.7974705696106</v>
+        <v>3.79747104644775</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.94061255455017</v>
+        <v>3.94061231613159</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849361419678</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.75</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.99955320358276</v>
+        <v>3.99955296516418</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849361419678</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.75</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.99955320358276</v>
+        <v>3.99955296516418</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587252616882</v>
+        <v>3.96587300300598</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535186767578</v>
+        <v>3.91535210609436</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.86483216285706</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.65432858467102</v>
+        <v>3.6543288230896</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.72168970108032</v>
+        <v>3.72168946266174</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118659973145</v>
+        <v>3.51118683815002</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.58696794509888</v>
+        <v>3.5869677066803</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.78063035011292</v>
+        <v>3.78063011169434</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644728660583</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276660919189</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434685707092</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.11544156074524</v>
+        <v>3.11544179916382</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.86283850669861</v>
+        <v>2.86283826828003</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80389738082886</v>
+        <v>2.80389714241028</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.16596221923828</v>
+        <v>3.16596245765686</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41084337234497</v>
+        <v>3.41084361076355</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209770202637</v>
+        <v>3.40209794044495</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.3321316242218</v>
+        <v>3.33213138580322</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.20094513893127</v>
+        <v>3.20094537734985</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.75491189956665</v>
+        <v>2.75491213798523</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>3</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.69369173049927</v>
+        <v>2.69369149208069</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.03477621078491</v>
+        <v>3.03477597236633</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.57999682426453</v>
+        <v>2.57999706268311</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.57999682426453</v>
+        <v>2.57999706268311</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.77240347862244</v>
+        <v>2.77240371704102</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.69369173049927</v>
+        <v>2.69369149208069</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.57999682426453</v>
+        <v>2.57999706268311</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.77240347862244</v>
+        <v>2.77240371704102</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.80738639831543</v>
+        <v>2.80738663673401</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.25341963768005</v>
+        <v>3.25341987609863</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.29714846611023</v>
+        <v>3.29714870452881</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.16596221923828</v>
+        <v>3.16596245765686</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470788955688</v>
+        <v>3.17470836639404</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.03477621078491</v>
+        <v>3.03477597236633</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.99979305267334</v>
+        <v>2.99979329109192</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.73742055892944</v>
+        <v>2.73742032051086</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.049156665802</v>
+        <v>3.04915642738342</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30746984481812</v>
+        <v>2.30747008323669</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -59704,6 +59704,32 @@
         <v>5.48000001907349</v>
       </c>
       <c r="H2282" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2283" t="n">
+        <v>9875</v>
+      </c>
+      <c r="C2283" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="H2283" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417598724365</v>
+        <v>2.91417622566223</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802340507507</v>
+        <v>2.85802316665649</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459358215332</v>
+        <v>2.78459334373474</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522245407104</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85082459449768</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82922744750977</v>
+        <v>2.82922697067261</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8709819316864</v>
+        <v>2.87098145484924</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818121910095</v>
+        <v>2.87818050384521</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569470405579</v>
+        <v>2.92569446563721</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94873189926147</v>
+        <v>2.9487316608429</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009280204773</v>
+        <v>2.94009304046631</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522245407104</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697741508484</v>
+        <v>2.90697717666626</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.90121793746948</v>
+        <v>2.90121746063232</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91561627388</v>
+        <v>2.91561603546143</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841674804688</v>
+        <v>2.9084165096283</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113903045654</v>
+        <v>2.89113879203796</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.91561627388</v>
+        <v>2.91561603546143</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433356285095</v>
+        <v>2.93433380126953</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433356285095</v>
+        <v>2.93433380126953</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113903045654</v>
+        <v>2.89113879203796</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.85082459449768</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.82922744750977</v>
+        <v>2.82922697067261</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G40" t="n">
-        <v>2.80331087112427</v>
+        <v>2.80331110954285</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338953971863</v>
+        <v>2.81338906288147</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818121910095</v>
+        <v>2.87818050384521</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.80043125152588</v>
+        <v>2.80043148994446</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77883386611938</v>
+        <v>2.77883410453796</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532489776611</v>
+        <v>2.69532465934753</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>2.79323196411133</v>
+        <v>2.79323244094849</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.64349150657654</v>
+        <v>2.6434919834137</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.67804741859436</v>
+        <v>2.67804718017578</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686667442322</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686667442322</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767737388611</v>
+        <v>2.44767761230469</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647380828857</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647380828857</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767737388611</v>
+        <v>2.44767761230469</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165859222412</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686667442322</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686667442322</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686667442322</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165859222412</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165859222412</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165859222412</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686667442322</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165859222412</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165859222412</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445930480957</v>
+        <v>2.58445906639099</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.80043125152588</v>
+        <v>2.80043148994446</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>2.80043125152588</v>
+        <v>2.80043148994446</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.80762982368469</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G162" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G163" t="n">
-        <v>2.80043125152588</v>
+        <v>2.80043148994446</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G164" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.85082459449768</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362578392029</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G169" t="n">
-        <v>2.77883386611938</v>
+        <v>2.77883410453796</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857922554016</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G178" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360203742981</v>
+        <v>2.74360179901123</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>2.63865566253662</v>
+        <v>2.63865542411804</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66114377975464</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612096786499</v>
+        <v>2.70612120628357</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.9010214805603</v>
+        <v>2.90102171897888</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G193" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G198" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G203" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G205" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612096786499</v>
+        <v>2.70612120628357</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618235588074</v>
+        <v>2.58618211746216</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867071151733</v>
+        <v>2.60867094993591</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.66114377975464</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G232" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609039306641</v>
+        <v>2.76609063148499</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G255" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857922554016</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381629943848</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635027885437</v>
+        <v>2.25635004043579</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883911132812</v>
+        <v>2.27883887290955</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.15140342712402</v>
+        <v>2.1514036655426</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398410320282</v>
+        <v>1.99398386478424</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G296" t="n">
-        <v>2.06894588470459</v>
+        <v>2.06894564628601</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644176483154</v>
+        <v>2.07644200325012</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625855445862</v>
+        <v>2.43625831604004</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630441665649</v>
+        <v>2.34630417823792</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35380077362061</v>
+        <v>2.35380053520203</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G327" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G328" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G330" t="n">
-        <v>2.45874738693237</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381629943848</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381629943848</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G342" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>2.36129665374756</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381629943848</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.2113733291626</v>
+        <v>2.21137309074402</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383111000061</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383111000061</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381629943848</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381629943848</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>2.61616683006287</v>
+        <v>2.61616706848145</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.48873209953308</v>
+        <v>2.48873138427734</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>2.48123550415039</v>
+        <v>2.48123574256897</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.66114377975464</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607510566711</v>
+        <v>2.79607534408569</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604429244995</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604429244995</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604429244995</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G387" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856417655945</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G391" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856417655945</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G408" t="n">
-        <v>2.95349526405334</v>
+        <v>2.95349478721619</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848773956299</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848773956299</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866302490234</v>
+        <v>2.91866278648376</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278029441833</v>
+        <v>3.15278005599976</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.02791786193848</v>
+        <v>3.02791810035706</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G477" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G478" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G480" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>3.16838812828064</v>
+        <v>3.16838788986206</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717246055603</v>
+        <v>3.13717269897461</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474136352539</v>
+        <v>3.07474112510681</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278029441833</v>
+        <v>3.15278005599976</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183952331543</v>
+        <v>2.87183976173401</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.7625846862793</v>
+        <v>2.76258444786072</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697685241699</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.5</v>
       </c>
       <c r="G540" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>2.63772201538086</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G550" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.79380011558533</v>
+        <v>2.79380035400391</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697685241699</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>2.79380011558533</v>
+        <v>2.79380035400391</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>2.79380011558533</v>
+        <v>2.79380035400391</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.79380011558533</v>
+        <v>2.79380035400391</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>2.7625846862793</v>
+        <v>2.76258444786072</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407501220703</v>
+        <v>2.54407525062561</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G596" t="n">
-        <v>2.52846741676331</v>
+        <v>2.52846765518188</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63772201538086</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.5</v>
       </c>
       <c r="G605" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>2.7625846862793</v>
+        <v>2.76258444786072</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697685241699</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.5</v>
       </c>
       <c r="G608" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63772201538086</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631121635437</v>
+        <v>2.21631097793579</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>2.31910824775696</v>
+        <v>2.31910800933838</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3</v>
       </c>
       <c r="G642" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>2.36845111846924</v>
+        <v>2.36845088005066</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.53292679786682</v>
+        <v>2.53292655944824</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3</v>
       </c>
       <c r="G649" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3</v>
       </c>
       <c r="G650" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.53292679786682</v>
+        <v>2.53292655944824</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3</v>
       </c>
       <c r="G653" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>2.53292679786682</v>
+        <v>2.53292655944824</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.61516427993774</v>
+        <v>2.6151647567749</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3</v>
       </c>
       <c r="G663" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555603027344</v>
+        <v>2.33555579185486</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G670" t="n">
-        <v>2.31910824775696</v>
+        <v>2.31910800933838</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G671" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G677" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G678" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G690" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G703" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G712" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>2.36845111846924</v>
+        <v>2.36845088005066</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G716" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G721" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G731" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G759" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370898723602</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.03949928283691</v>
+        <v>2.03949952125549</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.03949928283691</v>
+        <v>2.03949952125549</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212851524353</v>
+        <v>1.84212875366211</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.80923354625702</v>
+        <v>1.80923330783844</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633833885193</v>
+        <v>1.77633845806122</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212851524353</v>
+        <v>1.84212875366211</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212851524353</v>
+        <v>1.84212875366211</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G787" t="n">
-        <v>1.80923354625702</v>
+        <v>1.80923330783844</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502384185791</v>
+        <v>1.87502360343933</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502384185791</v>
+        <v>1.87502360343933</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="n">
-        <v>1.92436635494232</v>
+        <v>1.92436623573303</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370898723602</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>2.03949928283691</v>
+        <v>2.03949952125549</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G803" t="n">
-        <v>2.18752765655518</v>
+        <v>2.1875274181366</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G811" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G812" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G814" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G820" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G821" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G823" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G824" t="n">
-        <v>2.28621315956116</v>
+        <v>2.28621339797974</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964043617249</v>
+        <v>2.77964067459106</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.66450762748718</v>
+        <v>2.6645073890686</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>2.6316123008728</v>
+        <v>2.63161206245422</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3</v>
       </c>
       <c r="G842" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3</v>
       </c>
       <c r="G843" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3</v>
       </c>
       <c r="G844" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G854" t="n">
-        <v>2.6316123008728</v>
+        <v>2.63161206245422</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>2.66450762748718</v>
+        <v>2.6645073890686</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G857" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G859" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G860" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="n">
-        <v>2.82898354530334</v>
+        <v>2.82898330688477</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>2.86187863349915</v>
+        <v>2.86187839508057</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G872" t="n">
-        <v>2.86187863349915</v>
+        <v>2.86187839508057</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766880989075</v>
+        <v>2.92766857147217</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>2.94411587715149</v>
+        <v>2.94411611557007</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.94411587715149</v>
+        <v>2.94411611557007</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.94411587715149</v>
+        <v>2.94411611557007</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766880989075</v>
+        <v>2.92766857147217</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G892" t="n">
-        <v>3.00168251991272</v>
+        <v>3.0016827583313</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G895" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G896" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G897" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G898" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G899" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G900" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.051025390625</v>
+        <v>3.05102562904358</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>3.11681580543518</v>
+        <v>3.1168155670166</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>3.11681580543518</v>
+        <v>3.1168155670166</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G907" t="n">
-        <v>3.12503957748413</v>
+        <v>3.12503933906555</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>3.14971113204956</v>
+        <v>3.14971089363098</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.14971113204956</v>
+        <v>3.14971089363098</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727729797363</v>
+        <v>3.20727753639221</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>3.0674729347229</v>
+        <v>3.06747317314148</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>3.11681580543518</v>
+        <v>3.1168155670166</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G919" t="n">
-        <v>3.17438197135925</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.17438197135925</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G922" t="n">
-        <v>3.20806288719177</v>
+        <v>3.20806264877319</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.14912176132202</v>
+        <v>3.1491219997406</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46066617965698</v>
+        <v>3.46066641807556</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646532058716</v>
+        <v>3.37646508216858</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>3.38488531112671</v>
+        <v>3.38488507270813</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>3.38488531112671</v>
+        <v>3.38488507270813</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276660919189</v>
+        <v>3.50276684761047</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644704818726</v>
+        <v>3.53644680976868</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.46066617965698</v>
+        <v>3.46066641807556</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G950" t="n">
-        <v>3.4269859790802</v>
+        <v>3.42698574066162</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490310668945</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068421363831</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594442367554</v>
+        <v>3.32594466209412</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068421363831</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G974" t="n">
-        <v>3.28384375572205</v>
+        <v>3.28384399414062</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068421363831</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172505378723</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>3.4269859790802</v>
+        <v>3.42698574066162</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646532058716</v>
+        <v>3.37646508216858</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>3.38488531112671</v>
+        <v>3.38488507270813</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>3.38488531112671</v>
+        <v>3.38488507270813</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>3.38488531112671</v>
+        <v>3.38488507270813</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>3.38488531112671</v>
+        <v>3.38488507270813</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.6543288230896</v>
+        <v>3.65432906150818</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059404373169</v>
+        <v>4.10059452056885</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.76378965377808</v>
+        <v>3.76378989219666</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957123756409</v>
+        <v>3.83957099914551</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.78905034065247</v>
+        <v>3.78905081748962</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.92377233505249</v>
+        <v>3.92377185821533</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957123756409</v>
+        <v>3.83957099914551</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.86483120918274</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.92377233505249</v>
+        <v>3.92377185821533</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.86483120918274</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849361419678</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.13427495956421</v>
+        <v>4.13427543640137</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.06691455841064</v>
+        <v>4.06691408157349</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.01639366149902</v>
+        <v>4.01639318466187</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.01639366149902</v>
+        <v>4.01639318466187</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849361419678</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535210609436</v>
+        <v>3.91535258293152</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.86483120918274</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.78905034065247</v>
+        <v>3.78905081748962</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274857521057</v>
+        <v>3.66274881362915</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.6543288230896</v>
+        <v>3.65432906150818</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484948158264</v>
+        <v>3.70484924316406</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.63748860359192</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484948158264</v>
+        <v>3.70484924316406</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.81431102752686</v>
+        <v>3.81431126594543</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.72168946266174</v>
+        <v>3.72168970108032</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906837463379</v>
+        <v>3.62906861305237</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484948158264</v>
+        <v>3.70484924316406</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.63748860359192</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118683815002</v>
+        <v>3.51118659973145</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.60380816459656</v>
+        <v>3.60380792617798</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.63748860359192</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274857521057</v>
+        <v>3.66274881362915</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326971054077</v>
+        <v>3.71326923370361</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.78905034065247</v>
+        <v>3.78905081748962</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326971054077</v>
+        <v>3.71326923370361</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.78063011169434</v>
+        <v>3.78063035011292</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.60380816459656</v>
+        <v>3.60380792617798</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.60380816459656</v>
+        <v>3.60380792617798</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906837463379</v>
+        <v>3.62906861305237</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644704818726</v>
+        <v>3.53644680976868</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276660919189</v>
+        <v>3.50276684761047</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.4269859790802</v>
+        <v>3.42698574066162</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172505378723</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.4269859790802</v>
+        <v>3.42698574066162</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46066617965698</v>
+        <v>3.46066641807556</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.48592638969421</v>
+        <v>3.48592662811279</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.4269859790802</v>
+        <v>3.42698574066162</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.4269859790802</v>
+        <v>3.42698574066162</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172505378723</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.48592638969421</v>
+        <v>3.48592662811279</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068421363831</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594442367554</v>
+        <v>3.32594466209412</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490310668945</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.20806288719177</v>
+        <v>3.20806264877319</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.20806288719177</v>
+        <v>3.20806264877319</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.20806288719177</v>
+        <v>3.20806264877319</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.20806288719177</v>
+        <v>3.20806264877319</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.28384375572205</v>
+        <v>3.28384399414062</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -59730,6 +59730,32 @@
         <v>5.46000003814697</v>
       </c>
       <c r="H2283" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2284" t="n">
+        <v>10312</v>
+      </c>
+      <c r="C2284" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="D2284" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="G2284" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="H2284" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802316665649</v>
+        <v>2.85802340507507</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459334373474</v>
+        <v>2.784592628479</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.87242150306702</v>
+        <v>2.8724217414856</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522269248962</v>
+        <v>2.86522245407104</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85514378547668</v>
+        <v>2.85514402389526</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82922697067261</v>
+        <v>2.82922744750977</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.87242150306702</v>
+        <v>2.8724217414856</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818050384521</v>
+        <v>2.87818074226379</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569446563721</v>
+        <v>2.92569470405579</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009304046631</v>
+        <v>2.94009256362915</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522269248962</v>
+        <v>2.86522245407104</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.90121746063232</v>
+        <v>2.90121793746948</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9084165096283</v>
+        <v>2.90841698646545</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8522641658783</v>
+        <v>2.85226440429688</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>2.89401888847351</v>
+        <v>2.89401865005493</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.82922697067261</v>
+        <v>2.82922744750977</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G40" t="n">
-        <v>2.80331110954285</v>
+        <v>2.80331087112427</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179239273071</v>
+        <v>2.79179215431213</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818050384521</v>
+        <v>2.87818074226379</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050968170166</v>
+        <v>2.81050992012024</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.80043148994446</v>
+        <v>2.80043077468872</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.80475044250488</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80475044250488</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80475044250488</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.80475044250488</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723648071289</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412109375</v>
+        <v>2.72412133216858</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77883410453796</v>
+        <v>2.77883386611938</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532465934753</v>
+        <v>2.69532489776611</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>2.79323244094849</v>
+        <v>2.79323220252991</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723648071289</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723648071289</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6434919834137</v>
+        <v>2.64349174499512</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G81" t="n">
-        <v>2.65069055557251</v>
+        <v>2.65069079399109</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.67804718017578</v>
+        <v>2.6780469417572</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.69244503974915</v>
+        <v>2.69244527816772</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.69244503974915</v>
+        <v>2.69244527816772</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52686667442322</v>
+        <v>2.52686738967896</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52686667442322</v>
+        <v>2.52686738967896</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286215782166</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.60605669021606</v>
+        <v>2.60605645179749</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.52686667442322</v>
+        <v>2.52686738967896</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.52686667442322</v>
+        <v>2.52686738967896</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.52686667442322</v>
+        <v>2.52686738967896</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006120681763</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006120681763</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.52686667442322</v>
+        <v>2.52686738967896</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286215782166</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445906639099</v>
+        <v>2.58445954322815</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.80043148994446</v>
+        <v>2.80043077468872</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>2.80043148994446</v>
+        <v>2.80043077468872</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G163" t="n">
-        <v>2.80043148994446</v>
+        <v>2.80043077468872</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G169" t="n">
-        <v>2.77883410453796</v>
+        <v>2.77883386611938</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>2.78857922554016</v>
+        <v>2.78857898712158</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.6011745929718</v>
+        <v>2.60117483139038</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>2.8260600566864</v>
+        <v>2.82605981826782</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360179901123</v>
+        <v>2.74360203742981</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612120628357</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.90102171897888</v>
+        <v>2.90102124214172</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G198" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G202" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G205" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G213" t="n">
-        <v>2.89352536201477</v>
+        <v>2.89352560043335</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75</v>
       </c>
       <c r="G215" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109815597534</v>
+        <v>2.75109839439392</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612120628357</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618211746216</v>
+        <v>2.58618235588074</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.5</v>
       </c>
       <c r="G226" t="n">
-        <v>2.62366318702698</v>
+        <v>2.6236629486084</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>2.65364789962769</v>
+        <v>2.65364766120911</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.6011745929718</v>
+        <v>2.60117483139038</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355641365051</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>2.8260600566864</v>
+        <v>2.82605981826782</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111368179321</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103676795959</v>
+        <v>2.87103652954102</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103676795959</v>
+        <v>2.87103652954102</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609063148499</v>
+        <v>2.76609015464783</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.75</v>
       </c>
       <c r="G248" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.75</v>
       </c>
       <c r="G249" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.75</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.75</v>
       </c>
       <c r="G251" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.75</v>
       </c>
       <c r="G252" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>2.78857922554016</v>
+        <v>2.78857898712158</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883887290955</v>
+        <v>2.27883863449097</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638085365295</v>
+        <v>2.19638061523438</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.13641142845154</v>
+        <v>2.13641119003296</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398386478424</v>
+        <v>1.99398410320282</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390754699707</v>
+        <v>2.14390730857849</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625831604004</v>
+        <v>2.4362587928772</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630417823792</v>
+        <v>2.34630489349365</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35380053520203</v>
+        <v>2.35380077362061</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.46624326705933</v>
+        <v>2.46624350547791</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46624326705933</v>
+        <v>2.46624350547791</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G322" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>2.28633499145508</v>
+        <v>2.2863347530365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>2.28633499145508</v>
+        <v>2.2863347530365</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383087158203</v>
+        <v>2.29383134841919</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383087158203</v>
+        <v>2.29383134841919</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885392189026</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.48873138427734</v>
+        <v>2.4887318611145</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.54870128631592</v>
+        <v>2.5487015247345</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.54870128631592</v>
+        <v>2.5487015247345</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.5</v>
       </c>
       <c r="G374" t="n">
-        <v>2.62366318702698</v>
+        <v>2.6236629486084</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.5</v>
       </c>
       <c r="G375" t="n">
-        <v>2.62366318702698</v>
+        <v>2.6236629486084</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607534408569</v>
+        <v>2.79607486724854</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>2.8260600566864</v>
+        <v>2.82605981826782</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355641365051</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856393814087</v>
+        <v>2.81856369972229</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.9385027885437</v>
+        <v>2.93850255012512</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355641365051</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355641365051</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856393814087</v>
+        <v>2.81856369972229</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357146263123</v>
+        <v>2.8035717010498</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355641365051</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848726272583</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848726272583</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>2.94987869262695</v>
+        <v>2.94987893104553</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866278648376</v>
+        <v>2.91866326332092</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>2.94987869262695</v>
+        <v>2.94987893104553</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94987869262695</v>
+        <v>2.94987893104553</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G438" t="n">
-        <v>2.94987869262695</v>
+        <v>2.94987893104553</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>2.94987869262695</v>
+        <v>2.94987893104553</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.29325079917908</v>
+        <v>3.29325032234192</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G450" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278005599976</v>
+        <v>3.15278053283691</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.02791810035706</v>
+        <v>3.0279176235199</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G477" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G478" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G480" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764296531677</v>
+        <v>3.27764272689819</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764296531677</v>
+        <v>3.27764272689819</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.37129020690918</v>
+        <v>3.37128973007202</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203513145447</v>
+        <v>3.26203465461731</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717269897461</v>
+        <v>3.13717246055603</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278005599976</v>
+        <v>3.15278053283691</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183976173401</v>
+        <v>2.87183952331543</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.76258444786072</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697709083557</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.5</v>
       </c>
       <c r="G540" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697709083557</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>2.76258444786072</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G579" t="n">
-        <v>2.80940842628479</v>
+        <v>2.80940818786621</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>2.80940842628479</v>
+        <v>2.80940818786621</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407525062561</v>
+        <v>2.54407501220703</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G596" t="n">
-        <v>2.52846765518188</v>
+        <v>2.52846741676331</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G598" t="n">
-        <v>2.59089851379395</v>
+        <v>2.59089875221252</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G601" t="n">
-        <v>2.59089851379395</v>
+        <v>2.59089875221252</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.5</v>
       </c>
       <c r="G605" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>2.76258444786072</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697709083557</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.5</v>
       </c>
       <c r="G608" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51285982131958</v>
+        <v>2.51285934448242</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.49725198745728</v>
+        <v>2.49725151062012</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>2.45042824745178</v>
+        <v>2.45042848587036</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>2.37238931655884</v>
+        <v>2.37238907814026</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631097793579</v>
+        <v>2.21631073951721</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>2.31910800933838</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015665054321</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.9572616815567</v>
+        <v>1.95726156234741</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015665054321</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G639" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>2.36845088005066</v>
+        <v>2.36845111846924</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G648" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>2.51647901535034</v>
+        <v>2.51647925376892</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.54937410354614</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G656" t="n">
-        <v>2.51647901535034</v>
+        <v>2.51647925376892</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.6151647567749</v>
+        <v>2.61516451835632</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555579185486</v>
+        <v>2.33555555343628</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G670" t="n">
-        <v>2.31910800933838</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G673" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G678" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>2.36845088005066</v>
+        <v>2.36845111846924</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G731" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G759" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015665054321</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.9737092256546</v>
+        <v>1.97370910644531</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.9572616815567</v>
+        <v>1.95726156234741</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212875366211</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633845806122</v>
+        <v>1.77633810043335</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212875366211</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G779" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>1.90791893005371</v>
+        <v>1.90791881084442</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G781" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G782" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90791893005371</v>
+        <v>1.90791881084442</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278600215912</v>
+        <v>1.79278588294983</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278600215912</v>
+        <v>1.79278588294983</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212875366211</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502348423004</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502348423004</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>1.90791893005371</v>
+        <v>1.90791881084442</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="n">
-        <v>1.92436623573303</v>
+        <v>1.92436635494232</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015665054321</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.9737092256546</v>
+        <v>1.97370910644531</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108058929443</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G803" t="n">
-        <v>2.1875274181366</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>2.51647901535034</v>
+        <v>2.51647925376892</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>2.79608821868896</v>
+        <v>2.79608798027039</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G831" t="n">
-        <v>2.79608821868896</v>
+        <v>2.79608798027039</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964067459106</v>
+        <v>2.77964043617249</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>2.63161206245422</v>
+        <v>2.6316123008728</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>2.54937410354614</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>2.54937410354614</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>2.54937410354614</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.58226943016052</v>
+        <v>2.5822696685791</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>2.54937410354614</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58226943016052</v>
+        <v>2.5822696685791</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>2.6480598449707</v>
+        <v>2.64805960655212</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G854" t="n">
-        <v>2.63161206245422</v>
+        <v>2.6316123008728</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G856" t="n">
-        <v>2.6480598449707</v>
+        <v>2.64805960655212</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G858" t="n">
-        <v>2.76319289207458</v>
+        <v>2.76319265365601</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G871" t="n">
-        <v>2.79608821868896</v>
+        <v>2.79608798027039</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766857147217</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411635398865</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411635398865</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411635398865</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766857147217</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>2.96056365966797</v>
+        <v>2.96056389808655</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635431289673</v>
+        <v>3.02635407447815</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635431289673</v>
+        <v>3.02635407447815</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G895" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G896" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G897" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G898" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G899" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G900" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102562904358</v>
+        <v>3.051025390625</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793442726135</v>
+        <v>3.15793466567993</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>3.14971089363098</v>
+        <v>3.1497106552124</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793442726135</v>
+        <v>3.15793466567993</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.14971089363098</v>
+        <v>3.1497106552124</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.22372508049011</v>
+        <v>3.22372484207153</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.16615843772888</v>
+        <v>3.1661581993103</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>3.06747317314148</v>
+        <v>3.06747269630432</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G921" t="n">
-        <v>3.21648263931274</v>
+        <v>3.21648287773132</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276684761047</v>
+        <v>3.50276637077332</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434685707092</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G950" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434685707092</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G954" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>3.57012748718262</v>
+        <v>3.57012724876404</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G956" t="n">
-        <v>3.62064838409424</v>
+        <v>3.62064814567566</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G964" t="n">
-        <v>3.41014552116394</v>
+        <v>3.41014575958252</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>3.21648263931274</v>
+        <v>3.21648287773132</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490286827087</v>
+        <v>3.22490262985229</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G968" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594418525696</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752443313599</v>
+        <v>3.31752419471741</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G979" t="n">
-        <v>3.41014552116394</v>
+        <v>3.41014575958252</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>3.40172505378723</v>
+        <v>3.40172529220581</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.41014552116394</v>
+        <v>3.41014575958252</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>3.35120439529419</v>
+        <v>3.35120463371277</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.65432906150818</v>
+        <v>3.65432858467102</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481412887573</v>
+        <v>4.02481365203857</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.19321584701538</v>
+        <v>4.19321632385254</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059452056885</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.99113297462463</v>
+        <v>3.99113321304321</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.8058910369873</v>
+        <v>3.80589079856873</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.78905081748962</v>
+        <v>3.78905057907104</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.92377185821533</v>
+        <v>3.92377233505249</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429251670837</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641121864319</v>
+        <v>3.85641145706177</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.92377185821533</v>
+        <v>3.92377233505249</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.8058910369873</v>
+        <v>3.80589079856873</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.79747104644775</v>
+        <v>3.7974705696106</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.94903254508972</v>
+        <v>3.9490327835083</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429251670837</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849409103394</v>
+        <v>4.05849456787109</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.13427543640137</v>
+        <v>4.13427495956421</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.75</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.99955296516418</v>
+        <v>3.99955344200134</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.01639318466187</v>
+        <v>4.01639366149902</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.01639318466187</v>
+        <v>4.01639366149902</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849409103394</v>
+        <v>4.05849456787109</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.75</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.99955296516418</v>
+        <v>3.99955344200134</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587300300598</v>
+        <v>3.96587324142456</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535258293152</v>
+        <v>3.91535210609436</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.78905081748962</v>
+        <v>3.78905057907104</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.68800950050354</v>
+        <v>3.6880087852478</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.65432906150818</v>
+        <v>3.65432858467102</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748836517334</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641121864319</v>
+        <v>3.85641145706177</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429251670837</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009189605713</v>
+        <v>3.89009165763855</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.81431126594543</v>
+        <v>3.81431102752686</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.72168970108032</v>
+        <v>3.72168946266174</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906861305237</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748836517334</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.60380792617798</v>
+        <v>3.60380816459656</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748836517334</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.62064838409424</v>
+        <v>3.62064814567566</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326923370361</v>
+        <v>3.71326947212219</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.57854771614075</v>
+        <v>3.57854747772217</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.57854771614075</v>
+        <v>3.57854747772217</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.78905081748962</v>
+        <v>3.78905057907104</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62064838409424</v>
+        <v>3.62064814567566</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326923370361</v>
+        <v>3.71326947212219</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.60380792617798</v>
+        <v>3.60380816459656</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.60380792617798</v>
+        <v>3.60380816459656</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906861305237</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276684761047</v>
+        <v>3.50276637077332</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.40172505378723</v>
+        <v>3.40172529220581</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.48592662811279</v>
+        <v>3.48592638969421</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.57854771614075</v>
+        <v>3.57854747772217</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.62064838409424</v>
+        <v>3.62064814567566</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.40172505378723</v>
+        <v>3.40172529220581</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434685707092</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.48592662811279</v>
+        <v>3.48592638969421</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.27542400360107</v>
+        <v>3.2754237651825</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.11544179916382</v>
+        <v>3.11544156074524</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80389714241028</v>
+        <v>2.80389761924744</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594418525696</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490286827087</v>
+        <v>3.22490262985229</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.21648263931274</v>
+        <v>3.21648287773132</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.25858330726624</v>
+        <v>3.25858306884766</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.25858330726624</v>
+        <v>3.25858306884766</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.21648263931274</v>
+        <v>3.21648287773132</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.27542400360107</v>
+        <v>3.2754237651825</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.27542400360107</v>
+        <v>3.2754237651825</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.29226398468018</v>
+        <v>3.2922637462616</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.29226398468018</v>
+        <v>3.2922637462616</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.21648263931274</v>
+        <v>3.21648287773132</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.15754222869873</v>
+        <v>3.15754199028015</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.15754222869873</v>
+        <v>3.15754199028015</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.16596245765686</v>
+        <v>3.16596221923828</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41084361076355</v>
+        <v>3.41084337234497</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209794044495</v>
+        <v>3.40209770202637</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965712547302</v>
+        <v>3.27965688705444</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.07850456237793</v>
+        <v>3.07850480079651</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599614143372</v>
+        <v>3.09599637985229</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.07850456237793</v>
+        <v>3.07850480079651</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.84236931800842</v>
+        <v>2.842369556427</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.75491213798523</v>
+        <v>2.75491189956665</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.55375981330872</v>
+        <v>2.55375957489014</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.69369149208069</v>
+        <v>2.69369173049927</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.07850456237793</v>
+        <v>3.07850480079651</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.84236931800842</v>
+        <v>2.842369556427</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.6761999130249</v>
+        <v>2.67620015144348</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630191802979</v>
+        <v>2.46630215644836</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630191802979</v>
+        <v>2.46630215644836</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.55375981330872</v>
+        <v>2.55375957489014</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.57999706268311</v>
+        <v>2.57999682426453</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.57999706268311</v>
+        <v>2.57999682426453</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.77240371704102</v>
+        <v>2.77240347862244</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.69369149208069</v>
+        <v>2.69369173049927</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626799583435</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.55375981330872</v>
+        <v>2.55375957489014</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.57999706268311</v>
+        <v>2.57999682426453</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.51003074645996</v>
+        <v>2.51003050804138</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.8336238861084</v>
+        <v>2.83362364768982</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.77240371704102</v>
+        <v>2.77240347862244</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.8336238861084</v>
+        <v>2.83362364768982</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.80738663673401</v>
+        <v>2.80738639831543</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.98230171203613</v>
+        <v>2.98230147361755</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.98230171203613</v>
+        <v>2.98230147361755</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.98230171203613</v>
+        <v>2.98230147361755</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599614143372</v>
+        <v>3.09599637985229</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.25341987609863</v>
+        <v>3.25341963768005</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.29714870452881</v>
+        <v>3.29714846611023</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592853546143</v>
+        <v>3.23592829704285</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965712547302</v>
+        <v>3.27965688705444</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965712547302</v>
+        <v>3.27965688705444</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592853546143</v>
+        <v>3.23592829704285</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.16596245765686</v>
+        <v>3.16596221923828</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470836639404</v>
+        <v>3.17470812797546</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.99979329109192</v>
+        <v>2.99979305267334</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.98230171203613</v>
+        <v>2.98230147361755</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.90358948707581</v>
+        <v>2.90358972549438</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.73742032051086</v>
+        <v>2.73742055892944</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.71992874145508</v>
+        <v>2.71992897987366</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.71992874145508</v>
+        <v>2.71992897987366</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.04915642738342</v>
+        <v>3.049156665802</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30747008323669</v>
+        <v>2.30746984481812</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.5089156627655</v>
+        <v>2.50891590118408</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.5089156627655</v>
+        <v>2.50891590118408</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -59756,6 +59756,32 @@
         <v>5.42000007629395</v>
       </c>
       <c r="H2284" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2285" t="n">
+        <v>21090</v>
+      </c>
+      <c r="C2285" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2285" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="H2285" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802340507507</v>
+        <v>2.85802364349365</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.784592628479</v>
+        <v>2.78459310531616</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8724217414856</v>
+        <v>2.87242126464844</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522245407104</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930611610413</v>
+        <v>2.83930587768555</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8724217414856</v>
+        <v>2.87242126464844</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87098145484924</v>
+        <v>2.8709819316864</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569470405579</v>
+        <v>2.92569494247437</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9487316608429</v>
+        <v>2.94873189926147</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009256362915</v>
+        <v>2.94009280204773</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522245407104</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697717666626</v>
+        <v>2.90697693824768</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.90121793746948</v>
+        <v>2.9012176990509</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841698646545</v>
+        <v>2.90841674804688</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.9213752746582</v>
+        <v>2.92137551307678</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85226440429688</v>
+        <v>2.85226464271545</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G40" t="n">
-        <v>2.80331087112427</v>
+        <v>2.80331039428711</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338906288147</v>
+        <v>2.81338930130005</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050992012024</v>
+        <v>2.81050968170166</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.80043077468872</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.6794867515564</v>
+        <v>2.67948722839355</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G81" t="n">
-        <v>2.65069079399109</v>
+        <v>2.65069103240967</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.6780469417572</v>
+        <v>2.67804765701294</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524622917175</v>
+        <v>2.68524646759033</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52686738967896</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52686738967896</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>2.71404242515564</v>
+        <v>2.71404266357422</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.52686738967896</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.52686738967896</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.52686738967896</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.52686738967896</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G131" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G137" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G139" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G140" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.80043077468872</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>2.80043077468872</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>2.72844052314758</v>
+        <v>2.72844076156616</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G160" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G162" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G163" t="n">
-        <v>2.80043077468872</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G164" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.73563933372498</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857946395874</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.60117483139038</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.90102124214172</v>
+        <v>2.90102171897888</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109839439392</v>
+        <v>2.75109815597534</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618235588074</v>
+        <v>2.58618211746216</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.5</v>
       </c>
       <c r="G226" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867094993591</v>
+        <v>2.60867047309875</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.60117483139038</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103652954102</v>
+        <v>2.87103700637817</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103652954102</v>
+        <v>2.87103700637817</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609015464783</v>
+        <v>2.76609039306641</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105253219604</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G258" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105253219604</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105253219604</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105253219604</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857946395874</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105253219604</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635004043579</v>
+        <v>2.25635027885437</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639614105225</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.1514036655426</v>
+        <v>2.15140390396118</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639614105225</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638061523438</v>
+        <v>2.19638085365295</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.13641119003296</v>
+        <v>2.13641142845154</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398410320282</v>
+        <v>1.99398386478424</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644200325012</v>
+        <v>2.07644152641296</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G306" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.4362587928772</v>
+        <v>2.43625855445862</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630489349365</v>
+        <v>2.34630417823792</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35380077362061</v>
+        <v>2.35380053520203</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383134841919</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383134841919</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>2.61616706848145</v>
+        <v>2.61616683006287</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370904922485</v>
+        <v>2.53370881080627</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>2.56369376182556</v>
+        <v>2.56369352340698</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56369376182556</v>
+        <v>2.56369352340698</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.5487015247345</v>
+        <v>2.54870128631592</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.5487015247345</v>
+        <v>2.54870128631592</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.5</v>
       </c>
       <c r="G374" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.5</v>
       </c>
       <c r="G375" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66864013671875</v>
+        <v>2.66863989830017</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607486724854</v>
+        <v>2.79607534408569</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856369972229</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>2.90851783752441</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90851783752441</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93850255012512</v>
+        <v>2.9385027885437</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>2.90851783752441</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856369972229</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.8035717010498</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G408" t="n">
-        <v>2.95349478721619</v>
+        <v>2.95349526405334</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848726272583</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848726272583</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351055145264</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>2.90851783752441</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866326332092</v>
+        <v>2.91866278648376</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.01231002807617</v>
+        <v>3.01230978965759</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>3.01231002807617</v>
+        <v>3.01230978965759</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G438" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.29325032234192</v>
+        <v>3.2932505607605</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278053283691</v>
+        <v>3.15278029441833</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.0279176235199</v>
+        <v>3.02791810035706</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18399620056152</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960355758667</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764320373535</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764320373535</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.37128973007202</v>
+        <v>3.3712899684906</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203465461731</v>
+        <v>3.26203536987305</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G505" t="n">
-        <v>3.01231002807617</v>
+        <v>3.01230978965759</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474112510681</v>
+        <v>3.07474136352539</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278053283691</v>
+        <v>3.15278029441833</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913329124451</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407501220703</v>
+        <v>2.54407548904419</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51285934448242</v>
+        <v>2.51285982131958</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.49725151062012</v>
+        <v>2.49725198745728</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>2.45042848587036</v>
+        <v>2.45042824745178</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>2.37238907814026</v>
+        <v>2.37238931655884</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.23191857337952</v>
+        <v>2.2319188117981</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631073951721</v>
+        <v>2.21631097793579</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.5</v>
       </c>
       <c r="G628" t="n">
-        <v>2.05594730377197</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660419464111</v>
+        <v>2.00660443305969</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.95726156234741</v>
+        <v>1.9572616815567</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.5</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05594730377197</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.5</v>
       </c>
       <c r="G634" t="n">
-        <v>2.05594730377197</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.05594730377197</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.5</v>
       </c>
       <c r="G636" t="n">
-        <v>2.05594730377197</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>2.36845111846924</v>
+        <v>2.36845135688782</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G656" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G667" t="n">
-        <v>2.35200309753418</v>
+        <v>2.35200333595276</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555555343628</v>
+        <v>2.33555579185486</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G671" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G672" t="n">
-        <v>2.07239484786987</v>
+        <v>2.07239460945129</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G678" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G690" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G703" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G712" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>2.36845111846924</v>
+        <v>2.36845135688782</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G716" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G721" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G731" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G759" t="n">
-        <v>2.13818502426147</v>
+        <v>2.1381847858429</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660419464111</v>
+        <v>2.00660443305969</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370910644531</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660419464111</v>
+        <v>2.00660443305969</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.95726156234741</v>
+        <v>1.9572616815567</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.80923330783844</v>
+        <v>1.80923354625702</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633810043335</v>
+        <v>1.77633833885193</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G787" t="n">
-        <v>1.80923330783844</v>
+        <v>1.80923354625702</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502348423004</v>
+        <v>1.87502372264862</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502348423004</v>
+        <v>1.87502372264862</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370910644531</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="n">
-        <v>2.05594730377197</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G800" t="n">
-        <v>2.07239484786987</v>
+        <v>2.07239460945129</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108058929443</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G803" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G811" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G812" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G814" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G820" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G821" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G824" t="n">
-        <v>2.28621339797974</v>
+        <v>2.28621315956116</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385049819946</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608845710754</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G831" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608845710754</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964043617249</v>
+        <v>2.77964067459106</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385049819946</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>2.6316123008728</v>
+        <v>2.63161206245422</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G854" t="n">
-        <v>2.6316123008728</v>
+        <v>2.63161206245422</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G856" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G857" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G858" t="n">
-        <v>2.76319265365601</v>
+        <v>2.76319289207458</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G859" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G860" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.68095469474792</v>
+        <v>2.68095517158508</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.68095469474792</v>
+        <v>2.68095517158508</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385049819946</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385049819946</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="n">
-        <v>2.82898330688477</v>
+        <v>2.82898354530334</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G871" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608845710754</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>2.89477372169495</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766880989075</v>
+        <v>2.92766857147217</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>2.89477372169495</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>3.5</v>
       </c>
       <c r="G879" t="n">
-        <v>2.87832593917847</v>
+        <v>2.87832617759705</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.5</v>
       </c>
       <c r="G880" t="n">
-        <v>2.87832593917847</v>
+        <v>2.87832617759705</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.89477372169495</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.89477372169495</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>2.89477372169495</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766880989075</v>
+        <v>2.92766857147217</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>2.96056389808655</v>
+        <v>2.96056365966797</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635431289673</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635431289673</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>3.0181303024292</v>
+        <v>3.01813006401062</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G895" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G896" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G897" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G898" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G899" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G900" t="n">
-        <v>2.95233988761902</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.051025390625</v>
+        <v>3.05102562904358</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280185699463</v>
+        <v>3.04280161857605</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.22372484207153</v>
+        <v>3.22372531890869</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.1661581993103</v>
+        <v>3.16615843772888</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>3.06747269630432</v>
+        <v>3.0674729347229</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G921" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>3.09018135070801</v>
+        <v>3.09018111228943</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>3.05650091171265</v>
+        <v>3.05650067329407</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>3.09018135070801</v>
+        <v>3.09018111228943</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.1491219997406</v>
+        <v>3.14912176132202</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646532058716</v>
+        <v>3.37646508216858</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644680976868</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>3.52802705764771</v>
+        <v>3.52802729606628</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G954" t="n">
-        <v>3.55328702926636</v>
+        <v>3.55328726768494</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G956" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490262985229</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594418525696</v>
+        <v>3.32594466209412</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752419471741</v>
+        <v>3.31752443313599</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G977" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646532058716</v>
+        <v>3.37646508216858</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.65432858467102</v>
+        <v>3.6543288230896</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.5869677066803</v>
+        <v>3.58696818351746</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.19321632385254</v>
+        <v>4.19321584701538</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059452056885</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.99113321304321</v>
+        <v>3.99113297462463</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.76378989219666</v>
+        <v>3.76379013061523</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.94061231613159</v>
+        <v>3.94061279296875</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483216285706</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483216285706</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.7974705696106</v>
+        <v>3.79747080802917</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.94061231613159</v>
+        <v>3.94061279296875</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.9490327835083</v>
+        <v>3.94903254508972</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.04165410995483</v>
+        <v>4.04165458679199</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.01639366149902</v>
+        <v>4.01639318466187</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.01639366149902</v>
+        <v>4.01639318466187</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587324142456</v>
+        <v>3.96587300300598</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483216285706</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274857521057</v>
+        <v>3.66274881362915</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.6880087852478</v>
+        <v>3.68800973892212</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.65432858467102</v>
+        <v>3.6543288230896</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484924316406</v>
+        <v>3.70484972000122</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.63748836517334</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484924316406</v>
+        <v>3.70484972000122</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009165763855</v>
+        <v>3.89009189605713</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.81431102752686</v>
+        <v>3.81431126594543</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.72168946266174</v>
+        <v>3.72168970108032</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906837463379</v>
+        <v>3.62906789779663</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484924316406</v>
+        <v>3.70484972000122</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.63748836517334</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.55328702926636</v>
+        <v>3.55328726768494</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.5869677066803</v>
+        <v>3.58696818351746</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.63748836517334</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274857521057</v>
+        <v>3.66274881362915</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.57854747772217</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.57854747772217</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.55328702926636</v>
+        <v>3.55328726768494</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.55328702926636</v>
+        <v>3.55328726768494</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906837463379</v>
+        <v>3.62906789779663</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644680976868</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.57854747772217</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.30068397521973</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.86283826828003</v>
+        <v>2.86283850669861</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.81231737136841</v>
+        <v>2.81231760978699</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80389761924744</v>
+        <v>2.80389738082886</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05650091171265</v>
+        <v>3.05650067329407</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594418525696</v>
+        <v>3.32594466209412</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490262985229</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.25016331672668</v>
+        <v>3.25016307830811</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.25858306884766</v>
+        <v>3.25858330726624</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.25858306884766</v>
+        <v>3.25858330726624</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.15754199028015</v>
+        <v>3.15754222869873</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.15754199028015</v>
+        <v>3.15754222869873</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41084337234497</v>
+        <v>3.41084361076355</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209770202637</v>
+        <v>3.40209794044495</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233563423157</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233563423157</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.58874273300171</v>
+        <v>2.58874249458313</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.58874273300171</v>
+        <v>2.58874249458313</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.57125115394592</v>
+        <v>2.57125091552734</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.43131923675537</v>
+        <v>2.43131899833679</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.54501390457153</v>
+        <v>2.54501414299011</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.72867441177368</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.51003050804138</v>
+        <v>2.51003098487854</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.72867441177368</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.80738639831543</v>
+        <v>2.80738663673401</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.26216554641724</v>
+        <v>3.26216578483582</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.26216554641724</v>
+        <v>3.26216578483582</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.28840279579163</v>
+        <v>3.28840255737305</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.25341963768005</v>
+        <v>3.25342011451721</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.24467396736145</v>
+        <v>3.24467420578003</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233563423157</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.68494582176208</v>
+        <v>2.68494606018066</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.72867441177368</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.049156665802</v>
+        <v>3.04915642738342</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30746984481812</v>
+        <v>2.30747008323669</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -59782,6 +59782,32 @@
         <v>5.3600001335144</v>
       </c>
       <c r="H2285" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2286" t="n">
+        <v>11314</v>
+      </c>
+      <c r="C2286" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="G2286" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="H2286" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.87242197990417</v>
+        <v>2.87242150306702</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930635452271</v>
+        <v>2.83930587768555</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.87242197990417</v>
+        <v>2.87242150306702</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87098145484924</v>
+        <v>2.87098169326782</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818098068237</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569470405579</v>
+        <v>2.92569446563721</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009256362915</v>
+        <v>2.94009232521057</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697693824768</v>
+        <v>2.90697717666626</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.90121793746948</v>
+        <v>2.90121817588806</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>2.89401865005493</v>
+        <v>2.89401888847351</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179239273071</v>
+        <v>2.79179215431213</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338906288147</v>
+        <v>2.81338930130005</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818098068237</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050968170166</v>
+        <v>2.81051015853882</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770896911621</v>
+        <v>2.81770849227905</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412085533142</v>
+        <v>2.72412109375</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948698997498</v>
+        <v>2.67948722839355</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283885955811</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283885955811</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77883386611938</v>
+        <v>2.77883410453796</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532465934753</v>
+        <v>2.69532489776611</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>2.79323220252991</v>
+        <v>2.79323196411133</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69964480400085</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.69964480400085</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.69964480400085</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.69964480400085</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G79" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G80" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69964480400085</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59885764122009</v>
+        <v>2.59885787963867</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>2.59885764122009</v>
+        <v>2.59885787963867</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767761230469</v>
+        <v>2.44767737388611</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647380828857</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647380828857</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767761230469</v>
+        <v>2.44767737388611</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.5</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51966786384583</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286263465881</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.60605645179749</v>
+        <v>2.60605669021606</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283885955811</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>2.71404218673706</v>
+        <v>2.71404242515564</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.51966786384583</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.5</v>
       </c>
       <c r="G122" t="n">
-        <v>2.51966786384583</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286263465881</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445906639099</v>
+        <v>2.58445954322815</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>2.64205193519592</v>
+        <v>2.6420521736145</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.64205193519592</v>
+        <v>2.6420521736145</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.62765383720398</v>
+        <v>2.6276535987854</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G131" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G137" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G139" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G140" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G160" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76443600654602</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G162" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G163" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G164" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G169" t="n">
-        <v>2.77883386611938</v>
+        <v>2.77883410453796</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.60117411613464</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G178" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360203742981</v>
+        <v>2.74360179901123</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612096786499</v>
+        <v>2.70612120628357</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.90102171897888</v>
+        <v>2.9010214805603</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G193" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859403610229</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G213" t="n">
-        <v>2.89352536201477</v>
+        <v>2.89352560043335</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75</v>
       </c>
       <c r="G215" t="n">
-        <v>2.81106805801392</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109791755676</v>
+        <v>2.75109839439392</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612096786499</v>
+        <v>2.70612120628357</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G224" t="n">
-        <v>2.63115930557251</v>
+        <v>2.63115906715393</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618235588074</v>
+        <v>2.58618187904358</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.5</v>
       </c>
       <c r="G226" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>2.65364789962769</v>
+        <v>2.65364742279053</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867071151733</v>
+        <v>2.60867047309875</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.60117411613464</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G232" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859403610229</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859403610229</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859403610229</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111368179321</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.75</v>
       </c>
       <c r="G248" t="n">
-        <v>2.81106805801392</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.75</v>
       </c>
       <c r="G249" t="n">
-        <v>2.81106805801392</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.75</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81106805801392</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.75</v>
       </c>
       <c r="G251" t="n">
-        <v>2.81106805801392</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.75</v>
       </c>
       <c r="G252" t="n">
-        <v>2.81106805801392</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876267433167</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876267433167</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876267433167</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635004043579</v>
+        <v>2.25635027885437</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.2638463973999</v>
+        <v>2.26384663581848</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>2.2638463973999</v>
+        <v>2.26384663581848</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>2.24135780334473</v>
+        <v>2.24135804176331</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.15140318870544</v>
+        <v>2.1514036655426</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G286" t="n">
-        <v>2.10642623901367</v>
+        <v>2.10642647743225</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638061523438</v>
+        <v>2.19638085365295</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.13641119003296</v>
+        <v>2.13641142845154</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398398399353</v>
+        <v>1.99398410320282</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G296" t="n">
-        <v>2.06894564628601</v>
+        <v>2.06894588470459</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10642623901367</v>
+        <v>2.10642647743225</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390730857849</v>
+        <v>2.14390754699707</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G306" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876267433167</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630441665649</v>
+        <v>2.34630465507507</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G322" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G342" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>2.36129713058472</v>
+        <v>2.36129689216614</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.21137309074402</v>
+        <v>2.2113733291626</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383111000061</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383111000061</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.48873162269592</v>
+        <v>2.4887318611145</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370881080627</v>
+        <v>2.53370904922485</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>2.56369376182556</v>
+        <v>2.56369400024414</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56369376182556</v>
+        <v>2.56369400024414</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>2.59367823600769</v>
+        <v>2.59367847442627</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.5</v>
       </c>
       <c r="G374" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.5</v>
       </c>
       <c r="G375" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66864013671875</v>
+        <v>2.66864037513733</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859403610229</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604476928711</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604476928711</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604476928711</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859403610229</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G387" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.9385027885437</v>
+        <v>2.93850255012512</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866302490234</v>
+        <v>2.91866326332092</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109459877014</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109459877014</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G438" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109459877014</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109459877014</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.2932505607605</v>
+        <v>3.29325079917908</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G446" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521186828613</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4</v>
       </c>
       <c r="G452" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4</v>
       </c>
       <c r="G458" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4</v>
       </c>
       <c r="G461" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4</v>
       </c>
       <c r="G462" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.02791786193848</v>
+        <v>3.0279176235199</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521186828613</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521186828613</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>3.19960379600525</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203489303589</v>
+        <v>3.26203513145447</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G500" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521186828613</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G503" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G504" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G505" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109459877014</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717246055603</v>
+        <v>3.13717269897461</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474160194397</v>
+        <v>3.07474112510681</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4</v>
       </c>
       <c r="G514" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4</v>
       </c>
       <c r="G516" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4</v>
       </c>
       <c r="G517" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4</v>
       </c>
       <c r="G518" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4</v>
       </c>
       <c r="G522" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.8562319278717</v>
+        <v>2.85623168945312</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>2.8562319278717</v>
+        <v>2.85623168945312</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.76258492469788</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697661399841</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G550" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697661399841</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G577" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>2.76258492469788</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.8562319278717</v>
+        <v>2.85623168945312</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>2.70015335083008</v>
+        <v>2.70015358924866</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407525062561</v>
+        <v>2.54407501220703</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.60650658607483</v>
+        <v>2.60650634765625</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G602" t="n">
-        <v>2.60650658607483</v>
+        <v>2.60650634765625</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>2.76258492469788</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697661399841</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51285982131958</v>
+        <v>2.512859582901</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>2.65333032608032</v>
+        <v>2.65333008766174</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.57529067993164</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3</v>
       </c>
       <c r="G620" t="n">
-        <v>2.34117341041565</v>
+        <v>2.34117364883423</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>2.45042824745178</v>
+        <v>2.4504280090332</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.2319188117981</v>
+        <v>2.23191857337952</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631073951721</v>
+        <v>2.21631097793579</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>2.31910800933838</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.95726180076599</v>
+        <v>1.9572616815567</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G660" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.61516499519348</v>
+        <v>2.6151647567749</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G667" t="n">
-        <v>2.35200333595276</v>
+        <v>2.35200357437134</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G670" t="n">
-        <v>2.31910800933838</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G677" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G678" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G699" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G719" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G731" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370934486389</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.95726180076599</v>
+        <v>1.9572616815567</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212875366211</v>
+        <v>1.84212851524353</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633810043335</v>
+        <v>1.77633821964264</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212875366211</v>
+        <v>1.84212851524353</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>1.907919049263</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G783" t="n">
-        <v>1.907919049263</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278576374054</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278576374054</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212875366211</v>
+        <v>1.84212851524353</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502348423004</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502348423004</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>1.907919049263</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370934486389</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108011245728</v>
+        <v>2.1710798740387</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G803" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G804" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.15463280677795</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G823" t="n">
-        <v>2.22042274475098</v>
+        <v>2.2204225063324</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964043617249</v>
+        <v>2.77964067459106</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G848" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G849" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G850" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.68095469474792</v>
+        <v>2.6809549331665</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.68095469474792</v>
+        <v>2.6809549331665</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477348327637</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635383605957</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G892" t="n">
-        <v>3.00168251991272</v>
+        <v>3.0016827583313</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635383605957</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>3.0181303024292</v>
+        <v>3.01813054084778</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G895" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G896" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G897" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G898" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G899" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G900" t="n">
-        <v>2.95233964920044</v>
+        <v>2.95233988761902</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102515220642</v>
+        <v>3.051025390625</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.75</v>
       </c>
       <c r="G902" t="n">
-        <v>3.08392095565796</v>
+        <v>3.08392071723938</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280185699463</v>
+        <v>3.04280161857605</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793490409851</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G907" t="n">
-        <v>3.12503933906555</v>
+        <v>3.12503957748413</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>3.14971089363098</v>
+        <v>3.1497106552124</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793490409851</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.14971089363098</v>
+        <v>3.1497106552124</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727729797363</v>
+        <v>3.20727753639221</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.1661581993103</v>
+        <v>3.16615843772888</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>3.0674729347229</v>
+        <v>3.06747317314148</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G924" t="n">
-        <v>3.13228178024292</v>
+        <v>3.13228154182434</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>3.09018135070801</v>
+        <v>3.09018111228943</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>3.05650091171265</v>
+        <v>3.05650067329407</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>3.09018135070801</v>
+        <v>3.09018111228943</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.1491219997406</v>
+        <v>3.14912176132202</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434638023376</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434638023376</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G956" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>3.44382619857788</v>
+        <v>3.4438259601593</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G964" t="n">
-        <v>3.41014575958252</v>
+        <v>3.41014552116394</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490262985229</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594418525696</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G974" t="n">
-        <v>3.28384399414062</v>
+        <v>3.28384375572205</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G979" t="n">
-        <v>3.41014575958252</v>
+        <v>3.41014552116394</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.41014575958252</v>
+        <v>3.41014552116394</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.34278464317322</v>
+        <v>3.34278440475464</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G990" t="n">
-        <v>3.34278464317322</v>
+        <v>3.34278440475464</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.5869677066803</v>
+        <v>3.58696794509888</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.19321632385254</v>
+        <v>4.19321584701538</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007362365723</v>
+        <v>4.05007410049438</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059452056885</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589079856873</v>
+        <v>3.80589032173157</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.94061231613159</v>
+        <v>3.94061255455017</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.92377233505249</v>
+        <v>3.92377209663391</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641098022461</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.92377233505249</v>
+        <v>3.92377209663391</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589079856873</v>
+        <v>3.80589032173157</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.94061231613159</v>
+        <v>3.94061255455017</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.9490327835083</v>
+        <v>3.94903254508972</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.06691408157349</v>
+        <v>4.06691455841064</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.75</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.99955344200134</v>
+        <v>3.99955320358276</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323411941528</v>
+        <v>4.03323364257812</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.75</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.99955344200134</v>
+        <v>3.99955320358276</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587324142456</v>
+        <v>3.96587300300598</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535210609436</v>
+        <v>3.91535234451294</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.64590859413147</v>
+        <v>3.64590835571289</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.6880087852478</v>
+        <v>3.68800926208496</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484924316406</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.63748836517334</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484924316406</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641098022461</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009165763855</v>
+        <v>3.89009189605713</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906837463379</v>
+        <v>3.62906813621521</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484924316406</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.63748836517334</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.60380816459656</v>
+        <v>3.60380792617798</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.5869677066803</v>
+        <v>3.58696794509888</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.63748836517334</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326923370361</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.64590859413147</v>
+        <v>3.64590835571289</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326923370361</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.64590859413147</v>
+        <v>3.64590835571289</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.60380816459656</v>
+        <v>3.60380792617798</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.60380816459656</v>
+        <v>3.60380792617798</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906837463379</v>
+        <v>3.62906813621521</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434638023376</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80389761924744</v>
+        <v>2.80389738082886</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05650091171265</v>
+        <v>3.05650067329407</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594418525696</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490262985229</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.25016331672668</v>
+        <v>3.25016307830811</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.25858306884766</v>
+        <v>3.25858330726624</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.25858306884766</v>
+        <v>3.25858330726624</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.28384399414062</v>
+        <v>3.28384375572205</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.33213138580322</v>
+        <v>3.3321316242218</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.20094537734985</v>
+        <v>3.20094513893127</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.6237256526947</v>
+        <v>2.62372541427612</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>3</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.6237256526947</v>
+        <v>2.62372541427612</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.03477597236633</v>
+        <v>3.03477621078491</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.67620015144348</v>
+        <v>2.6761999130249</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.6237256526947</v>
+        <v>2.62372541427612</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.51003050804138</v>
+        <v>2.51003074645996</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.6237256526947</v>
+        <v>2.62372541427612</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470812797546</v>
+        <v>3.17470788955688</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.03477597236633</v>
+        <v>3.03477621078491</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -59860,6 +59860,32 @@
         <v>5.55999994277954</v>
       </c>
       <c r="H2288" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2289" t="n">
+        <v>15823</v>
+      </c>
+      <c r="C2289" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="G2289" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="H2289" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53081,8 +53081,31 @@
       <c r="E2292" t="n">
         <v>5.40000009536743</v>
       </c>
-      <c r="F2292"/>
+      <c r="F2292" t="n">
+        <v>5.3600001335144</v>
+      </c>
       <c r="G2292" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2293" t="n">
+        <v>13353</v>
+      </c>
+      <c r="C2293" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="F2293"/>
+      <c r="G2293" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53104,8 +53104,31 @@
       <c r="E2293" t="n">
         <v>5.38000011444092</v>
       </c>
-      <c r="F2293"/>
+      <c r="F2293" t="n">
+        <v>5.38000011444092</v>
+      </c>
       <c r="G2293" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2294" t="n">
+        <v>9125</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>5.23999977111816</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="F2294"/>
+      <c r="G2294" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53127,8 +53127,31 @@
       <c r="E2294" t="n">
         <v>5.32000017166138</v>
       </c>
-      <c r="F2294"/>
+      <c r="F2294" t="n">
+        <v>5.30000019073486</v>
+      </c>
       <c r="G2294" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2295" t="n">
+        <v>13466</v>
+      </c>
+      <c r="C2295" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="F2295"/>
+      <c r="G2295" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53150,8 +53150,31 @@
       <c r="E2295" t="n">
         <v>5.19999980926514</v>
       </c>
-      <c r="F2295"/>
+      <c r="F2295" t="n">
+        <v>5.38000011444092</v>
+      </c>
       <c r="G2295" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2296" t="n">
+        <v>10767</v>
+      </c>
+      <c r="C2296" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F2296"/>
+      <c r="G2296" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53180,6 +53180,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2297">
+      <c r="A2297" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2297" t="n">
+        <v>9576</v>
+      </c>
+      <c r="C2297" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802340507507</v>
+        <v>2.85802316665649</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459310531616</v>
+        <v>2.78459286689758</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522245407104</v>
+        <v>2.86522221565247</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930587768555</v>
+        <v>2.83930611610413</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85082459449768</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87098169326782</v>
+        <v>2.8709819316864</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569446563721</v>
+        <v>2.92569494247437</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94585227966309</v>
+        <v>2.94585204124451</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9487316608429</v>
+        <v>2.94873142242432</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522245407104</v>
+        <v>2.86522221565247</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91561579704285</v>
+        <v>2.91561627388</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92137551307678</v>
+        <v>2.9213752746582</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.91561579704285</v>
+        <v>2.91561627388</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433356285095</v>
+        <v>2.93433380126953</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433356285095</v>
+        <v>2.93433380126953</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8522641658783</v>
+        <v>2.85226440429688</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>2.89401888847351</v>
+        <v>2.89401865005493</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.85082459449768</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770896911621</v>
+        <v>2.81770920753479</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723695755005</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412109375</v>
+        <v>2.72412085533142</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948698997498</v>
+        <v>2.67948722839355</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>2.79323196411133</v>
+        <v>2.79323172569275</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723695755005</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723695755005</v>
+        <v>2.75723671913147</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.64349150657654</v>
+        <v>2.6434919834137</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G79" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G80" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G82" t="n">
-        <v>2.66364884376526</v>
+        <v>2.66364908218384</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.69244527816772</v>
+        <v>2.69244503974915</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.66364884376526</v>
+        <v>2.66364908218384</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.69244527816772</v>
+        <v>2.69244503974915</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52686667442322</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52686667442322</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647356987</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647356987</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286215782166</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165835380554</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>2.71404242515564</v>
+        <v>2.71404266357422</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485336303711</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485336303711</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485336303711</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.52686667442322</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.52686667442322</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.52686667442322</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006120681763</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006120681763</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165835380554</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165835380554</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165835380554</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.52686667442322</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286215782166</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165835380554</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165835380554</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>2.64205193519592</v>
+        <v>2.6420521736145</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.64205193519592</v>
+        <v>2.6420521736145</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.62765383720398</v>
+        <v>2.62765407562256</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163505554199</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962055206299</v>
+        <v>2.87962079048157</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G162" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G163" t="n">
-        <v>2.8004310131073</v>
+        <v>2.80043125152588</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G164" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563981056213</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.85082459449768</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G178" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G179" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360203742981</v>
+        <v>2.74360227584839</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66114377975464</v>
+        <v>2.6611442565918</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G193" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G198" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G203" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G205" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859475135803</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G213" t="n">
-        <v>2.89352560043335</v>
+        <v>2.89352536201477</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109815597534</v>
+        <v>2.75109791755676</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G224" t="n">
-        <v>2.63115906715393</v>
+        <v>2.63115930557251</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618235588074</v>
+        <v>2.58618211746216</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867071151733</v>
+        <v>2.60867047309875</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.66114377975464</v>
+        <v>2.6611442565918</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G232" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859475135803</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859475135803</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859475135803</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103724479675</v>
+        <v>2.87103700637817</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103724479675</v>
+        <v>2.87103700637817</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635027885437</v>
+        <v>2.25635004043579</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639590263367</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.15140342712402</v>
+        <v>2.1514036655426</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639590263367</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G286" t="n">
-        <v>2.10642623901367</v>
+        <v>2.10642647743225</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>2.17389249801636</v>
+        <v>2.17389225959778</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.13641119003296</v>
+        <v>2.13641095161438</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644200325012</v>
+        <v>2.07644152641296</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.09893035888672</v>
+        <v>2.0989305973053</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.09893035888672</v>
+        <v>2.0989305973053</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.09893035888672</v>
+        <v>2.0989305973053</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10642623901367</v>
+        <v>2.10642647743225</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630441665649</v>
+        <v>2.34630465507507</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G322" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G327" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G328" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G330" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.2113733291626</v>
+        <v>2.21137356758118</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885392189026</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>2.61616683006287</v>
+        <v>2.61616659164429</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.48873162269592</v>
+        <v>2.4887318611145</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370904922485</v>
+        <v>2.53370881080627</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>2.48123550415039</v>
+        <v>2.48123574256897</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868647575378</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868647575378</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.54870128631592</v>
+        <v>2.54870104789734</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.54870128631592</v>
+        <v>2.54870104789734</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868647575378</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.66114377975464</v>
+        <v>2.6611442565918</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66864037513733</v>
+        <v>2.66864013671875</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859475135803</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607486724854</v>
+        <v>2.79607510566711</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604476928711</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604476928711</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604476928711</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859475135803</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G387" t="n">
-        <v>2.72860980033875</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856346130371</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G390" t="n">
-        <v>2.86354088783264</v>
+        <v>2.86354041099548</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93850255012512</v>
+        <v>2.93850302696228</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>2.77358651161194</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856346130371</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G408" t="n">
-        <v>2.95349502563477</v>
+        <v>2.95349526405334</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866302490234</v>
+        <v>2.91866278648376</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.01231002807617</v>
+        <v>3.01230978965759</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>3.01231002807617</v>
+        <v>3.01230978965759</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744783401489</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.2932505607605</v>
+        <v>3.29325008392334</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G446" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G450" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913376808167</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913376808167</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913376808167</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.3712899684906</v>
+        <v>3.37129020690918</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203489303589</v>
+        <v>3.26203513145447</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G500" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G503" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G504" t="n">
-        <v>3.23081922531128</v>
+        <v>3.23081946372986</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G505" t="n">
-        <v>3.01231002807617</v>
+        <v>3.01230978965759</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744783401489</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474136352539</v>
+        <v>3.07474160194397</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595679283142</v>
+        <v>3.10595655441284</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913376808167</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744783401489</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183952331543</v>
+        <v>2.87183976173401</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>2.63772249221802</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G550" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744783401489</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744783401489</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744783401489</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454575538635</v>
+        <v>2.68454599380493</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G598" t="n">
-        <v>2.59089851379395</v>
+        <v>2.59089875221252</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.60650634765625</v>
+        <v>2.60650610923767</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G601" t="n">
-        <v>2.59089851379395</v>
+        <v>2.59089875221252</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G602" t="n">
-        <v>2.60650634765625</v>
+        <v>2.60650610923767</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63772249221802</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63772249221802</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.512859582901</v>
+        <v>2.51285982131958</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65332984924316</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.49725222587585</v>
+        <v>2.49725198745728</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.23191857337952</v>
+        <v>2.23191833496094</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>2.31910824775696</v>
+        <v>2.31910800933838</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3</v>
       </c>
       <c r="G642" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3</v>
       </c>
       <c r="G649" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3</v>
       </c>
       <c r="G650" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3</v>
       </c>
       <c r="G653" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.5493745803833</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G656" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G660" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.61516451835632</v>
+        <v>2.61516427993774</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3</v>
       </c>
       <c r="G663" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G667" t="n">
-        <v>2.35200333595276</v>
+        <v>2.35200309753418</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G670" t="n">
-        <v>2.31910824775696</v>
+        <v>2.31910800933838</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G677" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.9737092256546</v>
+        <v>1.97370898723602</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.03949952125549</v>
+        <v>2.03949928283691</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.03949952125549</v>
+        <v>2.03949928283691</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212851524353</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.80923354625702</v>
+        <v>1.80923342704773</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633845806122</v>
+        <v>1.77633833885193</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212851524353</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212851524353</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G787" t="n">
-        <v>1.80923354625702</v>
+        <v>1.80923342704773</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147138595581</v>
+        <v>1.89147114753723</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.9737092256546</v>
+        <v>1.97370898723602</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>2.03949952125549</v>
+        <v>2.03949928283691</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G823" t="n">
-        <v>2.2204225063324</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>2.79608821868896</v>
+        <v>2.79608798027039</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G831" t="n">
-        <v>2.79608821868896</v>
+        <v>2.79608798027039</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.6645073890686</v>
+        <v>2.66450762748718</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>2.6316123008728</v>
+        <v>2.63161206245422</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>2.5493745803833</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>2.5493745803833</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>2.5493745803833</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>2.5493745803833</v>
+        <v>2.54937434196472</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3</v>
       </c>
       <c r="G842" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3</v>
       </c>
       <c r="G843" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3</v>
       </c>
       <c r="G844" t="n">
-        <v>2.46713614463806</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50003147125244</v>
+        <v>2.50003170967102</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G848" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G849" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G850" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871745109558</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G854" t="n">
-        <v>2.6316123008728</v>
+        <v>2.63161206245422</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>2.6645073890686</v>
+        <v>2.66450762748718</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G856" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G858" t="n">
-        <v>2.76319241523743</v>
+        <v>2.76319265365601</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.68095517158508</v>
+        <v>2.6809549331665</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.68095517158508</v>
+        <v>2.6809549331665</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>2.86187815666199</v>
+        <v>2.86187839508057</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G871" t="n">
-        <v>2.79608821868896</v>
+        <v>2.79608798027039</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G872" t="n">
-        <v>2.86187815666199</v>
+        <v>2.86187839508057</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122078895569</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477324485779</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122078895569</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122078895569</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766833305359</v>
+        <v>2.92766857147217</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477324485779</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122078895569</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477324485779</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477324485779</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>2.89477348327637</v>
+        <v>2.89477324485779</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122078895569</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766833305359</v>
+        <v>2.92766857147217</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G892" t="n">
-        <v>3.00168299674988</v>
+        <v>3.0016827583313</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102562904358</v>
+        <v>3.051025390625</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280161857605</v>
+        <v>3.04280185699463</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G907" t="n">
-        <v>3.12503933906555</v>
+        <v>3.12503957748413</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G919" t="n">
-        <v>3.17438220977783</v>
+        <v>3.17438197135925</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.17438220977783</v>
+        <v>3.17438197135925</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438268661499</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>3.09018111228943</v>
+        <v>3.09018135070801</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>3.09018111228943</v>
+        <v>3.09018135070801</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646555900574</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276660919189</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>3.52802729606628</v>
+        <v>3.52802705764771</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G954" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>3.57012724876404</v>
+        <v>3.57012748718262</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G965" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G968" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752419471741</v>
+        <v>3.31752443313599</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G984" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.34278464317322</v>
+        <v>3.34278440475464</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646555900574</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>3.35120463371277</v>
+        <v>3.35120439529419</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G990" t="n">
-        <v>3.34278464317322</v>
+        <v>3.34278440475464</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.65432858467102</v>
+        <v>3.6543288230896</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.73853015899658</v>
+        <v>3.73852968215942</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481365203857</v>
+        <v>4.02481412887573</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.19321584701538</v>
+        <v>4.19321632385254</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007457733154</v>
+        <v>4.05007410049438</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059452056885</v>
+        <v>4.10059404373169</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.86483216285706</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.86483216285706</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.7974705696106</v>
+        <v>3.79747080802917</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.04165410995483</v>
+        <v>4.04165363311768</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587252616882</v>
+        <v>3.96587300300598</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535186767578</v>
+        <v>3.91535234451294</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.73853015899658</v>
+        <v>3.73852968215942</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.86483216285706</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.64590859413147</v>
+        <v>3.64590835571289</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.65432858467102</v>
+        <v>3.6543288230896</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.67116904258728</v>
+        <v>3.67116928100586</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906861305237</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118659973145</v>
+        <v>3.51118683815002</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.64590859413147</v>
+        <v>3.64590835571289</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.78063035011292</v>
+        <v>3.78063011169434</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.73853015899658</v>
+        <v>3.73852968215942</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.64590859413147</v>
+        <v>3.64590835571289</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.55328726768494</v>
+        <v>3.55328702926636</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906861305237</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276660919189</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.11544156074524</v>
+        <v>3.11544179916382</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.86283850669861</v>
+        <v>2.86283826828003</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.45224595069885</v>
+        <v>3.45224571228027</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436441421509</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.25016331672668</v>
+        <v>3.25016307830811</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438268661499</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209770202637</v>
+        <v>3.40209794044495</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.36711454391479</v>
+        <v>3.36711430549622</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.32338571548462</v>
+        <v>3.3233859539032</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.36711454391479</v>
+        <v>3.36711430549622</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.27091121673584</v>
+        <v>3.27091145515442</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.78989505767822</v>
+        <v>2.78989481925964</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233515739441</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.01728463172913</v>
+        <v>3.01728439331055</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.95606446266174</v>
+        <v>2.95606422424316</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233515739441</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.03477621078491</v>
+        <v>3.03477597236633</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.95606446266174</v>
+        <v>2.95606422424316</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.95606446266174</v>
+        <v>2.95606422424316</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78989505767822</v>
+        <v>2.78989481925964</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.77240347862244</v>
+        <v>2.77240371704102</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626823425293</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.78989505767822</v>
+        <v>2.78989481925964</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.77240347862244</v>
+        <v>2.77240371704102</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.82487797737122</v>
+        <v>2.82487821578979</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.82487797737122</v>
+        <v>2.82487821578979</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.01728463172913</v>
+        <v>3.01728439331055</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96480989456177</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01728463172913</v>
+        <v>3.01728439331055</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96480989456177</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.95606446266174</v>
+        <v>2.95606422424316</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.95606446266174</v>
+        <v>2.95606422424316</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.32338571548462</v>
+        <v>3.3233859539032</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.32338571548462</v>
+        <v>3.3233859539032</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.27091121673584</v>
+        <v>3.27091145515442</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.29714846611023</v>
+        <v>3.29714870452881</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470788955688</v>
+        <v>3.17470812797546</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.03477621078491</v>
+        <v>3.03477597236633</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96480989456177</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233515739441</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96480989456177</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.04352188110352</v>
+        <v>3.04352164268494</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.01728463172913</v>
+        <v>3.01728439331055</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96480989456177</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.049156665802</v>
+        <v>3.04915642738342</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30746984481812</v>
+        <v>2.30747008323669</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -60131,7 +60131,7 @@
         <v>6223</v>
       </c>
       <c r="C2299" t="n">
-        <v>5.30000019073486</v>
+        <v>5.32000017166138</v>
       </c>
       <c r="D2299" t="n">
         <v>5.21999979019165</v>
@@ -60146,6 +60146,32 @@
         <v>5.32000017166138</v>
       </c>
       <c r="H2299" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2300" t="n">
+        <v>13895</v>
+      </c>
+      <c r="C2300" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>5.23999977111816</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>5.23999977111816</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="G2300" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="H2300" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417598724365</v>
+        <v>2.91417622566223</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802316665649</v>
+        <v>2.85802340507507</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459286689758</v>
+        <v>2.78459310531616</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.87242150306702</v>
+        <v>2.87242126464844</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522221565247</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85514378547668</v>
+        <v>2.85514402389526</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.87242150306702</v>
+        <v>2.87242126464844</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8709819316864</v>
+        <v>2.87098169326782</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818098068237</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569494247437</v>
+        <v>2.92569470405579</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94873142242432</v>
+        <v>2.94873189926147</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009256362915</v>
+        <v>2.94009280204773</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522221565247</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697717666626</v>
+        <v>2.90697693824768</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841698646545</v>
+        <v>2.9084165096283</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.9213752746582</v>
+        <v>2.92137551307678</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113926887512</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113926887512</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>2.89401865005493</v>
+        <v>2.89401888847351</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338930130005</v>
+        <v>2.81338953971863</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818098068237</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050944328308</v>
+        <v>2.81050968170166</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770920753479</v>
+        <v>2.81770873069763</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412085533142</v>
+        <v>2.72412109375</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948722839355</v>
+        <v>2.67948698997498</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>2.79323172569275</v>
+        <v>2.79323196411133</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6434919834137</v>
+        <v>2.64349174499512</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.67804718017578</v>
+        <v>2.67804741859436</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.69244503974915</v>
+        <v>2.69244527816772</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.69244503974915</v>
+        <v>2.69244527816772</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59885764122009</v>
+        <v>2.59885787963867</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>2.59885764122009</v>
+        <v>2.59885787963867</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767761230469</v>
+        <v>2.44767713546753</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647404670715</v>
+        <v>2.47647380828857</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647404670715</v>
+        <v>2.47647380828857</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767761230469</v>
+        <v>2.44767713546753</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286215782166</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485336303711</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485336303711</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485336303711</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.5268669128418</v>
+        <v>2.52686715126038</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286215782166</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>2.6420521736145</v>
+        <v>2.64205193519592</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.6420521736145</v>
+        <v>2.64205193519592</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.62765407562256</v>
+        <v>2.62765383720398</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G131" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G137" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G139" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G140" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G160" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76443576812744</v>
+        <v>2.76443552970886</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G162" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G164" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.73563981056213</v>
+        <v>2.73563957214355</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082459449768</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857922554016</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.60117435455322</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G179" t="n">
-        <v>2.71361708641052</v>
+        <v>2.71361684799194</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360227584839</v>
+        <v>2.74360203742981</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.6611442565918</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.90102171897888</v>
+        <v>2.90102195739746</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G198" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G202" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G205" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859475135803</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75</v>
       </c>
       <c r="G215" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109791755676</v>
+        <v>2.75109815597534</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>2.71361708641052</v>
+        <v>2.71361684799194</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618211746216</v>
+        <v>2.58618187904358</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867047309875</v>
+        <v>2.60867094993591</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.60117435455322</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.6611442565918</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>2.71361708641052</v>
+        <v>2.71361684799194</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859475135803</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859475135803</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859475135803</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609039306641</v>
+        <v>2.76609063148499</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.75</v>
       </c>
       <c r="G248" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.75</v>
       </c>
       <c r="G249" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.75</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.75</v>
       </c>
       <c r="G251" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.75</v>
       </c>
       <c r="G252" t="n">
-        <v>2.81106758117676</v>
+        <v>2.81106734275818</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857922554016</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635004043579</v>
+        <v>2.25635027885437</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883887290955</v>
+        <v>2.27883863449097</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639637947083</v>
+        <v>2.16639614105225</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639637947083</v>
+        <v>2.16639614105225</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G286" t="n">
-        <v>2.10642647743225</v>
+        <v>2.10642623901367</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638109207153</v>
+        <v>2.19638085365295</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18138861656189</v>
+        <v>2.18138837814331</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18138861656189</v>
+        <v>2.18138837814331</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.13641095161438</v>
+        <v>2.13641119003296</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398386478424</v>
+        <v>1.99398410320282</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03146505355835</v>
+        <v>2.03146481513977</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644152641296</v>
+        <v>2.07644200325012</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.0989305973053</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.0989305973053</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.0989305973053</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10642647743225</v>
+        <v>2.10642623901367</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390730857849</v>
+        <v>2.14390754699707</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G306" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.27134251594543</v>
+        <v>2.27134275436401</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625831604004</v>
+        <v>2.43625855445862</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.46624326705933</v>
+        <v>2.46624302864075</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46624326705933</v>
+        <v>2.46624302864075</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G342" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.21137356758118</v>
+        <v>2.2113733291626</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383111000061</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383111000061</v>
+        <v>2.29383087158203</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>2.61616659164429</v>
+        <v>2.61616683006287</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370881080627</v>
+        <v>2.53370904922485</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868647575378</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868647575378</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868647575378</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.6611442565918</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859475135803</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607510566711</v>
+        <v>2.79607486724854</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604476928711</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604476928711</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604476928711</v>
+        <v>2.85604453086853</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859475135803</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G390" t="n">
-        <v>2.86354041099548</v>
+        <v>2.86354064941406</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93850302696228</v>
+        <v>2.9385027885437</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G408" t="n">
-        <v>2.95349526405334</v>
+        <v>2.95349502563477</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848726272583</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848726272583</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866278648376</v>
+        <v>2.91866326332092</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G418" t="n">
-        <v>2.90305519104004</v>
+        <v>2.90305542945862</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G419" t="n">
-        <v>2.90305519104004</v>
+        <v>2.90305542945862</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G420" t="n">
-        <v>2.90305519104004</v>
+        <v>2.90305542945862</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>2.96548652648926</v>
+        <v>2.96548628807068</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>2.96548652648926</v>
+        <v>2.96548628807068</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744783401489</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G436" t="n">
-        <v>2.96548652648926</v>
+        <v>2.96548628807068</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G441" t="n">
-        <v>2.90305519104004</v>
+        <v>2.90305542945862</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G442" t="n">
-        <v>2.90305519104004</v>
+        <v>2.90305542945862</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.29325008392334</v>
+        <v>3.29325032234192</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G446" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G450" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4</v>
       </c>
       <c r="G452" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278029441833</v>
+        <v>3.15278005599976</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4</v>
       </c>
       <c r="G458" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913376808167</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4</v>
       </c>
       <c r="G461" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4</v>
       </c>
       <c r="G462" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913376808167</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913376808167</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G477" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G478" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G480" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>3.16838788986206</v>
+        <v>3.16838812828064</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18399596214294</v>
+        <v>3.18399572372437</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.37129020690918</v>
+        <v>3.3712899684906</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>3.24642729759216</v>
+        <v>3.24642705917358</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G500" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G503" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G504" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081970214844</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.90305519104004</v>
+        <v>2.90305542945862</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744783401489</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.98109412193298</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717246055603</v>
+        <v>3.13717269897461</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474160194397</v>
+        <v>3.07474136352539</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4</v>
       </c>
       <c r="G514" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.09034895896912</v>
+        <v>3.0903491973877</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4</v>
       </c>
       <c r="G516" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4</v>
       </c>
       <c r="G517" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4</v>
       </c>
       <c r="G518" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278029441833</v>
+        <v>3.15278005599976</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4</v>
       </c>
       <c r="G522" t="n">
-        <v>3.1215648651123</v>
+        <v>3.12156462669373</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913376808167</v>
+        <v>3.05913352966309</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.96548652648926</v>
+        <v>2.96548628807068</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744783401489</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183976173401</v>
+        <v>2.87183952331543</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697685241699</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.5</v>
       </c>
       <c r="G540" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697685241699</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G579" t="n">
-        <v>2.80940818786621</v>
+        <v>2.80940794944763</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744783401489</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>2.80940818786621</v>
+        <v>2.80940794944763</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744783401489</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744783401489</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576166152954</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.60650610923767</v>
+        <v>2.60650634765625</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G602" t="n">
-        <v>2.60650610923767</v>
+        <v>2.60650634765625</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.5</v>
       </c>
       <c r="G605" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697685241699</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.5</v>
       </c>
       <c r="G608" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51285982131958</v>
+        <v>2.51285934448242</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.57529091835022</v>
+        <v>2.57529067993164</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211441993713</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.49725198745728</v>
+        <v>2.49725222587585</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3</v>
       </c>
       <c r="G620" t="n">
-        <v>2.34117364883423</v>
+        <v>2.34117388725281</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>2.37238931655884</v>
+        <v>2.37238907814026</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631073951721</v>
+        <v>2.21631097793579</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>2.31910800933838</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.5</v>
       </c>
       <c r="G628" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.5</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.08884215354919</v>
+        <v>2.08884239196777</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.5</v>
       </c>
       <c r="G634" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.5</v>
       </c>
       <c r="G636" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>2.36845088005066</v>
+        <v>2.36845111846924</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.53292679786682</v>
+        <v>2.53292655944824</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G648" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.53292679786682</v>
+        <v>2.53292655944824</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>2.53292679786682</v>
+        <v>2.53292655944824</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G660" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.61516427993774</v>
+        <v>2.61516451835632</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>2.45068907737732</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G667" t="n">
-        <v>2.35200309753418</v>
+        <v>2.35200333595276</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>2.38489890098572</v>
+        <v>2.38489866256714</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G670" t="n">
-        <v>2.31910800933838</v>
+        <v>2.31910824775696</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.38489890098572</v>
+        <v>2.38489866256714</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G684" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G694" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G696" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G698" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266094207764</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G708" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G709" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G710" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266094207764</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G713" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266094207764</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266094207764</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>2.36845088005066</v>
+        <v>2.36845111846924</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>2.08884215354919</v>
+        <v>2.08884239196777</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>2.08884215354919</v>
+        <v>2.08884239196777</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G735" t="n">
-        <v>2.08884215354919</v>
+        <v>2.08884239196777</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>2.08884215354919</v>
+        <v>2.08884239196777</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370898723602</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.03949928283691</v>
+        <v>2.03949952125549</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.03949928283691</v>
+        <v>2.03949952125549</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633833885193</v>
+        <v>1.77633821964264</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278600215912</v>
+        <v>1.79278588294983</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278600215912</v>
+        <v>1.79278588294983</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502372264862</v>
+        <v>1.87502360343933</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502372264862</v>
+        <v>1.87502360343933</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147114753723</v>
+        <v>1.89147126674652</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="n">
-        <v>1.92436647415161</v>
+        <v>1.92436635494232</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370898723602</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>2.03949928283691</v>
+        <v>2.03949952125549</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594730377197</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>2.12173748016357</v>
+        <v>2.121737241745</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G805" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266094207764</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G818" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>2.38489890098572</v>
+        <v>2.38489866256714</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266094207764</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G831" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964043617249</v>
+        <v>2.77964067459106</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.66450762748718</v>
+        <v>2.6645073890686</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>2.63161206245422</v>
+        <v>2.6316123008728</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G848" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G849" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G850" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.59871745109558</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G854" t="n">
-        <v>2.63161206245422</v>
+        <v>2.6316123008728</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>2.66450762748718</v>
+        <v>2.6645073890686</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G857" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G859" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G860" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G871" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.91122078895569</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.91122078895569</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.91122078895569</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.91122078895569</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411635398865</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411635398865</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>2.89477324485779</v>
+        <v>2.89477372169495</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.94411611557007</v>
+        <v>2.94411635398865</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>2.91122078895569</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635383605957</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635383605957</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G895" t="n">
-        <v>2.95233988761902</v>
+        <v>2.9523401260376</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G896" t="n">
-        <v>2.95233988761902</v>
+        <v>2.9523401260376</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G897" t="n">
-        <v>2.95233988761902</v>
+        <v>2.9523401260376</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G898" t="n">
-        <v>2.95233988761902</v>
+        <v>2.9523401260376</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G899" t="n">
-        <v>2.95233988761902</v>
+        <v>2.9523401260376</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G900" t="n">
-        <v>2.95233988761902</v>
+        <v>2.9523401260376</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.051025390625</v>
+        <v>3.05102515220642</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.75</v>
       </c>
       <c r="G902" t="n">
-        <v>3.08392071723938</v>
+        <v>3.0839204788208</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280185699463</v>
+        <v>3.04280161857605</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.22372484207153</v>
+        <v>3.22372508049011</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727729797363</v>
+        <v>3.20727753639221</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.16615843772888</v>
+        <v>3.1661581993103</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G919" t="n">
-        <v>3.17438197135925</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.17438197135925</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>3.17438268661499</v>
+        <v>3.17438244819641</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G924" t="n">
-        <v>3.13228178024292</v>
+        <v>3.13228154182434</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>3.09018135070801</v>
+        <v>3.09018111228943</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>3.09860134124756</v>
+        <v>3.09860110282898</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>3.09018135070801</v>
+        <v>3.09018111228943</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46066617965698</v>
+        <v>3.46066641807556</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646555900574</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276660919189</v>
+        <v>3.50276637077332</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434638023376</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644728660583</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.46066617965698</v>
+        <v>3.46066641807556</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434638023376</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>3.57012748718262</v>
+        <v>3.57012724876404</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G964" t="n">
-        <v>3.41014552116394</v>
+        <v>3.41014575958252</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G965" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490310668945</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752443313599</v>
+        <v>3.31752419471741</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G979" t="n">
-        <v>3.41014552116394</v>
+        <v>3.41014575958252</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.41014552116394</v>
+        <v>3.41014575958252</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.34278440475464</v>
+        <v>3.34278464317322</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646555900574</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>3.35120439529419</v>
+        <v>3.35120463371277</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G990" t="n">
-        <v>3.34278440475464</v>
+        <v>3.34278464317322</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.6543288230896</v>
+        <v>3.65432858467102</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.73852968215942</v>
+        <v>3.73853015899658</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481412887573</v>
+        <v>4.02481365203857</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059404373169</v>
+        <v>4.10059452056885</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.8058910369873</v>
+        <v>3.80589079856873</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.86483120918274</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.86483120918274</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.8058910369873</v>
+        <v>3.80589079856873</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.79747080802917</v>
+        <v>3.7974705696106</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849409103394</v>
+        <v>4.05849456787109</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.04165363311768</v>
+        <v>4.04165410995483</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849409103394</v>
+        <v>4.05849456787109</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535234451294</v>
+        <v>3.91535186767578</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.73852968215942</v>
+        <v>3.73853015899658</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.86483120918274</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.64590835571289</v>
+        <v>3.64590859413147</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274857521057</v>
+        <v>3.66274833679199</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.68800950050354</v>
+        <v>3.68800902366638</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.6543288230896</v>
+        <v>3.65432858467102</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484948158264</v>
+        <v>3.70484924316406</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484948158264</v>
+        <v>3.70484924316406</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.67116928100586</v>
+        <v>3.67116904258728</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906861305237</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67958903312683</v>
+        <v>3.67958879470825</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484948158264</v>
+        <v>3.70484924316406</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118683815002</v>
+        <v>3.51118659973145</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274857521057</v>
+        <v>3.66274833679199</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854747772217</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854747772217</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.64590835571289</v>
+        <v>3.64590859413147</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.78063011169434</v>
+        <v>3.78063035011292</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.67958903312683</v>
+        <v>3.67958879470825</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.73852968215942</v>
+        <v>3.73853015899658</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.64590835571289</v>
+        <v>3.64590859413147</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642877578735</v>
+        <v>3.69642901420593</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906861305237</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644728660583</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276660919189</v>
+        <v>3.50276637077332</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46066617965698</v>
+        <v>3.46066641807556</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854747772217</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434638023376</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960682868958</v>
+        <v>3.519606590271</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.27542400360107</v>
+        <v>3.2754237651825</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.11544179916382</v>
+        <v>3.11544156074524</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.86283826828003</v>
+        <v>2.86283850669861</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.45224571228027</v>
+        <v>3.45224595069885</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436441421509</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490310668945</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.25016307830811</v>
+        <v>3.25016331672668</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.27542400360107</v>
+        <v>3.2754237651825</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.27542400360107</v>
+        <v>3.2754237651825</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.29226398468018</v>
+        <v>3.2922637462616</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.29226398468018</v>
+        <v>3.2922637462616</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.17438268661499</v>
+        <v>3.17438244819641</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209794044495</v>
+        <v>3.40209770202637</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.36711430549622</v>
+        <v>3.36711454391479</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.3233859539032</v>
+        <v>3.32338571548462</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.36711430549622</v>
+        <v>3.36711454391479</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965712547302</v>
+        <v>3.27965688705444</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.27091145515442</v>
+        <v>3.27091121673584</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.07850456237793</v>
+        <v>3.07850480079651</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.07850456237793</v>
+        <v>3.07850480079651</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.84236931800842</v>
+        <v>2.842369556427</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.78989481925964</v>
+        <v>2.78989505767822</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.91233515739441</v>
+        <v>2.91233539581299</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.01728439331055</v>
+        <v>3.01728463172913</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.07850456237793</v>
+        <v>3.07850480079651</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.95606422424316</v>
+        <v>2.95606446266174</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.91233515739441</v>
+        <v>2.91233539581299</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.03477597236633</v>
+        <v>3.03477621078491</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.95606422424316</v>
+        <v>2.95606446266174</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.95606422424316</v>
+        <v>2.95606446266174</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.84236931800842</v>
+        <v>2.842369556427</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78989481925964</v>
+        <v>2.78989505767822</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.77240371704102</v>
+        <v>2.77240347862244</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.6062343120575</v>
+        <v>2.60623407363892</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.78989481925964</v>
+        <v>2.78989505767822</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.77240371704102</v>
+        <v>2.77240347862244</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.82487821578979</v>
+        <v>2.82487797737122</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.82487821578979</v>
+        <v>2.82487797737122</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.01728439331055</v>
+        <v>3.01728463172913</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96480989456177</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01728439331055</v>
+        <v>3.01728463172913</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96480989456177</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.95606422424316</v>
+        <v>2.95606446266174</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.95606422424316</v>
+        <v>2.95606446266174</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.3233859539032</v>
+        <v>3.32338571548462</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.3233859539032</v>
+        <v>3.32338571548462</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.27091145515442</v>
+        <v>3.27091121673584</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.29714870452881</v>
+        <v>3.29714846611023</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592853546143</v>
+        <v>3.23592829704285</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965712547302</v>
+        <v>3.27965688705444</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965712547302</v>
+        <v>3.27965688705444</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592853546143</v>
+        <v>3.23592829704285</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470812797546</v>
+        <v>3.17470788955688</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972520828247</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.03477597236633</v>
+        <v>3.03477621078491</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96480989456177</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.91233515739441</v>
+        <v>2.91233539581299</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96480989456177</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.04352164268494</v>
+        <v>3.04352188110352</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.01728439331055</v>
+        <v>3.01728463172913</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96480989456177</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.04915642738342</v>
+        <v>3.049156665802</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30747008323669</v>
+        <v>2.30746984481812</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.5089156627655</v>
+        <v>2.50891590118408</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.5089156627655</v>
+        <v>2.50891590118408</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -60172,6 +60172,32 @@
         <v>5.32000017166138</v>
       </c>
       <c r="H2300" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2301" t="n">
+        <v>11982</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="G2301" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="H2301" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417598724365</v>
+        <v>2.91417574882507</v>
       </c>
       <c r="H2" t="n">
         <v>507500</v>
@@ -485,7 +485,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459310531616</v>
+        <v>2.78459286689758</v>
       </c>
       <c r="H4" t="n">
         <v>65500</v>
@@ -543,7 +543,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522269248962</v>
+        <v>2.86522245407104</v>
       </c>
       <c r="H6" t="n">
         <v>89500</v>
@@ -572,7 +572,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930587768555</v>
+        <v>2.83930611610413</v>
       </c>
       <c r="H7" t="n">
         <v>35500</v>
@@ -601,7 +601,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082411766052</v>
       </c>
       <c r="H8" t="n">
         <v>34500</v>
@@ -630,7 +630,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85514402389526</v>
+        <v>2.85514378547668</v>
       </c>
       <c r="H9" t="n">
         <v>36500</v>
@@ -804,7 +804,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569446563721</v>
+        <v>2.92569470405579</v>
       </c>
       <c r="H15" t="n">
         <v>25500</v>
@@ -833,7 +833,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94585180282593</v>
+        <v>2.94585204124451</v>
       </c>
       <c r="H16" t="n">
         <v>41500</v>
@@ -862,7 +862,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94873189926147</v>
+        <v>2.9487316608429</v>
       </c>
       <c r="H17" t="n">
         <v>16000</v>
@@ -920,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H19" t="n">
         <v>13500</v>
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522269248962</v>
+        <v>2.86522245407104</v>
       </c>
       <c r="H21" t="n">
         <v>7500</v>
@@ -1007,7 +1007,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H22" t="n">
         <v>19000</v>
@@ -1036,7 +1036,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697693824768</v>
+        <v>2.90697717666626</v>
       </c>
       <c r="H23" t="n">
         <v>43500</v>
@@ -1094,7 +1094,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91561627388</v>
+        <v>2.91561579704285</v>
       </c>
       <c r="H25" t="n">
         <v>12500</v>
@@ -1152,7 +1152,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.9213752746582</v>
+        <v>2.92137551307678</v>
       </c>
       <c r="H27" t="n">
         <v>1000</v>
@@ -1181,7 +1181,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113903045654</v>
+        <v>2.89113926887512</v>
       </c>
       <c r="H28" t="n">
         <v>6000</v>
@@ -1210,7 +1210,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.91561627388</v>
+        <v>2.91561579704285</v>
       </c>
       <c r="H29" t="n">
         <v>8500</v>
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H32" t="n">
         <v>6500</v>
@@ -1326,7 +1326,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113903045654</v>
+        <v>2.89113926887512</v>
       </c>
       <c r="H33" t="n">
         <v>15500</v>
@@ -1384,7 +1384,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>2.89401865005493</v>
+        <v>2.89401888847351</v>
       </c>
       <c r="H35" t="n">
         <v>6000</v>
@@ -1413,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H36" t="n">
         <v>2500</v>
@@ -1442,7 +1442,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082411766052</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1645,7 +1645,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179215431213</v>
+        <v>2.79179239273071</v>
       </c>
       <c r="H44" t="n">
         <v>4500</v>
@@ -1674,7 +1674,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338930130005</v>
+        <v>2.81338906288147</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1732,7 +1732,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050992012024</v>
+        <v>2.81051015853882</v>
       </c>
       <c r="H47" t="n">
         <v>1500</v>
@@ -1819,7 +1819,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.80043148994446</v>
+        <v>2.8004310131073</v>
       </c>
       <c r="H50" t="n">
         <v>500</v>
@@ -1848,7 +1848,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770896911621</v>
+        <v>2.81770849227905</v>
       </c>
       <c r="H56" t="n">
         <v>15500</v>
@@ -2022,7 +2022,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H57" t="n">
         <v>15500</v>
@@ -2051,7 +2051,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412109375</v>
+        <v>2.72412133216858</v>
       </c>
       <c r="H59" t="n">
         <v>8000</v>
@@ -2109,7 +2109,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948698997498</v>
+        <v>2.67948722839355</v>
       </c>
       <c r="H60" t="n">
         <v>12500</v>
@@ -2138,7 +2138,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283885955811</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283885955811</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H63" t="n">
         <v>4000</v>
@@ -2225,7 +2225,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2312,7 +2312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H67" t="n">
         <v>5000</v>
@@ -2457,7 +2457,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H72" t="n">
         <v>4000</v>
@@ -2486,7 +2486,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H73" t="n">
         <v>8500</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69964408874512</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H74" t="n">
         <v>11500</v>
@@ -2544,7 +2544,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.69964408874512</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.69964408874512</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H76" t="n">
         <v>1000</v>
@@ -2602,7 +2602,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.69964408874512</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H77" t="n">
         <v>7500</v>
@@ -2718,7 +2718,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G81" t="n">
-        <v>2.65069079399109</v>
+        <v>2.65069055557251</v>
       </c>
       <c r="H81" t="n">
         <v>5000</v>
@@ -2776,7 +2776,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.6780469417572</v>
+        <v>2.67804741859436</v>
       </c>
       <c r="H83" t="n">
         <v>4000</v>
@@ -2805,7 +2805,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524599075317</v>
+        <v>2.68524622917175</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2834,7 +2834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.69244503974915</v>
+        <v>2.6924455165863</v>
       </c>
       <c r="H85" t="n">
         <v>500</v>
@@ -2863,7 +2863,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69964408874512</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2921,7 +2921,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.69244503974915</v>
+        <v>2.6924455165863</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -3008,7 +3008,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H91" t="n">
         <v>6500</v>
@@ -3095,7 +3095,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767737388611</v>
+        <v>2.44767808914185</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3124,7 +3124,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647404670715</v>
+        <v>2.47647380828857</v>
       </c>
       <c r="H95" t="n">
         <v>1000</v>
@@ -3153,7 +3153,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647404670715</v>
+        <v>2.47647380828857</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767737388611</v>
+        <v>2.44767808914185</v>
       </c>
       <c r="H97" t="n">
         <v>4500</v>
@@ -3211,7 +3211,7 @@
         <v>3.5</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51966834068298</v>
+        <v>2.51966786384583</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3240,7 +3240,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286191940308</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H99" t="n">
         <v>23000</v>
@@ -3327,7 +3327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283885955811</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H102" t="n">
         <v>21000</v>
@@ -3356,7 +3356,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H103" t="n">
         <v>24500</v>
@@ -3385,7 +3385,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H104" t="n">
         <v>10500</v>
@@ -3414,7 +3414,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>2.71404266357422</v>
+        <v>2.71404242515564</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H112" t="n">
         <v>24000</v>
@@ -3733,7 +3733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006168365479</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H116" t="n">
         <v>11000</v>
@@ -3762,7 +3762,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006168365479</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>3.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.51966834068298</v>
+        <v>2.51966786384583</v>
       </c>
       <c r="H121" t="n">
         <v>500</v>
@@ -3907,7 +3907,7 @@
         <v>3.5</v>
       </c>
       <c r="G122" t="n">
-        <v>2.51966834068298</v>
+        <v>2.51966786384583</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286191940308</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H124" t="n">
         <v>3500</v>
@@ -4052,7 +4052,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445978164673</v>
+        <v>2.58445954322815</v>
       </c>
       <c r="H127" t="n">
         <v>22500</v>
@@ -4139,7 +4139,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.62765383720398</v>
+        <v>2.62765407562256</v>
       </c>
       <c r="H130" t="n">
         <v>2500</v>
@@ -4168,7 +4168,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G131" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H131" t="n">
         <v>14000</v>
@@ -4197,7 +4197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H132" t="n">
         <v>31000</v>
@@ -4255,7 +4255,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H134" t="n">
         <v>17500</v>
@@ -4284,7 +4284,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G137" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H137" t="n">
         <v>3500</v>
@@ -4371,7 +4371,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G138" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G139" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G140" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H141" t="n">
         <v>22000</v>
@@ -4487,7 +4487,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.80043148994446</v>
+        <v>2.8004310131073</v>
       </c>
       <c r="H143" t="n">
         <v>2500</v>
@@ -4545,7 +4545,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>2.80043148994446</v>
+        <v>2.8004310131073</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4603,7 +4603,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>2.72844076156616</v>
+        <v>2.72844052314758</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H147" t="n">
         <v>15500</v>
@@ -4661,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -4690,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G160" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H160" t="n">
         <v>1000</v>
@@ -5038,7 +5038,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76443552970886</v>
+        <v>2.76443576812744</v>
       </c>
       <c r="H161" t="n">
         <v>33500</v>
@@ -5067,7 +5067,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G162" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H162" t="n">
         <v>2000</v>
@@ -5096,7 +5096,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G163" t="n">
-        <v>2.80043148994446</v>
+        <v>2.8004310131073</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G164" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H164" t="n">
         <v>4000</v>
@@ -5154,7 +5154,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.73563957214355</v>
+        <v>2.73563933372498</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H166" t="n">
         <v>20000</v>
@@ -5212,7 +5212,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.8508243560791</v>
+        <v>2.85082411766052</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H168" t="n">
         <v>8500</v>
@@ -5357,7 +5357,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H172" t="n">
         <v>28500</v>
@@ -5386,7 +5386,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H173" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G178" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H178" t="n">
         <v>7000</v>
@@ -5560,7 +5560,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G179" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360203742981</v>
+        <v>2.74360179901123</v>
       </c>
       <c r="H180" t="n">
         <v>1500</v>
@@ -5763,7 +5763,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612120628357</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5792,7 +5792,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.90102171897888</v>
+        <v>2.9010214805603</v>
       </c>
       <c r="H187" t="n">
         <v>2000</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H188" t="n">
         <v>5500</v>
@@ -5850,7 +5850,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H189" t="n">
         <v>9000</v>
@@ -5908,7 +5908,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H191" t="n">
         <v>2500</v>
@@ -5966,7 +5966,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G193" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H193" t="n">
         <v>6500</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H196" t="n">
         <v>1000</v>
@@ -6082,7 +6082,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.78108263015747</v>
+        <v>2.78108310699463</v>
       </c>
       <c r="H197" t="n">
         <v>11500</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.78108263015747</v>
+        <v>2.78108310699463</v>
       </c>
       <c r="H212" t="n">
         <v>3000</v>
@@ -6546,7 +6546,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G213" t="n">
-        <v>2.89352536201477</v>
+        <v>2.89352560043335</v>
       </c>
       <c r="H213" t="n">
         <v>18000</v>
@@ -6575,7 +6575,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H214" t="n">
         <v>13500</v>
@@ -6604,7 +6604,7 @@
         <v>3.75</v>
       </c>
       <c r="G215" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H215" t="n">
         <v>12000</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.78108263015747</v>
+        <v>2.78108310699463</v>
       </c>
       <c r="H216" t="n">
         <v>5500</v>
@@ -6720,7 +6720,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H219" t="n">
         <v>61000</v>
@@ -6749,7 +6749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H220" t="n">
         <v>40500</v>
@@ -6778,7 +6778,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H221" t="n">
         <v>500</v>
@@ -6836,7 +6836,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612120628357</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H223" t="n">
         <v>5500</v>
@@ -6865,7 +6865,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G224" t="n">
-        <v>2.63115930557251</v>
+        <v>2.63115906715393</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6894,7 +6894,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618211746216</v>
+        <v>2.58618235588074</v>
       </c>
       <c r="H225" t="n">
         <v>6500</v>
@@ -6981,7 +6981,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867071151733</v>
+        <v>2.60867047309875</v>
       </c>
       <c r="H228" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G232" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H232" t="n">
         <v>1500</v>
@@ -7126,7 +7126,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H236" t="n">
         <v>3000</v>
@@ -7242,7 +7242,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H237" t="n">
         <v>24000</v>
@@ -7561,7 +7561,7 @@
         <v>3.75</v>
       </c>
       <c r="G248" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H248" t="n">
         <v>16000</v>
@@ -7590,7 +7590,7 @@
         <v>3.75</v>
       </c>
       <c r="G249" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H249" t="n">
         <v>1500</v>
@@ -7619,7 +7619,7 @@
         <v>3.75</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>3.75</v>
       </c>
       <c r="G251" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H251" t="n">
         <v>7500</v>
@@ -7677,7 +7677,7 @@
         <v>3.75</v>
       </c>
       <c r="G252" t="n">
-        <v>2.81106734275818</v>
+        <v>2.81106758117676</v>
       </c>
       <c r="H252" t="n">
         <v>5000</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H254" t="n">
         <v>1000</v>
@@ -7822,7 +7822,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H257" t="n">
         <v>4500</v>
@@ -7851,7 +7851,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G258" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H258" t="n">
         <v>16500</v>
@@ -7880,7 +7880,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H264" t="n">
         <v>19500</v>
@@ -8054,7 +8054,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H273" t="n">
         <v>2500</v>
@@ -8315,7 +8315,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635027885437</v>
+        <v>2.25635004043579</v>
       </c>
       <c r="H277" t="n">
         <v>5000</v>
@@ -8431,7 +8431,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.26384663581848</v>
+        <v>2.2638463973999</v>
       </c>
       <c r="H278" t="n">
         <v>5500</v>
@@ -8460,7 +8460,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>2.26384663581848</v>
+        <v>2.2638463973999</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883911132812</v>
+        <v>2.27883863449097</v>
       </c>
       <c r="H280" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639590263367</v>
+        <v>2.16639614105225</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8576,7 +8576,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>2.24135804176331</v>
+        <v>2.24135780334473</v>
       </c>
       <c r="H283" t="n">
         <v>70000</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.1514036655426</v>
+        <v>2.15140342712402</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639590263367</v>
+        <v>2.16639614105225</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8692,7 +8692,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638061523438</v>
+        <v>2.19638085365295</v>
       </c>
       <c r="H287" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18138837814331</v>
+        <v>2.18138861656189</v>
       </c>
       <c r="H288" t="n">
         <v>8000</v>
@@ -8750,7 +8750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18138837814331</v>
+        <v>2.18138861656189</v>
       </c>
       <c r="H289" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398386478424</v>
+        <v>1.99398410320282</v>
       </c>
       <c r="H295" t="n">
         <v>16500</v>
@@ -8982,7 +8982,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03146457672119</v>
+        <v>2.03146481513977</v>
       </c>
       <c r="H297" t="n">
         <v>14000</v>
@@ -9011,7 +9011,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644176483154</v>
+        <v>2.07644200325012</v>
       </c>
       <c r="H298" t="n">
         <v>7500</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.09893035888672</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H299" t="n">
         <v>9500</v>
@@ -9069,7 +9069,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.09893035888672</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H300" t="n">
         <v>1500</v>
@@ -9098,7 +9098,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.09893035888672</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625831604004</v>
+        <v>2.43625855445862</v>
       </c>
       <c r="H311" t="n">
         <v>27000</v>
@@ -9417,7 +9417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H312" t="n">
         <v>12000</v>
@@ -9475,7 +9475,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.34630465507507</v>
+        <v>2.34630441665649</v>
       </c>
       <c r="H314" t="n">
         <v>7500</v>
@@ -9649,7 +9649,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.46624302864075</v>
+        <v>2.46624326705933</v>
       </c>
       <c r="H320" t="n">
         <v>16000</v>
@@ -9678,7 +9678,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46624302864075</v>
+        <v>2.46624326705933</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H325" t="n">
         <v>1000</v>
@@ -9823,7 +9823,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G327" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G328" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G330" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.2113733291626</v>
+        <v>2.21137309074402</v>
       </c>
       <c r="H351" t="n">
         <v>94500</v>
@@ -10664,7 +10664,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>2.29383087158203</v>
+        <v>2.29383111000061</v>
       </c>
       <c r="H355" t="n">
         <v>6000</v>
@@ -10693,7 +10693,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>2.29383087158203</v>
+        <v>2.29383111000061</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.48873162269592</v>
+        <v>2.4887318611145</v>
       </c>
       <c r="H361" t="n">
         <v>6000</v>
@@ -10867,7 +10867,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370904922485</v>
+        <v>2.53370928764343</v>
       </c>
       <c r="H362" t="n">
         <v>5000</v>
@@ -10896,7 +10896,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10983,7 +10983,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H366" t="n">
         <v>500</v>
@@ -11012,7 +11012,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120540618896</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66864037513733</v>
+        <v>2.66864013671875</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11418,7 +11418,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H381" t="n">
         <v>73500</v>
@@ -11476,7 +11476,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H383" t="n">
         <v>32500</v>
@@ -11505,7 +11505,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H385" t="n">
         <v>5000</v>
@@ -11592,7 +11592,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G387" t="n">
-        <v>2.72860932350159</v>
+        <v>2.72860956192017</v>
       </c>
       <c r="H387" t="n">
         <v>48000</v>
@@ -11650,7 +11650,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H389" t="n">
         <v>20000</v>
@@ -11795,7 +11795,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.9385027885437</v>
+        <v>2.93850255012512</v>
       </c>
       <c r="H394" t="n">
         <v>4000</v>
@@ -11824,7 +11824,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H395" t="n">
         <v>4000</v>
@@ -11853,7 +11853,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11940,7 +11940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H399" t="n">
         <v>8000</v>
@@ -11969,7 +11969,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H400" t="n">
         <v>3500</v>
@@ -11998,7 +11998,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H401" t="n">
         <v>500</v>
@@ -12085,7 +12085,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12114,7 +12114,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355641365051</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H407" t="n">
         <v>119000</v>
@@ -12288,7 +12288,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H411" t="n">
         <v>2000</v>
@@ -12317,7 +12317,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351055145264</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12433,7 +12433,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987845420837</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12578,7 +12578,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H421" t="n">
         <v>2000</v>
@@ -12607,7 +12607,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H423" t="n">
         <v>7500</v>
@@ -12665,7 +12665,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H426" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H427" t="n">
         <v>4000</v>
@@ -12781,7 +12781,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H430" t="n">
         <v>2000</v>
@@ -12868,7 +12868,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H431" t="n">
         <v>2500</v>
@@ -12897,7 +12897,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987845420837</v>
       </c>
       <c r="H432" t="n">
         <v>8000</v>
@@ -12926,7 +12926,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G433" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H433" t="n">
         <v>500</v>
@@ -12955,7 +12955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H435" t="n">
         <v>500</v>
@@ -13013,7 +13013,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G436" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987845420837</v>
       </c>
       <c r="H437" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G438" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987845420837</v>
       </c>
       <c r="H438" t="n">
         <v>4000</v>
@@ -13100,7 +13100,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H439" t="n">
         <v>7000</v>
@@ -13129,7 +13129,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>2.94987893104553</v>
+        <v>2.94987845420837</v>
       </c>
       <c r="H443" t="n">
         <v>7500</v>
@@ -13245,7 +13245,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H444" t="n">
         <v>40000</v>
@@ -13303,7 +13303,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G446" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H446" t="n">
         <v>20000</v>
@@ -13332,7 +13332,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H447" t="n">
         <v>7500</v>
@@ -13361,7 +13361,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H448" t="n">
         <v>8000</v>
@@ -13390,7 +13390,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H449" t="n">
         <v>7500</v>
@@ -13419,7 +13419,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G450" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H451" t="n">
         <v>11500</v>
@@ -13506,7 +13506,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H453" t="n">
         <v>1000</v>
@@ -13535,7 +13535,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H454" t="n">
         <v>20000</v>
@@ -13564,7 +13564,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278005599976</v>
+        <v>3.15278053283691</v>
       </c>
       <c r="H455" t="n">
         <v>16000</v>
@@ -13593,7 +13593,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H456" t="n">
         <v>500</v>
@@ -13680,7 +13680,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H459" t="n">
         <v>24500</v>
@@ -13796,7 +13796,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H463" t="n">
         <v>6500</v>
@@ -13825,7 +13825,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H465" t="n">
         <v>500</v>
@@ -13941,7 +13941,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H468" t="n">
         <v>22500</v>
@@ -13970,7 +13970,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.0279176235199</v>
+        <v>3.02791786193848</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -13999,7 +13999,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H470" t="n">
         <v>6000</v>
@@ -14028,7 +14028,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H471" t="n">
         <v>4500</v>
@@ -14057,7 +14057,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H472" t="n">
         <v>15500</v>
@@ -14144,7 +14144,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H475" t="n">
         <v>500</v>
@@ -14173,7 +14173,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H476" t="n">
         <v>5500</v>
@@ -14318,7 +14318,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H481" t="n">
         <v>11500</v>
@@ -14405,7 +14405,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H484" t="n">
         <v>6000</v>
@@ -14434,7 +14434,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H488" t="n">
         <v>5000</v>
@@ -14550,7 +14550,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18399572372437</v>
+        <v>3.18399620056152</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14608,7 +14608,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>3.19960355758667</v>
+        <v>3.19960403442383</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14637,7 +14637,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764248847961</v>
       </c>
       <c r="H492" t="n">
         <v>65000</v>
@@ -14666,7 +14666,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H493" t="n">
         <v>77000</v>
@@ -14695,7 +14695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764248847961</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14782,7 +14782,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H497" t="n">
         <v>26000</v>
@@ -14811,7 +14811,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>3.246426820755</v>
+        <v>3.24642753601074</v>
       </c>
       <c r="H499" t="n">
         <v>1000</v>
@@ -14869,7 +14869,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G500" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H500" t="n">
         <v>13000</v>
@@ -14898,7 +14898,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H502" t="n">
         <v>20500</v>
@@ -14956,7 +14956,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G503" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H503" t="n">
         <v>31000</v>
@@ -14985,7 +14985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G504" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G505" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H505" t="n">
         <v>28500</v>
@@ -15072,7 +15072,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H507" t="n">
         <v>6000</v>
@@ -15101,7 +15101,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.98109436035156</v>
+        <v>2.98109412193298</v>
       </c>
       <c r="H508" t="n">
         <v>12500</v>
@@ -15159,7 +15159,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H510" t="n">
         <v>3000</v>
@@ -15188,7 +15188,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H511" t="n">
         <v>3500</v>
@@ -15246,7 +15246,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H513" t="n">
         <v>39000</v>
@@ -15304,7 +15304,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H515" t="n">
         <v>6500</v>
@@ -15420,7 +15420,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278005599976</v>
+        <v>3.15278053283691</v>
       </c>
       <c r="H519" t="n">
         <v>4000</v>
@@ -15449,7 +15449,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595703125</v>
+        <v>3.10595679283142</v>
       </c>
       <c r="H521" t="n">
         <v>500</v>
@@ -15565,7 +15565,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.96548628807068</v>
+        <v>2.96548652648926</v>
       </c>
       <c r="H524" t="n">
         <v>17500</v>
@@ -15594,7 +15594,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.8562319278717</v>
+        <v>2.85623168945312</v>
       </c>
       <c r="H525" t="n">
         <v>9500</v>
@@ -15623,7 +15623,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H526" t="n">
         <v>15000</v>
@@ -15652,7 +15652,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>2.8562319278717</v>
+        <v>2.85623168945312</v>
       </c>
       <c r="H527" t="n">
         <v>50000</v>
@@ -15681,7 +15681,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183952331543</v>
+        <v>2.87183976173401</v>
       </c>
       <c r="H528" t="n">
         <v>17500</v>
@@ -16000,7 +16000,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H539" t="n">
         <v>3000</v>
@@ -16029,7 +16029,7 @@
         <v>3.5</v>
       </c>
       <c r="G540" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H540" t="n">
         <v>8000</v>
@@ -16087,7 +16087,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H542" t="n">
         <v>6000</v>
@@ -16116,7 +16116,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H543" t="n">
         <v>75500</v>
@@ -16145,7 +16145,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772249221802</v>
       </c>
       <c r="H544" t="n">
         <v>5000</v>
@@ -16261,7 +16261,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H548" t="n">
         <v>20000</v>
@@ -16348,7 +16348,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H551" t="n">
         <v>9000</v>
@@ -16551,7 +16551,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H558" t="n">
         <v>1000</v>
@@ -16696,7 +16696,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16754,7 +16754,7 @@
         <v>3.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H565" t="n">
         <v>3000</v>
@@ -16957,7 +16957,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H572" t="n">
         <v>5500</v>
@@ -17073,7 +17073,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H576" t="n">
         <v>4000</v>
@@ -17218,7 +17218,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H581" t="n">
         <v>10500</v>
@@ -17276,7 +17276,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H583" t="n">
         <v>1000</v>
@@ -17305,7 +17305,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.8562319278717</v>
+        <v>2.85623168945312</v>
       </c>
       <c r="H585" t="n">
         <v>12500</v>
@@ -17421,7 +17421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576166152954</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H588" t="n">
         <v>25500</v>
@@ -17479,7 +17479,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H590" t="n">
         <v>2000</v>
@@ -17595,7 +17595,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407525062561</v>
+        <v>2.54407501220703</v>
       </c>
       <c r="H594" t="n">
         <v>5500</v>
@@ -17624,7 +17624,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H595" t="n">
         <v>13500</v>
@@ -17653,7 +17653,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G596" t="n">
-        <v>2.52846765518188</v>
+        <v>2.52846741676331</v>
       </c>
       <c r="H596" t="n">
         <v>98500</v>
@@ -17682,7 +17682,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H597" t="n">
         <v>41000</v>
@@ -17740,7 +17740,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H599" t="n">
         <v>13500</v>
@@ -17769,7 +17769,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.60650610923767</v>
+        <v>2.60650658607483</v>
       </c>
       <c r="H600" t="n">
         <v>12500</v>
@@ -17827,7 +17827,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G602" t="n">
-        <v>2.60650610923767</v>
+        <v>2.60650658607483</v>
       </c>
       <c r="H602" t="n">
         <v>6000</v>
@@ -17856,7 +17856,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H603" t="n">
         <v>17500</v>
@@ -17885,7 +17885,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772249221802</v>
       </c>
       <c r="H604" t="n">
         <v>500</v>
@@ -17914,7 +17914,7 @@
         <v>3.5</v>
       </c>
       <c r="G605" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H605" t="n">
         <v>45000</v>
@@ -18001,7 +18001,7 @@
         <v>3.5</v>
       </c>
       <c r="G608" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H608" t="n">
         <v>36000</v>
@@ -18030,7 +18030,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772249221802</v>
       </c>
       <c r="H609" t="n">
         <v>47000</v>
@@ -18059,7 +18059,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H610" t="n">
         <v>20500</v>
@@ -18088,7 +18088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H611" t="n">
         <v>27500</v>
@@ -18117,7 +18117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H612" t="n">
         <v>6000</v>
@@ -18146,7 +18146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H613" t="n">
         <v>3000</v>
@@ -18233,7 +18233,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H616" t="n">
         <v>22500</v>
@@ -18262,7 +18262,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.57529067993164</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211418151855</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H618" t="n">
         <v>1000</v>
@@ -18320,7 +18320,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.49725222587585</v>
+        <v>2.4972517490387</v>
       </c>
       <c r="H619" t="n">
         <v>3000</v>
@@ -18349,7 +18349,7 @@
         <v>3</v>
       </c>
       <c r="G620" t="n">
-        <v>2.34117388725281</v>
+        <v>2.34117364883423</v>
       </c>
       <c r="H620" t="n">
         <v>7500</v>
@@ -18407,7 +18407,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>2.37238931655884</v>
+        <v>2.37238907814026</v>
       </c>
       <c r="H622" t="n">
         <v>1000</v>
@@ -18436,7 +18436,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.23191857337952</v>
+        <v>2.2319188117981</v>
       </c>
       <c r="H623" t="n">
         <v>16000</v>
@@ -18494,7 +18494,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H625" t="n">
         <v>13000</v>
@@ -18581,7 +18581,7 @@
         <v>2.5</v>
       </c>
       <c r="G628" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H628" t="n">
         <v>11000</v>
@@ -18610,7 +18610,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660467147827</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H629" t="n">
         <v>18500</v>
@@ -18639,7 +18639,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.99015688896179</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.9572616815567</v>
+        <v>1.95726180076599</v>
       </c>
       <c r="H631" t="n">
         <v>14000</v>
@@ -18697,7 +18697,7 @@
         <v>2.5</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H632" t="n">
         <v>9000</v>
@@ -18755,7 +18755,7 @@
         <v>2.5</v>
       </c>
       <c r="G634" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H634" t="n">
         <v>1000</v>
@@ -18784,7 +18784,7 @@
         <v>2.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>2.5</v>
       </c>
       <c r="G636" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.99015688896179</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H637" t="n">
         <v>2000</v>
@@ -18871,7 +18871,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -19074,7 +19074,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H645" t="n">
         <v>14000</v>
@@ -19103,7 +19103,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H646" t="n">
         <v>3000</v>
@@ -19335,7 +19335,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H654" t="n">
         <v>21000</v>
@@ -19509,7 +19509,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G660" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H660" t="n">
         <v>2500</v>
@@ -19625,7 +19625,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H664" t="n">
         <v>1000</v>
@@ -19654,7 +19654,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H665" t="n">
         <v>2000</v>
@@ -19741,7 +19741,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555555343628</v>
+        <v>2.33555603027344</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H669" t="n">
         <v>76500</v>
@@ -19944,7 +19944,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331830978394</v>
       </c>
       <c r="H675" t="n">
         <v>13631</v>
@@ -19973,7 +19973,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H676" t="n">
         <v>5030</v>
@@ -20002,7 +20002,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G677" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H677" t="n">
         <v>1635</v>
@@ -20060,7 +20060,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H679" t="n">
         <v>12145</v>
@@ -20118,7 +20118,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H681" t="n">
         <v>21760</v>
@@ -20147,7 +20147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H682" t="n">
         <v>21900</v>
@@ -20205,7 +20205,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G684" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H684" t="n">
         <v>3500</v>
@@ -20234,7 +20234,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H685" t="n">
         <v>13500</v>
@@ -20292,7 +20292,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H687" t="n">
         <v>3000</v>
@@ -20321,7 +20321,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H688" t="n">
         <v>2025</v>
@@ -20408,7 +20408,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H691" t="n">
         <v>14460</v>
@@ -20495,7 +20495,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G694" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H694" t="n">
         <v>4200</v>
@@ -20524,7 +20524,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G696" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H696" t="n">
         <v>10100</v>
@@ -20640,7 +20640,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G699" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331830978394</v>
       </c>
       <c r="H699" t="n">
         <v>2600</v>
@@ -20785,7 +20785,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H704" t="n">
         <v>5880</v>
@@ -20901,7 +20901,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G708" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H708" t="n">
         <v>1125</v>
@@ -20930,7 +20930,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G709" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H718" t="n">
         <v>4000</v>
@@ -21220,7 +21220,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G719" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331830978394</v>
       </c>
       <c r="H719" t="n">
         <v>1000</v>
@@ -21249,7 +21249,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H720" t="n">
         <v>2579</v>
@@ -21336,7 +21336,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H723" t="n">
         <v>800</v>
@@ -21597,7 +21597,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H732" t="n">
         <v>10280</v>
@@ -21713,7 +21713,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H736" t="n">
         <v>3700</v>
@@ -21771,7 +21771,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21800,7 +21800,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H739" t="n">
         <v>7950</v>
@@ -21829,7 +21829,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -22061,7 +22061,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22090,7 +22090,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H750" t="n">
         <v>17333</v>
@@ -22177,7 +22177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22235,7 +22235,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H754" t="n">
         <v>14100</v>
@@ -22293,7 +22293,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H756" t="n">
         <v>6282</v>
@@ -22322,7 +22322,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H757" t="n">
         <v>3679</v>
@@ -22409,7 +22409,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H760" t="n">
         <v>210</v>
@@ -22496,7 +22496,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22525,7 +22525,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H764" t="n">
         <v>10600</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660467147827</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H766" t="n">
         <v>7000</v>
@@ -22612,7 +22612,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.99015688896179</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H767" t="n">
         <v>11020</v>
@@ -22641,7 +22641,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081377983093</v>
       </c>
       <c r="H768" t="n">
         <v>7167</v>
@@ -22670,7 +22670,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370946407318</v>
+        <v>1.97370934486389</v>
       </c>
       <c r="H769" t="n">
         <v>2120</v>
@@ -22728,7 +22728,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H771" t="n">
         <v>5351</v>
@@ -22786,7 +22786,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660467147827</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H773" t="n">
         <v>10000</v>
@@ -22815,7 +22815,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.9572616815567</v>
+        <v>1.95726180076599</v>
       </c>
       <c r="H774" t="n">
         <v>10000</v>
@@ -22844,7 +22844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212839603424</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H775" t="n">
         <v>26371</v>
@@ -22873,7 +22873,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.80923342704773</v>
+        <v>1.80923354625702</v>
       </c>
       <c r="H776" t="n">
         <v>9400</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212839603424</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H778" t="n">
         <v>8200</v>
@@ -22960,7 +22960,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G779" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081377983093</v>
       </c>
       <c r="H779" t="n">
         <v>23341</v>
@@ -22989,7 +22989,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791881084442</v>
       </c>
       <c r="H780" t="n">
         <v>5771</v>
@@ -23018,7 +23018,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G781" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081377983093</v>
       </c>
       <c r="H781" t="n">
         <v>12683</v>
@@ -23047,7 +23047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G782" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081377983093</v>
       </c>
       <c r="H782" t="n">
         <v>2000</v>
@@ -23076,7 +23076,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791881084442</v>
       </c>
       <c r="H783" t="n">
         <v>5208</v>
@@ -23105,7 +23105,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278576374054</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H784" t="n">
         <v>9450</v>
@@ -23134,7 +23134,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278576374054</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H785" t="n">
         <v>6000</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212839603424</v>
+        <v>1.84212863445282</v>
       </c>
       <c r="H786" t="n">
         <v>500</v>
@@ -23192,7 +23192,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G787" t="n">
-        <v>1.80923342704773</v>
+        <v>1.80923354625702</v>
       </c>
       <c r="H787" t="n">
         <v>1000</v>
@@ -23279,7 +23279,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147126674652</v>
+        <v>1.89147114753723</v>
       </c>
       <c r="H790" t="n">
         <v>2551</v>
@@ -23308,7 +23308,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>1.90791869163513</v>
+        <v>1.90791881084442</v>
       </c>
       <c r="H791" t="n">
         <v>8501</v>
@@ -23366,7 +23366,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H793" t="n">
         <v>8769</v>
@@ -23395,7 +23395,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.99015688896179</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H794" t="n">
         <v>5000</v>
@@ -23424,7 +23424,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370946407318</v>
+        <v>1.97370934486389</v>
       </c>
       <c r="H795" t="n">
         <v>5168</v>
@@ -23482,7 +23482,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H797" t="n">
         <v>12411</v>
@@ -23511,7 +23511,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H798" t="n">
         <v>20346</v>
@@ -23540,7 +23540,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H799" t="n">
         <v>3200</v>
@@ -23627,7 +23627,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H802" t="n">
         <v>15886</v>
@@ -23685,7 +23685,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G804" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331830978394</v>
       </c>
       <c r="H804" t="n">
         <v>6170</v>
@@ -23772,7 +23772,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H807" t="n">
         <v>11874</v>
@@ -23946,7 +23946,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H813" t="n">
         <v>15111</v>
@@ -24004,7 +24004,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331830978394</v>
       </c>
       <c r="H815" t="n">
         <v>4017</v>
@@ -24033,7 +24033,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H816" t="n">
         <v>4950</v>
@@ -24062,7 +24062,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H817" t="n">
         <v>3243</v>
@@ -24091,7 +24091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G818" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H818" t="n">
         <v>2250</v>
@@ -24120,7 +24120,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H819" t="n">
         <v>48040</v>
@@ -24207,7 +24207,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H822" t="n">
         <v>2000</v>
@@ -24236,7 +24236,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G823" t="n">
-        <v>2.22042274475098</v>
+        <v>2.22042298316956</v>
       </c>
       <c r="H823" t="n">
         <v>4050</v>
@@ -24294,7 +24294,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>2.25331783294678</v>
+        <v>2.25331830978394</v>
       </c>
       <c r="H825" t="n">
         <v>6850</v>
@@ -24410,7 +24410,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H829" t="n">
         <v>292926</v>
@@ -24439,7 +24439,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H830" t="n">
         <v>183827</v>
@@ -24468,7 +24468,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G831" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H831" t="n">
         <v>72777</v>
@@ -24497,7 +24497,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964067459106</v>
+        <v>2.77964043617249</v>
       </c>
       <c r="H832" t="n">
         <v>51937</v>
@@ -24526,7 +24526,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H833" t="n">
         <v>25716</v>
@@ -24613,7 +24613,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H836" t="n">
         <v>41850</v>
@@ -24642,7 +24642,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H837" t="n">
         <v>6850</v>
@@ -24671,7 +24671,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H838" t="n">
         <v>1000</v>
@@ -24700,7 +24700,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.58226943016052</v>
+        <v>2.5822696685791</v>
       </c>
       <c r="H839" t="n">
         <v>12621</v>
@@ -24729,7 +24729,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>2.54937434196472</v>
+        <v>2.54937410354614</v>
       </c>
       <c r="H840" t="n">
         <v>8233</v>
@@ -24758,7 +24758,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H841" t="n">
         <v>18272</v>
@@ -24903,7 +24903,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58226943016052</v>
+        <v>2.5822696685791</v>
       </c>
       <c r="H846" t="n">
         <v>14130</v>
@@ -24932,7 +24932,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H847" t="n">
         <v>6888</v>
@@ -24961,7 +24961,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G848" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H848" t="n">
         <v>6294</v>
@@ -24990,7 +24990,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G849" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H849" t="n">
         <v>15015</v>
@@ -25019,7 +25019,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G850" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H850" t="n">
         <v>5171</v>
@@ -25048,7 +25048,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H851" t="n">
         <v>2601</v>
@@ -25077,7 +25077,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.598717212677</v>
+        <v>2.59871697425842</v>
       </c>
       <c r="H852" t="n">
         <v>20412</v>
@@ -25106,7 +25106,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H853" t="n">
         <v>9189</v>
@@ -25193,7 +25193,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G856" t="n">
-        <v>2.64805960655212</v>
+        <v>2.6480598449707</v>
       </c>
       <c r="H856" t="n">
         <v>37418</v>
@@ -25222,7 +25222,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G857" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H857" t="n">
         <v>36588</v>
@@ -25251,7 +25251,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G858" t="n">
-        <v>2.76319265365601</v>
+        <v>2.76319289207458</v>
       </c>
       <c r="H858" t="n">
         <v>24533</v>
@@ -25280,7 +25280,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G859" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H859" t="n">
         <v>14827</v>
@@ -25309,7 +25309,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G860" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H860" t="n">
         <v>9138</v>
@@ -25396,7 +25396,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H863" t="n">
         <v>4900</v>
@@ -25425,7 +25425,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H864" t="n">
         <v>1600</v>
@@ -25454,7 +25454,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H865" t="n">
         <v>12720</v>
@@ -25512,7 +25512,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H867" t="n">
         <v>11963</v>
@@ -25541,7 +25541,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H868" t="n">
         <v>12942</v>
@@ -25570,7 +25570,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="n">
-        <v>2.82898330688477</v>
+        <v>2.82898306846619</v>
       </c>
       <c r="H869" t="n">
         <v>30735</v>
@@ -25628,7 +25628,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G871" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H871" t="n">
         <v>32365</v>
@@ -25802,7 +25802,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766857147217</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H877" t="n">
         <v>15518</v>
@@ -25860,7 +25860,7 @@
         <v>3.5</v>
       </c>
       <c r="G879" t="n">
-        <v>2.87832593917847</v>
+        <v>2.87832617759705</v>
       </c>
       <c r="H879" t="n">
         <v>14907</v>
@@ -25889,7 +25889,7 @@
         <v>3.5</v>
       </c>
       <c r="G880" t="n">
-        <v>2.87832593917847</v>
+        <v>2.87832617759705</v>
       </c>
       <c r="H880" t="n">
         <v>11224</v>
@@ -26150,7 +26150,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766857147217</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H889" t="n">
         <v>9439</v>
@@ -26237,7 +26237,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G892" t="n">
-        <v>3.00168299674988</v>
+        <v>3.0016827583313</v>
       </c>
       <c r="H892" t="n">
         <v>9588</v>
@@ -26498,7 +26498,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102562904358</v>
+        <v>3.051025390625</v>
       </c>
       <c r="H901" t="n">
         <v>43084</v>
@@ -26556,7 +26556,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280138015747</v>
+        <v>3.04280185699463</v>
       </c>
       <c r="H903" t="n">
         <v>10299</v>
@@ -26585,7 +26585,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>3.11681580543518</v>
+        <v>3.1168155670166</v>
       </c>
       <c r="H904" t="n">
         <v>35002</v>
@@ -26614,7 +26614,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H905" t="n">
         <v>9395</v>
@@ -26643,7 +26643,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>3.11681580543518</v>
+        <v>3.1168155670166</v>
       </c>
       <c r="H906" t="n">
         <v>18842</v>
@@ -26730,7 +26730,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H909" t="n">
         <v>1061</v>
@@ -26759,7 +26759,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H910" t="n">
         <v>3156</v>
@@ -26817,7 +26817,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H912" t="n">
         <v>16945</v>
@@ -26846,7 +26846,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H913" t="n">
         <v>6168</v>
@@ -26875,7 +26875,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.22372508049011</v>
+        <v>3.22372484207153</v>
       </c>
       <c r="H914" t="n">
         <v>32683</v>
@@ -26904,7 +26904,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727777481079</v>
+        <v>3.20727729797363</v>
       </c>
       <c r="H915" t="n">
         <v>20765</v>
@@ -26933,7 +26933,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.1661581993103</v>
+        <v>3.16615843772888</v>
       </c>
       <c r="H916" t="n">
         <v>23119</v>
@@ -26991,7 +26991,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>3.11681580543518</v>
+        <v>3.1168155670166</v>
       </c>
       <c r="H918" t="n">
         <v>36796</v>
@@ -27020,7 +27020,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G919" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H919" t="n">
         <v>11492</v>
@@ -27049,7 +27049,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H920" t="n">
         <v>4050</v>
@@ -27136,7 +27136,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H923" t="n">
         <v>16638</v>
@@ -27223,7 +27223,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>3.03966045379639</v>
+        <v>3.03966021537781</v>
       </c>
       <c r="H926" t="n">
         <v>12523</v>
@@ -27397,7 +27397,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H932" t="n">
         <v>46107</v>
@@ -27455,7 +27455,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H934" t="n">
         <v>17505</v>
@@ -27484,7 +27484,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H935" t="n">
         <v>4667</v>
@@ -27571,7 +27571,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H938" t="n">
         <v>4663</v>
@@ -27600,7 +27600,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H939" t="n">
         <v>1901</v>
@@ -27629,7 +27629,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H940" t="n">
         <v>4174</v>
@@ -27716,7 +27716,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276684761047</v>
       </c>
       <c r="H943" t="n">
         <v>26715</v>
@@ -27745,7 +27745,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H944" t="n">
         <v>9943</v>
@@ -27832,7 +27832,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644728660583</v>
+        <v>3.53644680976868</v>
       </c>
       <c r="H947" t="n">
         <v>5552</v>
@@ -27861,7 +27861,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H948" t="n">
         <v>6445</v>
@@ -27948,7 +27948,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>3.52802729606628</v>
+        <v>3.52802705764771</v>
       </c>
       <c r="H951" t="n">
         <v>10788</v>
@@ -27977,7 +27977,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H952" t="n">
         <v>3722</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H953" t="n">
         <v>4381</v>
@@ -28180,7 +28180,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>3.44382619857788</v>
+        <v>3.4438259601593</v>
       </c>
       <c r="H959" t="n">
         <v>19778</v>
@@ -28238,7 +28238,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H961" t="n">
         <v>1261</v>
@@ -28267,7 +28267,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H962" t="n">
         <v>25266</v>
@@ -28325,7 +28325,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G964" t="n">
-        <v>3.41014552116394</v>
+        <v>3.4101459980011</v>
       </c>
       <c r="H964" t="n">
         <v>9510</v>
@@ -28412,7 +28412,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490310668945</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H967" t="n">
         <v>12089</v>
@@ -28441,7 +28441,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G968" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H968" t="n">
         <v>13367</v>
@@ -28499,7 +28499,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594418525696</v>
       </c>
       <c r="H970" t="n">
         <v>650</v>
@@ -28644,7 +28644,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H975" t="n">
         <v>750</v>
@@ -28702,7 +28702,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G977" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H977" t="n">
         <v>2819</v>
@@ -28760,7 +28760,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G979" t="n">
-        <v>3.41014552116394</v>
+        <v>3.4101459980011</v>
       </c>
       <c r="H979" t="n">
         <v>7866</v>
@@ -28789,7 +28789,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172553062439</v>
       </c>
       <c r="H980" t="n">
         <v>8597</v>
@@ -28818,7 +28818,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H981" t="n">
         <v>410</v>
@@ -28963,7 +28963,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.41014552116394</v>
+        <v>3.4101459980011</v>
       </c>
       <c r="H986" t="n">
         <v>1700</v>
@@ -28992,7 +28992,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.34278464317322</v>
+        <v>3.34278440475464</v>
       </c>
       <c r="H987" t="n">
         <v>2000</v>
@@ -29079,7 +29079,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G990" t="n">
-        <v>3.34278464317322</v>
+        <v>3.34278440475464</v>
       </c>
       <c r="H990" t="n">
         <v>74</v>
@@ -29108,7 +29108,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H991" t="n">
         <v>1174</v>
@@ -29137,7 +29137,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H992" t="n">
         <v>4350</v>
@@ -29166,7 +29166,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H993" t="n">
         <v>933</v>
@@ -29195,7 +29195,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H994" t="n">
         <v>9158</v>
@@ -29224,7 +29224,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H995" t="n">
         <v>6453</v>
@@ -29253,7 +29253,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>3.65432858467102</v>
+        <v>3.65432906150818</v>
       </c>
       <c r="H996" t="n">
         <v>91213</v>
@@ -29369,7 +29369,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1000" t="n">
         <v>56572</v>
@@ -29398,7 +29398,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481365203857</v>
+        <v>4.02481412887573</v>
       </c>
       <c r="H1001" t="n">
         <v>96367</v>
@@ -29427,7 +29427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.15953540802002</v>
+        <v>4.15953493118286</v>
       </c>
       <c r="H1002" t="n">
         <v>111881</v>
@@ -29514,7 +29514,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007457733154</v>
+        <v>4.05007410049438</v>
       </c>
       <c r="H1005" t="n">
         <v>28674</v>
@@ -29572,7 +29572,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.99113321304321</v>
+        <v>3.99113297462463</v>
       </c>
       <c r="H1007" t="n">
         <v>22534</v>
@@ -29601,7 +29601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.76378989219666</v>
+        <v>3.76379013061523</v>
       </c>
       <c r="H1008" t="n">
         <v>79946</v>
@@ -29630,7 +29630,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957123756409</v>
+        <v>3.83957099914551</v>
       </c>
       <c r="H1009" t="n">
         <v>18829</v>
@@ -29659,7 +29659,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589079856873</v>
+        <v>3.80589056015015</v>
       </c>
       <c r="H1010" t="n">
         <v>35109</v>
@@ -29688,7 +29688,7 @@
         <v>4.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905010223389</v>
       </c>
       <c r="H1011" t="n">
         <v>18176</v>
@@ -29717,7 +29717,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.94061255455017</v>
+        <v>3.94061231613159</v>
       </c>
       <c r="H1012" t="n">
         <v>29223</v>
@@ -29746,7 +29746,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.92377209663391</v>
+        <v>3.92377233505249</v>
       </c>
       <c r="H1013" t="n">
         <v>15579</v>
@@ -29775,7 +29775,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429299354553</v>
       </c>
       <c r="H1014" t="n">
         <v>7495</v>
@@ -29804,7 +29804,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1015" t="n">
         <v>10368</v>
@@ -29833,7 +29833,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957123756409</v>
+        <v>3.83957099914551</v>
       </c>
       <c r="H1016" t="n">
         <v>27929</v>
@@ -29862,7 +29862,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.86483216285706</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1017" t="n">
         <v>43128</v>
@@ -29891,7 +29891,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.92377209663391</v>
+        <v>3.92377233505249</v>
       </c>
       <c r="H1018" t="n">
         <v>7168</v>
@@ -29920,7 +29920,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.86483216285706</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1019" t="n">
         <v>2641</v>
@@ -29949,7 +29949,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589079856873</v>
+        <v>3.80589056015015</v>
       </c>
       <c r="H1020" t="n">
         <v>5690</v>
@@ -30007,7 +30007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.94061255455017</v>
+        <v>3.94061231613159</v>
       </c>
       <c r="H1022" t="n">
         <v>17855</v>
@@ -30036,7 +30036,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.94903254508972</v>
+        <v>3.9490327835083</v>
       </c>
       <c r="H1023" t="n">
         <v>8504</v>
@@ -30065,7 +30065,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429299354553</v>
       </c>
       <c r="H1024" t="n">
         <v>24153</v>
@@ -30094,7 +30094,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1025" t="n">
         <v>31402</v>
@@ -30152,7 +30152,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.13427495956421</v>
+        <v>4.13427448272705</v>
       </c>
       <c r="H1027" t="n">
         <v>10172</v>
@@ -30210,7 +30210,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.06691455841064</v>
+        <v>4.06691408157349</v>
       </c>
       <c r="H1029" t="n">
         <v>29092</v>
@@ -30268,7 +30268,7 @@
         <v>4.75</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.99955320358276</v>
+        <v>3.99955344200134</v>
       </c>
       <c r="H1031" t="n">
         <v>4755</v>
@@ -30413,7 +30413,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849409103394</v>
       </c>
       <c r="H1036" t="n">
         <v>12669</v>
@@ -30442,7 +30442,7 @@
         <v>4.75</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.99955320358276</v>
+        <v>3.99955344200134</v>
       </c>
       <c r="H1037" t="n">
         <v>9609</v>
@@ -30471,7 +30471,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587252616882</v>
+        <v>3.96587300300598</v>
       </c>
       <c r="H1038" t="n">
         <v>10631</v>
@@ -30500,7 +30500,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535186767578</v>
+        <v>3.91535234451294</v>
       </c>
       <c r="H1039" t="n">
         <v>7070</v>
@@ -30529,7 +30529,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1040" t="n">
         <v>27791</v>
@@ -30558,7 +30558,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.86483216285706</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1041" t="n">
         <v>2683</v>
@@ -30587,7 +30587,7 @@
         <v>4.5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905010223389</v>
       </c>
       <c r="H1042" t="n">
         <v>23151</v>
@@ -30674,7 +30674,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.68800950050354</v>
+        <v>3.68800926208496</v>
       </c>
       <c r="H1045" t="n">
         <v>6158</v>
@@ -30703,7 +30703,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.65432858467102</v>
+        <v>3.65432906150818</v>
       </c>
       <c r="H1046" t="n">
         <v>6515</v>
@@ -30732,7 +30732,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1047" t="n">
         <v>3054</v>
@@ -30790,7 +30790,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1049" t="n">
         <v>10041</v>
@@ -30848,7 +30848,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641145706177</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1051" t="n">
         <v>38739</v>
@@ -30877,7 +30877,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429299354553</v>
       </c>
       <c r="H1052" t="n">
         <v>48655</v>
@@ -30906,7 +30906,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009189605713</v>
+        <v>3.89009165763855</v>
       </c>
       <c r="H1053" t="n">
         <v>34250</v>
@@ -30935,7 +30935,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.81431102752686</v>
+        <v>3.81431078910828</v>
       </c>
       <c r="H1054" t="n">
         <v>20837</v>
@@ -30993,7 +30993,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.72168970108032</v>
+        <v>3.7216899394989</v>
       </c>
       <c r="H1056" t="n">
         <v>4318</v>
@@ -31022,7 +31022,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1057" t="n">
         <v>6922</v>
@@ -31051,7 +31051,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1058" t="n">
         <v>2298</v>
@@ -31109,7 +31109,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1060" t="n">
         <v>6645</v>
@@ -31138,7 +31138,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118659973145</v>
+        <v>3.5111870765686</v>
       </c>
       <c r="H1061" t="n">
         <v>19148</v>
@@ -31167,7 +31167,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1062" t="n">
         <v>6225</v>
@@ -31283,7 +31283,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1066" t="n">
         <v>38758</v>
@@ -31341,7 +31341,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1068" t="n">
         <v>988</v>
@@ -31486,7 +31486,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1073" t="n">
         <v>64565</v>
@@ -31515,7 +31515,7 @@
         <v>4.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1074" t="n">
         <v>46520</v>
@@ -31544,7 +31544,7 @@
         <v>4.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1075" t="n">
         <v>22473</v>
@@ -31631,7 +31631,7 @@
         <v>4.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.78905057907104</v>
+        <v>3.78905010223389</v>
       </c>
       <c r="H1078" t="n">
         <v>26882</v>
@@ -31660,7 +31660,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1079" t="n">
         <v>74698</v>
@@ -31776,7 +31776,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1083" t="n">
         <v>17149</v>
@@ -31834,7 +31834,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.67958879470825</v>
+        <v>3.67958903312683</v>
       </c>
       <c r="H1085" t="n">
         <v>11959</v>
@@ -31863,7 +31863,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1086" t="n">
         <v>12229</v>
@@ -31921,7 +31921,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642901420593</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1088" t="n">
         <v>3360</v>
@@ -32037,7 +32037,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1092" t="n">
         <v>2683</v>
@@ -32153,7 +32153,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1096" t="n">
         <v>7457</v>
@@ -32182,7 +32182,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644728660583</v>
+        <v>3.53644680976868</v>
       </c>
       <c r="H1097" t="n">
         <v>8056</v>
@@ -32211,7 +32211,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276684761047</v>
       </c>
       <c r="H1098" t="n">
         <v>4264</v>
@@ -32269,7 +32269,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172553062439</v>
       </c>
       <c r="H1100" t="n">
         <v>6138</v>
@@ -32414,7 +32414,7 @@
         <v>4.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.57854795455933</v>
+        <v>3.57854771614075</v>
       </c>
       <c r="H1105" t="n">
         <v>4054</v>
@@ -32472,7 +32472,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1107" t="n">
         <v>9024</v>
@@ -32501,7 +32501,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1108" t="n">
         <v>34399</v>
@@ -32617,7 +32617,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1112" t="n">
         <v>4545</v>
@@ -32646,7 +32646,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1113" t="n">
         <v>300</v>
@@ -32675,7 +32675,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172553062439</v>
       </c>
       <c r="H1114" t="n">
         <v>9295</v>
@@ -32733,7 +32733,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H1116" t="n">
         <v>1500</v>
@@ -32762,7 +32762,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H1117" t="n">
         <v>1899</v>
@@ -32849,7 +32849,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1120" t="n">
         <v>15675</v>
@@ -32936,7 +32936,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1123" t="n">
         <v>12666</v>
@@ -33023,7 +33023,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1126" t="n">
         <v>3443</v>
@@ -33226,7 +33226,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.81231737136841</v>
+        <v>2.81231760978699</v>
       </c>
       <c r="H1133" t="n">
         <v>28149</v>
@@ -33313,7 +33313,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1136" t="n">
         <v>66796</v>
@@ -33371,7 +33371,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1138" t="n">
         <v>8053</v>
@@ -33400,7 +33400,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H1139" t="n">
         <v>5055</v>
@@ -33487,7 +33487,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1142" t="n">
         <v>11790</v>
@@ -33516,7 +33516,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1143" t="n">
         <v>1920</v>
@@ -33574,7 +33574,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1145" t="n">
         <v>5210</v>
@@ -33603,7 +33603,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594418525696</v>
       </c>
       <c r="H1146" t="n">
         <v>2889</v>
@@ -33632,7 +33632,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1147" t="n">
         <v>2050</v>
@@ -33661,7 +33661,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1148" t="n">
         <v>1680</v>
@@ -33748,7 +33748,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1151" t="n">
         <v>3053</v>
@@ -33777,7 +33777,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1152" t="n">
         <v>1252</v>
@@ -33806,7 +33806,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490310668945</v>
+        <v>3.22490286827087</v>
       </c>
       <c r="H1153" t="n">
         <v>3850</v>
@@ -33893,7 +33893,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.233323097229</v>
+        <v>3.23332285881042</v>
       </c>
       <c r="H1156" t="n">
         <v>1332</v>
@@ -34009,7 +34009,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.26700401306152</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1160" t="n">
         <v>1350</v>
@@ -34212,7 +34212,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1167" t="n">
         <v>256</v>
@@ -34270,7 +34270,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.2922637462616</v>
+        <v>3.29226398468018</v>
       </c>
       <c r="H1169" t="n">
         <v>78</v>
@@ -34328,7 +34328,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.17438244819641</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H1171" t="n">
         <v>1224</v>
@@ -34357,7 +34357,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1172" t="n">
         <v>767</v>
@@ -34386,7 +34386,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1173" t="n">
         <v>300</v>
@@ -34647,7 +34647,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.3321316242218</v>
+        <v>3.33213138580322</v>
       </c>
       <c r="H1182" t="n">
         <v>400</v>
@@ -34705,7 +34705,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1184" t="n">
         <v>1051</v>
@@ -34734,7 +34734,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1185" t="n">
         <v>1629</v>
@@ -34821,7 +34821,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1188" t="n">
         <v>437</v>
@@ -34850,7 +34850,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1189" t="n">
         <v>0</v>
@@ -34879,7 +34879,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1190" t="n">
         <v>0</v>
@@ -34908,7 +34908,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1192" t="n">
         <v>2500</v>
@@ -35024,7 +35024,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1195" t="n">
         <v>5820</v>
@@ -35053,7 +35053,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.20094513893127</v>
+        <v>3.20094537734985</v>
       </c>
       <c r="H1196" t="n">
         <v>3100</v>
@@ -35140,7 +35140,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.27091121673584</v>
+        <v>3.27091145515442</v>
       </c>
       <c r="H1199" t="n">
         <v>1010</v>
@@ -35285,7 +35285,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1204" t="n">
         <v>9575</v>
@@ -35372,7 +35372,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599614143372</v>
+        <v>3.09599637985229</v>
       </c>
       <c r="H1207" t="n">
         <v>8591</v>
@@ -35575,7 +35575,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1214" t="n">
         <v>2847</v>
@@ -35633,7 +35633,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1216" t="n">
         <v>19487</v>
@@ -35662,7 +35662,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1217" t="n">
         <v>7777</v>
@@ -35923,7 +35923,7 @@
         <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1226" t="n">
         <v>8635</v>
@@ -35952,7 +35952,7 @@
         <v>3</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1227" t="n">
         <v>3800</v>
@@ -36126,7 +36126,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1233" t="n">
         <v>7495</v>
@@ -36213,7 +36213,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1236" t="n">
         <v>212</v>
@@ -36416,7 +36416,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1243" t="n">
         <v>2327</v>
@@ -36532,7 +36532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1247" t="n">
         <v>10</v>
@@ -36561,7 +36561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1248" t="n">
         <v>93</v>
@@ -36590,7 +36590,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1249" t="n">
         <v>0</v>
@@ -36648,7 +36648,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1251" t="n">
         <v>132</v>
@@ -36677,7 +36677,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1252" t="n">
         <v>650</v>
@@ -36706,7 +36706,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1253" t="n">
         <v>0</v>
@@ -36735,7 +36735,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.03477621078491</v>
+        <v>3.03477597236633</v>
       </c>
       <c r="H1254" t="n">
         <v>290</v>
@@ -36822,7 +36822,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1257" t="n">
         <v>364</v>
@@ -36851,7 +36851,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1258" t="n">
         <v>948</v>
@@ -36880,7 +36880,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1259" t="n">
         <v>0</v>
@@ -36967,7 +36967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1262" t="n">
         <v>500</v>
@@ -37112,7 +37112,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1267" t="n">
         <v>423</v>
@@ -37141,7 +37141,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1268" t="n">
         <v>3807</v>
@@ -37257,7 +37257,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.6761999130249</v>
+        <v>2.67620015144348</v>
       </c>
       <c r="H1272" t="n">
         <v>600</v>
@@ -37576,7 +37576,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630191802979</v>
+        <v>2.46630215644836</v>
       </c>
       <c r="H1283" t="n">
         <v>2421</v>
@@ -37605,7 +37605,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.43131923675537</v>
+        <v>2.43131899833679</v>
       </c>
       <c r="H1284" t="n">
         <v>7210</v>
@@ -37663,7 +37663,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630191802979</v>
+        <v>2.46630215644836</v>
       </c>
       <c r="H1286" t="n">
         <v>5150</v>
@@ -37750,7 +37750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.54501390457153</v>
+        <v>2.54501414299011</v>
       </c>
       <c r="H1289" t="n">
         <v>597</v>
@@ -37924,7 +37924,7 @@
         <v>3</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1295" t="n">
         <v>1600</v>
@@ -38127,7 +38127,7 @@
         <v>3</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.62372541427612</v>
+        <v>2.6237256526947</v>
       </c>
       <c r="H1302" t="n">
         <v>2450</v>
@@ -38388,7 +38388,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1311" t="n">
         <v>750</v>
@@ -38591,7 +38591,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1318" t="n">
         <v>5551</v>
@@ -38620,7 +38620,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1319" t="n">
         <v>10275</v>
@@ -38649,7 +38649,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1320" t="n">
         <v>2763</v>
@@ -38765,7 +38765,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1324" t="n">
         <v>500</v>
@@ -38794,7 +38794,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1325" t="n">
         <v>6498</v>
@@ -38823,7 +38823,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1326" t="n">
         <v>5429</v>
@@ -38968,7 +38968,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1331" t="n">
         <v>2844</v>
@@ -39084,7 +39084,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1335" t="n">
         <v>3359</v>
@@ -39113,7 +39113,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1336" t="n">
         <v>1510</v>
@@ -39229,7 +39229,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1340" t="n">
         <v>6322</v>
@@ -39258,7 +39258,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1341" t="n">
         <v>11551</v>
@@ -39316,7 +39316,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1343" t="n">
         <v>5050</v>
@@ -39345,7 +39345,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1344" t="n">
         <v>940</v>
@@ -39403,7 +39403,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1346" t="n">
         <v>5826</v>
@@ -39432,7 +39432,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1347" t="n">
         <v>1291</v>
@@ -39461,7 +39461,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1348" t="n">
         <v>5413</v>
@@ -39490,7 +39490,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1349" t="n">
         <v>61323</v>
@@ -39519,7 +39519,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1350" t="n">
         <v>5239</v>
@@ -39577,7 +39577,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1352" t="n">
         <v>1660</v>
@@ -39722,7 +39722,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1357" t="n">
         <v>855</v>
@@ -39751,7 +39751,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1358" t="n">
         <v>0</v>
@@ -39780,7 +39780,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1359" t="n">
         <v>0</v>
@@ -39838,7 +39838,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1361" t="n">
         <v>22818</v>
@@ -39896,7 +39896,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599614143372</v>
+        <v>3.09599637985229</v>
       </c>
       <c r="H1363" t="n">
         <v>19094</v>
@@ -40041,7 +40041,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.27091121673584</v>
+        <v>3.27091145515442</v>
       </c>
       <c r="H1368" t="n">
         <v>10067</v>
@@ -40099,7 +40099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.25341963768005</v>
+        <v>3.25341987609863</v>
       </c>
       <c r="H1370" t="n">
         <v>23028</v>
@@ -40186,7 +40186,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.24467396736145</v>
+        <v>3.24467420578003</v>
       </c>
       <c r="H1373" t="n">
         <v>4880</v>
@@ -40244,7 +40244,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1375" t="n">
         <v>1200</v>
@@ -40273,7 +40273,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1376" t="n">
         <v>750</v>
@@ -40360,7 +40360,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1379" t="n">
         <v>13793</v>
@@ -40418,7 +40418,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1381" t="n">
         <v>3079</v>
@@ -40447,7 +40447,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1382" t="n">
         <v>2200</v>
@@ -40476,7 +40476,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1383" t="n">
         <v>2020</v>
@@ -40505,7 +40505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1384" t="n">
         <v>300</v>
@@ -40534,7 +40534,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1385" t="n">
         <v>200</v>
@@ -40650,7 +40650,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470788955688</v>
+        <v>3.17470812797546</v>
       </c>
       <c r="H1389" t="n">
         <v>942</v>
@@ -40708,7 +40708,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1391" t="n">
         <v>442</v>
@@ -40737,7 +40737,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1392" t="n">
         <v>950</v>
@@ -40766,7 +40766,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.03477621078491</v>
+        <v>3.03477597236633</v>
       </c>
       <c r="H1393" t="n">
         <v>13610</v>
@@ -40824,7 +40824,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1395" t="n">
         <v>64822</v>
@@ -40911,7 +40911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1398" t="n">
         <v>400</v>
@@ -41114,7 +41114,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1405" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1405" t="n">
         <v>4985</v>
@@ -41201,7 +41201,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1408" t="n">
         <v>141</v>
@@ -41230,7 +41230,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1409" t="n">
         <v>7666</v>
@@ -41346,7 +41346,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1413" t="n">
         <v>1559</v>
@@ -41404,7 +41404,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1415" t="n">
         <v>7825</v>
@@ -41462,7 +41462,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1417" t="n">
         <v>2002</v>
@@ -41491,7 +41491,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1418" t="n">
         <v>14401</v>
@@ -41607,7 +41607,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.00853896141052</v>
+        <v>3.00853872299194</v>
       </c>
       <c r="H1422" t="n">
         <v>3025</v>
@@ -41636,7 +41636,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1423" t="n">
         <v>3547</v>
@@ -41665,7 +41665,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1424" t="n">
         <v>6125</v>
@@ -41955,7 +41955,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1434" t="n">
         <v>6060</v>
@@ -41984,7 +41984,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1435" t="n">
         <v>9210</v>
@@ -67104,6 +67104,64 @@
         <v>11982</v>
       </c>
       <c r="I2301" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2302" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2302" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="G2302" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="H2302" t="n">
+        <v>3406</v>
+      </c>
+      <c r="I2302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2303" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2303" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D2303" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2303" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="H2303" t="n">
+        <v>4074</v>
+      </c>
+      <c r="I2303" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802340507507</v>
+        <v>2.85802364349365</v>
       </c>
       <c r="H3" t="n">
         <v>168500</v>
@@ -485,7 +485,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459286689758</v>
+        <v>2.78459334373474</v>
       </c>
       <c r="H4" t="n">
         <v>65500</v>
@@ -543,7 +543,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522221565247</v>
+        <v>2.8652229309082</v>
       </c>
       <c r="H6" t="n">
         <v>89500</v>
@@ -572,7 +572,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930611610413</v>
+        <v>2.83930635452271</v>
       </c>
       <c r="H7" t="n">
         <v>35500</v>
@@ -630,7 +630,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85514378547668</v>
+        <v>2.85514402389526</v>
       </c>
       <c r="H9" t="n">
         <v>36500</v>
@@ -659,7 +659,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82922720909119</v>
+        <v>2.82922744750977</v>
       </c>
       <c r="H10" t="n">
         <v>7500</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H11" t="n">
         <v>24000</v>
@@ -746,7 +746,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8709819316864</v>
+        <v>2.87098169326782</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818098068237</v>
       </c>
       <c r="H14" t="n">
         <v>11000</v>
@@ -804,7 +804,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92569470405579</v>
+        <v>2.92569446563721</v>
       </c>
       <c r="H15" t="n">
         <v>25500</v>
@@ -833,7 +833,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94585204124451</v>
+        <v>2.94585180282593</v>
       </c>
       <c r="H16" t="n">
         <v>41500</v>
@@ -978,7 +978,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522221565247</v>
+        <v>2.8652229309082</v>
       </c>
       <c r="H21" t="n">
         <v>7500</v>
@@ -1036,7 +1036,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697693824768</v>
+        <v>2.90697717666626</v>
       </c>
       <c r="H23" t="n">
         <v>43500</v>
@@ -1065,7 +1065,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.90121793746948</v>
+        <v>2.9012176990509</v>
       </c>
       <c r="H24" t="n">
         <v>38500</v>
@@ -1123,7 +1123,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841674804688</v>
+        <v>2.90841722488403</v>
       </c>
       <c r="H26" t="n">
         <v>9000</v>
@@ -1152,7 +1152,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.9213752746582</v>
+        <v>2.92137551307678</v>
       </c>
       <c r="H27" t="n">
         <v>1000</v>
@@ -1384,7 +1384,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>2.89401865005493</v>
+        <v>2.89401888847351</v>
       </c>
       <c r="H35" t="n">
         <v>6000</v>
@@ -1471,7 +1471,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.82922720909119</v>
+        <v>2.82922744750977</v>
       </c>
       <c r="H38" t="n">
         <v>1500</v>
@@ -1529,7 +1529,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G40" t="n">
-        <v>2.80331087112427</v>
+        <v>2.80331110954285</v>
       </c>
       <c r="H40" t="n">
         <v>1000</v>
@@ -1558,7 +1558,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H41" t="n">
         <v>30500</v>
@@ -1616,7 +1616,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1645,7 +1645,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179215431213</v>
+        <v>2.79179239273071</v>
       </c>
       <c r="H44" t="n">
         <v>4500</v>
@@ -1674,7 +1674,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338953971863</v>
+        <v>2.81338930130005</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818098068237</v>
       </c>
       <c r="H46" t="n">
         <v>500</v>
@@ -1761,7 +1761,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H48" t="n">
         <v>1500</v>
@@ -1790,7 +1790,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H49" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.80475068092346</v>
+        <v>2.80475044250488</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H55" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770873069763</v>
+        <v>2.81770896911621</v>
       </c>
       <c r="H56" t="n">
         <v>15500</v>
@@ -2051,7 +2051,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723695755005</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412133216858</v>
+        <v>2.72412109375</v>
       </c>
       <c r="H59" t="n">
         <v>8000</v>
@@ -2109,7 +2109,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948698997498</v>
+        <v>2.6794867515564</v>
       </c>
       <c r="H60" t="n">
         <v>12500</v>
@@ -2283,7 +2283,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532465934753</v>
+        <v>2.69532489776611</v>
       </c>
       <c r="H66" t="n">
         <v>11000</v>
@@ -2341,7 +2341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H68" t="n">
         <v>3000</v>
@@ -2370,7 +2370,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723695755005</v>
       </c>
       <c r="H72" t="n">
         <v>4000</v>
@@ -2486,7 +2486,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723671913147</v>
+        <v>2.75723695755005</v>
       </c>
       <c r="H73" t="n">
         <v>8500</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H74" t="n">
         <v>11500</v>
@@ -2544,7 +2544,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H76" t="n">
         <v>1000</v>
@@ -2602,7 +2602,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H77" t="n">
         <v>7500</v>
@@ -2660,7 +2660,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G79" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H79" t="n">
         <v>14500</v>
@@ -2689,7 +2689,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G80" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980166435242</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524599075317</v>
+        <v>2.68524670600891</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2863,7 +2863,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964456558228</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2950,7 +2950,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59885787963867</v>
+        <v>2.59885764122009</v>
       </c>
       <c r="H89" t="n">
         <v>5000</v>
@@ -2979,7 +2979,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>2.59885787963867</v>
+        <v>2.59885764122009</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647404670715</v>
+        <v>2.47647380828857</v>
       </c>
       <c r="H95" t="n">
         <v>1000</v>
@@ -3153,7 +3153,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647404670715</v>
+        <v>2.47647380828857</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.5</v>
       </c>
       <c r="G98" t="n">
-        <v>2.5196681022644</v>
+        <v>2.51966834068298</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3298,7 +3298,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.60605621337891</v>
+        <v>2.60605645179749</v>
       </c>
       <c r="H101" t="n">
         <v>500</v>
@@ -3385,7 +3385,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H104" t="n">
         <v>10500</v>
@@ -3414,7 +3414,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>2.71404242515564</v>
+        <v>2.71404266357422</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485264778137</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H109" t="n">
         <v>4000</v>
@@ -3559,7 +3559,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485264778137</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485264778137</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006144523621</v>
+        <v>2.57006192207336</v>
       </c>
       <c r="H116" t="n">
         <v>11000</v>
@@ -3762,7 +3762,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006144523621</v>
+        <v>2.57006192207336</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>3.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.5196681022644</v>
+        <v>2.51966834068298</v>
       </c>
       <c r="H121" t="n">
         <v>500</v>
@@ -3907,7 +3907,7 @@
         <v>3.5</v>
       </c>
       <c r="G122" t="n">
-        <v>2.5196681022644</v>
+        <v>2.51966834068298</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H125" t="n">
         <v>5500</v>
@@ -4023,7 +4023,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165859222412</v>
+        <v>2.59165835380554</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77163505554199</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H133" t="n">
         <v>45500</v>
@@ -4574,7 +4574,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4603,7 +4603,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>2.728440284729</v>
+        <v>2.72844099998474</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4835,7 +4835,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H154" t="n">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80763030052185</v>
       </c>
       <c r="H158" t="n">
         <v>1000</v>
@@ -5299,7 +5299,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857922554016</v>
       </c>
       <c r="H170" t="n">
         <v>7000</v>
@@ -5444,7 +5444,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H175" t="n">
         <v>2500</v>
@@ -5473,7 +5473,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H177" t="n">
         <v>1000</v>
@@ -5531,7 +5531,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G178" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H178" t="n">
         <v>7000</v>
@@ -5560,7 +5560,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G179" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5618,7 +5618,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H181" t="n">
         <v>1000</v>
@@ -5647,7 +5647,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H182" t="n">
         <v>2000</v>
@@ -5676,7 +5676,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H183" t="n">
         <v>1500</v>
@@ -5705,7 +5705,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>2.63865542411804</v>
+        <v>2.63865566253662</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66114401817322</v>
+        <v>2.6611442565918</v>
       </c>
       <c r="H185" t="n">
         <v>500</v>
@@ -5763,7 +5763,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612120628357</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5850,7 +5850,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H189" t="n">
         <v>9000</v>
@@ -5879,7 +5879,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H190" t="n">
         <v>9500</v>
@@ -5908,7 +5908,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H191" t="n">
         <v>2500</v>
@@ -5937,7 +5937,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H192" t="n">
         <v>500</v>
@@ -5966,7 +5966,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G193" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H193" t="n">
         <v>6500</v>
@@ -5995,7 +5995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H196" t="n">
         <v>1000</v>
@@ -6082,7 +6082,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.78108263015747</v>
+        <v>2.78108286857605</v>
       </c>
       <c r="H197" t="n">
         <v>11500</v>
@@ -6111,7 +6111,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G198" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H198" t="n">
         <v>500</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G202" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G203" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G205" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H209" t="n">
         <v>6000</v>
@@ -6459,7 +6459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H210" t="n">
         <v>2500</v>
@@ -6488,7 +6488,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H211" t="n">
         <v>9500</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.78108263015747</v>
+        <v>2.78108286857605</v>
       </c>
       <c r="H212" t="n">
         <v>3000</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.78108263015747</v>
+        <v>2.78108286857605</v>
       </c>
       <c r="H216" t="n">
         <v>5500</v>
@@ -6720,7 +6720,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H219" t="n">
         <v>61000</v>
@@ -6807,7 +6807,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H222" t="n">
         <v>10000</v>
@@ -6836,7 +6836,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612120628357</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H223" t="n">
         <v>5500</v>
@@ -6865,7 +6865,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G224" t="n">
-        <v>2.63115930557251</v>
+        <v>2.63115906715393</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6894,7 +6894,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618235588074</v>
+        <v>2.58618211746216</v>
       </c>
       <c r="H225" t="n">
         <v>6500</v>
@@ -6923,7 +6923,7 @@
         <v>3.5</v>
       </c>
       <c r="G226" t="n">
-        <v>2.62366318702698</v>
+        <v>2.6236629486084</v>
       </c>
       <c r="H226" t="n">
         <v>22000</v>
@@ -6981,7 +6981,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867047309875</v>
+        <v>2.60867071151733</v>
       </c>
       <c r="H228" t="n">
         <v>1500</v>
@@ -7039,7 +7039,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.66114401817322</v>
+        <v>2.6611442565918</v>
       </c>
       <c r="H230" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>2.71361684799194</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G232" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H232" t="n">
         <v>1500</v>
@@ -7126,7 +7126,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355617523193</v>
       </c>
       <c r="H237" t="n">
         <v>24000</v>
@@ -7329,7 +7329,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H240" t="n">
         <v>1500</v>
@@ -7358,7 +7358,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H244" t="n">
         <v>24500</v>
@@ -7474,7 +7474,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7503,7 +7503,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>2.87103700637817</v>
+        <v>2.87103676795959</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609063148499</v>
+        <v>2.76609039306641</v>
       </c>
       <c r="H247" t="n">
         <v>5000</v>
@@ -7706,7 +7706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H253" t="n">
         <v>500</v>
@@ -7938,7 +7938,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>2.78857898712158</v>
+        <v>2.78857922554016</v>
       </c>
       <c r="H261" t="n">
         <v>5500</v>
@@ -7996,7 +7996,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8025,7 +8025,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H264" t="n">
         <v>19500</v>
@@ -8054,7 +8054,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H273" t="n">
         <v>2500</v>
@@ -8315,7 +8315,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635004043579</v>
+        <v>2.25635027885437</v>
       </c>
       <c r="H277" t="n">
         <v>5000</v>
@@ -8431,7 +8431,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.2638463973999</v>
+        <v>2.26384663581848</v>
       </c>
       <c r="H278" t="n">
         <v>5500</v>
@@ -8460,7 +8460,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>2.2638463973999</v>
+        <v>2.26384663581848</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883887290955</v>
+        <v>2.27883863449097</v>
       </c>
       <c r="H280" t="n">
         <v>3000</v>
@@ -8518,7 +8518,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H281" t="n">
         <v>7500</v>
@@ -8547,7 +8547,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639614105225</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.15140342712402</v>
+        <v>2.1514036655426</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639614105225</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G286" t="n">
-        <v>2.10642647743225</v>
+        <v>2.10642671585083</v>
       </c>
       <c r="H286" t="n">
         <v>15500</v>
@@ -8692,7 +8692,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638085365295</v>
+        <v>2.19638061523438</v>
       </c>
       <c r="H287" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18138790130615</v>
+        <v>2.18138837814331</v>
       </c>
       <c r="H288" t="n">
         <v>8000</v>
@@ -8750,7 +8750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18138790130615</v>
+        <v>2.18138837814331</v>
       </c>
       <c r="H289" t="n">
         <v>13000</v>
@@ -8779,7 +8779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H290" t="n">
         <v>8500</v>
@@ -8808,7 +8808,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H291" t="n">
         <v>11000</v>
@@ -8837,7 +8837,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>2.17389225959778</v>
+        <v>2.17389249801636</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.13641142845154</v>
+        <v>2.13641119003296</v>
       </c>
       <c r="H294" t="n">
         <v>1000</v>
@@ -8982,7 +8982,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03146481513977</v>
+        <v>2.03146457672119</v>
       </c>
       <c r="H297" t="n">
         <v>14000</v>
@@ -9011,7 +9011,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644200325012</v>
+        <v>2.07644176483154</v>
       </c>
       <c r="H298" t="n">
         <v>7500</v>
@@ -9127,7 +9127,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10642647743225</v>
+        <v>2.10642671585083</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390730857849</v>
+        <v>2.14390754699707</v>
       </c>
       <c r="H303" t="n">
         <v>2500</v>
@@ -9185,7 +9185,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H304" t="n">
         <v>5500</v>
@@ -9214,7 +9214,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G306" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.27134275436401</v>
+        <v>2.27134251594543</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625855445862</v>
+        <v>2.43625831604004</v>
       </c>
       <c r="H311" t="n">
         <v>27000</v>
@@ -9417,7 +9417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876243591309</v>
+        <v>2.42876219749451</v>
       </c>
       <c r="H312" t="n">
         <v>12000</v>
@@ -10229,7 +10229,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H340" t="n">
         <v>6000</v>
@@ -10258,7 +10258,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G342" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G346" t="n">
-        <v>2.36129689216614</v>
+        <v>2.36129665374756</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10490,7 +10490,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885368347168</v>
       </c>
       <c r="H349" t="n">
         <v>6000</v>
@@ -10519,7 +10519,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885368347168</v>
       </c>
       <c r="H350" t="n">
         <v>2500</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.2113733291626</v>
+        <v>2.21137309074402</v>
       </c>
       <c r="H351" t="n">
         <v>94500</v>
@@ -10577,7 +10577,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885368347168</v>
       </c>
       <c r="H352" t="n">
         <v>16000</v>
@@ -10606,7 +10606,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885368347168</v>
       </c>
       <c r="H353" t="n">
         <v>9500</v>
@@ -10635,7 +10635,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>2.2863347530365</v>
+        <v>2.28633499145508</v>
       </c>
       <c r="H354" t="n">
         <v>11500</v>
@@ -10722,7 +10722,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885416030884</v>
+        <v>2.24885368347168</v>
       </c>
       <c r="H357" t="n">
         <v>1000</v>
@@ -10809,7 +10809,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>2.61616706848145</v>
+        <v>2.61616683006287</v>
       </c>
       <c r="H360" t="n">
         <v>20500</v>
@@ -10896,7 +10896,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>2.56369400024414</v>
+        <v>2.56369352340698</v>
       </c>
       <c r="H364" t="n">
         <v>500</v>
@@ -10954,7 +10954,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56369400024414</v>
+        <v>2.56369352340698</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H366" t="n">
         <v>500</v>
@@ -11012,7 +11012,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120540618896</v>
+        <v>2.54120516777039</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>2.48123574256897</v>
+        <v>2.48123598098755</v>
       </c>
       <c r="H368" t="n">
         <v>16500</v>
@@ -11070,7 +11070,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868623733521</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H369" t="n">
         <v>1500</v>
@@ -11099,7 +11099,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868623733521</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.54870128631592</v>
+        <v>2.54870104789734</v>
       </c>
       <c r="H371" t="n">
         <v>500</v>
@@ -11157,7 +11157,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.54870128631592</v>
+        <v>2.54870104789734</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11215,7 +11215,7 @@
         <v>3.5</v>
       </c>
       <c r="G374" t="n">
-        <v>2.62366318702698</v>
+        <v>2.6236629486084</v>
       </c>
       <c r="H374" t="n">
         <v>2500</v>
@@ -11244,7 +11244,7 @@
         <v>3.5</v>
       </c>
       <c r="G375" t="n">
-        <v>2.62366318702698</v>
+        <v>2.6236629486084</v>
       </c>
       <c r="H375" t="n">
         <v>4000</v>
@@ -11273,7 +11273,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868623733521</v>
+        <v>2.57868599891663</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11302,7 +11302,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.66114401817322</v>
+        <v>2.6611442565918</v>
       </c>
       <c r="H377" t="n">
         <v>12500</v>
@@ -11360,7 +11360,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H379" t="n">
         <v>19000</v>
@@ -11389,7 +11389,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607486724854</v>
+        <v>2.79607534408569</v>
       </c>
       <c r="H380" t="n">
         <v>11500</v>
@@ -11534,7 +11534,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355617523193</v>
       </c>
       <c r="H385" t="n">
         <v>5000</v>
@@ -11563,7 +11563,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859427452087</v>
+        <v>2.75859451293945</v>
       </c>
       <c r="H386" t="n">
         <v>3000</v>
@@ -11592,7 +11592,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G387" t="n">
-        <v>2.72860956192017</v>
+        <v>2.72860980033875</v>
       </c>
       <c r="H387" t="n">
         <v>48000</v>
@@ -11621,7 +11621,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856369972229</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H388" t="n">
         <v>48000</v>
@@ -11650,7 +11650,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H389" t="n">
         <v>20000</v>
@@ -11679,7 +11679,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G390" t="n">
-        <v>2.86354041099548</v>
+        <v>2.86354064941406</v>
       </c>
       <c r="H390" t="n">
         <v>5500</v>
@@ -11737,7 +11737,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851831436157</v>
       </c>
       <c r="H392" t="n">
         <v>8000</v>
@@ -11766,7 +11766,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851831436157</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851831436157</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11940,7 +11940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355617523193</v>
       </c>
       <c r="H399" t="n">
         <v>8000</v>
@@ -11969,7 +11969,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355617523193</v>
       </c>
       <c r="H400" t="n">
         <v>3500</v>
@@ -11998,7 +11998,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H401" t="n">
         <v>500</v>
@@ -12027,7 +12027,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>2.77358675003052</v>
+        <v>2.7735869884491</v>
       </c>
       <c r="H402" t="n">
         <v>1500</v>
@@ -12056,7 +12056,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856369972229</v>
+        <v>2.81856393814087</v>
       </c>
       <c r="H403" t="n">
         <v>4000</v>
@@ -12085,7 +12085,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12114,7 +12114,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355593681335</v>
+        <v>2.83355617523193</v>
       </c>
       <c r="H407" t="n">
         <v>119000</v>
@@ -12230,7 +12230,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848773956299</v>
       </c>
       <c r="H409" t="n">
         <v>16000</v>
@@ -12259,7 +12259,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848773956299</v>
       </c>
       <c r="H410" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851831436157</v>
       </c>
       <c r="H415" t="n">
         <v>1000</v>
@@ -12433,7 +12433,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G416" t="n">
-        <v>2.94987845420837</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866302490234</v>
+        <v>2.91866278648376</v>
       </c>
       <c r="H417" t="n">
         <v>2500</v>
@@ -12636,7 +12636,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>2.9810938835144</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H423" t="n">
         <v>7500</v>
@@ -12665,7 +12665,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G424" t="n">
-        <v>2.9810938835144</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>2.94987845420837</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H432" t="n">
         <v>8000</v>
@@ -12984,7 +12984,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H435" t="n">
         <v>500</v>
@@ -13042,7 +13042,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94987845420837</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H437" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G438" t="n">
-        <v>2.94987845420837</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H438" t="n">
         <v>4000</v>
@@ -13100,7 +13100,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.9810938835144</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H439" t="n">
         <v>7000</v>
@@ -13129,7 +13129,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>2.9810938835144</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>2.94987845420837</v>
+        <v>2.94987869262695</v>
       </c>
       <c r="H443" t="n">
         <v>7500</v>
@@ -13303,7 +13303,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G446" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H446" t="n">
         <v>20000</v>
@@ -13332,7 +13332,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H447" t="n">
         <v>7500</v>
@@ -13361,7 +13361,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H448" t="n">
         <v>8000</v>
@@ -13448,7 +13448,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H451" t="n">
         <v>11500</v>
@@ -13506,7 +13506,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19960403442383</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H453" t="n">
         <v>1000</v>
@@ -13680,7 +13680,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H459" t="n">
         <v>24500</v>
@@ -13796,7 +13796,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H463" t="n">
         <v>6500</v>
@@ -13970,7 +13970,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.02791786193848</v>
+        <v>3.02791810035706</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -13999,7 +13999,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H470" t="n">
         <v>6000</v>
@@ -14057,7 +14057,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H472" t="n">
         <v>15500</v>
@@ -14144,7 +14144,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G475" t="n">
-        <v>3.19960403442383</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H475" t="n">
         <v>500</v>
@@ -14173,7 +14173,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>3.19960403442383</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H476" t="n">
         <v>5500</v>
@@ -14579,7 +14579,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14608,7 +14608,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>3.19960403442383</v>
+        <v>3.19960379600525</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14637,7 +14637,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764248847961</v>
+        <v>3.27764296531677</v>
       </c>
       <c r="H492" t="n">
         <v>65000</v>
@@ -14695,7 +14695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764248847961</v>
+        <v>3.27764296531677</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.37128973007202</v>
+        <v>3.37129020690918</v>
       </c>
       <c r="H495" t="n">
         <v>17000</v>
@@ -14753,7 +14753,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203489303589</v>
+        <v>3.26203513145447</v>
       </c>
       <c r="H496" t="n">
         <v>21000</v>
@@ -14869,7 +14869,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G500" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H500" t="n">
         <v>13000</v>
@@ -14898,7 +14898,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H502" t="n">
         <v>20500</v>
@@ -14956,7 +14956,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G503" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H503" t="n">
         <v>31000</v>
@@ -14985,7 +14985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G504" t="n">
-        <v>3.23081946372986</v>
+        <v>3.23081922531128</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H507" t="n">
         <v>6000</v>
@@ -15101,7 +15101,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G508" t="n">
-        <v>2.9810938835144</v>
+        <v>2.98109436035156</v>
       </c>
       <c r="H508" t="n">
         <v>12500</v>
@@ -15130,7 +15130,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717246055603</v>
+        <v>3.13717293739319</v>
       </c>
       <c r="H509" t="n">
         <v>6000</v>
@@ -15159,7 +15159,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G510" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H510" t="n">
         <v>3000</v>
@@ -15188,7 +15188,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H511" t="n">
         <v>3500</v>
@@ -15217,7 +15217,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474136352539</v>
+        <v>3.07474112510681</v>
       </c>
       <c r="H512" t="n">
         <v>3000</v>
@@ -15246,7 +15246,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H513" t="n">
         <v>39000</v>
@@ -15449,7 +15449,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>3.10595655441284</v>
+        <v>3.10595703125</v>
       </c>
       <c r="H521" t="n">
         <v>500</v>
@@ -15623,7 +15623,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H526" t="n">
         <v>15000</v>
@@ -15681,7 +15681,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183952331543</v>
+        <v>2.87183976173401</v>
       </c>
       <c r="H528" t="n">
         <v>17500</v>
@@ -15739,7 +15739,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G530" t="n">
-        <v>2.7781925201416</v>
+        <v>2.77819228172302</v>
       </c>
       <c r="H530" t="n">
         <v>4000</v>
@@ -15768,7 +15768,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.76258492469788</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H531" t="n">
         <v>34500</v>
@@ -15797,7 +15797,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697709083557</v>
       </c>
       <c r="H532" t="n">
         <v>1309000</v>
@@ -15826,7 +15826,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H533" t="n">
         <v>7500</v>
@@ -15855,7 +15855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H534" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H539" t="n">
         <v>3000</v>
@@ -16029,7 +16029,7 @@
         <v>3.5</v>
       </c>
       <c r="G540" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H540" t="n">
         <v>8000</v>
@@ -16087,7 +16087,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H542" t="n">
         <v>6000</v>
@@ -16116,7 +16116,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H543" t="n">
         <v>75500</v>
@@ -16261,7 +16261,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H548" t="n">
         <v>20000</v>
@@ -16290,7 +16290,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H549" t="n">
         <v>500</v>
@@ -16348,7 +16348,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H551" t="n">
         <v>9000</v>
@@ -16464,7 +16464,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H555" t="n">
         <v>5500</v>
@@ -16522,7 +16522,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H557" t="n">
         <v>4000</v>
@@ -16551,7 +16551,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H558" t="n">
         <v>1000</v>
@@ -16696,7 +16696,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16754,7 +16754,7 @@
         <v>3.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H565" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G566" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H566" t="n">
         <v>42500</v>
@@ -16812,7 +16812,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697709083557</v>
       </c>
       <c r="H567" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G569" t="n">
-        <v>2.7781925201416</v>
+        <v>2.77819228172302</v>
       </c>
       <c r="H569" t="n">
         <v>11000</v>
@@ -16899,7 +16899,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G570" t="n">
-        <v>2.7781925201416</v>
+        <v>2.77819228172302</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.7781925201416</v>
+        <v>2.77819228172302</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H572" t="n">
         <v>5500</v>
@@ -17073,7 +17073,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H576" t="n">
         <v>4000</v>
@@ -17131,7 +17131,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>2.76258492469788</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H578" t="n">
         <v>29000</v>
@@ -17189,7 +17189,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.7781925201416</v>
+        <v>2.77819228172302</v>
       </c>
       <c r="H580" t="n">
         <v>32000</v>
@@ -17218,7 +17218,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H581" t="n">
         <v>10500</v>
@@ -17276,7 +17276,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H583" t="n">
         <v>1000</v>
@@ -17305,7 +17305,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744735717773</v>
+        <v>2.88744759559631</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.7781925201416</v>
+        <v>2.77819228172302</v>
       </c>
       <c r="H586" t="n">
         <v>5000</v>
@@ -17421,7 +17421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576118469238</v>
+        <v>2.71576142311096</v>
       </c>
       <c r="H588" t="n">
         <v>25500</v>
@@ -17479,7 +17479,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>2.66893815994263</v>
+        <v>2.66893792152405</v>
       </c>
       <c r="H590" t="n">
         <v>2000</v>
@@ -17537,7 +17537,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G592" t="n">
-        <v>2.68454599380493</v>
+        <v>2.68454575538635</v>
       </c>
       <c r="H592" t="n">
         <v>1000</v>
@@ -17740,7 +17740,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H599" t="n">
         <v>13500</v>
@@ -17769,7 +17769,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.60650682449341</v>
+        <v>2.60650658607483</v>
       </c>
       <c r="H600" t="n">
         <v>12500</v>
@@ -17827,7 +17827,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G602" t="n">
-        <v>2.60650682449341</v>
+        <v>2.60650658607483</v>
       </c>
       <c r="H602" t="n">
         <v>6000</v>
@@ -17914,7 +17914,7 @@
         <v>3.5</v>
       </c>
       <c r="G605" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H605" t="n">
         <v>45000</v>
@@ -17943,7 +17943,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>2.76258492469788</v>
+        <v>2.7625846862793</v>
       </c>
       <c r="H606" t="n">
         <v>12000</v>
@@ -17972,7 +17972,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74697685241699</v>
+        <v>2.74697709083557</v>
       </c>
       <c r="H607" t="n">
         <v>35500</v>
@@ -18001,7 +18001,7 @@
         <v>3.5</v>
       </c>
       <c r="G608" t="n">
-        <v>2.73136925697327</v>
+        <v>2.73136901855469</v>
       </c>
       <c r="H608" t="n">
         <v>36000</v>
@@ -18291,7 +18291,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211441993713</v>
+        <v>2.62211394309998</v>
       </c>
       <c r="H618" t="n">
         <v>1000</v>
@@ -18349,7 +18349,7 @@
         <v>3</v>
       </c>
       <c r="G620" t="n">
-        <v>2.34117364883423</v>
+        <v>2.34117341041565</v>
       </c>
       <c r="H620" t="n">
         <v>7500</v>
@@ -18407,7 +18407,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>2.37238931655884</v>
+        <v>2.37238907814026</v>
       </c>
       <c r="H622" t="n">
         <v>1000</v>
@@ -18436,7 +18436,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.23191857337952</v>
+        <v>2.2319188117981</v>
       </c>
       <c r="H623" t="n">
         <v>16000</v>
@@ -18465,7 +18465,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631097793579</v>
+        <v>2.21631073951721</v>
       </c>
       <c r="H624" t="n">
         <v>3000</v>
@@ -18494,7 +18494,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H625" t="n">
         <v>13000</v>
@@ -18552,7 +18552,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H627" t="n">
         <v>2000</v>
@@ -18581,7 +18581,7 @@
         <v>2.5</v>
       </c>
       <c r="G628" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H628" t="n">
         <v>11000</v>
@@ -18610,7 +18610,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H629" t="n">
         <v>18500</v>
@@ -18639,7 +18639,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.95726156234741</v>
+        <v>1.9572616815567</v>
       </c>
       <c r="H631" t="n">
         <v>14000</v>
@@ -18697,7 +18697,7 @@
         <v>2.5</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H632" t="n">
         <v>9000</v>
@@ -18726,7 +18726,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.08884239196777</v>
+        <v>2.08884215354919</v>
       </c>
       <c r="H633" t="n">
         <v>6000</v>
@@ -18755,7 +18755,7 @@
         <v>2.5</v>
       </c>
       <c r="G634" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H634" t="n">
         <v>1000</v>
@@ -18784,7 +18784,7 @@
         <v>2.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>2.5</v>
       </c>
       <c r="G636" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H637" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H645" t="n">
         <v>14000</v>
@@ -19103,7 +19103,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H646" t="n">
         <v>3000</v>
@@ -19509,7 +19509,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G660" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H660" t="n">
         <v>2500</v>
@@ -19625,7 +19625,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H664" t="n">
         <v>1000</v>
@@ -19654,7 +19654,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H665" t="n">
         <v>2000</v>
@@ -19712,7 +19712,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G667" t="n">
-        <v>2.35200309753418</v>
+        <v>2.35200333595276</v>
       </c>
       <c r="H667" t="n">
         <v>9000</v>
@@ -19741,7 +19741,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555603027344</v>
+        <v>2.33555555343628</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G671" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H671" t="n">
         <v>31000</v>
@@ -19944,7 +19944,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.25331830978394</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H675" t="n">
         <v>13631</v>
@@ -20205,7 +20205,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G684" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H684" t="n">
         <v>3500</v>
@@ -20234,7 +20234,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H685" t="n">
         <v>13500</v>
@@ -20292,7 +20292,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H687" t="n">
         <v>3000</v>
@@ -20321,7 +20321,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H688" t="n">
         <v>2025</v>
@@ -20350,7 +20350,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H689" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G690" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20495,7 +20495,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G694" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H694" t="n">
         <v>4200</v>
@@ -20524,7 +20524,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G696" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H696" t="n">
         <v>10100</v>
@@ -20611,7 +20611,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G698" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266046524048</v>
       </c>
       <c r="H698" t="n">
         <v>5110</v>
@@ -20640,7 +20640,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G699" t="n">
-        <v>2.25331830978394</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H699" t="n">
         <v>2600</v>
@@ -20785,7 +20785,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H704" t="n">
         <v>5880</v>
@@ -20814,7 +20814,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H705" t="n">
         <v>4500</v>
@@ -20901,7 +20901,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G708" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H708" t="n">
         <v>1125</v>
@@ -20930,7 +20930,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G709" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G710" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266046524048</v>
       </c>
       <c r="H710" t="n">
         <v>15630</v>
@@ -21046,7 +21046,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G713" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266046524048</v>
       </c>
       <c r="H713" t="n">
         <v>7300</v>
@@ -21075,7 +21075,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266046524048</v>
       </c>
       <c r="H714" t="n">
         <v>14000</v>
@@ -21220,7 +21220,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G719" t="n">
-        <v>2.25331830978394</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H719" t="n">
         <v>1000</v>
@@ -21249,7 +21249,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H720" t="n">
         <v>2579</v>
@@ -21597,7 +21597,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H732" t="n">
         <v>10280</v>
@@ -21626,7 +21626,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>2.08884239196777</v>
+        <v>2.08884215354919</v>
       </c>
       <c r="H733" t="n">
         <v>6970</v>
@@ -21655,7 +21655,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>2.08884239196777</v>
+        <v>2.08884215354919</v>
       </c>
       <c r="H734" t="n">
         <v>3500</v>
@@ -21684,7 +21684,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G735" t="n">
-        <v>2.08884239196777</v>
+        <v>2.08884215354919</v>
       </c>
       <c r="H735" t="n">
         <v>991</v>
@@ -21713,7 +21713,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H736" t="n">
         <v>3700</v>
@@ -21742,7 +21742,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H737" t="n">
         <v>10300</v>
@@ -21771,7 +21771,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21800,7 +21800,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H739" t="n">
         <v>7950</v>
@@ -21829,7 +21829,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H750" t="n">
         <v>17333</v>
@@ -22177,7 +22177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H753" t="n">
         <v>64103</v>
@@ -22235,7 +22235,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H754" t="n">
         <v>14100</v>
@@ -22264,7 +22264,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H755" t="n">
         <v>5477</v>
@@ -22322,7 +22322,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H757" t="n">
         <v>3679</v>
@@ -22351,7 +22351,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H758" t="n">
         <v>2966</v>
@@ -22409,7 +22409,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H760" t="n">
         <v>210</v>
@@ -22438,7 +22438,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H761" t="n">
         <v>2170</v>
@@ -22467,7 +22467,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H762" t="n">
         <v>5110</v>
@@ -22496,7 +22496,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22525,7 +22525,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528945922852</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H764" t="n">
         <v>10600</v>
@@ -22554,7 +22554,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>2.08884239196777</v>
+        <v>2.08884215354919</v>
       </c>
       <c r="H765" t="n">
         <v>11000</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H766" t="n">
         <v>7000</v>
@@ -22612,7 +22612,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H767" t="n">
         <v>11020</v>
@@ -22641,7 +22641,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>1.94081377983093</v>
+        <v>1.94081389904022</v>
       </c>
       <c r="H768" t="n">
         <v>7167</v>
@@ -22670,7 +22670,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370934486389</v>
+        <v>1.97370946407318</v>
       </c>
       <c r="H769" t="n">
         <v>2120</v>
@@ -22786,7 +22786,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660443305969</v>
+        <v>2.00660467147827</v>
       </c>
       <c r="H773" t="n">
         <v>10000</v>
@@ -22815,7 +22815,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.95726156234741</v>
+        <v>1.9572616815567</v>
       </c>
       <c r="H774" t="n">
         <v>10000</v>
@@ -22844,7 +22844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212863445282</v>
+        <v>1.84212839603424</v>
       </c>
       <c r="H775" t="n">
         <v>26371</v>
@@ -22902,7 +22902,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633821964264</v>
+        <v>1.77633845806122</v>
       </c>
       <c r="H777" t="n">
         <v>21350</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212863445282</v>
+        <v>1.84212839603424</v>
       </c>
       <c r="H778" t="n">
         <v>8200</v>
@@ -22960,7 +22960,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G779" t="n">
-        <v>1.94081377983093</v>
+        <v>1.94081389904022</v>
       </c>
       <c r="H779" t="n">
         <v>23341</v>
@@ -23018,7 +23018,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G781" t="n">
-        <v>1.94081377983093</v>
+        <v>1.94081389904022</v>
       </c>
       <c r="H781" t="n">
         <v>12683</v>
@@ -23047,7 +23047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G782" t="n">
-        <v>1.94081377983093</v>
+        <v>1.94081389904022</v>
       </c>
       <c r="H782" t="n">
         <v>2000</v>
@@ -23105,7 +23105,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278576374054</v>
+        <v>1.79278588294983</v>
       </c>
       <c r="H784" t="n">
         <v>9450</v>
@@ -23134,7 +23134,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278576374054</v>
+        <v>1.79278588294983</v>
       </c>
       <c r="H785" t="n">
         <v>6000</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212863445282</v>
+        <v>1.84212839603424</v>
       </c>
       <c r="H786" t="n">
         <v>500</v>
@@ -23221,7 +23221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502348423004</v>
       </c>
       <c r="H788" t="n">
         <v>4000</v>
@@ -23250,7 +23250,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502348423004</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147114753723</v>
+        <v>1.89147126674652</v>
       </c>
       <c r="H790" t="n">
         <v>2551</v>
@@ -23395,7 +23395,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.99015665054321</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H794" t="n">
         <v>5000</v>
@@ -23424,7 +23424,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370934486389</v>
+        <v>1.97370946407318</v>
       </c>
       <c r="H795" t="n">
         <v>5168</v>
@@ -23482,7 +23482,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="n">
-        <v>2.05594706535339</v>
+        <v>2.05594682693481</v>
       </c>
       <c r="H797" t="n">
         <v>12411</v>
@@ -23511,7 +23511,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H798" t="n">
         <v>20346</v>
@@ -23627,7 +23627,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108011245728</v>
+        <v>2.17108035087585</v>
       </c>
       <c r="H802" t="n">
         <v>15886</v>
@@ -23685,7 +23685,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G804" t="n">
-        <v>2.25331830978394</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H804" t="n">
         <v>6170</v>
@@ -23714,7 +23714,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G805" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266046524048</v>
       </c>
       <c r="H805" t="n">
         <v>9350</v>
@@ -23772,7 +23772,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H807" t="n">
         <v>11874</v>
@@ -23801,7 +23801,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20397520065308</v>
+        <v>2.20397543907166</v>
       </c>
       <c r="H808" t="n">
         <v>8250</v>
@@ -23830,7 +23830,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.15463256835938</v>
+        <v>2.1546323299408</v>
       </c>
       <c r="H809" t="n">
         <v>3200</v>
@@ -23946,7 +23946,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H813" t="n">
         <v>15111</v>
@@ -24004,7 +24004,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.25331830978394</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H815" t="n">
         <v>4017</v>
@@ -24033,7 +24033,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H816" t="n">
         <v>4950</v>
@@ -24062,7 +24062,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H817" t="n">
         <v>3243</v>
@@ -24091,7 +24091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G818" t="n">
-        <v>2.26976561546326</v>
+        <v>2.26976537704468</v>
       </c>
       <c r="H818" t="n">
         <v>2250</v>
@@ -24294,7 +24294,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>2.25331830978394</v>
+        <v>2.25331807136536</v>
       </c>
       <c r="H825" t="n">
         <v>6850</v>
@@ -24352,7 +24352,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30266070365906</v>
+        <v>2.30266046524048</v>
       </c>
       <c r="H827" t="n">
         <v>20716</v>
@@ -24410,7 +24410,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H829" t="n">
         <v>292926</v>
@@ -24439,7 +24439,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H830" t="n">
         <v>183827</v>
@@ -24468,7 +24468,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G831" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H831" t="n">
         <v>72777</v>
@@ -24497,7 +24497,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964043617249</v>
+        <v>2.77964067459106</v>
       </c>
       <c r="H832" t="n">
         <v>51937</v>
@@ -24526,7 +24526,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H833" t="n">
         <v>25716</v>
@@ -24700,7 +24700,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H839" t="n">
         <v>12621</v>
@@ -24758,7 +24758,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>2.48358392715454</v>
+        <v>2.48358416557312</v>
       </c>
       <c r="H841" t="n">
         <v>18272</v>
@@ -24903,7 +24903,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H846" t="n">
         <v>14130</v>
@@ -24932,7 +24932,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H847" t="n">
         <v>6888</v>
@@ -24961,7 +24961,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G848" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H848" t="n">
         <v>6294</v>
@@ -24990,7 +24990,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G849" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H849" t="n">
         <v>15015</v>
@@ -25019,7 +25019,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G850" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H850" t="n">
         <v>5171</v>
@@ -25048,7 +25048,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H851" t="n">
         <v>2601</v>
@@ -25077,7 +25077,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.59871697425842</v>
+        <v>2.598717212677</v>
       </c>
       <c r="H852" t="n">
         <v>20412</v>
@@ -25222,7 +25222,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G857" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H857" t="n">
         <v>36588</v>
@@ -25280,7 +25280,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G859" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H859" t="n">
         <v>14827</v>
@@ -25309,7 +25309,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G860" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H860" t="n">
         <v>9138</v>
@@ -25338,7 +25338,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H861" t="n">
         <v>8401</v>
@@ -25367,7 +25367,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H862" t="n">
         <v>800</v>
@@ -25396,7 +25396,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095517158508</v>
       </c>
       <c r="H863" t="n">
         <v>4900</v>
@@ -25425,7 +25425,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.6809549331665</v>
+        <v>2.68095517158508</v>
       </c>
       <c r="H864" t="n">
         <v>1600</v>
@@ -25454,7 +25454,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>2.73029756546021</v>
+        <v>2.73029780387878</v>
       </c>
       <c r="H865" t="n">
         <v>12720</v>
@@ -25483,7 +25483,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.6974024772644</v>
+        <v>2.69740271568298</v>
       </c>
       <c r="H866" t="n">
         <v>8639</v>
@@ -25512,7 +25512,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H867" t="n">
         <v>11963</v>
@@ -25541,7 +25541,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.7138500213623</v>
+        <v>2.71385025978088</v>
       </c>
       <c r="H868" t="n">
         <v>12942</v>
@@ -25628,7 +25628,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G871" t="n">
-        <v>2.79608798027039</v>
+        <v>2.79608821868896</v>
       </c>
       <c r="H871" t="n">
         <v>32365</v>
@@ -26208,7 +26208,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635431289673</v>
       </c>
       <c r="H891" t="n">
         <v>20227</v>
@@ -26266,7 +26266,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635407447815</v>
+        <v>3.02635431289673</v>
       </c>
       <c r="H893" t="n">
         <v>6123</v>
@@ -26295,7 +26295,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>3.0181303024292</v>
+        <v>3.01813006401062</v>
       </c>
       <c r="H894" t="n">
         <v>4722</v>
@@ -26324,7 +26324,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G895" t="n">
-        <v>2.9523401260376</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H895" t="n">
         <v>16315</v>
@@ -26353,7 +26353,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G896" t="n">
-        <v>2.9523401260376</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H896" t="n">
         <v>10691</v>
@@ -26382,7 +26382,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G897" t="n">
-        <v>2.9523401260376</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H897" t="n">
         <v>14571</v>
@@ -26411,7 +26411,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G898" t="n">
-        <v>2.9523401260376</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H898" t="n">
         <v>18523</v>
@@ -26440,7 +26440,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G899" t="n">
-        <v>2.9523401260376</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H899" t="n">
         <v>3178</v>
@@ -26469,7 +26469,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G900" t="n">
-        <v>2.9523401260376</v>
+        <v>2.95233964920044</v>
       </c>
       <c r="H900" t="n">
         <v>5388</v>
@@ -26498,7 +26498,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102515220642</v>
+        <v>3.05102562904358</v>
       </c>
       <c r="H901" t="n">
         <v>43084</v>
@@ -26527,7 +26527,7 @@
         <v>3.75</v>
       </c>
       <c r="G902" t="n">
-        <v>3.0839204788208</v>
+        <v>3.08392071723938</v>
       </c>
       <c r="H902" t="n">
         <v>70956</v>
@@ -26759,7 +26759,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.19082999229431</v>
+        <v>3.19083023071289</v>
       </c>
       <c r="H910" t="n">
         <v>3156</v>
@@ -26817,7 +26817,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>3.19082999229431</v>
+        <v>3.19083023071289</v>
       </c>
       <c r="H912" t="n">
         <v>16945</v>
@@ -26846,7 +26846,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.19082999229431</v>
+        <v>3.19083023071289</v>
       </c>
       <c r="H913" t="n">
         <v>6168</v>
@@ -26904,7 +26904,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727729797363</v>
+        <v>3.20727753639221</v>
       </c>
       <c r="H915" t="n">
         <v>20765</v>
@@ -26962,7 +26962,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>3.0674729347229</v>
+        <v>3.06747317314148</v>
       </c>
       <c r="H917" t="n">
         <v>29437</v>
@@ -27020,7 +27020,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G919" t="n">
-        <v>3.17438197135925</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H919" t="n">
         <v>11492</v>
@@ -27049,7 +27049,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.17438197135925</v>
+        <v>3.17438220977783</v>
       </c>
       <c r="H920" t="n">
         <v>4050</v>
@@ -27078,7 +27078,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G921" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H921" t="n">
         <v>21897</v>
@@ -27165,7 +27165,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G924" t="n">
-        <v>3.13228154182434</v>
+        <v>3.13228178024292</v>
       </c>
       <c r="H924" t="n">
         <v>4945</v>
@@ -27281,7 +27281,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>3.05650091171265</v>
+        <v>3.05650067329407</v>
       </c>
       <c r="H928" t="n">
         <v>100</v>
@@ -27339,7 +27339,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.1491219997406</v>
+        <v>3.14912176132202</v>
       </c>
       <c r="H930" t="n">
         <v>4469</v>
@@ -27397,7 +27397,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H932" t="n">
         <v>46107</v>
@@ -27571,7 +27571,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H938" t="n">
         <v>4663</v>
@@ -27600,7 +27600,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H939" t="n">
         <v>1901</v>
@@ -27716,7 +27716,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276660919189</v>
+        <v>3.50276637077332</v>
       </c>
       <c r="H943" t="n">
         <v>26715</v>
@@ -27745,7 +27745,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H944" t="n">
         <v>9943</v>
@@ -27774,7 +27774,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H945" t="n">
         <v>61318</v>
@@ -27803,7 +27803,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H946" t="n">
         <v>9308</v>
@@ -27832,7 +27832,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644680976868</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H947" t="n">
         <v>5552</v>
@@ -27861,7 +27861,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H948" t="n">
         <v>6445</v>
@@ -27919,7 +27919,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G950" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H950" t="n">
         <v>3123</v>
@@ -27948,7 +27948,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>3.52802705764771</v>
+        <v>3.52802729606628</v>
       </c>
       <c r="H951" t="n">
         <v>10788</v>
@@ -27977,7 +27977,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H952" t="n">
         <v>3722</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H953" t="n">
         <v>4381</v>
@@ -28093,7 +28093,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G956" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H956" t="n">
         <v>7217</v>
@@ -28122,7 +28122,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H957" t="n">
         <v>5268</v>
@@ -28151,7 +28151,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H958" t="n">
         <v>4435</v>
@@ -28180,7 +28180,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>3.4438259601593</v>
+        <v>3.44382619857788</v>
       </c>
       <c r="H959" t="n">
         <v>19778</v>
@@ -28209,7 +28209,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H960" t="n">
         <v>1627</v>
@@ -28238,7 +28238,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H961" t="n">
         <v>1261</v>
@@ -28267,7 +28267,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H962" t="n">
         <v>25266</v>
@@ -28383,7 +28383,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H966" t="n">
         <v>29816</v>
@@ -28441,7 +28441,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G968" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H968" t="n">
         <v>13367</v>
@@ -28470,7 +28470,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H969" t="n">
         <v>1754</v>
@@ -28499,7 +28499,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594442367554</v>
+        <v>3.32594466209412</v>
       </c>
       <c r="H970" t="n">
         <v>650</v>
@@ -28528,7 +28528,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H971" t="n">
         <v>3678</v>
@@ -28586,7 +28586,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>3.35962510108948</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H973" t="n">
         <v>150</v>
@@ -28615,7 +28615,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G974" t="n">
-        <v>3.28384375572205</v>
+        <v>3.28384399414062</v>
       </c>
       <c r="H974" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H975" t="n">
         <v>750</v>
@@ -28673,7 +28673,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H976" t="n">
         <v>1030</v>
@@ -28818,7 +28818,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H981" t="n">
         <v>410</v>
@@ -28847,7 +28847,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G982" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H982" t="n">
         <v>15961</v>
@@ -29050,7 +29050,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>3.35120487213135</v>
+        <v>3.35120463371277</v>
       </c>
       <c r="H989" t="n">
         <v>4795</v>
@@ -29108,7 +29108,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G991" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H991" t="n">
         <v>1174</v>
@@ -29137,7 +29137,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H992" t="n">
         <v>4350</v>
@@ -29166,7 +29166,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H993" t="n">
         <v>933</v>
@@ -29195,7 +29195,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H994" t="n">
         <v>9158</v>
@@ -29224,7 +29224,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>3.38488507270813</v>
+        <v>3.38488531112671</v>
       </c>
       <c r="H995" t="n">
         <v>6453</v>
@@ -29282,7 +29282,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H997" t="n">
         <v>30034</v>
@@ -29311,7 +29311,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H998" t="n">
         <v>9678</v>
@@ -29340,7 +29340,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.58696794509888</v>
+        <v>3.58696818351746</v>
       </c>
       <c r="H999" t="n">
         <v>24870</v>
@@ -29398,7 +29398,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481412887573</v>
+        <v>4.02481365203857</v>
       </c>
       <c r="H1001" t="n">
         <v>96367</v>
@@ -29456,7 +29456,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.19321632385254</v>
+        <v>4.19321584701538</v>
       </c>
       <c r="H1003" t="n">
         <v>114905</v>
@@ -29514,7 +29514,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007410049438</v>
+        <v>4.05007362365723</v>
       </c>
       <c r="H1005" t="n">
         <v>28674</v>
@@ -29543,7 +29543,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059452056885</v>
       </c>
       <c r="H1006" t="n">
         <v>23823</v>
@@ -29601,7 +29601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.76378965377808</v>
+        <v>3.76379013061523</v>
       </c>
       <c r="H1008" t="n">
         <v>79946</v>
@@ -29630,7 +29630,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1009" t="n">
         <v>18829</v>
@@ -29659,7 +29659,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589056015015</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1010" t="n">
         <v>35109</v>
@@ -29688,7 +29688,7 @@
         <v>4.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.78905010223389</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1011" t="n">
         <v>18176</v>
@@ -29717,7 +29717,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.94061231613159</v>
+        <v>3.94061279296875</v>
       </c>
       <c r="H1012" t="n">
         <v>29223</v>
@@ -29775,7 +29775,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429299354553</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1014" t="n">
         <v>7495</v>
@@ -29833,7 +29833,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1016" t="n">
         <v>27929</v>
@@ -29862,7 +29862,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483216285706</v>
       </c>
       <c r="H1017" t="n">
         <v>43128</v>
@@ -29920,7 +29920,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483216285706</v>
       </c>
       <c r="H1019" t="n">
         <v>2641</v>
@@ -29949,7 +29949,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589056015015</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1020" t="n">
         <v>5690</v>
@@ -29978,7 +29978,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.7974705696106</v>
+        <v>3.79747080802917</v>
       </c>
       <c r="H1021" t="n">
         <v>5537</v>
@@ -30007,7 +30007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.94061231613159</v>
+        <v>3.94061279296875</v>
       </c>
       <c r="H1022" t="n">
         <v>17855</v>
@@ -30036,7 +30036,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.9490327835083</v>
+        <v>3.94903254508972</v>
       </c>
       <c r="H1023" t="n">
         <v>8504</v>
@@ -30065,7 +30065,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429299354553</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1024" t="n">
         <v>24153</v>
@@ -30123,7 +30123,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.14269542694092</v>
+        <v>4.14269495010376</v>
       </c>
       <c r="H1026" t="n">
         <v>25432</v>
@@ -30181,7 +30181,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.14269542694092</v>
+        <v>4.14269495010376</v>
       </c>
       <c r="H1028" t="n">
         <v>46180</v>
@@ -30239,7 +30239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.04165410995483</v>
+        <v>4.04165458679199</v>
       </c>
       <c r="H1030" t="n">
         <v>6575</v>
@@ -30297,7 +30297,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.01639366149902</v>
+        <v>4.01639318466187</v>
       </c>
       <c r="H1032" t="n">
         <v>9065</v>
@@ -30326,7 +30326,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.01639366149902</v>
+        <v>4.01639318466187</v>
       </c>
       <c r="H1033" t="n">
         <v>16236</v>
@@ -30500,7 +30500,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91535234451294</v>
+        <v>3.91535210609436</v>
       </c>
       <c r="H1039" t="n">
         <v>7070</v>
@@ -30558,7 +30558,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483216285706</v>
       </c>
       <c r="H1041" t="n">
         <v>2683</v>
@@ -30587,7 +30587,7 @@
         <v>4.5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.78905010223389</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1042" t="n">
         <v>23151</v>
@@ -30616,7 +30616,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.64590835571289</v>
+        <v>3.64590859413147</v>
       </c>
       <c r="H1043" t="n">
         <v>57248</v>
@@ -30674,7 +30674,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.68800926208496</v>
+        <v>3.68800973892212</v>
       </c>
       <c r="H1045" t="n">
         <v>6158</v>
@@ -30732,7 +30732,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1047" t="n">
         <v>3054</v>
@@ -30790,7 +30790,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.63748836517334</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1049" t="n">
         <v>10041</v>
@@ -30877,7 +30877,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429299354553</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1052" t="n">
         <v>48655</v>
@@ -30906,7 +30906,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009165763855</v>
+        <v>3.89009189605713</v>
       </c>
       <c r="H1053" t="n">
         <v>34250</v>
@@ -30935,7 +30935,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.81431078910828</v>
+        <v>3.81431126594543</v>
       </c>
       <c r="H1054" t="n">
         <v>20837</v>
@@ -30993,7 +30993,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.7216899394989</v>
+        <v>3.72168970108032</v>
       </c>
       <c r="H1056" t="n">
         <v>4318</v>
@@ -31022,7 +31022,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906789779663</v>
       </c>
       <c r="H1057" t="n">
         <v>6922</v>
@@ -31109,7 +31109,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.63748836517334</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1060" t="n">
         <v>6645</v>
@@ -31138,7 +31138,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118683815002</v>
+        <v>3.51118659973145</v>
       </c>
       <c r="H1061" t="n">
         <v>19148</v>
@@ -31167,7 +31167,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1062" t="n">
         <v>6225</v>
@@ -31196,7 +31196,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1063" t="n">
         <v>18811</v>
@@ -31283,7 +31283,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1066" t="n">
         <v>38758</v>
@@ -31312,7 +31312,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.58696794509888</v>
+        <v>3.58696818351746</v>
       </c>
       <c r="H1067" t="n">
         <v>9893</v>
@@ -31341,7 +31341,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.63748836517334</v>
+        <v>3.6374888420105</v>
       </c>
       <c r="H1068" t="n">
         <v>988</v>
@@ -31370,7 +31370,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1069" t="n">
         <v>1867</v>
@@ -31428,7 +31428,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1071" t="n">
         <v>5768</v>
@@ -31457,7 +31457,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1072" t="n">
         <v>30702</v>
@@ -31486,7 +31486,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1073" t="n">
         <v>64565</v>
@@ -31602,7 +31602,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1077" t="n">
         <v>15491</v>
@@ -31631,7 +31631,7 @@
         <v>4.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.78905010223389</v>
+        <v>3.78905034065247</v>
       </c>
       <c r="H1078" t="n">
         <v>26882</v>
@@ -31660,7 +31660,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1079" t="n">
         <v>74698</v>
@@ -31689,7 +31689,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1080" t="n">
         <v>46059</v>
@@ -31718,7 +31718,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.64590835571289</v>
+        <v>3.64590859413147</v>
       </c>
       <c r="H1081" t="n">
         <v>9289</v>
@@ -31747,7 +31747,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1082" t="n">
         <v>5435</v>
@@ -31776,7 +31776,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1083" t="n">
         <v>17149</v>
@@ -31805,7 +31805,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.78062987327576</v>
+        <v>3.78063035011292</v>
       </c>
       <c r="H1084" t="n">
         <v>3484</v>
@@ -31892,7 +31892,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.64590835571289</v>
+        <v>3.64590859413147</v>
       </c>
       <c r="H1087" t="n">
         <v>4413</v>
@@ -31921,7 +31921,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642949104309</v>
       </c>
       <c r="H1088" t="n">
         <v>3360</v>
@@ -32037,7 +32037,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906813621521</v>
+        <v>3.62906789779663</v>
       </c>
       <c r="H1092" t="n">
         <v>2683</v>
@@ -32066,7 +32066,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1093" t="n">
         <v>8026</v>
@@ -32095,7 +32095,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.61222815513611</v>
+        <v>3.61222791671753</v>
       </c>
       <c r="H1094" t="n">
         <v>7359</v>
@@ -32124,7 +32124,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56170749664307</v>
+        <v>3.56170725822449</v>
       </c>
       <c r="H1095" t="n">
         <v>1188</v>
@@ -32153,7 +32153,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1096" t="n">
         <v>7457</v>
@@ -32182,7 +32182,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644680976868</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H1097" t="n">
         <v>8056</v>
@@ -32211,7 +32211,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276660919189</v>
+        <v>3.50276637077332</v>
       </c>
       <c r="H1098" t="n">
         <v>4264</v>
@@ -32240,7 +32240,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1099" t="n">
         <v>9056</v>
@@ -32327,7 +32327,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1102" t="n">
         <v>85</v>
@@ -32443,7 +32443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.62064814567566</v>
+        <v>3.62064838409424</v>
       </c>
       <c r="H1106" t="n">
         <v>23274</v>
@@ -32472,7 +32472,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1107" t="n">
         <v>9024</v>
@@ -32501,7 +32501,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1108" t="n">
         <v>34399</v>
@@ -32530,7 +32530,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1109" t="n">
         <v>4680</v>
@@ -32559,7 +32559,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.42698574066162</v>
+        <v>3.4269859790802</v>
       </c>
       <c r="H1110" t="n">
         <v>2608</v>
@@ -32617,7 +32617,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1112" t="n">
         <v>4545</v>
@@ -32646,7 +32646,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1113" t="n">
         <v>300</v>
@@ -32733,7 +32733,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434638023376</v>
+        <v>3.49434661865234</v>
       </c>
       <c r="H1116" t="n">
         <v>1500</v>
@@ -32762,7 +32762,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750639915466</v>
+        <v>3.47750663757324</v>
       </c>
       <c r="H1117" t="n">
         <v>1899</v>
@@ -32820,7 +32820,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.35962510108948</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1119" t="n">
         <v>13064</v>
@@ -32849,7 +32849,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.519606590271</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1120" t="n">
         <v>15675</v>
@@ -32936,7 +32936,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H1123" t="n">
         <v>12666</v>
@@ -32965,7 +32965,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.30068421363831</v>
+        <v>3.30068445205688</v>
       </c>
       <c r="H1124" t="n">
         <v>10488</v>
@@ -33110,7 +33110,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.86283826828003</v>
+        <v>2.86283850669861</v>
       </c>
       <c r="H1129" t="n">
         <v>14846</v>
@@ -33284,7 +33284,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05650091171265</v>
+        <v>3.05650067329407</v>
       </c>
       <c r="H1135" t="n">
         <v>32492</v>
@@ -33313,7 +33313,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1136" t="n">
         <v>66796</v>
@@ -33342,7 +33342,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.35962510108948</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1137" t="n">
         <v>80725</v>
@@ -33371,7 +33371,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1138" t="n">
         <v>8053</v>
@@ -33487,7 +33487,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1142" t="n">
         <v>11790</v>
@@ -33516,7 +33516,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1143" t="n">
         <v>1920</v>
@@ -33574,7 +33574,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1145" t="n">
         <v>5210</v>
@@ -33603,7 +33603,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594442367554</v>
+        <v>3.32594466209412</v>
       </c>
       <c r="H1146" t="n">
         <v>2889</v>
@@ -33632,7 +33632,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1147" t="n">
         <v>2050</v>
@@ -33661,7 +33661,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804485321045</v>
+        <v>3.36804509162903</v>
       </c>
       <c r="H1148" t="n">
         <v>1680</v>
@@ -33690,7 +33690,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.35962510108948</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1149" t="n">
         <v>4800</v>
@@ -33835,7 +33835,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1154" t="n">
         <v>8627</v>
@@ -33864,7 +33864,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.25016331672668</v>
+        <v>3.25016307830811</v>
       </c>
       <c r="H1155" t="n">
         <v>1166</v>
@@ -34009,7 +34009,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.26700377464294</v>
+        <v>3.26700353622437</v>
       </c>
       <c r="H1160" t="n">
         <v>1350</v>
@@ -34096,7 +34096,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1163" t="n">
         <v>481</v>
@@ -34241,7 +34241,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.28384375572205</v>
+        <v>3.28384399414062</v>
       </c>
       <c r="H1168" t="n">
         <v>3031</v>
@@ -34299,7 +34299,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.21648287773132</v>
+        <v>3.21648263931274</v>
       </c>
       <c r="H1170" t="n">
         <v>516</v>
@@ -34357,7 +34357,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1172" t="n">
         <v>767</v>
@@ -34386,7 +34386,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964265823364</v>
+        <v>3.19964241981506</v>
       </c>
       <c r="H1173" t="n">
         <v>300</v>
@@ -34415,7 +34415,7 @@
         <v>3.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.15754199028015</v>
+        <v>3.15754222869873</v>
       </c>
       <c r="H1174" t="n">
         <v>2264</v>
@@ -34444,7 +34444,7 @@
         <v>3.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.15754199028015</v>
+        <v>3.15754222869873</v>
       </c>
       <c r="H1175" t="n">
         <v>2738</v>
@@ -34560,7 +34560,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41084337234497</v>
+        <v>3.41084361076355</v>
       </c>
       <c r="H1179" t="n">
         <v>122</v>
@@ -34589,7 +34589,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209770202637</v>
+        <v>3.40209794044495</v>
       </c>
       <c r="H1180" t="n">
         <v>1022</v>
@@ -34705,7 +34705,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1184" t="n">
         <v>1051</v>
@@ -34734,7 +34734,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1185" t="n">
         <v>1629</v>
@@ -34821,7 +34821,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1188" t="n">
         <v>437</v>
@@ -34850,7 +34850,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1189" t="n">
         <v>0</v>
@@ -34879,7 +34879,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1190" t="n">
         <v>0</v>
@@ -34908,7 +34908,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1192" t="n">
         <v>2500</v>
@@ -35024,7 +35024,7 @@
         <v>3.75</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1195" t="n">
         <v>5820</v>
@@ -35082,7 +35082,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1197" t="n">
         <v>4630</v>
@@ -35111,7 +35111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1198" t="n">
         <v>2600</v>
@@ -35169,7 +35169,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1200" t="n">
         <v>4965</v>
@@ -35227,7 +35227,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1202" t="n">
         <v>3125</v>
@@ -35256,7 +35256,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1203" t="n">
         <v>1800</v>
@@ -35285,7 +35285,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1204" t="n">
         <v>9575</v>
@@ -35314,7 +35314,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1205" t="n">
         <v>3220</v>
@@ -35372,7 +35372,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1207" t="n">
         <v>8591</v>
@@ -35488,7 +35488,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1211" t="n">
         <v>2900</v>
@@ -35575,7 +35575,7 @@
         <v>3.25</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1214" t="n">
         <v>2847</v>
@@ -35865,7 +35865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1224" t="n">
         <v>4675</v>
@@ -36010,7 +36010,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1229" t="n">
         <v>6115</v>
@@ -36039,7 +36039,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1230" t="n">
         <v>2300</v>
@@ -36126,7 +36126,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1233" t="n">
         <v>7495</v>
@@ -36155,7 +36155,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233563423157</v>
       </c>
       <c r="H1234" t="n">
         <v>12178</v>
@@ -36213,7 +36213,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1236" t="n">
         <v>212</v>
@@ -36358,7 +36358,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1241" t="n">
         <v>1810</v>
@@ -36416,7 +36416,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1243" t="n">
         <v>2327</v>
@@ -36445,7 +36445,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1244" t="n">
         <v>500</v>
@@ -36474,7 +36474,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1245" t="n">
         <v>3906</v>
@@ -36503,7 +36503,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233563423157</v>
       </c>
       <c r="H1246" t="n">
         <v>2163</v>
@@ -36532,7 +36532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1247" t="n">
         <v>10</v>
@@ -36561,7 +36561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1248" t="n">
         <v>93</v>
@@ -36590,7 +36590,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1249" t="n">
         <v>0</v>
@@ -36619,7 +36619,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1250" t="n">
         <v>1625</v>
@@ -36648,7 +36648,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1251" t="n">
         <v>132</v>
@@ -36677,7 +36677,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1252" t="n">
         <v>650</v>
@@ -36706,7 +36706,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1253" t="n">
         <v>0</v>
@@ -36851,7 +36851,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1258" t="n">
         <v>948</v>
@@ -36880,7 +36880,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1259" t="n">
         <v>0</v>
@@ -36938,7 +36938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1261" t="n">
         <v>3355</v>
@@ -37141,7 +37141,7 @@
         <v>3.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.842369556427</v>
+        <v>2.84236931800842</v>
       </c>
       <c r="H1268" t="n">
         <v>3807</v>
@@ -37315,7 +37315,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1274" t="n">
         <v>3270</v>
@@ -37344,7 +37344,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1275" t="n">
         <v>5827</v>
@@ -37373,7 +37373,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1276" t="n">
         <v>2131</v>
@@ -37402,7 +37402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.58874273300171</v>
+        <v>2.58874249458313</v>
       </c>
       <c r="H1277" t="n">
         <v>5176</v>
@@ -37431,7 +37431,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1278" t="n">
         <v>1108</v>
@@ -37460,7 +37460,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.58874273300171</v>
+        <v>2.58874249458313</v>
       </c>
       <c r="H1279" t="n">
         <v>1252</v>
@@ -37489,7 +37489,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1280" t="n">
         <v>1000</v>
@@ -37518,7 +37518,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1281" t="n">
         <v>3050</v>
@@ -37547,7 +37547,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.57125115394592</v>
+        <v>2.57125091552734</v>
       </c>
       <c r="H1282" t="n">
         <v>1150</v>
@@ -37576,7 +37576,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1283" t="n">
         <v>2421</v>
@@ -37605,7 +37605,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.43131923675537</v>
+        <v>2.43131899833679</v>
       </c>
       <c r="H1284" t="n">
         <v>7210</v>
@@ -37634,7 +37634,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1285" t="n">
         <v>1200</v>
@@ -37663,7 +37663,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1286" t="n">
         <v>5150</v>
@@ -37692,7 +37692,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1287" t="n">
         <v>7150</v>
@@ -37750,7 +37750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.54501390457153</v>
+        <v>2.54501414299011</v>
       </c>
       <c r="H1289" t="n">
         <v>597</v>
@@ -37837,7 +37837,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.72867441177368</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1292" t="n">
         <v>2990</v>
@@ -37895,7 +37895,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1294" t="n">
         <v>1467</v>
@@ -37953,7 +37953,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626799583435</v>
+        <v>2.53626847267151</v>
       </c>
       <c r="H1296" t="n">
         <v>9500</v>
@@ -37982,7 +37982,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1297" t="n">
         <v>565</v>
@@ -38040,7 +38040,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.51003050804138</v>
+        <v>2.51003098487854</v>
       </c>
       <c r="H1299" t="n">
         <v>1517</v>
@@ -38185,7 +38185,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.72867441177368</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1304" t="n">
         <v>4415</v>
@@ -38243,7 +38243,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1306" t="n">
         <v>8457</v>
@@ -38417,7 +38417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1312" t="n">
         <v>1050</v>
@@ -38533,7 +38533,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.80738639831543</v>
+        <v>2.80738663673401</v>
       </c>
       <c r="H1316" t="n">
         <v>3648</v>
@@ -38678,7 +38678,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1321" t="n">
         <v>9850</v>
@@ -38707,7 +38707,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1322" t="n">
         <v>2900</v>
@@ -38794,7 +38794,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1325" t="n">
         <v>6498</v>
@@ -38823,7 +38823,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1326" t="n">
         <v>5429</v>
@@ -38968,7 +38968,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1331" t="n">
         <v>2844</v>
@@ -39084,7 +39084,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1335" t="n">
         <v>3359</v>
@@ -39113,7 +39113,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1336" t="n">
         <v>1510</v>
@@ -39258,7 +39258,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1341" t="n">
         <v>11551</v>
@@ -39287,7 +39287,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1342" t="n">
         <v>1846</v>
@@ -39316,7 +39316,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1343" t="n">
         <v>5050</v>
@@ -39374,7 +39374,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1345" t="n">
         <v>1883</v>
@@ -39548,7 +39548,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1351" t="n">
         <v>1532</v>
@@ -39664,7 +39664,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1355" t="n">
         <v>140</v>
@@ -39693,7 +39693,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1356" t="n">
         <v>2099</v>
@@ -39722,7 +39722,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1357" t="n">
         <v>855</v>
@@ -39751,7 +39751,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1358" t="n">
         <v>0</v>
@@ -39780,7 +39780,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1359" t="n">
         <v>0</v>
@@ -39809,7 +39809,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1360" t="n">
         <v>4110</v>
@@ -39838,7 +39838,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1361" t="n">
         <v>22818</v>
@@ -39867,7 +39867,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1362" t="n">
         <v>16893</v>
@@ -39896,7 +39896,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1363" t="n">
         <v>19094</v>
@@ -39925,7 +39925,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.26216554641724</v>
+        <v>3.26216578483582</v>
       </c>
       <c r="H1364" t="n">
         <v>27870</v>
@@ -39954,7 +39954,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.26216554641724</v>
+        <v>3.26216578483582</v>
       </c>
       <c r="H1365" t="n">
         <v>5010</v>
@@ -40070,7 +40070,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.28840279579163</v>
+        <v>3.28840255737305</v>
       </c>
       <c r="H1369" t="n">
         <v>3567</v>
@@ -40099,7 +40099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.25341963768005</v>
+        <v>3.25342011451721</v>
       </c>
       <c r="H1370" t="n">
         <v>23028</v>
@@ -40186,7 +40186,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.24467396736145</v>
+        <v>3.24467420578003</v>
       </c>
       <c r="H1373" t="n">
         <v>4880</v>
@@ -40215,7 +40215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1374" t="n">
         <v>9425</v>
@@ -40244,7 +40244,7 @@
         <v>3.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1375" t="n">
         <v>1200</v>
@@ -40273,7 +40273,7 @@
         <v>3.75</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.27965688705444</v>
+        <v>3.27965712547302</v>
       </c>
       <c r="H1376" t="n">
         <v>750</v>
@@ -40302,7 +40302,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1377" t="n">
         <v>1800</v>
@@ -40360,7 +40360,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1379" t="n">
         <v>13793</v>
@@ -40418,7 +40418,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1381" t="n">
         <v>3079</v>
@@ -40447,7 +40447,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725047111511</v>
+        <v>3.08725070953369</v>
       </c>
       <c r="H1382" t="n">
         <v>2200</v>
@@ -40476,7 +40476,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1383" t="n">
         <v>2020</v>
@@ -40505,7 +40505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1384" t="n">
         <v>300</v>
@@ -40534,7 +40534,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.15721654891968</v>
+        <v>3.1572163105011</v>
       </c>
       <c r="H1385" t="n">
         <v>200</v>
@@ -40563,7 +40563,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.14847087860107</v>
+        <v>3.1484706401825</v>
       </c>
       <c r="H1386" t="n">
         <v>1215</v>
@@ -40592,7 +40592,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1387" t="n">
         <v>1000</v>
@@ -40621,7 +40621,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1388" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1391" t="n">
         <v>442</v>
@@ -40737,7 +40737,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972520828247</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1392" t="n">
         <v>950</v>
@@ -40824,7 +40824,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731855392456</v>
+        <v>2.94731831550598</v>
       </c>
       <c r="H1395" t="n">
         <v>64822</v>
@@ -40882,7 +40882,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1397" t="n">
         <v>597</v>
@@ -40911,7 +40911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1398" t="n">
         <v>400</v>
@@ -40998,7 +40998,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1401" t="n">
         <v>1744</v>
@@ -41027,7 +41027,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1402" t="n">
         <v>233</v>
@@ -41056,7 +41056,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1403" t="n">
         <v>625</v>
@@ -41085,7 +41085,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1404" t="n">
         <v>5552</v>
@@ -41143,7 +41143,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.91233539581299</v>
+        <v>2.91233563423157</v>
       </c>
       <c r="H1406" t="n">
         <v>1650</v>
@@ -41201,7 +41201,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1408" t="n">
         <v>141</v>
@@ -41375,7 +41375,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1414" t="n">
         <v>5019</v>
@@ -41462,7 +41462,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1417" t="n">
         <v>2002</v>
@@ -41491,7 +41491,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1418" t="n">
         <v>14401</v>
@@ -41520,7 +41520,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.98230147361755</v>
+        <v>2.98230171203613</v>
       </c>
       <c r="H1419" t="n">
         <v>105</v>
@@ -41549,7 +41549,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1420" t="n">
         <v>50</v>
@@ -41578,7 +41578,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.99104738235474</v>
+        <v>2.99104714393616</v>
       </c>
       <c r="H1421" t="n">
         <v>0</v>
@@ -41636,7 +41636,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1423" t="n">
         <v>3547</v>
@@ -41665,7 +41665,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1424" t="n">
         <v>6125</v>
@@ -41723,7 +41723,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1426" t="n">
         <v>2150</v>
@@ -41868,7 +41868,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.68494582176208</v>
+        <v>2.68494606018066</v>
       </c>
       <c r="H1431" t="n">
         <v>21472</v>
@@ -41955,7 +41955,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1434" t="n">
         <v>6060</v>
@@ -41984,7 +41984,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.71992897987366</v>
+        <v>2.71992874145508</v>
       </c>
       <c r="H1435" t="n">
         <v>9210</v>
@@ -42013,7 +42013,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.72867441177368</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1436" t="n">
         <v>1951</v>
@@ -42042,7 +42042,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1437" t="n">
         <v>3539</v>
@@ -42448,7 +42448,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1451" t="n">
         <v>5102</v>
@@ -42506,7 +42506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1453" t="n">
         <v>8150</v>
@@ -42622,7 +42622,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1457" t="n">
         <v>2600</v>
@@ -42651,7 +42651,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1458" t="n">
         <v>6595</v>
@@ -42680,7 +42680,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1459" t="n">
         <v>4900</v>
@@ -42709,7 +42709,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1460" t="n">
         <v>0</v>
@@ -42738,7 +42738,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1461" t="n">
         <v>957</v>
@@ -42796,7 +42796,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1463" t="n">
         <v>3565</v>
@@ -42854,7 +42854,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1465" t="n">
         <v>1000</v>
@@ -42912,7 +42912,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1467" t="n">
         <v>3295</v>
@@ -42941,7 +42941,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1468" t="n">
         <v>2753</v>
@@ -42970,7 +42970,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1469" t="n">
         <v>7000</v>
@@ -43057,7 +43057,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1472" t="n">
         <v>1042</v>
@@ -43144,7 +43144,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1475" t="n">
         <v>8292</v>
@@ -43173,7 +43173,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1476" t="n">
         <v>7332</v>
@@ -43231,7 +43231,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1478" t="n">
         <v>252613</v>
@@ -43376,7 +43376,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1483" t="n">
         <v>18307</v>
@@ -43434,7 +43434,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1485" t="n">
         <v>11067</v>
@@ -43898,7 +43898,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1501" t="n">
         <v>16390</v>
@@ -44188,7 +44188,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1511" t="n">
         <v>200</v>
@@ -44275,7 +44275,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1514" t="n">
         <v>4539</v>
@@ -44304,7 +44304,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1515" t="n">
         <v>11432</v>
@@ -44333,7 +44333,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1516" t="n">
         <v>12387</v>
@@ -44478,7 +44478,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1521" t="n">
         <v>1669</v>
@@ -44594,7 +44594,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1525" t="n">
         <v>4558</v>
@@ -44623,7 +44623,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1526" t="n">
         <v>1820</v>
@@ -44652,7 +44652,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1527" t="n">
         <v>150</v>
@@ -45029,7 +45029,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1540" t="n">
         <v>50</v>
@@ -45348,7 +45348,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1551" t="n">
         <v>10350</v>
@@ -45377,7 +45377,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1552" t="n">
         <v>3808</v>
@@ -45406,7 +45406,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1553" t="n">
         <v>50</v>
@@ -45435,7 +45435,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1554" t="n">
         <v>18555</v>
@@ -45464,7 +45464,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1555" t="n">
         <v>1118</v>
@@ -45493,7 +45493,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1556" t="n">
         <v>1873</v>
@@ -45609,7 +45609,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1560" t="n">
         <v>2650</v>
@@ -45667,7 +45667,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1562" t="n">
         <v>6000</v>
@@ -45696,7 +45696,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1563" t="n">
         <v>1789</v>
@@ -45725,7 +45725,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1564" t="n">
         <v>2600</v>
@@ -45754,7 +45754,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1565" t="n">
         <v>8722</v>
@@ -45783,7 +45783,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1566" t="n">
         <v>6062</v>
@@ -45812,7 +45812,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1567" t="n">
         <v>25683</v>
@@ -45870,7 +45870,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1569" t="n">
         <v>14198</v>
@@ -45899,7 +45899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1570" t="n">
         <v>5400</v>
@@ -45986,7 +45986,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1573" t="n">
         <v>3411</v>
@@ -46015,7 +46015,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1574" t="n">
         <v>10144</v>
@@ -46073,7 +46073,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1576" t="n">
         <v>6055</v>
@@ -46189,7 +46189,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1580" t="n">
         <v>8200</v>
@@ -46247,7 +46247,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1582" t="n">
         <v>21214</v>
@@ -46595,7 +46595,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1594" t="n">
         <v>24870</v>
@@ -46624,7 +46624,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1595" t="n">
         <v>18412</v>
@@ -46769,7 +46769,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1600" t="n">
         <v>4085</v>
@@ -46972,7 +46972,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1607" t="n">
         <v>1951</v>
@@ -47030,7 +47030,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1609" t="n">
         <v>2751</v>
@@ -47059,7 +47059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1610" t="n">
         <v>1618</v>
@@ -47175,7 +47175,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1614" t="n">
         <v>10351</v>
@@ -47320,7 +47320,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1619" t="n">
         <v>1735</v>
@@ -47465,7 +47465,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1624" t="n">
         <v>1361</v>
@@ -47610,7 +47610,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1629" t="n">
         <v>7874</v>
@@ -47784,7 +47784,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1635" t="n">
         <v>10171</v>
@@ -47813,7 +47813,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1636" t="n">
         <v>6601</v>
@@ -47871,7 +47871,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1638" t="n">
         <v>2344</v>
@@ -47900,7 +47900,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1639" t="n">
         <v>4700</v>
@@ -47958,7 +47958,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1641" t="n">
         <v>1566</v>
@@ -47987,7 +47987,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1642" t="n">
         <v>9227</v>
@@ -48016,7 +48016,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1643" t="n">
         <v>7310</v>
@@ -48045,7 +48045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1644" t="n">
         <v>1000</v>
@@ -48132,7 +48132,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1647" t="n">
         <v>6041</v>
@@ -48161,7 +48161,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1648" t="n">
         <v>1964</v>
@@ -48248,7 +48248,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1651" t="n">
         <v>200</v>
@@ -48364,7 +48364,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1655" t="n">
         <v>5050</v>
@@ -48683,7 +48683,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1666" t="n">
         <v>2600</v>
@@ -48944,7 +48944,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1675" t="n">
         <v>6817</v>
@@ -48973,7 +48973,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1676" t="n">
         <v>5212</v>
@@ -49060,7 +49060,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1679" t="n">
         <v>5506</v>
@@ -49263,7 +49263,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1686" t="n">
         <v>19737</v>
@@ -49292,7 +49292,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1687" t="n">
         <v>2100</v>
@@ -49350,7 +49350,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1689" t="n">
         <v>10000</v>
@@ -49437,7 +49437,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1692" t="n">
         <v>7400</v>
@@ -49669,7 +49669,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1700" t="n">
         <v>17055</v>
@@ -49727,7 +49727,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1702" t="n">
         <v>23657</v>
@@ -49756,7 +49756,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1703" t="n">
         <v>6507</v>
@@ -49814,7 +49814,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1705" t="n">
         <v>39</v>
@@ -49843,7 +49843,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1706" t="n">
         <v>6965</v>
@@ -49872,7 +49872,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1707" t="n">
         <v>14247</v>
@@ -50133,7 +50133,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1716" t="n">
         <v>12714</v>
@@ -50162,7 +50162,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1717" t="n">
         <v>8150</v>
@@ -50539,7 +50539,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.049156665802</v>
+        <v>3.04915642738342</v>
       </c>
       <c r="H1730" t="n">
         <v>2212</v>
@@ -50684,7 +50684,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1735" t="n">
         <v>1964</v>
@@ -50713,7 +50713,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1736" t="n">
         <v>5543</v>
@@ -50800,7 +50800,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1739" t="n">
         <v>5500</v>
@@ -50829,7 +50829,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1740" t="n">
         <v>2956</v>
@@ -51902,7 +51902,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1777" t="n">
         <v>500</v>
@@ -52076,7 +52076,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1783" t="n">
         <v>695</v>
@@ -52656,7 +52656,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1803" t="n">
         <v>1000</v>
@@ -52743,7 +52743,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1806" t="n">
         <v>1500</v>
@@ -52801,7 +52801,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1808" t="n">
         <v>708</v>
@@ -52830,7 +52830,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1809" t="n">
         <v>0</v>
@@ -53033,7 +53033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1816" t="n">
         <v>4470</v>
@@ -53062,7 +53062,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1817" t="n">
         <v>4905</v>
@@ -53091,7 +53091,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1818" t="n">
         <v>5181</v>
@@ -53149,7 +53149,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1820" t="n">
         <v>5370</v>
@@ -53178,7 +53178,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1821" t="n">
         <v>0</v>
@@ -53207,7 +53207,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1822" t="n">
         <v>0</v>
@@ -53294,7 +53294,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1825" t="n">
         <v>2500</v>
@@ -53352,7 +53352,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53468,7 +53468,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1831" t="n">
         <v>2764</v>
@@ -53497,7 +53497,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1832" t="n">
         <v>7985</v>
@@ -53526,7 +53526,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1833" t="n">
         <v>13237</v>
@@ -53642,7 +53642,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1837" t="n">
         <v>3566</v>
@@ -53671,7 +53671,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1838" t="n">
         <v>4827</v>
@@ -53729,7 +53729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1840" t="n">
         <v>4580</v>
@@ -53758,7 +53758,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1841" t="n">
         <v>1250</v>
@@ -53874,7 +53874,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1845" t="n">
         <v>4344</v>
@@ -53961,7 +53961,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1848" t="n">
         <v>1420</v>
@@ -53990,7 +53990,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1849" t="n">
         <v>2250</v>
@@ -54077,7 +54077,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1852" t="n">
         <v>9811</v>
@@ -54251,7 +54251,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1858" t="n">
         <v>32665</v>
@@ -54309,7 +54309,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1860" t="n">
         <v>5060</v>
@@ -54570,7 +54570,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1869" t="n">
         <v>995</v>
@@ -54686,7 +54686,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1873" t="n">
         <v>1966</v>
@@ -54802,7 +54802,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1877" t="n">
         <v>84</v>
@@ -54831,7 +54831,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1878" t="n">
         <v>856</v>
@@ -54947,7 +54947,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1882" t="n">
         <v>4480</v>
@@ -54976,7 +54976,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1883" t="n">
         <v>0</v>
@@ -55063,7 +55063,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1886" t="n">
         <v>1550</v>
@@ -55121,7 +55121,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1888" t="n">
         <v>2000</v>
@@ -55150,7 +55150,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1889" t="n">
         <v>1694</v>
@@ -55208,7 +55208,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1891" t="n">
         <v>5040</v>
@@ -55266,7 +55266,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1893" t="n">
         <v>255</v>
@@ -55295,7 +55295,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1894" t="n">
         <v>2350</v>
@@ -55324,7 +55324,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1895" t="n">
         <v>3524</v>
@@ -55353,7 +55353,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1896" t="n">
         <v>7241</v>
@@ -55382,7 +55382,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1897" t="n">
         <v>0</v>
@@ -55411,7 +55411,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1898" t="n">
         <v>9000</v>
@@ -55469,7 +55469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1900" t="n">
         <v>4150</v>
@@ -55614,7 +55614,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1905" t="n">
         <v>4525</v>
@@ -55643,7 +55643,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1906" t="n">
         <v>4000</v>
@@ -55759,7 +55759,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1910" t="n">
         <v>1000</v>
@@ -55875,7 +55875,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30746984481812</v>
+        <v>2.30747008323669</v>
       </c>
       <c r="H1914" t="n">
         <v>52544</v>
@@ -55962,7 +55962,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1917" t="n">
         <v>13522</v>
@@ -55991,7 +55991,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1918" t="n">
         <v>5361</v>
@@ -56426,7 +56426,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1933" t="n">
         <v>1893</v>
@@ -56455,7 +56455,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1934" t="n">
         <v>1786</v>
@@ -56542,7 +56542,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1937" t="n">
         <v>7603</v>
@@ -56571,7 +56571,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1938" t="n">
         <v>3411</v>
@@ -67191,6 +67191,35 @@
         <v>1920</v>
       </c>
       <c r="I2304" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2305" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2305" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="D2305" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="G2305" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="H2305" t="n">
+        <v>2172</v>
+      </c>
+      <c r="I2305" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417598724365</v>
+        <v>2.91417574882507</v>
       </c>
       <c r="H2" t="n">
         <v>507500</v>
@@ -456,7 +456,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802364349365</v>
+        <v>2.85802340507507</v>
       </c>
       <c r="H3" t="n">
         <v>168500</v>
@@ -485,7 +485,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459334373474</v>
+        <v>2.78459310531616</v>
       </c>
       <c r="H4" t="n">
         <v>65500</v>
@@ -514,7 +514,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8724217414856</v>
+        <v>2.87242150306702</v>
       </c>
       <c r="H5" t="n">
         <v>117500</v>
@@ -543,7 +543,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8652229309082</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H6" t="n">
         <v>89500</v>
@@ -572,7 +572,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930635452271</v>
+        <v>2.83930611610413</v>
       </c>
       <c r="H7" t="n">
         <v>35500</v>
@@ -601,7 +601,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85082459449768</v>
+        <v>2.85082411766052</v>
       </c>
       <c r="H8" t="n">
         <v>34500</v>
@@ -659,7 +659,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82922744750977</v>
+        <v>2.82922720909119</v>
       </c>
       <c r="H10" t="n">
         <v>7500</v>
@@ -717,7 +717,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8724217414856</v>
+        <v>2.87242150306702</v>
       </c>
       <c r="H12" t="n">
         <v>41000</v>
@@ -746,7 +746,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87098169326782</v>
+        <v>2.87098145484924</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818098068237</v>
+        <v>2.87818074226379</v>
       </c>
       <c r="H14" t="n">
         <v>11000</v>
@@ -833,7 +833,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94585180282593</v>
+        <v>2.94585204124451</v>
       </c>
       <c r="H16" t="n">
         <v>41500</v>
@@ -891,7 +891,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009280204773</v>
+        <v>2.94009256362915</v>
       </c>
       <c r="H18" t="n">
         <v>3000</v>
@@ -920,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H19" t="n">
         <v>13500</v>
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8652229309082</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H21" t="n">
         <v>7500</v>
@@ -1007,7 +1007,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H22" t="n">
         <v>19000</v>
@@ -1036,7 +1036,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697717666626</v>
+        <v>2.90697693824768</v>
       </c>
       <c r="H23" t="n">
         <v>43500</v>
@@ -1065,7 +1065,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9012176990509</v>
+        <v>2.90121793746948</v>
       </c>
       <c r="H24" t="n">
         <v>38500</v>
@@ -1123,7 +1123,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841722488403</v>
+        <v>2.90841698646545</v>
       </c>
       <c r="H26" t="n">
         <v>9000</v>
@@ -1152,7 +1152,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92137551307678</v>
+        <v>2.9213752746582</v>
       </c>
       <c r="H27" t="n">
         <v>1000</v>
@@ -1181,7 +1181,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113926887512</v>
       </c>
       <c r="H28" t="n">
         <v>6000</v>
@@ -1239,7 +1239,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433356285095</v>
+        <v>2.93433380126953</v>
       </c>
       <c r="H30" t="n">
         <v>4500</v>
@@ -1268,7 +1268,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433356285095</v>
+        <v>2.93433380126953</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H32" t="n">
         <v>6500</v>
@@ -1326,7 +1326,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113879203796</v>
+        <v>2.89113926887512</v>
       </c>
       <c r="H33" t="n">
         <v>15500</v>
@@ -1355,7 +1355,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85226440429688</v>
+        <v>2.85226392745972</v>
       </c>
       <c r="H34" t="n">
         <v>3000</v>
@@ -1413,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H36" t="n">
         <v>2500</v>
@@ -1442,7 +1442,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.85082459449768</v>
+        <v>2.85082411766052</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1471,7 +1471,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.82922744750977</v>
+        <v>2.82922720909119</v>
       </c>
       <c r="H38" t="n">
         <v>1500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H39" t="n">
         <v>5500</v>
@@ -1529,7 +1529,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G40" t="n">
-        <v>2.80331110954285</v>
+        <v>2.80331063270569</v>
       </c>
       <c r="H40" t="n">
         <v>1000</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H42" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179239273071</v>
+        <v>2.79179215431213</v>
       </c>
       <c r="H44" t="n">
         <v>4500</v>
@@ -1674,7 +1674,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338930130005</v>
+        <v>2.81338906288147</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818098068237</v>
+        <v>2.87818074226379</v>
       </c>
       <c r="H46" t="n">
         <v>500</v>
@@ -1790,7 +1790,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H49" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.80475044250488</v>
+        <v>2.8047502040863</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H55" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770896911621</v>
+        <v>2.81770873069763</v>
       </c>
       <c r="H56" t="n">
         <v>15500</v>
@@ -2051,7 +2051,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.75723695755005</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2109,7 +2109,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.6794867515564</v>
+        <v>2.67948722839355</v>
       </c>
       <c r="H60" t="n">
         <v>12500</v>
@@ -2138,7 +2138,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283862113953</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283862113953</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2254,7 +2254,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77883386611938</v>
+        <v>2.77883362770081</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2457,7 +2457,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>2.75723695755005</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H72" t="n">
         <v>4000</v>
@@ -2486,7 +2486,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.75723695755005</v>
+        <v>2.75723648071289</v>
       </c>
       <c r="H73" t="n">
         <v>8500</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H74" t="n">
         <v>11500</v>
@@ -2544,7 +2544,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H76" t="n">
         <v>1000</v>
@@ -2602,7 +2602,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H77" t="n">
         <v>7500</v>
@@ -2631,7 +2631,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.64349174499512</v>
+        <v>2.6434919834137</v>
       </c>
       <c r="H78" t="n">
         <v>7500</v>
@@ -2660,7 +2660,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71980166435242</v>
+        <v>2.719801902771</v>
       </c>
       <c r="H79" t="n">
         <v>14500</v>
@@ -2689,7 +2689,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71980166435242</v>
+        <v>2.719801902771</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G81" t="n">
-        <v>2.65069079399109</v>
+        <v>2.65069055557251</v>
       </c>
       <c r="H81" t="n">
         <v>5000</v>
@@ -2747,7 +2747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G82" t="n">
-        <v>2.66364908218384</v>
+        <v>2.66364932060242</v>
       </c>
       <c r="H82" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524670600891</v>
+        <v>2.68524646759033</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2834,7 +2834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.69244527816772</v>
+        <v>2.6924455165863</v>
       </c>
       <c r="H85" t="n">
         <v>500</v>
@@ -2863,7 +2863,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69964456558228</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2892,7 +2892,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.66364908218384</v>
+        <v>2.66364932060242</v>
       </c>
       <c r="H87" t="n">
         <v>6500</v>
@@ -2921,7 +2921,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.69244527816772</v>
+        <v>2.6924455165863</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -3095,7 +3095,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767761230469</v>
+        <v>2.44767785072327</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3182,7 +3182,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767761230469</v>
+        <v>2.44767785072327</v>
       </c>
       <c r="H97" t="n">
         <v>4500</v>
@@ -3211,7 +3211,7 @@
         <v>3.5</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51966834068298</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3240,7 +3240,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286215782166</v>
       </c>
       <c r="H99" t="n">
         <v>23000</v>
@@ -3327,7 +3327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283862113953</v>
+        <v>2.74283838272095</v>
       </c>
       <c r="H102" t="n">
         <v>21000</v>
@@ -3501,7 +3501,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>2.71404266357422</v>
+        <v>2.71404242515564</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H109" t="n">
         <v>4000</v>
@@ -3559,7 +3559,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485288619995</v>
+        <v>2.63485312461853</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006192207336</v>
+        <v>2.57006168365479</v>
       </c>
       <c r="H116" t="n">
         <v>11000</v>
@@ -3762,7 +3762,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006192207336</v>
+        <v>2.57006168365479</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>3.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2.51966834068298</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H121" t="n">
         <v>500</v>
@@ -3907,7 +3907,7 @@
         <v>3.5</v>
       </c>
       <c r="G122" t="n">
-        <v>2.51966834068298</v>
+        <v>2.5196681022644</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286239624023</v>
+        <v>2.56286215782166</v>
       </c>
       <c r="H124" t="n">
         <v>3500</v>
@@ -4052,7 +4052,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445954322815</v>
+        <v>2.58445930480957</v>
       </c>
       <c r="H127" t="n">
         <v>22500</v>
@@ -4081,7 +4081,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>2.64205193519592</v>
+        <v>2.6420521736145</v>
       </c>
       <c r="H128" t="n">
         <v>5000</v>
@@ -4110,7 +4110,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.64205193519592</v>
+        <v>2.6420521736145</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H132" t="n">
         <v>31000</v>
@@ -4255,7 +4255,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H134" t="n">
         <v>17500</v>
@@ -4284,7 +4284,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>2.72844099998474</v>
+        <v>2.72844052314758</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H147" t="n">
         <v>15500</v>
@@ -4661,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -4690,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962079048157</v>
+        <v>2.87962031364441</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H166" t="n">
         <v>20000</v>
@@ -5212,7 +5212,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.85082459449768</v>
+        <v>2.85082411766052</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362530708313</v>
       </c>
       <c r="H168" t="n">
         <v>8500</v>
@@ -5270,7 +5270,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G169" t="n">
-        <v>2.77883386611938</v>
+        <v>2.77883362770081</v>
       </c>
       <c r="H169" t="n">
         <v>35000</v>
@@ -5299,7 +5299,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>2.78857922554016</v>
+        <v>2.78857898712158</v>
       </c>
       <c r="H170" t="n">
         <v>7000</v>
@@ -5328,7 +5328,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.6011745929718</v>
+        <v>2.60117435455322</v>
       </c>
       <c r="H171" t="n">
         <v>17000</v>
@@ -5357,7 +5357,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H172" t="n">
         <v>28500</v>
@@ -5386,7 +5386,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H173" t="n">
         <v>500</v>
@@ -5444,7 +5444,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H175" t="n">
         <v>2500</v>
@@ -5473,7 +5473,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H177" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G179" t="n">
-        <v>2.71361708641052</v>
+        <v>2.7136173248291</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G180" t="n">
-        <v>2.74360179901123</v>
+        <v>2.74360203742981</v>
       </c>
       <c r="H180" t="n">
         <v>1500</v>
@@ -5618,7 +5618,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H181" t="n">
         <v>1000</v>
@@ -5647,7 +5647,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H182" t="n">
         <v>2000</v>
@@ -5676,7 +5676,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H183" t="n">
         <v>1500</v>
@@ -5705,7 +5705,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>2.63865566253662</v>
+        <v>2.63865542411804</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.6611442565918</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H185" t="n">
         <v>500</v>
@@ -5763,7 +5763,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612096786499</v>
+        <v>2.70612072944641</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>2.848548412323</v>
+        <v>2.84854865074158</v>
       </c>
       <c r="H188" t="n">
         <v>5500</v>
@@ -5850,7 +5850,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H189" t="n">
         <v>9000</v>
@@ -5879,7 +5879,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H190" t="n">
         <v>9500</v>
@@ -5908,7 +5908,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H191" t="n">
         <v>2500</v>
@@ -5937,7 +5937,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H192" t="n">
         <v>500</v>
@@ -5995,7 +5995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.78108286857605</v>
+        <v>2.78108310699463</v>
       </c>
       <c r="H197" t="n">
         <v>11500</v>
@@ -6111,7 +6111,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G198" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H198" t="n">
         <v>500</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G202" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G203" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G204" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G205" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6372,7 +6372,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H207" t="n">
         <v>2500</v>
@@ -6401,7 +6401,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H209" t="n">
         <v>6000</v>
@@ -6459,7 +6459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H210" t="n">
         <v>2500</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.78108286857605</v>
+        <v>2.78108310699463</v>
       </c>
       <c r="H212" t="n">
         <v>3000</v>
@@ -6546,7 +6546,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G213" t="n">
-        <v>2.89352536201477</v>
+        <v>2.89352560043335</v>
       </c>
       <c r="H213" t="n">
         <v>18000</v>
@@ -6575,7 +6575,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.848548412323</v>
+        <v>2.84854865074158</v>
       </c>
       <c r="H214" t="n">
         <v>13500</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.78108286857605</v>
+        <v>2.78108310699463</v>
       </c>
       <c r="H216" t="n">
         <v>5500</v>
@@ -6662,7 +6662,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109815597534</v>
+        <v>2.75109791755676</v>
       </c>
       <c r="H217" t="n">
         <v>7000</v>
@@ -6691,7 +6691,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H218" t="n">
         <v>10000</v>
@@ -6720,7 +6720,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>2.71361708641052</v>
+        <v>2.7136173248291</v>
       </c>
       <c r="H219" t="n">
         <v>61000</v>
@@ -6749,7 +6749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H220" t="n">
         <v>40500</v>
@@ -6778,7 +6778,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H221" t="n">
         <v>500</v>
@@ -6807,7 +6807,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H222" t="n">
         <v>10000</v>
@@ -6836,7 +6836,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612096786499</v>
+        <v>2.70612072944641</v>
       </c>
       <c r="H223" t="n">
         <v>5500</v>
@@ -6894,7 +6894,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618211746216</v>
+        <v>2.58618235588074</v>
       </c>
       <c r="H225" t="n">
         <v>6500</v>
@@ -6923,7 +6923,7 @@
         <v>3.5</v>
       </c>
       <c r="G226" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H226" t="n">
         <v>22000</v>
@@ -7010,7 +7010,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.6011745929718</v>
+        <v>2.60117435455322</v>
       </c>
       <c r="H229" t="n">
         <v>500</v>
@@ -7039,7 +7039,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.6611442565918</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H230" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>2.71361708641052</v>
+        <v>2.7136173248291</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7184,7 +7184,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.7361056804657</v>
+        <v>2.73610591888428</v>
       </c>
       <c r="H236" t="n">
         <v>3000</v>
@@ -7242,7 +7242,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H237" t="n">
         <v>24000</v>
@@ -7416,7 +7416,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111344337463</v>
+        <v>2.72111320495605</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7445,7 +7445,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H244" t="n">
         <v>24500</v>
@@ -7532,7 +7532,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609039306641</v>
+        <v>2.76609063148499</v>
       </c>
       <c r="H247" t="n">
         <v>5000</v>
@@ -7706,7 +7706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H253" t="n">
         <v>500</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105229377747</v>
       </c>
       <c r="H254" t="n">
         <v>1000</v>
@@ -7764,7 +7764,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G255" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.848548412323</v>
+        <v>2.84854865074158</v>
       </c>
       <c r="H257" t="n">
         <v>4500</v>
@@ -7851,7 +7851,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G258" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105229377747</v>
       </c>
       <c r="H258" t="n">
         <v>16500</v>
@@ -7880,7 +7880,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105229377747</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105229377747</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>2.78857922554016</v>
+        <v>2.78857898712158</v>
       </c>
       <c r="H261" t="n">
         <v>5500</v>
@@ -7967,7 +7967,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>2.84105205535889</v>
+        <v>2.84105229377747</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862461090088</v>
+        <v>2.69862484931946</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8025,7 +8025,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120564460754</v>
       </c>
       <c r="H264" t="n">
         <v>19500</v>
@@ -8054,7 +8054,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120564460754</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120564460754</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H273" t="n">
         <v>2500</v>
@@ -8315,7 +8315,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H276" t="n">
         <v>4000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635027885437</v>
+        <v>2.25635004043579</v>
       </c>
       <c r="H277" t="n">
         <v>5000</v>
@@ -8431,7 +8431,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.26384663581848</v>
+        <v>2.2638463973999</v>
       </c>
       <c r="H278" t="n">
         <v>5500</v>
@@ -8460,7 +8460,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>2.26384663581848</v>
+        <v>2.2638463973999</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883863449097</v>
+        <v>2.27883887290955</v>
       </c>
       <c r="H280" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639637947083</v>
+        <v>2.16639590263367</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.1514036655426</v>
+        <v>2.15140342712402</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639637947083</v>
+        <v>2.16639590263367</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G286" t="n">
-        <v>2.10642671585083</v>
+        <v>2.10642647743225</v>
       </c>
       <c r="H286" t="n">
         <v>15500</v>
@@ -8692,7 +8692,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638061523438</v>
+        <v>2.19638085365295</v>
       </c>
       <c r="H287" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18138837814331</v>
+        <v>2.18138861656189</v>
       </c>
       <c r="H288" t="n">
         <v>8000</v>
@@ -8750,7 +8750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18138837814331</v>
+        <v>2.18138861656189</v>
       </c>
       <c r="H289" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398386478424</v>
+        <v>1.99398398399353</v>
       </c>
       <c r="H295" t="n">
         <v>16500</v>
@@ -9011,7 +9011,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644176483154</v>
+        <v>2.07644152641296</v>
       </c>
       <c r="H298" t="n">
         <v>7500</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.09893035888672</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H299" t="n">
         <v>9500</v>
@@ -9069,7 +9069,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.09893035888672</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H300" t="n">
         <v>1500</v>
@@ -9098,7 +9098,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.09893035888672</v>
+        <v>2.09893012046814</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10642671585083</v>
+        <v>2.10642647743225</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390754699707</v>
+        <v>2.14390730857849</v>
       </c>
       <c r="H303" t="n">
         <v>2500</v>
@@ -9359,7 +9359,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H310" t="n">
         <v>18500</v>
@@ -9417,7 +9417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>2.42876219749451</v>
+        <v>2.42876243591309</v>
       </c>
       <c r="H312" t="n">
         <v>12000</v>
@@ -9446,7 +9446,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H313" t="n">
         <v>4500</v>
@@ -9504,7 +9504,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H315" t="n">
         <v>3000</v>
@@ -9533,7 +9533,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H316" t="n">
         <v>10500</v>
@@ -9562,7 +9562,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H317" t="n">
         <v>10500</v>
@@ -9591,7 +9591,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H318" t="n">
         <v>5000</v>
@@ -9707,7 +9707,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G322" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H322" t="n">
         <v>500</v>
@@ -9736,7 +9736,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H325" t="n">
         <v>1000</v>
@@ -9823,7 +9823,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G327" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G328" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G330" t="n">
-        <v>2.45874714851379</v>
+        <v>2.45874691009521</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -9997,7 +9997,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H336" t="n">
         <v>1000</v>
@@ -10142,7 +10142,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H338" t="n">
         <v>8000</v>
@@ -10200,7 +10200,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.39877796173096</v>
+        <v>2.39877772331238</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H348" t="n">
         <v>4000</v>
@@ -10490,7 +10490,7 @@
         <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>2.24885368347168</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H349" t="n">
         <v>6000</v>
@@ -10519,7 +10519,7 @@
         <v>3</v>
       </c>
       <c r="G350" t="n">
-        <v>2.24885368347168</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H350" t="n">
         <v>2500</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.21137309074402</v>
+        <v>2.21137285232544</v>
       </c>
       <c r="H351" t="n">
         <v>94500</v>
@@ -10577,7 +10577,7 @@
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>2.24885368347168</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H352" t="n">
         <v>16000</v>
@@ -10606,7 +10606,7 @@
         <v>3</v>
       </c>
       <c r="G353" t="n">
-        <v>2.24885368347168</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H353" t="n">
         <v>9500</v>
@@ -10722,7 +10722,7 @@
         <v>3</v>
       </c>
       <c r="G357" t="n">
-        <v>2.24885368347168</v>
+        <v>2.24885416030884</v>
       </c>
       <c r="H357" t="n">
         <v>1000</v>
@@ -10751,7 +10751,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10780,7 +10780,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381582260132</v>
+        <v>2.32381558418274</v>
       </c>
       <c r="H359" t="n">
         <v>2500</v>
@@ -10838,7 +10838,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G361" t="n">
-        <v>2.48873162269592</v>
+        <v>2.4887318611145</v>
       </c>
       <c r="H361" t="n">
         <v>6000</v>
@@ -10896,7 +10896,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120564460754</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>2.56369352340698</v>
+        <v>2.56369376182556</v>
       </c>
       <c r="H364" t="n">
         <v>500</v>
@@ -10954,7 +10954,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56369352340698</v>
+        <v>2.56369376182556</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120564460754</v>
       </c>
       <c r="H366" t="n">
         <v>500</v>
@@ -11012,7 +11012,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120516777039</v>
+        <v>2.54120564460754</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>2.48123598098755</v>
+        <v>2.48123550415039</v>
       </c>
       <c r="H368" t="n">
         <v>16500</v>
@@ -11128,7 +11128,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.54870104789734</v>
+        <v>2.5487015247345</v>
       </c>
       <c r="H371" t="n">
         <v>500</v>
@@ -11157,7 +11157,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.54870104789734</v>
+        <v>2.5487015247345</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11215,7 +11215,7 @@
         <v>3.5</v>
       </c>
       <c r="G374" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H374" t="n">
         <v>2500</v>
@@ -11244,7 +11244,7 @@
         <v>3.5</v>
       </c>
       <c r="G375" t="n">
-        <v>2.6236629486084</v>
+        <v>2.62366318702698</v>
       </c>
       <c r="H375" t="n">
         <v>4000</v>
@@ -11302,7 +11302,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.6611442565918</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H377" t="n">
         <v>12500</v>
@@ -11331,7 +11331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66864013671875</v>
+        <v>2.66864037513733</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11389,7 +11389,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>2.79607534408569</v>
+        <v>2.79607510566711</v>
       </c>
       <c r="H380" t="n">
         <v>11500</v>
@@ -11418,7 +11418,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H381" t="n">
         <v>73500</v>
@@ -11476,7 +11476,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H383" t="n">
         <v>32500</v>
@@ -11505,7 +11505,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604453086853</v>
+        <v>2.85604429244995</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H385" t="n">
         <v>5000</v>
@@ -11650,7 +11650,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H389" t="n">
         <v>20000</v>
@@ -11679,7 +11679,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G390" t="n">
-        <v>2.86354064941406</v>
+        <v>2.86354088783264</v>
       </c>
       <c r="H390" t="n">
         <v>5500</v>
@@ -11708,7 +11708,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G391" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H391" t="n">
         <v>1500</v>
@@ -11737,7 +11737,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>2.90851831436157</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H392" t="n">
         <v>8000</v>
@@ -11766,7 +11766,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90851831436157</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11795,7 +11795,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.9385027885437</v>
+        <v>2.93850255012512</v>
       </c>
       <c r="H394" t="n">
         <v>4000</v>
@@ -11824,7 +11824,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H395" t="n">
         <v>4000</v>
@@ -11853,7 +11853,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>2.90851831436157</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11911,7 +11911,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H398" t="n">
         <v>8500</v>
@@ -11940,7 +11940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H399" t="n">
         <v>8000</v>
@@ -11969,7 +11969,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H400" t="n">
         <v>3500</v>
@@ -11998,7 +11998,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G401" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H401" t="n">
         <v>500</v>
@@ -12027,7 +12027,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>2.7735869884491</v>
+        <v>2.77358675003052</v>
       </c>
       <c r="H402" t="n">
         <v>1500</v>
@@ -12085,7 +12085,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12114,7 +12114,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G405" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G406" t="n">
-        <v>2.80357122421265</v>
+        <v>2.80357146263123</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>2.83355617523193</v>
+        <v>2.83355593681335</v>
       </c>
       <c r="H407" t="n">
         <v>119000</v>
@@ -12230,7 +12230,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848773956299</v>
+        <v>2.96848726272583</v>
       </c>
       <c r="H409" t="n">
         <v>16000</v>
@@ -12259,7 +12259,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848773956299</v>
+        <v>2.96848726272583</v>
       </c>
       <c r="H410" t="n">
         <v>3000</v>
@@ -12288,7 +12288,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H411" t="n">
         <v>2000</v>
@@ -12317,7 +12317,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351007461548</v>
+        <v>2.92351031303406</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H413" t="n">
         <v>500</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.848548412323</v>
+        <v>2.84854865074158</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>2.90851831436157</v>
+        <v>2.90851807594299</v>
       </c>
       <c r="H415" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866278648376</v>
+        <v>2.91866326332092</v>
       </c>
       <c r="H417" t="n">
         <v>2500</v>
@@ -12578,7 +12578,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H421" t="n">
         <v>2000</v>
@@ -12607,7 +12607,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H426" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H427" t="n">
         <v>4000</v>
@@ -12781,7 +12781,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670219421387</v>
+        <v>2.99670195579529</v>
       </c>
       <c r="H430" t="n">
         <v>2000</v>
@@ -12868,7 +12868,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H431" t="n">
         <v>2500</v>
@@ -13274,7 +13274,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.2932505607605</v>
+        <v>3.29325032234192</v>
       </c>
       <c r="H445" t="n">
         <v>36000</v>
@@ -13332,7 +13332,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H447" t="n">
         <v>7500</v>
@@ -13390,7 +13390,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H449" t="n">
         <v>7500</v>
@@ -13419,7 +13419,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G450" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G454" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H454" t="n">
         <v>20000</v>
@@ -13564,7 +13564,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278029441833</v>
+        <v>3.15278053283691</v>
       </c>
       <c r="H455" t="n">
         <v>16000</v>
@@ -13709,7 +13709,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H460" t="n">
         <v>5500</v>
@@ -13825,7 +13825,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G464" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H465" t="n">
         <v>500</v>
@@ -13883,7 +13883,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -13912,7 +13912,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H468" t="n">
         <v>22500</v>
@@ -13970,7 +13970,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>3.02791810035706</v>
+        <v>3.02791786193848</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -14057,7 +14057,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H472" t="n">
         <v>15500</v>
@@ -14579,7 +14579,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14637,7 +14637,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764296531677</v>
+        <v>3.27764272689819</v>
       </c>
       <c r="H492" t="n">
         <v>65000</v>
@@ -14666,7 +14666,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H493" t="n">
         <v>77000</v>
@@ -14695,7 +14695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764296531677</v>
+        <v>3.27764272689819</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.37129020690918</v>
+        <v>3.3712899684906</v>
       </c>
       <c r="H495" t="n">
         <v>17000</v>
@@ -14753,7 +14753,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203513145447</v>
+        <v>3.26203489303589</v>
       </c>
       <c r="H496" t="n">
         <v>21000</v>
@@ -14782,7 +14782,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H497" t="n">
         <v>26000</v>
@@ -14811,7 +14811,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>3.24642705917358</v>
+        <v>3.24642729759216</v>
       </c>
       <c r="H499" t="n">
         <v>1000</v>
@@ -14927,7 +14927,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521139144897</v>
+        <v>3.21521162986755</v>
       </c>
       <c r="H502" t="n">
         <v>20500</v>
@@ -15014,7 +15014,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G505" t="n">
-        <v>3.01230978965759</v>
+        <v>3.01231002807617</v>
       </c>
       <c r="H505" t="n">
         <v>28500</v>
@@ -15130,7 +15130,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13717293739319</v>
+        <v>3.13717246055603</v>
       </c>
       <c r="H509" t="n">
         <v>6000</v>
@@ -15217,7 +15217,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474112510681</v>
+        <v>3.07474136352539</v>
       </c>
       <c r="H512" t="n">
         <v>3000</v>
@@ -15304,7 +15304,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.0903491973877</v>
+        <v>3.09034895896912</v>
       </c>
       <c r="H515" t="n">
         <v>6500</v>
@@ -15420,7 +15420,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278029441833</v>
+        <v>3.15278053283691</v>
       </c>
       <c r="H519" t="n">
         <v>4000</v>
@@ -15536,7 +15536,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.05913352966309</v>
+        <v>3.05913329124451</v>
       </c>
       <c r="H523" t="n">
         <v>11000</v>
@@ -15594,7 +15594,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H525" t="n">
         <v>9500</v>
@@ -15652,7 +15652,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H527" t="n">
         <v>50000</v>
@@ -15739,7 +15739,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G530" t="n">
-        <v>2.77819228172302</v>
+        <v>2.77819275856018</v>
       </c>
       <c r="H530" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H535" t="n">
         <v>10500</v>
@@ -15913,7 +15913,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H536" t="n">
         <v>2500</v>
@@ -15942,7 +15942,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H538" t="n">
         <v>4000</v>
@@ -16000,7 +16000,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H539" t="n">
         <v>3000</v>
@@ -16029,7 +16029,7 @@
         <v>3.5</v>
       </c>
       <c r="G540" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H540" t="n">
         <v>8000</v>
@@ -16087,7 +16087,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H542" t="n">
         <v>6000</v>
@@ -16145,7 +16145,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772249221802</v>
       </c>
       <c r="H544" t="n">
         <v>5000</v>
@@ -16319,7 +16319,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G550" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H550" t="n">
         <v>7500</v>
@@ -16406,7 +16406,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H553" t="n">
         <v>77000</v>
@@ -16435,7 +16435,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H554" t="n">
         <v>39500</v>
@@ -16493,7 +16493,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H556" t="n">
         <v>4000</v>
@@ -16638,7 +16638,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H561" t="n">
         <v>11000</v>
@@ -16667,7 +16667,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H562" t="n">
         <v>2500</v>
@@ -16754,7 +16754,7 @@
         <v>3.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H565" t="n">
         <v>3000</v>
@@ -16870,7 +16870,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77819228172302</v>
+        <v>2.77819275856018</v>
       </c>
       <c r="H569" t="n">
         <v>11000</v>
@@ -16899,7 +16899,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77819228172302</v>
+        <v>2.77819275856018</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.77819228172302</v>
+        <v>2.77819275856018</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.77819228172302</v>
+        <v>2.77819275856018</v>
       </c>
       <c r="H580" t="n">
         <v>32000</v>
@@ -17334,7 +17334,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.85623168945312</v>
+        <v>2.8562319278717</v>
       </c>
       <c r="H585" t="n">
         <v>12500</v>
@@ -17363,7 +17363,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.77819228172302</v>
+        <v>2.77819275856018</v>
       </c>
       <c r="H586" t="n">
         <v>5000</v>
@@ -17508,7 +17508,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H591" t="n">
         <v>3000</v>
@@ -17566,7 +17566,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H593" t="n">
         <v>6000</v>
@@ -17595,7 +17595,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407548904419</v>
+        <v>2.54407501220703</v>
       </c>
       <c r="H594" t="n">
         <v>5500</v>
@@ -17624,7 +17624,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H595" t="n">
         <v>13500</v>
@@ -17682,7 +17682,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H597" t="n">
         <v>41000</v>
@@ -17711,7 +17711,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G598" t="n">
-        <v>2.59089851379395</v>
+        <v>2.5908989906311</v>
       </c>
       <c r="H598" t="n">
         <v>6000</v>
@@ -17740,7 +17740,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H599" t="n">
         <v>13500</v>
@@ -17798,7 +17798,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G601" t="n">
-        <v>2.59089851379395</v>
+        <v>2.5908989906311</v>
       </c>
       <c r="H601" t="n">
         <v>6500</v>
@@ -17856,7 +17856,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H603" t="n">
         <v>17500</v>
@@ -17885,7 +17885,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772249221802</v>
       </c>
       <c r="H604" t="n">
         <v>500</v>
@@ -17914,7 +17914,7 @@
         <v>3.5</v>
       </c>
       <c r="G605" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H605" t="n">
         <v>45000</v>
@@ -18001,7 +18001,7 @@
         <v>3.5</v>
       </c>
       <c r="G608" t="n">
-        <v>2.73136901855469</v>
+        <v>2.73136925697327</v>
       </c>
       <c r="H608" t="n">
         <v>36000</v>
@@ -18030,7 +18030,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63772225379944</v>
+        <v>2.63772249221802</v>
       </c>
       <c r="H609" t="n">
         <v>47000</v>
@@ -18059,7 +18059,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H610" t="n">
         <v>20500</v>
@@ -18088,7 +18088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H611" t="n">
         <v>27500</v>
@@ -18117,7 +18117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H612" t="n">
         <v>6000</v>
@@ -18146,7 +18146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H613" t="n">
         <v>3000</v>
@@ -18204,7 +18204,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>2.65333008766174</v>
+        <v>2.65333032608032</v>
       </c>
       <c r="H615" t="n">
         <v>2500</v>
@@ -18233,7 +18233,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H616" t="n">
         <v>22500</v>
@@ -18262,7 +18262,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.57529091835022</v>
+        <v>2.5752911567688</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211394309998</v>
+        <v>2.62211465835571</v>
       </c>
       <c r="H618" t="n">
         <v>1000</v>
@@ -18320,7 +18320,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.49725198745728</v>
+        <v>2.4972517490387</v>
       </c>
       <c r="H619" t="n">
         <v>3000</v>
@@ -18349,7 +18349,7 @@
         <v>3</v>
       </c>
       <c r="G620" t="n">
-        <v>2.34117341041565</v>
+        <v>2.34117364883423</v>
       </c>
       <c r="H620" t="n">
         <v>7500</v>
@@ -18436,7 +18436,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.2319188117981</v>
+        <v>2.23191857337952</v>
       </c>
       <c r="H623" t="n">
         <v>16000</v>
@@ -18465,7 +18465,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631073951721</v>
+        <v>2.21631097793579</v>
       </c>
       <c r="H624" t="n">
         <v>3000</v>
@@ -18494,7 +18494,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H625" t="n">
         <v>13000</v>
@@ -18581,7 +18581,7 @@
         <v>2.5</v>
       </c>
       <c r="G628" t="n">
-        <v>2.05594682693481</v>
+        <v>2.05594706535339</v>
       </c>
       <c r="H628" t="n">
         <v>11000</v>
@@ -18610,7 +18610,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660467147827</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H629" t="n">
         <v>18500</v>
@@ -18639,7 +18639,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.9572616815567</v>
+        <v>1.95726180076599</v>
       </c>
       <c r="H631" t="n">
         <v>14000</v>
@@ -18697,7 +18697,7 @@
         <v>2.5</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05594682693481</v>
+        <v>2.05594706535339</v>
       </c>
       <c r="H632" t="n">
         <v>9000</v>
@@ -18755,7 +18755,7 @@
         <v>2.5</v>
       </c>
       <c r="G634" t="n">
-        <v>2.05594682693481</v>
+        <v>2.05594706535339</v>
       </c>
       <c r="H634" t="n">
         <v>1000</v>
@@ -18784,7 +18784,7 @@
         <v>2.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.05594682693481</v>
+        <v>2.05594706535339</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>2.5</v>
       </c>
       <c r="G636" t="n">
-        <v>2.05594682693481</v>
+        <v>2.05594706535339</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H637" t="n">
         <v>2000</v>
@@ -18871,7 +18871,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -18900,7 +18900,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H639" t="n">
         <v>10000</v>
@@ -18958,7 +18958,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H641" t="n">
         <v>18000</v>
@@ -18987,7 +18987,7 @@
         <v>3</v>
       </c>
       <c r="G642" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H642" t="n">
         <v>19000</v>
@@ -19016,7 +19016,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>2.45068883895874</v>
+        <v>2.45068860054016</v>
       </c>
       <c r="H643" t="n">
         <v>18000</v>
@@ -19161,7 +19161,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G648" t="n">
-        <v>2.45068883895874</v>
+        <v>2.45068860054016</v>
       </c>
       <c r="H648" t="n">
         <v>6000</v>
@@ -19190,7 +19190,7 @@
         <v>3</v>
       </c>
       <c r="G649" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H649" t="n">
         <v>28500</v>
@@ -19219,7 +19219,7 @@
         <v>3</v>
       </c>
       <c r="G650" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H650" t="n">
         <v>11500</v>
@@ -19277,7 +19277,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>2.51647901535034</v>
+        <v>2.51647925376892</v>
       </c>
       <c r="H652" t="n">
         <v>6000</v>
@@ -19306,7 +19306,7 @@
         <v>3</v>
       </c>
       <c r="G653" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H653" t="n">
         <v>6500</v>
@@ -19364,7 +19364,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>2.45068883895874</v>
+        <v>2.45068860054016</v>
       </c>
       <c r="H655" t="n">
         <v>8000</v>
@@ -19393,7 +19393,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G656" t="n">
-        <v>2.51647901535034</v>
+        <v>2.51647925376892</v>
       </c>
       <c r="H656" t="n">
         <v>16000</v>
@@ -19596,7 +19596,7 @@
         <v>3</v>
       </c>
       <c r="G663" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H663" t="n">
         <v>11000</v>
@@ -19683,7 +19683,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>2.45068883895874</v>
+        <v>2.45068860054016</v>
       </c>
       <c r="H666" t="n">
         <v>44000</v>
@@ -19741,7 +19741,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555555343628</v>
+        <v>2.33555579185486</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H669" t="n">
         <v>76500</v>
@@ -19857,7 +19857,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G672" t="n">
-        <v>2.07239460945129</v>
+        <v>2.07239437103271</v>
       </c>
       <c r="H672" t="n">
         <v>11560</v>
@@ -19886,7 +19886,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H673" t="n">
         <v>7000</v>
@@ -19915,7 +19915,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H674" t="n">
         <v>2530</v>
@@ -20031,7 +20031,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G678" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H678" t="n">
         <v>7225</v>
@@ -20089,7 +20089,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H680" t="n">
         <v>8410</v>
@@ -20147,7 +20147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H682" t="n">
         <v>21900</v>
@@ -20176,7 +20176,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H683" t="n">
         <v>19301</v>
@@ -20205,7 +20205,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G684" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H684" t="n">
         <v>3500</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H686" t="n">
         <v>2000</v>
@@ -20437,7 +20437,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G692" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H692" t="n">
         <v>12500</v>
@@ -20495,7 +20495,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G694" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H694" t="n">
         <v>4200</v>
@@ -20524,7 +20524,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G696" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H696" t="n">
         <v>10100</v>
@@ -20582,7 +20582,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G697" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H697" t="n">
         <v>13340</v>
@@ -20611,7 +20611,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G698" t="n">
-        <v>2.30266046524048</v>
+        <v>2.30266070365906</v>
       </c>
       <c r="H698" t="n">
         <v>5110</v>
@@ -20669,7 +20669,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H700" t="n">
         <v>11550</v>
@@ -20698,7 +20698,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G701" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H701" t="n">
         <v>1600</v>
@@ -20727,7 +20727,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H702" t="n">
         <v>1010</v>
@@ -20785,7 +20785,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H704" t="n">
         <v>5880</v>
@@ -20843,7 +20843,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H706" t="n">
         <v>500</v>
@@ -20872,7 +20872,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H707" t="n">
         <v>3875</v>
@@ -20901,7 +20901,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G708" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H708" t="n">
         <v>1125</v>
@@ -20930,7 +20930,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G709" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G710" t="n">
-        <v>2.30266046524048</v>
+        <v>2.30266070365906</v>
       </c>
       <c r="H710" t="n">
         <v>15630</v>
@@ -21046,7 +21046,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G713" t="n">
-        <v>2.30266046524048</v>
+        <v>2.30266070365906</v>
       </c>
       <c r="H713" t="n">
         <v>7300</v>
@@ -21075,7 +21075,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>2.30266046524048</v>
+        <v>2.30266070365906</v>
       </c>
       <c r="H714" t="n">
         <v>14000</v>
@@ -21162,7 +21162,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H717" t="n">
         <v>1920</v>
@@ -21249,7 +21249,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H720" t="n">
         <v>2579</v>
@@ -21307,7 +21307,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G722" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H722" t="n">
         <v>8900</v>
@@ -21365,7 +21365,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G724" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21394,7 +21394,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G725" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H725" t="n">
         <v>9500</v>
@@ -21423,7 +21423,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H726" t="n">
         <v>1500</v>
@@ -21452,7 +21452,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H727" t="n">
         <v>588</v>
@@ -21481,7 +21481,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H728" t="n">
         <v>3100</v>
@@ -21510,7 +21510,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G729" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G730" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G731" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H731" t="n">
         <v>8000</v>
@@ -22061,7 +22061,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22090,7 +22090,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G749" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G751" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H751" t="n">
         <v>14535</v>
@@ -22293,7 +22293,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H756" t="n">
         <v>6282</v>
@@ -22322,7 +22322,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H757" t="n">
         <v>3679</v>
@@ -22409,7 +22409,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H760" t="n">
         <v>210</v>
@@ -22496,7 +22496,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22525,7 +22525,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528969764709</v>
+        <v>2.10528993606567</v>
       </c>
       <c r="H764" t="n">
         <v>10600</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660467147827</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H766" t="n">
         <v>7000</v>
@@ -22612,7 +22612,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H767" t="n">
         <v>11020</v>
@@ -22670,7 +22670,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370946407318</v>
+        <v>1.97370934486389</v>
       </c>
       <c r="H769" t="n">
         <v>2120</v>
@@ -22728,7 +22728,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H771" t="n">
         <v>5351</v>
@@ -22786,7 +22786,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660467147827</v>
+        <v>2.00660419464111</v>
       </c>
       <c r="H773" t="n">
         <v>10000</v>
@@ -22815,7 +22815,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.9572616815567</v>
+        <v>1.95726180076599</v>
       </c>
       <c r="H774" t="n">
         <v>10000</v>
@@ -22844,7 +22844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.84212839603424</v>
+        <v>1.84212875366211</v>
       </c>
       <c r="H775" t="n">
         <v>26371</v>
@@ -22902,7 +22902,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G777" t="n">
-        <v>1.77633845806122</v>
+        <v>1.77633833885193</v>
       </c>
       <c r="H777" t="n">
         <v>21350</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84212839603424</v>
+        <v>1.84212875366211</v>
       </c>
       <c r="H778" t="n">
         <v>8200</v>
@@ -23105,7 +23105,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H784" t="n">
         <v>9450</v>
@@ -23134,7 +23134,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278588294983</v>
+        <v>1.79278600215912</v>
       </c>
       <c r="H785" t="n">
         <v>6000</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.84212839603424</v>
+        <v>1.84212875366211</v>
       </c>
       <c r="H786" t="n">
         <v>500</v>
@@ -23221,7 +23221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502348423004</v>
+        <v>1.87502360343933</v>
       </c>
       <c r="H788" t="n">
         <v>4000</v>
@@ -23250,7 +23250,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502348423004</v>
+        <v>1.87502360343933</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147126674652</v>
+        <v>1.89147114753723</v>
       </c>
       <c r="H790" t="n">
         <v>2551</v>
@@ -23366,7 +23366,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305197715759</v>
+        <v>2.02305173873901</v>
       </c>
       <c r="H793" t="n">
         <v>8769</v>
@@ -23395,7 +23395,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.9901567697525</v>
+        <v>1.99015641212463</v>
       </c>
       <c r="H794" t="n">
         <v>5000</v>
@@ -23424,7 +23424,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370946407318</v>
+        <v>1.97370934486389</v>
       </c>
       <c r="H795" t="n">
         <v>5168</v>
@@ -23482,7 +23482,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="n">
-        <v>2.05594682693481</v>
+        <v>2.05594706535339</v>
       </c>
       <c r="H797" t="n">
         <v>12411</v>
@@ -23540,7 +23540,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>2.121737241745</v>
+        <v>2.12173748016357</v>
       </c>
       <c r="H799" t="n">
         <v>3200</v>
@@ -23569,7 +23569,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G800" t="n">
-        <v>2.07239460945129</v>
+        <v>2.07239437103271</v>
       </c>
       <c r="H800" t="n">
         <v>5199</v>
@@ -23598,7 +23598,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H801" t="n">
         <v>18700</v>
@@ -23656,7 +23656,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G803" t="n">
-        <v>2.18752765655518</v>
+        <v>2.18752789497375</v>
       </c>
       <c r="H803" t="n">
         <v>39306</v>
@@ -23714,7 +23714,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G805" t="n">
-        <v>2.30266046524048</v>
+        <v>2.30266070365906</v>
       </c>
       <c r="H805" t="n">
         <v>9350</v>
@@ -23743,7 +23743,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G806" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H806" t="n">
         <v>4149</v>
@@ -23772,7 +23772,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H807" t="n">
         <v>11874</v>
@@ -23859,7 +23859,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H810" t="n">
         <v>9326</v>
@@ -23946,7 +23946,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H813" t="n">
         <v>15111</v>
@@ -24033,7 +24033,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H816" t="n">
         <v>4950</v>
@@ -24062,7 +24062,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H817" t="n">
         <v>3243</v>
@@ -24091,7 +24091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G818" t="n">
-        <v>2.26976537704468</v>
+        <v>2.26976561546326</v>
       </c>
       <c r="H818" t="n">
         <v>2250</v>
@@ -24120,7 +24120,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>2.38489866256714</v>
+        <v>2.38489890098572</v>
       </c>
       <c r="H819" t="n">
         <v>48040</v>
@@ -24323,7 +24323,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G826" t="n">
-        <v>2.23687052726746</v>
+        <v>2.23687028884888</v>
       </c>
       <c r="H826" t="n">
         <v>4285</v>
@@ -24352,7 +24352,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30266046524048</v>
+        <v>2.30266070365906</v>
       </c>
       <c r="H827" t="n">
         <v>20716</v>
@@ -24381,7 +24381,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>2.51647901535034</v>
+        <v>2.51647925376892</v>
       </c>
       <c r="H828" t="n">
         <v>256671</v>
@@ -24497,7 +24497,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964067459106</v>
+        <v>2.77964043617249</v>
       </c>
       <c r="H832" t="n">
         <v>51937</v>
@@ -24700,7 +24700,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.58226943016052</v>
+        <v>2.5822696685791</v>
       </c>
       <c r="H839" t="n">
         <v>12621</v>
@@ -24787,7 +24787,7 @@
         <v>3</v>
       </c>
       <c r="G842" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H842" t="n">
         <v>9887</v>
@@ -24816,7 +24816,7 @@
         <v>3</v>
       </c>
       <c r="G843" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H843" t="n">
         <v>16149</v>
@@ -24845,7 +24845,7 @@
         <v>3</v>
       </c>
       <c r="G844" t="n">
-        <v>2.46713662147522</v>
+        <v>2.46713638305664</v>
       </c>
       <c r="H844" t="n">
         <v>15762</v>
@@ -24903,7 +24903,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58226943016052</v>
+        <v>2.5822696685791</v>
       </c>
       <c r="H846" t="n">
         <v>14130</v>
@@ -25251,7 +25251,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G858" t="n">
-        <v>2.76319265365601</v>
+        <v>2.76319289207458</v>
       </c>
       <c r="H858" t="n">
         <v>24533</v>
@@ -25338,7 +25338,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H861" t="n">
         <v>8401</v>
@@ -25367,7 +25367,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G862" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H862" t="n">
         <v>800</v>
@@ -25396,7 +25396,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.68095517158508</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H863" t="n">
         <v>4900</v>
@@ -25425,7 +25425,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.68095517158508</v>
+        <v>2.68095469474792</v>
       </c>
       <c r="H864" t="n">
         <v>1600</v>
@@ -25483,7 +25483,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G866" t="n">
-        <v>2.69740271568298</v>
+        <v>2.6974024772644</v>
       </c>
       <c r="H866" t="n">
         <v>8639</v>
@@ -25570,7 +25570,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="n">
-        <v>2.82898330688477</v>
+        <v>2.82898306846619</v>
       </c>
       <c r="H869" t="n">
         <v>30735</v>
@@ -25599,7 +25599,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>2.86187839508057</v>
+        <v>2.86187815666199</v>
       </c>
       <c r="H870" t="n">
         <v>110702</v>
@@ -25657,7 +25657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G872" t="n">
-        <v>2.86187839508057</v>
+        <v>2.86187815666199</v>
       </c>
       <c r="H872" t="n">
         <v>56730</v>
@@ -25686,7 +25686,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H873" t="n">
         <v>27201</v>
@@ -25744,7 +25744,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H875" t="n">
         <v>19182</v>
@@ -25773,7 +25773,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H876" t="n">
         <v>20608</v>
@@ -25802,7 +25802,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>2.92766857147217</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H877" t="n">
         <v>15518</v>
@@ -25860,7 +25860,7 @@
         <v>3.5</v>
       </c>
       <c r="G879" t="n">
-        <v>2.87832617759705</v>
+        <v>2.87832593917847</v>
       </c>
       <c r="H879" t="n">
         <v>14907</v>
@@ -25889,7 +25889,7 @@
         <v>3.5</v>
       </c>
       <c r="G880" t="n">
-        <v>2.87832617759705</v>
+        <v>2.87832593917847</v>
       </c>
       <c r="H880" t="n">
         <v>11224</v>
@@ -25918,7 +25918,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H881" t="n">
         <v>26805</v>
@@ -26121,7 +26121,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>2.91122126579285</v>
+        <v>2.91122102737427</v>
       </c>
       <c r="H888" t="n">
         <v>9185</v>
@@ -26150,7 +26150,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>2.92766857147217</v>
+        <v>2.92766880989075</v>
       </c>
       <c r="H889" t="n">
         <v>9439</v>
@@ -26295,7 +26295,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>3.01813006401062</v>
+        <v>3.0181303024292</v>
       </c>
       <c r="H894" t="n">
         <v>4722</v>
@@ -26498,7 +26498,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>3.05102562904358</v>
+        <v>3.051025390625</v>
       </c>
       <c r="H901" t="n">
         <v>43084</v>
@@ -26556,7 +26556,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280161857605</v>
+        <v>3.04280185699463</v>
       </c>
       <c r="H903" t="n">
         <v>10299</v>
@@ -26614,7 +26614,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H905" t="n">
         <v>9395</v>
@@ -26672,7 +26672,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G907" t="n">
-        <v>3.12503957748413</v>
+        <v>3.12503933906555</v>
       </c>
       <c r="H907" t="n">
         <v>5477</v>
@@ -26730,7 +26730,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793466567993</v>
+        <v>3.15793442726135</v>
       </c>
       <c r="H909" t="n">
         <v>1061</v>
@@ -26759,7 +26759,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H910" t="n">
         <v>3156</v>
@@ -26817,7 +26817,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H912" t="n">
         <v>16945</v>
@@ -26846,7 +26846,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>3.19083023071289</v>
+        <v>3.19082999229431</v>
       </c>
       <c r="H913" t="n">
         <v>6168</v>
@@ -26875,7 +26875,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.22372508049011</v>
+        <v>3.22372484207153</v>
       </c>
       <c r="H914" t="n">
         <v>32683</v>
@@ -26904,7 +26904,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G915" t="n">
-        <v>3.20727753639221</v>
+        <v>3.20727729797363</v>
       </c>
       <c r="H915" t="n">
         <v>20765</v>
@@ -26933,7 +26933,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.16615843772888</v>
+        <v>3.1661581993103</v>
       </c>
       <c r="H916" t="n">
         <v>23119</v>
@@ -27165,7 +27165,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G924" t="n">
-        <v>3.13228178024292</v>
+        <v>3.1322820186615</v>
       </c>
       <c r="H924" t="n">
         <v>4945</v>
@@ -27194,7 +27194,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>3.09018111228943</v>
+        <v>3.09018135070801</v>
       </c>
       <c r="H925" t="n">
         <v>12908</v>
@@ -27281,7 +27281,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>3.05650067329407</v>
+        <v>3.05650091171265</v>
       </c>
       <c r="H928" t="n">
         <v>100</v>
@@ -27310,7 +27310,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>3.09018111228943</v>
+        <v>3.09018135070801</v>
       </c>
       <c r="H929" t="n">
         <v>3279</v>
@@ -27339,7 +27339,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.14912176132202</v>
+        <v>3.1491219997406</v>
       </c>
       <c r="H930" t="n">
         <v>4469</v>
@@ -27397,7 +27397,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H932" t="n">
         <v>46107</v>
@@ -27455,7 +27455,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H934" t="n">
         <v>17505</v>
@@ -27484,7 +27484,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H935" t="n">
         <v>4667</v>
@@ -27542,7 +27542,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H937" t="n">
         <v>9999</v>
@@ -27629,7 +27629,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H940" t="n">
         <v>4174</v>
@@ -27658,7 +27658,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>3.41856551170349</v>
+        <v>3.41856575012207</v>
       </c>
       <c r="H941" t="n">
         <v>13248</v>
@@ -27687,7 +27687,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>3.41856551170349</v>
+        <v>3.41856575012207</v>
       </c>
       <c r="H942" t="n">
         <v>56586</v>
@@ -27716,7 +27716,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G943" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276660919189</v>
       </c>
       <c r="H943" t="n">
         <v>26715</v>
@@ -27745,7 +27745,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434685707092</v>
       </c>
       <c r="H944" t="n">
         <v>9943</v>
@@ -27774,7 +27774,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>3.61222791671753</v>
+        <v>3.61222815513611</v>
       </c>
       <c r="H945" t="n">
         <v>61318</v>
@@ -27803,7 +27803,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G946" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H946" t="n">
         <v>9308</v>
@@ -27832,7 +27832,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644704818726</v>
+        <v>3.53644680976868</v>
       </c>
       <c r="H947" t="n">
         <v>5552</v>
@@ -27861,7 +27861,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H948" t="n">
         <v>6445</v>
@@ -27948,7 +27948,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>3.52802729606628</v>
+        <v>3.52802705764771</v>
       </c>
       <c r="H951" t="n">
         <v>10788</v>
@@ -27977,7 +27977,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434685707092</v>
       </c>
       <c r="H952" t="n">
         <v>3722</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960682868958</v>
+        <v>3.51960706710815</v>
       </c>
       <c r="H953" t="n">
         <v>4381</v>
@@ -28122,7 +28122,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>3.61222791671753</v>
+        <v>3.61222815513611</v>
       </c>
       <c r="H957" t="n">
         <v>5268</v>
@@ -28151,7 +28151,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H958" t="n">
         <v>4435</v>
@@ -28180,7 +28180,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>3.44382619857788</v>
+        <v>3.4438259601593</v>
       </c>
       <c r="H959" t="n">
         <v>19778</v>
@@ -28209,7 +28209,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H960" t="n">
         <v>1627</v>
@@ -28238,7 +28238,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H961" t="n">
         <v>1261</v>
@@ -28267,7 +28267,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G962" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H962" t="n">
         <v>25266</v>
@@ -28470,7 +28470,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>3.30068445205688</v>
+        <v>3.30068373680115</v>
       </c>
       <c r="H969" t="n">
         <v>1754</v>
@@ -28499,7 +28499,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594418525696</v>
       </c>
       <c r="H970" t="n">
         <v>650</v>
@@ -28528,7 +28528,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>3.30068445205688</v>
+        <v>3.30068373680115</v>
       </c>
       <c r="H971" t="n">
         <v>3678</v>
@@ -28557,7 +28557,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752443313599</v>
+        <v>3.31752419471741</v>
       </c>
       <c r="H972" t="n">
         <v>4735</v>
@@ -28586,7 +28586,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H973" t="n">
         <v>150</v>
@@ -28673,7 +28673,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>3.30068445205688</v>
+        <v>3.30068373680115</v>
       </c>
       <c r="H976" t="n">
         <v>1030</v>
@@ -28702,7 +28702,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G977" t="n">
-        <v>3.23332285881042</v>
+        <v>3.233323097229</v>
       </c>
       <c r="H977" t="n">
         <v>2819</v>
@@ -28731,7 +28731,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436417579651</v>
       </c>
       <c r="H978" t="n">
         <v>24159</v>
@@ -28789,7 +28789,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172553062439</v>
       </c>
       <c r="H980" t="n">
         <v>8597</v>
@@ -28818,7 +28818,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H981" t="n">
         <v>410</v>
@@ -28876,7 +28876,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436417579651</v>
       </c>
       <c r="H983" t="n">
         <v>3909</v>
@@ -28905,7 +28905,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G984" t="n">
-        <v>3.41856551170349</v>
+        <v>3.41856575012207</v>
       </c>
       <c r="H984" t="n">
         <v>10480</v>
@@ -29021,7 +29021,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>3.37646508216858</v>
+        <v>3.37646532058716</v>
       </c>
       <c r="H988" t="n">
         <v>535</v>
@@ -29195,7 +29195,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H994" t="n">
         <v>9158</v>
@@ -29282,7 +29282,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>3.61222791671753</v>
+        <v>3.61222815513611</v>
       </c>
       <c r="H997" t="n">
         <v>30034</v>
@@ -29311,7 +29311,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H998" t="n">
         <v>9678</v>
@@ -29340,7 +29340,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.58696818351746</v>
+        <v>3.58696794509888</v>
       </c>
       <c r="H999" t="n">
         <v>24870</v>
@@ -29369,7 +29369,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.738529920578</v>
+        <v>3.73853015899658</v>
       </c>
       <c r="H1000" t="n">
         <v>56572</v>
@@ -29427,7 +29427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.15953540802002</v>
+        <v>4.15953493118286</v>
       </c>
       <c r="H1002" t="n">
         <v>111881</v>
@@ -29514,7 +29514,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007362365723</v>
+        <v>4.05007410049438</v>
       </c>
       <c r="H1005" t="n">
         <v>28674</v>
@@ -29572,7 +29572,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.99113297462463</v>
+        <v>3.99113321304321</v>
       </c>
       <c r="H1007" t="n">
         <v>22534</v>
@@ -29630,7 +29630,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957123756409</v>
+        <v>3.83957099914551</v>
       </c>
       <c r="H1009" t="n">
         <v>18829</v>
@@ -29659,7 +29659,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.8058910369873</v>
+        <v>3.80589079856873</v>
       </c>
       <c r="H1010" t="n">
         <v>35109</v>
@@ -29717,7 +29717,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.94061279296875</v>
+        <v>3.94061231613159</v>
       </c>
       <c r="H1012" t="n">
         <v>29223</v>
@@ -29775,7 +29775,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429251670837</v>
       </c>
       <c r="H1014" t="n">
         <v>7495</v>
@@ -29804,7 +29804,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641121864319</v>
+        <v>3.85641098022461</v>
       </c>
       <c r="H1015" t="n">
         <v>10368</v>
@@ -29833,7 +29833,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957123756409</v>
+        <v>3.83957099914551</v>
       </c>
       <c r="H1016" t="n">
         <v>27929</v>
@@ -29862,7 +29862,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.86483216285706</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1017" t="n">
         <v>43128</v>
@@ -29920,7 +29920,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.86483216285706</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1019" t="n">
         <v>2641</v>
@@ -29949,7 +29949,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.8058910369873</v>
+        <v>3.80589079856873</v>
       </c>
       <c r="H1020" t="n">
         <v>5690</v>
@@ -29978,7 +29978,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.79747080802917</v>
+        <v>3.7974705696106</v>
       </c>
       <c r="H1021" t="n">
         <v>5537</v>
@@ -30007,7 +30007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.94061279296875</v>
+        <v>3.94061231613159</v>
       </c>
       <c r="H1022" t="n">
         <v>17855</v>
@@ -30036,7 +30036,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.94903254508972</v>
+        <v>3.9490327835083</v>
       </c>
       <c r="H1023" t="n">
         <v>8504</v>
@@ -30065,7 +30065,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429251670837</v>
       </c>
       <c r="H1024" t="n">
         <v>24153</v>
@@ -30094,7 +30094,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849409103394</v>
+        <v>4.05849456787109</v>
       </c>
       <c r="H1025" t="n">
         <v>31402</v>
@@ -30152,7 +30152,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.13427495956421</v>
+        <v>4.13427448272705</v>
       </c>
       <c r="H1027" t="n">
         <v>10172</v>
@@ -30239,7 +30239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.04165458679199</v>
+        <v>4.04165410995483</v>
       </c>
       <c r="H1030" t="n">
         <v>6575</v>
@@ -30297,7 +30297,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.01639318466187</v>
+        <v>4.01639366149902</v>
       </c>
       <c r="H1032" t="n">
         <v>9065</v>
@@ -30326,7 +30326,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.01639318466187</v>
+        <v>4.01639366149902</v>
       </c>
       <c r="H1033" t="n">
         <v>16236</v>
@@ -30413,7 +30413,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849409103394</v>
+        <v>4.05849456787109</v>
       </c>
       <c r="H1036" t="n">
         <v>12669</v>
@@ -30471,7 +30471,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.96587300300598</v>
+        <v>3.9658727645874</v>
       </c>
       <c r="H1038" t="n">
         <v>10631</v>
@@ -30529,7 +30529,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.738529920578</v>
+        <v>3.73853015899658</v>
       </c>
       <c r="H1040" t="n">
         <v>27791</v>
@@ -30558,7 +30558,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.86483216285706</v>
+        <v>3.8648316860199</v>
       </c>
       <c r="H1041" t="n">
         <v>2683</v>
@@ -30674,7 +30674,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.68800973892212</v>
+        <v>3.68800926208496</v>
       </c>
       <c r="H1045" t="n">
         <v>6158</v>
@@ -30732,7 +30732,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642949104309</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1047" t="n">
         <v>3054</v>
@@ -30790,7 +30790,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1049" t="n">
         <v>10041</v>
@@ -30848,7 +30848,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641121864319</v>
+        <v>3.85641098022461</v>
       </c>
       <c r="H1051" t="n">
         <v>38739</v>
@@ -30877,7 +30877,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429275512695</v>
+        <v>3.97429251670837</v>
       </c>
       <c r="H1052" t="n">
         <v>48655</v>
@@ -30906,7 +30906,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009189605713</v>
+        <v>3.89009165763855</v>
       </c>
       <c r="H1053" t="n">
         <v>34250</v>
@@ -30935,7 +30935,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.81431126594543</v>
+        <v>3.81431102752686</v>
       </c>
       <c r="H1054" t="n">
         <v>20837</v>
@@ -30964,7 +30964,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.67116904258728</v>
+        <v>3.67116928100586</v>
       </c>
       <c r="H1055" t="n">
         <v>24782</v>
@@ -31022,7 +31022,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.62906789779663</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1057" t="n">
         <v>6922</v>
@@ -31109,7 +31109,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1060" t="n">
         <v>6645</v>
@@ -31138,7 +31138,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.51118659973145</v>
+        <v>3.51118683815002</v>
       </c>
       <c r="H1061" t="n">
         <v>19148</v>
@@ -31167,7 +31167,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1062" t="n">
         <v>6225</v>
@@ -31196,7 +31196,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H1063" t="n">
         <v>18811</v>
@@ -31283,7 +31283,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1066" t="n">
         <v>38758</v>
@@ -31312,7 +31312,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.58696818351746</v>
+        <v>3.58696794509888</v>
       </c>
       <c r="H1067" t="n">
         <v>9893</v>
@@ -31341,7 +31341,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.6374888420105</v>
+        <v>3.63748860359192</v>
       </c>
       <c r="H1068" t="n">
         <v>988</v>
@@ -31428,7 +31428,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326971054077</v>
+        <v>3.71326947212219</v>
       </c>
       <c r="H1071" t="n">
         <v>5768</v>
@@ -31457,7 +31457,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H1072" t="n">
         <v>30702</v>
@@ -31486,7 +31486,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1073" t="n">
         <v>64565</v>
@@ -31602,7 +31602,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.61222791671753</v>
+        <v>3.61222815513611</v>
       </c>
       <c r="H1077" t="n">
         <v>15491</v>
@@ -31660,7 +31660,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642949104309</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1079" t="n">
         <v>74698</v>
@@ -31747,7 +31747,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326971054077</v>
+        <v>3.71326947212219</v>
       </c>
       <c r="H1082" t="n">
         <v>5435</v>
@@ -31776,7 +31776,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642949104309</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1083" t="n">
         <v>17149</v>
@@ -31863,7 +31863,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.738529920578</v>
+        <v>3.73853015899658</v>
       </c>
       <c r="H1086" t="n">
         <v>12229</v>
@@ -31921,7 +31921,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642949104309</v>
+        <v>3.69642925262451</v>
       </c>
       <c r="H1088" t="n">
         <v>3360</v>
@@ -32037,7 +32037,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.62906789779663</v>
+        <v>3.62906837463379</v>
       </c>
       <c r="H1092" t="n">
         <v>2683</v>
@@ -32066,7 +32066,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.61222791671753</v>
+        <v>3.61222815513611</v>
       </c>
       <c r="H1093" t="n">
         <v>8026</v>
@@ -32095,7 +32095,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.61222791671753</v>
+        <v>3.61222815513611</v>
       </c>
       <c r="H1094" t="n">
         <v>7359</v>
@@ -32124,7 +32124,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56170725822449</v>
+        <v>3.56170749664307</v>
       </c>
       <c r="H1095" t="n">
         <v>1188</v>
@@ -32153,7 +32153,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1096" t="n">
         <v>7457</v>
@@ -32182,7 +32182,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644704818726</v>
+        <v>3.53644680976868</v>
       </c>
       <c r="H1097" t="n">
         <v>8056</v>
@@ -32211,7 +32211,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.50276637077332</v>
+        <v>3.50276660919189</v>
       </c>
       <c r="H1098" t="n">
         <v>4264</v>
@@ -32269,7 +32269,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172553062439</v>
       </c>
       <c r="H1100" t="n">
         <v>6138</v>
@@ -32472,7 +32472,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486727714539</v>
+        <v>3.54486703872681</v>
       </c>
       <c r="H1107" t="n">
         <v>9024</v>
@@ -32501,7 +32501,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960682868958</v>
+        <v>3.51960706710815</v>
       </c>
       <c r="H1108" t="n">
         <v>34399</v>
@@ -32588,7 +32588,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.41856551170349</v>
+        <v>3.41856575012207</v>
       </c>
       <c r="H1111" t="n">
         <v>9772</v>
@@ -32617,7 +32617,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960682868958</v>
+        <v>3.51960706710815</v>
       </c>
       <c r="H1112" t="n">
         <v>4545</v>
@@ -32646,7 +32646,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960682868958</v>
+        <v>3.51960706710815</v>
       </c>
       <c r="H1113" t="n">
         <v>300</v>
@@ -32675,7 +32675,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.40172529220581</v>
+        <v>3.40172553062439</v>
       </c>
       <c r="H1114" t="n">
         <v>9295</v>
@@ -32733,7 +32733,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.49434661865234</v>
+        <v>3.49434685707092</v>
       </c>
       <c r="H1116" t="n">
         <v>1500</v>
@@ -32762,7 +32762,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.47750663757324</v>
+        <v>3.47750639915466</v>
       </c>
       <c r="H1117" t="n">
         <v>1899</v>
@@ -32820,7 +32820,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H1119" t="n">
         <v>13064</v>
@@ -32849,7 +32849,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960682868958</v>
+        <v>3.51960706710815</v>
       </c>
       <c r="H1120" t="n">
         <v>15675</v>
@@ -32878,7 +32878,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.41856551170349</v>
+        <v>3.41856575012207</v>
       </c>
       <c r="H1121" t="n">
         <v>26861</v>
@@ -32965,7 +32965,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.30068445205688</v>
+        <v>3.30068373680115</v>
       </c>
       <c r="H1124" t="n">
         <v>10488</v>
@@ -33023,7 +33023,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.23332285881042</v>
+        <v>3.233323097229</v>
       </c>
       <c r="H1126" t="n">
         <v>3443</v>
@@ -33197,7 +33197,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.84599804878235</v>
+        <v>2.84599828720093</v>
       </c>
       <c r="H1132" t="n">
         <v>8787</v>
@@ -33255,7 +33255,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80389738082886</v>
+        <v>2.80389761924744</v>
       </c>
       <c r="H1134" t="n">
         <v>22070</v>
@@ -33284,7 +33284,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05650067329407</v>
+        <v>3.05650091171265</v>
       </c>
       <c r="H1135" t="n">
         <v>32492</v>
@@ -33313,7 +33313,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1136" t="n">
         <v>66796</v>
@@ -33342,7 +33342,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H1137" t="n">
         <v>80725</v>
@@ -33371,7 +33371,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1138" t="n">
         <v>8053</v>
@@ -33400,7 +33400,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.43540573120117</v>
+        <v>3.43540596961975</v>
       </c>
       <c r="H1139" t="n">
         <v>5055</v>
@@ -33487,7 +33487,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1142" t="n">
         <v>11790</v>
@@ -33516,7 +33516,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1143" t="n">
         <v>1920</v>
@@ -33545,7 +33545,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436417579651</v>
       </c>
       <c r="H1144" t="n">
         <v>5530</v>
@@ -33574,7 +33574,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1145" t="n">
         <v>5210</v>
@@ -33603,7 +33603,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594466209412</v>
+        <v>3.32594418525696</v>
       </c>
       <c r="H1146" t="n">
         <v>2889</v>
@@ -33632,7 +33632,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1147" t="n">
         <v>2050</v>
@@ -33661,7 +33661,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804509162903</v>
+        <v>3.36804461479187</v>
       </c>
       <c r="H1148" t="n">
         <v>1680</v>
@@ -33690,7 +33690,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.3596248626709</v>
+        <v>3.35962462425232</v>
       </c>
       <c r="H1149" t="n">
         <v>4800</v>
@@ -33719,7 +33719,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436465263367</v>
+        <v>3.33436417579651</v>
       </c>
       <c r="H1150" t="n">
         <v>6812</v>
@@ -33748,7 +33748,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.23332285881042</v>
+        <v>3.233323097229</v>
       </c>
       <c r="H1151" t="n">
         <v>3053</v>
@@ -33777,7 +33777,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.23332285881042</v>
+        <v>3.233323097229</v>
       </c>
       <c r="H1152" t="n">
         <v>1252</v>
@@ -33864,7 +33864,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.25016307830811</v>
+        <v>3.25016331672668</v>
       </c>
       <c r="H1155" t="n">
         <v>1166</v>
@@ -33893,7 +33893,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.23332285881042</v>
+        <v>3.233323097229</v>
       </c>
       <c r="H1156" t="n">
         <v>1332</v>
@@ -34357,7 +34357,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1172" t="n">
         <v>767</v>
@@ -34386,7 +34386,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.19964241981506</v>
+        <v>3.19964265823364</v>
       </c>
       <c r="H1173" t="n">
         <v>300</v>
@@ -34415,7 +34415,7 @@
         <v>3.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.15754222869873</v>
+        <v>3.15754199028015</v>
       </c>
       <c r="H1174" t="n">
         <v>2264</v>
@@ -34444,7 +34444,7 @@
         <v>3.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.15754222869873</v>
+        <v>3.15754199028015</v>
       </c>
       <c r="H1175" t="n">
         <v>2738</v>
@@ -34560,7 +34560,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41084361076355</v>
+        <v>3.41084337234497</v>
       </c>
       <c r="H1179" t="n">
         <v>122</v>
@@ -34589,7 +34589,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209794044495</v>
+        <v>3.40209770202637</v>
       </c>
       <c r="H1180" t="n">
         <v>1022</v>
@@ -34705,7 +34705,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1184" t="n">
         <v>1051</v>
@@ -34734,7 +34734,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1185" t="n">
         <v>1629</v>
@@ -34821,7 +34821,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1188" t="n">
         <v>437</v>
@@ -34850,7 +34850,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1189" t="n">
         <v>0</v>
@@ -34879,7 +34879,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1190" t="n">
         <v>0</v>
@@ -34908,7 +34908,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836887359619</v>
+        <v>3.35836863517761</v>
       </c>
       <c r="H1192" t="n">
         <v>2500</v>
@@ -35140,7 +35140,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.27091121673584</v>
+        <v>3.27091145515442</v>
       </c>
       <c r="H1199" t="n">
         <v>1010</v>
@@ -35169,7 +35169,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1200" t="n">
         <v>4965</v>
@@ -35256,7 +35256,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1203" t="n">
         <v>1800</v>
@@ -35285,7 +35285,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1204" t="n">
         <v>9575</v>
@@ -35372,7 +35372,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599614143372</v>
+        <v>3.09599637985229</v>
       </c>
       <c r="H1207" t="n">
         <v>8591</v>
@@ -35488,7 +35488,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1211" t="n">
         <v>2900</v>
@@ -35633,7 +35633,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1216" t="n">
         <v>19487</v>
@@ -35662,7 +35662,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1217" t="n">
         <v>7777</v>
@@ -35865,7 +35865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1224" t="n">
         <v>4675</v>
@@ -36010,7 +36010,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.55375981330872</v>
+        <v>2.55375957489014</v>
       </c>
       <c r="H1229" t="n">
         <v>6115</v>
@@ -36039,7 +36039,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1230" t="n">
         <v>2300</v>
@@ -36126,7 +36126,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1233" t="n">
         <v>7495</v>
@@ -36155,7 +36155,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.91233563423157</v>
+        <v>2.91233539581299</v>
       </c>
       <c r="H1234" t="n">
         <v>12178</v>
@@ -36213,7 +36213,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1236" t="n">
         <v>212</v>
@@ -36358,7 +36358,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1241" t="n">
         <v>1810</v>
@@ -36416,7 +36416,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1243" t="n">
         <v>2327</v>
@@ -36445,7 +36445,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1244" t="n">
         <v>500</v>
@@ -36474,7 +36474,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1245" t="n">
         <v>3906</v>
@@ -36503,7 +36503,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.91233563423157</v>
+        <v>2.91233539581299</v>
       </c>
       <c r="H1246" t="n">
         <v>2163</v>
@@ -36532,7 +36532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1247" t="n">
         <v>10</v>
@@ -36561,7 +36561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1248" t="n">
         <v>93</v>
@@ -36590,7 +36590,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1249" t="n">
         <v>0</v>
@@ -36619,7 +36619,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1250" t="n">
         <v>1625</v>
@@ -36648,7 +36648,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1251" t="n">
         <v>132</v>
@@ -36677,7 +36677,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1252" t="n">
         <v>650</v>
@@ -36706,7 +36706,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1253" t="n">
         <v>0</v>
@@ -36822,7 +36822,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1257" t="n">
         <v>364</v>
@@ -36851,7 +36851,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1258" t="n">
         <v>948</v>
@@ -36880,7 +36880,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1259" t="n">
         <v>0</v>
@@ -36938,7 +36938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1261" t="n">
         <v>3355</v>
@@ -36967,7 +36967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1262" t="n">
         <v>500</v>
@@ -37112,7 +37112,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1267" t="n">
         <v>423</v>
@@ -37315,7 +37315,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1274" t="n">
         <v>3270</v>
@@ -37344,7 +37344,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1275" t="n">
         <v>5827</v>
@@ -37373,7 +37373,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1276" t="n">
         <v>2131</v>
@@ -37402,7 +37402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.58874249458313</v>
+        <v>2.58874273300171</v>
       </c>
       <c r="H1277" t="n">
         <v>5176</v>
@@ -37431,7 +37431,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1278" t="n">
         <v>1108</v>
@@ -37460,7 +37460,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.58874249458313</v>
+        <v>2.58874273300171</v>
       </c>
       <c r="H1279" t="n">
         <v>1252</v>
@@ -37489,7 +37489,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1280" t="n">
         <v>1000</v>
@@ -37518,7 +37518,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1281" t="n">
         <v>3050</v>
@@ -37547,7 +37547,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.57125091552734</v>
+        <v>2.57125115394592</v>
       </c>
       <c r="H1282" t="n">
         <v>1150</v>
@@ -37576,7 +37576,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630191802979</v>
+        <v>2.46630215644836</v>
       </c>
       <c r="H1283" t="n">
         <v>2421</v>
@@ -37634,7 +37634,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1285" t="n">
         <v>1200</v>
@@ -37663,7 +37663,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630191802979</v>
+        <v>2.46630215644836</v>
       </c>
       <c r="H1286" t="n">
         <v>5150</v>
@@ -37692,7 +37692,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.55375981330872</v>
+        <v>2.55375957489014</v>
       </c>
       <c r="H1287" t="n">
         <v>7150</v>
@@ -37837,7 +37837,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867441177368</v>
       </c>
       <c r="H1292" t="n">
         <v>2990</v>
@@ -37895,7 +37895,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.65870881080627</v>
+        <v>2.6587085723877</v>
       </c>
       <c r="H1294" t="n">
         <v>1467</v>
@@ -37953,7 +37953,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.53626847267151</v>
+        <v>2.53626823425293</v>
       </c>
       <c r="H1296" t="n">
         <v>9500</v>
@@ -37982,7 +37982,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.55375981330872</v>
+        <v>2.55375957489014</v>
       </c>
       <c r="H1297" t="n">
         <v>565</v>
@@ -38040,7 +38040,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.51003098487854</v>
+        <v>2.51003074645996</v>
       </c>
       <c r="H1299" t="n">
         <v>1517</v>
@@ -38185,7 +38185,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867441177368</v>
       </c>
       <c r="H1304" t="n">
         <v>4415</v>
@@ -38243,7 +38243,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.8336238861084</v>
+        <v>2.83362364768982</v>
       </c>
       <c r="H1306" t="n">
         <v>8457</v>
@@ -38388,7 +38388,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.85111522674561</v>
+        <v>2.85111498832703</v>
       </c>
       <c r="H1311" t="n">
         <v>750</v>
@@ -38417,7 +38417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.8336238861084</v>
+        <v>2.83362364768982</v>
       </c>
       <c r="H1312" t="n">
         <v>1050</v>
@@ -38533,7 +38533,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.80738663673401</v>
+        <v>2.80738639831543</v>
       </c>
       <c r="H1316" t="n">
         <v>3648</v>
@@ -38620,7 +38620,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1319" t="n">
         <v>10275</v>
@@ -38678,7 +38678,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1321" t="n">
         <v>9850</v>
@@ -38707,7 +38707,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1322" t="n">
         <v>2900</v>
@@ -38794,7 +38794,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1325" t="n">
         <v>6498</v>
@@ -38823,7 +38823,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1326" t="n">
         <v>5429</v>
@@ -38968,7 +38968,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1331" t="n">
         <v>2844</v>
@@ -39084,7 +39084,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1335" t="n">
         <v>3359</v>
@@ -39113,7 +39113,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1336" t="n">
         <v>1510</v>
@@ -39229,7 +39229,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1340" t="n">
         <v>6322</v>
@@ -39258,7 +39258,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1341" t="n">
         <v>11551</v>
@@ -39287,7 +39287,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1342" t="n">
         <v>1846</v>
@@ -39316,7 +39316,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1343" t="n">
         <v>5050</v>
@@ -39345,7 +39345,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1344" t="n">
         <v>940</v>
@@ -39374,7 +39374,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1345" t="n">
         <v>1883</v>
@@ -39519,7 +39519,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1350" t="n">
         <v>5239</v>
@@ -39548,7 +39548,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1351" t="n">
         <v>1532</v>
@@ -39577,7 +39577,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1352" t="n">
         <v>1660</v>
@@ -39722,7 +39722,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1357" t="n">
         <v>855</v>
@@ -39751,7 +39751,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1358" t="n">
         <v>0</v>
@@ -39780,7 +39780,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1359" t="n">
         <v>0</v>
@@ -39838,7 +39838,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.0610134601593</v>
+        <v>3.06101322174072</v>
       </c>
       <c r="H1361" t="n">
         <v>22818</v>
@@ -39896,7 +39896,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599614143372</v>
+        <v>3.09599637985229</v>
       </c>
       <c r="H1363" t="n">
         <v>19094</v>
@@ -39925,7 +39925,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.26216578483582</v>
+        <v>3.26216554641724</v>
       </c>
       <c r="H1364" t="n">
         <v>27870</v>
@@ -39954,7 +39954,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.26216578483582</v>
+        <v>3.26216554641724</v>
       </c>
       <c r="H1365" t="n">
         <v>5010</v>
@@ -40041,7 +40041,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.27091121673584</v>
+        <v>3.27091145515442</v>
       </c>
       <c r="H1368" t="n">
         <v>10067</v>
@@ -40070,7 +40070,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.28840255737305</v>
+        <v>3.28840279579163</v>
       </c>
       <c r="H1369" t="n">
         <v>3567</v>
@@ -40099,7 +40099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.25342011451721</v>
+        <v>3.25341987609863</v>
       </c>
       <c r="H1370" t="n">
         <v>23028</v>
@@ -40215,7 +40215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592853546143</v>
+        <v>3.23592829704285</v>
       </c>
       <c r="H1374" t="n">
         <v>9425</v>
@@ -40302,7 +40302,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592853546143</v>
+        <v>3.23592829704285</v>
       </c>
       <c r="H1377" t="n">
         <v>1800</v>
@@ -40360,7 +40360,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1379" t="n">
         <v>13793</v>
@@ -40418,7 +40418,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1381" t="n">
         <v>3079</v>
@@ -40447,7 +40447,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.08725070953369</v>
+        <v>3.08725047111511</v>
       </c>
       <c r="H1382" t="n">
         <v>2200</v>
@@ -40592,7 +40592,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1387" t="n">
         <v>1000</v>
@@ -40621,7 +40621,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.1134877204895</v>
+        <v>3.11348795890808</v>
       </c>
       <c r="H1388" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1391" t="n">
         <v>442</v>
@@ -40737,7 +40737,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972473144531</v>
+        <v>3.13972496986389</v>
       </c>
       <c r="H1392" t="n">
         <v>950</v>
@@ -40824,7 +40824,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.94731831550598</v>
+        <v>2.94731855392456</v>
       </c>
       <c r="H1395" t="n">
         <v>64822</v>
@@ -40882,7 +40882,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1397" t="n">
         <v>597</v>
@@ -40911,7 +40911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1398" t="n">
         <v>400</v>
@@ -40998,7 +40998,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1401" t="n">
         <v>1744</v>
@@ -41027,7 +41027,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1402" t="n">
         <v>233</v>
@@ -41056,7 +41056,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1403" t="n">
         <v>625</v>
@@ -41085,7 +41085,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1404" t="n">
         <v>5552</v>
@@ -41114,7 +41114,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1405" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1405" t="n">
         <v>4985</v>
@@ -41143,7 +41143,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.91233563423157</v>
+        <v>2.91233539581299</v>
       </c>
       <c r="H1406" t="n">
         <v>1650</v>
@@ -41201,7 +41201,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1408" t="n">
         <v>141</v>
@@ -41346,7 +41346,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1413" t="n">
         <v>1559</v>
@@ -41375,7 +41375,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1414" t="n">
         <v>5019</v>
@@ -41404,7 +41404,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.97355580329895</v>
+        <v>2.97355604171753</v>
       </c>
       <c r="H1415" t="n">
         <v>7825</v>
@@ -41462,7 +41462,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481013298035</v>
+        <v>2.96481037139893</v>
       </c>
       <c r="H1417" t="n">
         <v>2002</v>
@@ -41491,7 +41491,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1418" t="n">
         <v>14401</v>
@@ -41549,7 +41549,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1420" t="n">
         <v>50</v>
@@ -41578,7 +41578,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.99104714393616</v>
+        <v>2.99104738235474</v>
       </c>
       <c r="H1421" t="n">
         <v>0</v>
@@ -41636,7 +41636,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108106613159</v>
+        <v>2.92108130455017</v>
       </c>
       <c r="H1423" t="n">
         <v>3547</v>
@@ -41665,7 +41665,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857264518738</v>
+        <v>2.93857288360596</v>
       </c>
       <c r="H1424" t="n">
         <v>6125</v>
@@ -41723,7 +41723,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.9298267364502</v>
+        <v>2.92982697486877</v>
       </c>
       <c r="H1426" t="n">
         <v>2150</v>
@@ -41868,7 +41868,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.68494606018066</v>
+        <v>2.68494582176208</v>
       </c>
       <c r="H1431" t="n">
         <v>21472</v>
@@ -42013,7 +42013,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867441177368</v>
       </c>
       <c r="H1436" t="n">
         <v>1951</v>
@@ -42042,7 +42042,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1437" t="n">
         <v>3539</v>
@@ -42448,7 +42448,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1451" t="n">
         <v>5102</v>
@@ -42506,7 +42506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1453" t="n">
         <v>8150</v>
@@ -42622,7 +42622,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1457" t="n">
         <v>2600</v>
@@ -42651,7 +42651,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1458" t="n">
         <v>6595</v>
@@ -42680,7 +42680,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1459" t="n">
         <v>4900</v>
@@ -42709,7 +42709,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1460" t="n">
         <v>0</v>
@@ -42738,7 +42738,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1461" t="n">
         <v>957</v>
@@ -42796,7 +42796,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1463" t="n">
         <v>3565</v>
@@ -42854,7 +42854,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1465" t="n">
         <v>1000</v>
@@ -42912,7 +42912,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1467" t="n">
         <v>3295</v>
@@ -42941,7 +42941,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1468" t="n">
         <v>2753</v>
@@ -42970,7 +42970,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1469" t="n">
         <v>7000</v>
@@ -43057,7 +43057,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1472" t="n">
         <v>1042</v>
@@ -43144,7 +43144,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1475" t="n">
         <v>8292</v>
@@ -43173,7 +43173,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1476" t="n">
         <v>7332</v>
@@ -43231,7 +43231,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1478" t="n">
         <v>252613</v>
@@ -43376,7 +43376,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1483" t="n">
         <v>18307</v>
@@ -43434,7 +43434,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1485" t="n">
         <v>11067</v>
@@ -43898,7 +43898,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1501" t="n">
         <v>16390</v>
@@ -44188,7 +44188,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1511" t="n">
         <v>200</v>
@@ -44275,7 +44275,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1514" t="n">
         <v>4539</v>
@@ -44304,7 +44304,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1515" t="n">
         <v>11432</v>
@@ -44333,7 +44333,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1516" t="n">
         <v>12387</v>
@@ -44478,7 +44478,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1521" t="n">
         <v>1669</v>
@@ -44594,7 +44594,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1525" t="n">
         <v>4558</v>
@@ -44623,7 +44623,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1526" t="n">
         <v>1820</v>
@@ -44652,7 +44652,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1527" t="n">
         <v>150</v>
@@ -45029,7 +45029,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1540" t="n">
         <v>50</v>
@@ -45348,7 +45348,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1551" t="n">
         <v>10350</v>
@@ -45377,7 +45377,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1552" t="n">
         <v>3808</v>
@@ -45406,7 +45406,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1553" t="n">
         <v>50</v>
@@ -45435,7 +45435,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1554" t="n">
         <v>18555</v>
@@ -45464,7 +45464,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1555" t="n">
         <v>1118</v>
@@ -45493,7 +45493,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1556" t="n">
         <v>1873</v>
@@ -45609,7 +45609,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1560" t="n">
         <v>2650</v>
@@ -45667,7 +45667,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1562" t="n">
         <v>6000</v>
@@ -45696,7 +45696,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1563" t="n">
         <v>1789</v>
@@ -45725,7 +45725,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1564" t="n">
         <v>2600</v>
@@ -45754,7 +45754,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1565" t="n">
         <v>8722</v>
@@ -45783,7 +45783,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1566" t="n">
         <v>6062</v>
@@ -45812,7 +45812,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1567" t="n">
         <v>25683</v>
@@ -45870,7 +45870,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1569" t="n">
         <v>14198</v>
@@ -45899,7 +45899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1570" t="n">
         <v>5400</v>
@@ -45986,7 +45986,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1573" t="n">
         <v>3411</v>
@@ -46015,7 +46015,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1574" t="n">
         <v>10144</v>
@@ -46073,7 +46073,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1576" t="n">
         <v>6055</v>
@@ -46189,7 +46189,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1580" t="n">
         <v>8200</v>
@@ -46247,7 +46247,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1582" t="n">
         <v>21214</v>
@@ -46595,7 +46595,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1594" t="n">
         <v>24870</v>
@@ -46624,7 +46624,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1595" t="n">
         <v>18412</v>
@@ -46769,7 +46769,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1600" t="n">
         <v>4085</v>
@@ -46972,7 +46972,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1607" t="n">
         <v>1951</v>
@@ -47030,7 +47030,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1609" t="n">
         <v>2751</v>
@@ -47059,7 +47059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1610" t="n">
         <v>1618</v>
@@ -47175,7 +47175,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1614" t="n">
         <v>10351</v>
@@ -47320,7 +47320,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1619" t="n">
         <v>1735</v>
@@ -47465,7 +47465,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.90265083312988</v>
+        <v>2.9026505947113</v>
       </c>
       <c r="H1624" t="n">
         <v>1361</v>
@@ -47610,7 +47610,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1629" t="n">
         <v>7874</v>
@@ -47784,7 +47784,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1635" t="n">
         <v>10171</v>
@@ -47813,7 +47813,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1636" t="n">
         <v>6601</v>
@@ -47871,7 +47871,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1638" t="n">
         <v>2344</v>
@@ -47900,7 +47900,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1639" t="n">
         <v>4700</v>
@@ -47958,7 +47958,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1641" t="n">
         <v>1566</v>
@@ -47987,7 +47987,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1642" t="n">
         <v>9227</v>
@@ -48016,7 +48016,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1643" t="n">
         <v>7310</v>
@@ -48045,7 +48045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1644" t="n">
         <v>1000</v>
@@ -48132,7 +48132,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1647" t="n">
         <v>6041</v>
@@ -48161,7 +48161,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1648" t="n">
         <v>1964</v>
@@ -48248,7 +48248,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1651" t="n">
         <v>200</v>
@@ -48364,7 +48364,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1655" t="n">
         <v>5050</v>
@@ -48683,7 +48683,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1666" t="n">
         <v>2600</v>
@@ -48944,7 +48944,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975895881653</v>
+        <v>2.49975919723511</v>
       </c>
       <c r="H1675" t="n">
         <v>6817</v>
@@ -48973,7 +48973,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1676" t="n">
         <v>5212</v>
@@ -49060,7 +49060,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1679" t="n">
         <v>5506</v>
@@ -49263,7 +49263,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1686" t="n">
         <v>19737</v>
@@ -49292,7 +49292,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1687" t="n">
         <v>2100</v>
@@ -49350,7 +49350,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1689" t="n">
         <v>10000</v>
@@ -49437,7 +49437,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1692" t="n">
         <v>7400</v>
@@ -49669,7 +49669,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1700" t="n">
         <v>17055</v>
@@ -49727,7 +49727,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1702" t="n">
         <v>23657</v>
@@ -49756,7 +49756,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1703" t="n">
         <v>6507</v>
@@ -49814,7 +49814,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1705" t="n">
         <v>39</v>
@@ -49843,7 +49843,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1706" t="n">
         <v>6965</v>
@@ -49872,7 +49872,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1707" t="n">
         <v>14247</v>
@@ -50133,7 +50133,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1716" t="n">
         <v>12714</v>
@@ -50162,7 +50162,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1717" t="n">
         <v>8150</v>
@@ -50539,7 +50539,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.04915642738342</v>
+        <v>3.049156665802</v>
       </c>
       <c r="H1730" t="n">
         <v>2212</v>
@@ -50684,7 +50684,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1735" t="n">
         <v>1964</v>
@@ -50713,7 +50713,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1736" t="n">
         <v>5543</v>
@@ -50800,7 +50800,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759057998657</v>
+        <v>2.95759034156799</v>
       </c>
       <c r="H1739" t="n">
         <v>5500</v>
@@ -50829,7 +50829,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590351104736</v>
+        <v>2.97590374946594</v>
       </c>
       <c r="H1740" t="n">
         <v>2956</v>
@@ -51902,7 +51902,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1777" t="n">
         <v>500</v>
@@ -52076,7 +52076,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096376419067</v>
+        <v>2.92096400260925</v>
       </c>
       <c r="H1783" t="n">
         <v>695</v>
@@ -52656,7 +52656,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1803" t="n">
         <v>1000</v>
@@ -52743,7 +52743,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445793151855</v>
+        <v>2.77445769309998</v>
       </c>
       <c r="H1806" t="n">
         <v>1500</v>
@@ -52801,7 +52801,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1808" t="n">
         <v>708</v>
@@ -52830,7 +52830,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939767837524</v>
+        <v>2.82939743995667</v>
       </c>
       <c r="H1809" t="n">
         <v>0</v>
@@ -53033,7 +53033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1816" t="n">
         <v>4470</v>
@@ -53062,7 +53062,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1817" t="n">
         <v>4905</v>
@@ -53091,7 +53091,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1818" t="n">
         <v>5181</v>
@@ -53149,7 +53149,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1820" t="n">
         <v>5370</v>
@@ -53178,7 +53178,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1821" t="n">
         <v>0</v>
@@ -53207,7 +53207,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1822" t="n">
         <v>0</v>
@@ -53294,7 +53294,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1825" t="n">
         <v>2500</v>
@@ -53352,7 +53352,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53468,7 +53468,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1831" t="n">
         <v>2764</v>
@@ -53497,7 +53497,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1832" t="n">
         <v>7985</v>
@@ -53526,7 +53526,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.65542197227478</v>
+        <v>2.6554217338562</v>
       </c>
       <c r="H1833" t="n">
         <v>13237</v>
@@ -53642,7 +53642,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1837" t="n">
         <v>3566</v>
@@ -53671,7 +53671,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1838" t="n">
         <v>4827</v>
@@ -53729,7 +53729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1840" t="n">
         <v>4580</v>
@@ -53758,7 +53758,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1841" t="n">
         <v>1250</v>
@@ -53874,7 +53874,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1845" t="n">
         <v>4344</v>
@@ -53961,7 +53961,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1848" t="n">
         <v>1420</v>
@@ -53990,7 +53990,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1849" t="n">
         <v>2250</v>
@@ -54077,7 +54077,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626526832581</v>
+        <v>2.64626502990723</v>
       </c>
       <c r="H1852" t="n">
         <v>9811</v>
@@ -54251,7 +54251,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1858" t="n">
         <v>32665</v>
@@ -54309,7 +54309,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1860" t="n">
         <v>5060</v>
@@ -54570,7 +54570,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638553619385</v>
+        <v>2.53638577461243</v>
       </c>
       <c r="H1869" t="n">
         <v>995</v>
@@ -54686,7 +54686,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.55469870567322</v>
+        <v>2.5546989440918</v>
       </c>
       <c r="H1873" t="n">
         <v>1966</v>
@@ -54802,7 +54802,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1877" t="n">
         <v>84</v>
@@ -54831,7 +54831,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1878" t="n">
         <v>856</v>
@@ -54947,7 +54947,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1882" t="n">
         <v>4480</v>
@@ -54976,7 +54976,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1883" t="n">
         <v>0</v>
@@ -55063,7 +55063,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1886" t="n">
         <v>1550</v>
@@ -55121,7 +55121,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1888" t="n">
         <v>2000</v>
@@ -55150,7 +55150,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963869094849</v>
+        <v>2.60963845252991</v>
       </c>
       <c r="H1889" t="n">
         <v>1694</v>
@@ -55208,7 +55208,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1891" t="n">
         <v>5040</v>
@@ -55266,7 +55266,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1893" t="n">
         <v>255</v>
@@ -55295,7 +55295,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1894" t="n">
         <v>2350</v>
@@ -55324,7 +55324,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1895" t="n">
         <v>3524</v>
@@ -55353,7 +55353,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1896" t="n">
         <v>7241</v>
@@ -55382,7 +55382,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1897" t="n">
         <v>0</v>
@@ -55411,7 +55411,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132528305054</v>
+        <v>2.59132504463196</v>
       </c>
       <c r="H1898" t="n">
         <v>9000</v>
@@ -55469,7 +55469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1900" t="n">
         <v>4150</v>
@@ -55614,7 +55614,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277086257935</v>
+        <v>2.79277110099792</v>
       </c>
       <c r="H1905" t="n">
         <v>4525</v>
@@ -55643,7 +55643,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1906" t="n">
         <v>4000</v>
@@ -55759,7 +55759,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867488861084</v>
+        <v>2.72867465019226</v>
       </c>
       <c r="H1910" t="n">
         <v>1000</v>
@@ -55875,7 +55875,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30747008323669</v>
+        <v>2.30746984481812</v>
       </c>
       <c r="H1914" t="n">
         <v>52544</v>
@@ -55962,7 +55962,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.5089156627655</v>
+        <v>2.50891590118408</v>
       </c>
       <c r="H1917" t="n">
         <v>13522</v>
@@ -55991,7 +55991,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.5089156627655</v>
+        <v>2.50891590118408</v>
       </c>
       <c r="H1918" t="n">
         <v>5361</v>
@@ -56426,7 +56426,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1933" t="n">
         <v>1893</v>
@@ -56455,7 +56455,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048198699951</v>
+        <v>2.60048174858093</v>
       </c>
       <c r="H1934" t="n">
         <v>1786</v>
@@ -56542,7 +56542,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1937" t="n">
         <v>7603</v>
@@ -56571,7 +56571,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361463546753</v>
+        <v>2.78361439704895</v>
       </c>
       <c r="H1938" t="n">
         <v>3411</v>
@@ -67220,6 +67220,35 @@
         <v>2172</v>
       </c>
       <c r="I2305" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2306" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2306" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="D2306" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="G2306" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="H2306" t="n">
+        <v>4119</v>
+      </c>
+      <c r="I2306" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417574882507</v>
+        <v>2.91417598724365</v>
       </c>
       <c r="H2" t="n">
         <v>507500</v>
@@ -456,7 +456,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85802340507507</v>
+        <v>2.85802364349365</v>
       </c>
       <c r="H3" t="n">
         <v>168500</v>
@@ -485,7 +485,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459310531616</v>
+        <v>2.78459334373474</v>
       </c>
       <c r="H4" t="n">
         <v>65500</v>
@@ -514,7 +514,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.87242150306702</v>
+        <v>2.87242126464844</v>
       </c>
       <c r="H5" t="n">
         <v>117500</v>
@@ -543,7 +543,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86522269248962</v>
+        <v>2.8652229309082</v>
       </c>
       <c r="H6" t="n">
         <v>89500</v>
@@ -572,7 +572,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930611610413</v>
+        <v>2.83930587768555</v>
       </c>
       <c r="H7" t="n">
         <v>35500</v>
@@ -601,7 +601,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85082411766052</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H8" t="n">
         <v>34500</v>
@@ -630,7 +630,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85514402389526</v>
+        <v>2.85514378547668</v>
       </c>
       <c r="H9" t="n">
         <v>36500</v>
@@ -659,7 +659,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82922720909119</v>
+        <v>2.82922744750977</v>
       </c>
       <c r="H10" t="n">
         <v>7500</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H11" t="n">
         <v>24000</v>
@@ -717,7 +717,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.87242150306702</v>
+        <v>2.87242126464844</v>
       </c>
       <c r="H12" t="n">
         <v>41000</v>
@@ -746,7 +746,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87098145484924</v>
+        <v>2.8709819316864</v>
       </c>
       <c r="H13" t="n">
         <v>2000</v>
@@ -775,7 +775,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818121910095</v>
       </c>
       <c r="H14" t="n">
         <v>11000</v>
@@ -833,7 +833,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94585204124451</v>
+        <v>2.94585180282593</v>
       </c>
       <c r="H16" t="n">
         <v>41500</v>
@@ -862,7 +862,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9487316608429</v>
+        <v>2.94873189926147</v>
       </c>
       <c r="H17" t="n">
         <v>16000</v>
@@ -891,7 +891,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009256362915</v>
+        <v>2.94009280204773</v>
       </c>
       <c r="H18" t="n">
         <v>3000</v>
@@ -920,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H19" t="n">
         <v>13500</v>
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86522269248962</v>
+        <v>2.8652229309082</v>
       </c>
       <c r="H21" t="n">
         <v>7500</v>
@@ -1007,7 +1007,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H22" t="n">
         <v>19000</v>
@@ -1036,7 +1036,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G23" t="n">
-        <v>2.90697693824768</v>
+        <v>2.90697717666626</v>
       </c>
       <c r="H23" t="n">
         <v>43500</v>
@@ -1065,7 +1065,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.90121793746948</v>
+        <v>2.9012176990509</v>
       </c>
       <c r="H24" t="n">
         <v>38500</v>
@@ -1094,7 +1094,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91561603546143</v>
+        <v>2.91561579704285</v>
       </c>
       <c r="H25" t="n">
         <v>12500</v>
@@ -1123,7 +1123,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.90841698646545</v>
+        <v>2.90841674804688</v>
       </c>
       <c r="H26" t="n">
         <v>9000</v>
@@ -1181,7 +1181,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113926887512</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H28" t="n">
         <v>6000</v>
@@ -1210,7 +1210,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.91561603546143</v>
+        <v>2.91561579704285</v>
       </c>
       <c r="H29" t="n">
         <v>8500</v>
@@ -1297,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H32" t="n">
         <v>6500</v>
@@ -1326,7 +1326,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113926887512</v>
+        <v>2.89113903045654</v>
       </c>
       <c r="H33" t="n">
         <v>15500</v>
@@ -1355,7 +1355,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85226392745972</v>
+        <v>2.8522641658783</v>
       </c>
       <c r="H34" t="n">
         <v>3000</v>
@@ -1413,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H36" t="n">
         <v>2500</v>
@@ -1442,7 +1442,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>2.85082411766052</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1471,7 +1471,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.82922720909119</v>
+        <v>2.82922744750977</v>
       </c>
       <c r="H38" t="n">
         <v>1500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H39" t="n">
         <v>5500</v>
@@ -1529,7 +1529,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G40" t="n">
-        <v>2.80331063270569</v>
+        <v>2.80331087112427</v>
       </c>
       <c r="H40" t="n">
         <v>1000</v>
@@ -1558,7 +1558,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H41" t="n">
         <v>30500</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H42" t="n">
         <v>9000</v>
@@ -1616,7 +1616,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1674,7 +1674,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338906288147</v>
+        <v>2.81338930130005</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818074226379</v>
+        <v>2.87818121910095</v>
       </c>
       <c r="H46" t="n">
         <v>500</v>
@@ -1732,7 +1732,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81050992012024</v>
+        <v>2.81050968170166</v>
       </c>
       <c r="H47" t="n">
         <v>1500</v>
@@ -1761,7 +1761,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H48" t="n">
         <v>1500</v>
@@ -1790,7 +1790,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H49" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G51" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G53" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G54" t="n">
-        <v>2.8047502040863</v>
+        <v>2.80475068092346</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482911109924</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H55" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81770873069763</v>
+        <v>2.81770896911621</v>
       </c>
       <c r="H56" t="n">
         <v>15500</v>
@@ -2109,7 +2109,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G60" t="n">
-        <v>2.67948722839355</v>
+        <v>2.6794867515564</v>
       </c>
       <c r="H60" t="n">
         <v>12500</v>
@@ -2138,7 +2138,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2283,7 +2283,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532489776611</v>
+        <v>2.69532465934753</v>
       </c>
       <c r="H66" t="n">
         <v>11000</v>
@@ -2341,7 +2341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163457870483</v>
       </c>
       <c r="H68" t="n">
         <v>3000</v>
@@ -2370,7 +2370,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163457870483</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163457870483</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>2.79323220252991</v>
+        <v>2.79323196411133</v>
       </c>
       <c r="H71" t="n">
         <v>3000</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964408874512</v>
       </c>
       <c r="H74" t="n">
         <v>11500</v>
@@ -2544,7 +2544,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964408874512</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964408874512</v>
       </c>
       <c r="H76" t="n">
         <v>1000</v>
@@ -2602,7 +2602,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964408874512</v>
       </c>
       <c r="H77" t="n">
         <v>7500</v>
@@ -2631,7 +2631,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6434919834137</v>
+        <v>2.64349174499512</v>
       </c>
       <c r="H78" t="n">
         <v>7500</v>
@@ -2660,7 +2660,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G79" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980142593384</v>
       </c>
       <c r="H79" t="n">
         <v>14500</v>
@@ -2689,7 +2689,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G80" t="n">
-        <v>2.719801902771</v>
+        <v>2.71980142593384</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G81" t="n">
-        <v>2.65069055557251</v>
+        <v>2.65069079399109</v>
       </c>
       <c r="H81" t="n">
         <v>5000</v>
@@ -2747,7 +2747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G82" t="n">
-        <v>2.66364932060242</v>
+        <v>2.66364908218384</v>
       </c>
       <c r="H82" t="n">
         <v>5500</v>
@@ -2776,7 +2776,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.67804718017578</v>
+        <v>2.67804741859436</v>
       </c>
       <c r="H83" t="n">
         <v>4000</v>
@@ -2805,7 +2805,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524646759033</v>
+        <v>2.68524622917175</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2834,7 +2834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.6924455165863</v>
+        <v>2.69244527816772</v>
       </c>
       <c r="H85" t="n">
         <v>500</v>
@@ -2863,7 +2863,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.6996443271637</v>
+        <v>2.69964408874512</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2892,7 +2892,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.66364932060242</v>
+        <v>2.66364908218384</v>
       </c>
       <c r="H87" t="n">
         <v>6500</v>
@@ -2921,7 +2921,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.6924455165863</v>
+        <v>2.69244527816772</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -2950,7 +2950,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59885764122009</v>
+        <v>2.59885740280151</v>
       </c>
       <c r="H89" t="n">
         <v>5000</v>
@@ -2979,7 +2979,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>2.59885764122009</v>
+        <v>2.59885740280151</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55566334724426</v>
+        <v>2.55566310882568</v>
       </c>
       <c r="H91" t="n">
         <v>6500</v>
@@ -3037,7 +3037,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H92" t="n">
         <v>4500</v>
@@ -3066,7 +3066,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H93" t="n">
         <v>10000</v>
@@ -3095,7 +3095,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.44767785072327</v>
+        <v>2.44767761230469</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3124,7 +3124,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>2.47647380828857</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H95" t="n">
         <v>1000</v>
@@ -3153,7 +3153,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>2.47647380828857</v>
+        <v>2.47647404670715</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44767785072327</v>
+        <v>2.44767761230469</v>
       </c>
       <c r="H97" t="n">
         <v>4500</v>
@@ -3240,7 +3240,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56286215782166</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H99" t="n">
         <v>23000</v>
@@ -3269,7 +3269,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59165835380554</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3298,7 +3298,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.60605645179749</v>
+        <v>2.60605669021606</v>
       </c>
       <c r="H101" t="n">
         <v>500</v>
@@ -3327,7 +3327,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>2.74283838272095</v>
+        <v>2.74283862113953</v>
       </c>
       <c r="H102" t="n">
         <v>21000</v>
@@ -3385,7 +3385,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H104" t="n">
         <v>10500</v>
@@ -3414,7 +3414,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084813117981</v>
+        <v>2.67084789276123</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G109" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H109" t="n">
         <v>4000</v>
@@ -3559,7 +3559,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G111" t="n">
-        <v>2.63485312461853</v>
+        <v>2.63485288619995</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.55566334724426</v>
+        <v>2.55566310882568</v>
       </c>
       <c r="H112" t="n">
         <v>24000</v>
@@ -3646,7 +3646,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H113" t="n">
         <v>1500</v>
@@ -3675,7 +3675,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G114" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3704,7 +3704,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006168365479</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H116" t="n">
         <v>11000</v>
@@ -3762,7 +3762,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006168365479</v>
+        <v>2.57006144523621</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.59165835380554</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.59165835380554</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.59165835380554</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G123" t="n">
-        <v>2.52686715126038</v>
+        <v>2.5268669128418</v>
       </c>
       <c r="H123" t="n">
         <v>8000</v>
@@ -3965,7 +3965,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>2.56286215782166</v>
+        <v>2.56286239624023</v>
       </c>
       <c r="H124" t="n">
         <v>3500</v>
@@ -3994,7 +3994,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59165835380554</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H125" t="n">
         <v>5500</v>
@@ -4023,7 +4023,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.59165835380554</v>
+        <v>2.5916588306427</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G128" t="n">
-        <v>2.6420521736145</v>
+        <v>2.64205169677734</v>
       </c>
       <c r="H128" t="n">
         <v>5000</v>
@@ -4110,7 +4110,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.6420521736145</v>
+        <v>2.64205169677734</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.62765383720398</v>
+        <v>2.6276535987854</v>
       </c>
       <c r="H130" t="n">
         <v>2500</v>
@@ -4197,7 +4197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H132" t="n">
         <v>31000</v>
@@ -4226,7 +4226,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77163481712341</v>
+        <v>2.77163457870483</v>
       </c>
       <c r="H133" t="n">
         <v>45500</v>
@@ -4255,7 +4255,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H134" t="n">
         <v>17500</v>
@@ -4284,7 +4284,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4632,7 +4632,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H147" t="n">
         <v>15500</v>
@@ -4661,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -4690,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>2.87962031364441</v>
+        <v>2.87962055206299</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H154" t="n">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.80763030052185</v>
+        <v>2.80763006210327</v>
       </c>
       <c r="H158" t="n">
         <v>1000</v>
@@ -4980,7 +4980,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.82202816009521</v>
+        <v>2.82202839851379</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H166" t="n">
         <v>20000</v>
@@ -5212,7 +5212,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>2.85082411766052</v>
+        <v>2.8508243560791</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362530708313</v>
+        <v>2.84362554550171</v>
       </c>
       <c r="H168" t="n">
         <v>8500</v>
@@ -5328,7 +5328,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G171" t="n">
-        <v>2.60117435455322</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H171" t="n">
         <v>17000</v>
@@ -5357,7 +5357,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H172" t="n">
         <v>28500</v>
@@ -5386,7 +5386,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H173" t="n">
         <v>500</v>
@@ -5415,7 +5415,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H174" t="n">
         <v>5000</v>
@@ -5560,7 +5560,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G179" t="n">
-        <v>2.7136173248291</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5705,7 +5705,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>2.63865542411804</v>
+        <v>2.63865566253662</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66114401817322</v>
+        <v>2.66114377975464</v>
       </c>
       <c r="H185" t="n">
         <v>500</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H188" t="n">
         <v>5500</v>
@@ -6343,7 +6343,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G206" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6372,7 +6372,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H207" t="n">
         <v>2500</v>
@@ -6401,7 +6401,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G211" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H211" t="n">
         <v>9500</v>
@@ -6575,7 +6575,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H214" t="n">
         <v>13500</v>
@@ -6662,7 +6662,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.75109791755676</v>
+        <v>2.75109815597534</v>
       </c>
       <c r="H217" t="n">
         <v>7000</v>
@@ -6691,7 +6691,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G218" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H218" t="n">
         <v>10000</v>
@@ -6720,7 +6720,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>2.7136173248291</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H219" t="n">
         <v>61000</v>
@@ -6749,7 +6749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H220" t="n">
         <v>40500</v>
@@ -6778,7 +6778,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H221" t="n">
         <v>500</v>
@@ -6865,7 +6865,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G224" t="n">
-        <v>2.63115906715393</v>
+        <v>2.63115930557251</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6894,7 +6894,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618235588074</v>
+        <v>2.58618211746216</v>
       </c>
       <c r="H225" t="n">
         <v>6500</v>
@@ -7010,7 +7010,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G229" t="n">
-        <v>2.60117435455322</v>
+        <v>2.6011745929718</v>
       </c>
       <c r="H229" t="n">
         <v>500</v>
@@ -7039,7 +7039,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.66114401817322</v>
+        <v>2.66114377975464</v>
       </c>
       <c r="H230" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G231" t="n">
-        <v>2.7136173248291</v>
+        <v>2.71361708641052</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7184,7 +7184,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.73610591888428</v>
+        <v>2.7361056804657</v>
       </c>
       <c r="H236" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.88602948188782</v>
+        <v>2.88602900505066</v>
       </c>
       <c r="H238" t="n">
         <v>500</v>
@@ -7300,7 +7300,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H239" t="n">
         <v>4000</v>
@@ -7329,7 +7329,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H240" t="n">
         <v>1500</v>
@@ -7358,7 +7358,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G241" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>2.72111320495605</v>
+        <v>2.72111344337463</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H254" t="n">
         <v>1000</v>
@@ -7764,7 +7764,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G255" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H257" t="n">
         <v>4500</v>
@@ -7851,7 +7851,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G258" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H258" t="n">
         <v>16500</v>
@@ -7880,7 +7880,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H259" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>2.84105229377747</v>
+        <v>2.84105205535889</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120492935181</v>
       </c>
       <c r="H264" t="n">
         <v>19500</v>
@@ -8054,7 +8054,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G265" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120492935181</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G266" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120492935181</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G270" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H276" t="n">
         <v>4000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.25635004043579</v>
+        <v>2.25635027885437</v>
       </c>
       <c r="H277" t="n">
         <v>5000</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883887290955</v>
+        <v>2.27883863449097</v>
       </c>
       <c r="H280" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639590263367</v>
+        <v>2.16639614105225</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8576,7 +8576,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>2.24135780334473</v>
+        <v>2.24135804176331</v>
       </c>
       <c r="H283" t="n">
         <v>70000</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.15140342712402</v>
+        <v>2.1514036655426</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639590263367</v>
+        <v>2.16639614105225</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.18138861656189</v>
+        <v>2.18138837814331</v>
       </c>
       <c r="H288" t="n">
         <v>8000</v>
@@ -8750,7 +8750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G289" t="n">
-        <v>2.18138861656189</v>
+        <v>2.18138837814331</v>
       </c>
       <c r="H289" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G295" t="n">
-        <v>1.99398398399353</v>
+        <v>1.99398410320282</v>
       </c>
       <c r="H295" t="n">
         <v>16500</v>
@@ -8953,7 +8953,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G296" t="n">
-        <v>2.06894564628601</v>
+        <v>2.06894588470459</v>
       </c>
       <c r="H296" t="n">
         <v>3500</v>
@@ -8982,7 +8982,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03146457672119</v>
+        <v>2.03146481513977</v>
       </c>
       <c r="H297" t="n">
         <v>14000</v>
@@ -9011,7 +9011,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644152641296</v>
+        <v>2.07644200325012</v>
       </c>
       <c r="H298" t="n">
         <v>7500</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.09893012046814</v>
+        <v>2.09893035888672</v>
       </c>
       <c r="H299" t="n">
         <v>9500</v>
@@ -9069,7 +9069,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.09893012046814</v>
+        <v>2.09893035888672</v>
       </c>
       <c r="H300" t="n">
         <v>1500</v>
@@ -9098,7 +9098,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.09893012046814</v>
+        <v>2.09893035888672</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390730857849</v>
+        <v>2.14390754699707</v>
       </c>
       <c r="H303" t="n">
         <v>2500</v>
@@ -9359,7 +9359,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H310" t="n">
         <v>18500</v>
@@ -9388,7 +9388,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625831604004</v>
+        <v>2.43625855445862</v>
       </c>
       <c r="H311" t="n">
         <v>27000</v>
@@ -9446,7 +9446,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H313" t="n">
         <v>4500</v>
@@ -9504,7 +9504,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H315" t="n">
         <v>3000</v>
@@ -9533,7 +9533,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H316" t="n">
         <v>10500</v>
@@ -9562,7 +9562,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H317" t="n">
         <v>10500</v>
@@ -9591,7 +9591,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H318" t="n">
         <v>5000</v>
@@ -9620,7 +9620,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35380077362061</v>
+        <v>2.35380053520203</v>
       </c>
       <c r="H319" t="n">
         <v>10500</v>
@@ -9649,7 +9649,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.46624326705933</v>
+        <v>2.46624350547791</v>
       </c>
       <c r="H320" t="n">
         <v>16000</v>
@@ -9678,7 +9678,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46624326705933</v>
+        <v>2.46624350547791</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G322" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H322" t="n">
         <v>500</v>
@@ -9736,7 +9736,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H325" t="n">
         <v>1000</v>
@@ -9823,7 +9823,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G327" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G328" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G330" t="n">
-        <v>2.45874691009521</v>
+        <v>2.45874714851379</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -9997,7 +9997,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H336" t="n">
         <v>1000</v>
@@ -10142,7 +10142,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H338" t="n">
         <v>8000</v>
@@ -10200,7 +10200,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.39877772331238</v>
+        <v>2.3987774848938</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H348" t="n">
         <v>4000</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.21137285232544</v>
+        <v>2.2113733291626</v>
       </c>
       <c r="H351" t="n">
         <v>94500</v>
@@ -10751,7 +10751,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10780,7 +10780,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32381558418274</v>
+        <v>2.32381582260132</v>
       </c>
       <c r="H359" t="n">
         <v>2500</v>
@@ -10867,7 +10867,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.53370904922485</v>
+        <v>2.53370881080627</v>
       </c>
       <c r="H362" t="n">
         <v>5000</v>
@@ -10896,7 +10896,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120492935181</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>2.56369376182556</v>
+        <v>2.56369400024414</v>
       </c>
       <c r="H364" t="n">
         <v>500</v>
@@ -10954,7 +10954,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56369376182556</v>
+        <v>2.56369400024414</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G366" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120492935181</v>
       </c>
       <c r="H366" t="n">
         <v>500</v>
@@ -11012,7 +11012,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G367" t="n">
-        <v>2.54120564460754</v>
+        <v>2.54120492935181</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>2.48123550415039</v>
+        <v>2.48123574256897</v>
       </c>
       <c r="H368" t="n">
         <v>16500</v>
@@ -11070,7 +11070,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H369" t="n">
         <v>1500</v>
@@ -11099,7 +11099,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G371" t="n">
-        <v>2.5487015247345</v>
+        <v>2.54870128631592</v>
       </c>
       <c r="H371" t="n">
         <v>500</v>
@@ -11157,7 +11157,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>2.5487015247345</v>
+        <v>2.54870128631592</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11186,7 +11186,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>2.59367847442627</v>
+        <v>2.59367871284485</v>
       </c>
       <c r="H373" t="n">
         <v>20000</v>
@@ -11273,7 +11273,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57868599891663</v>
+        <v>2.57868623733521</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11302,7 +11302,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.66114401817322</v>
+        <v>2.66114377975464</v>
       </c>
       <c r="H377" t="n">
         <v>12500</v>
@@ -11331,7 +11331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>2.66864037513733</v>
+        <v>2.66864013671875</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G379" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H379" t="n">
         <v>19000</v>
@@ -11418,7 +11418,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85604429244995</v>
+        <v>2.85604476928711</v>
       </c>
       <c r="H381" t="n">
         <v>73500</v>
@@ -11447,7 +11447,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>2.82605981826782</v>
+        <v>2.8260600566864</v>
       </c>
       <c r="H382" t="n">
         <v>15000</v>
@@ -11476,7 +11476,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G383" t="n">
-        <v>2.85604429244995</v>
+        <v>2.85604476928711</v>
       </c>
       <c r="H383" t="n">
         <v>32500</v>
@@ -11505,7 +11505,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85604429244995</v>
+        <v>2.85604476928711</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75859451293945</v>
+        <v>2.75859427452087</v>
       </c>
       <c r="H386" t="n">
         <v>3000</v>
@@ -11621,7 +11621,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>2.81856393814087</v>
+        <v>2.81856417655945</v>
       </c>
       <c r="H388" t="n">
         <v>48000</v>
@@ -11679,7 +11679,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G390" t="n">
-        <v>2.86354088783264</v>
+        <v>2.86354064941406</v>
       </c>
       <c r="H390" t="n">
         <v>5500</v>
@@ -11708,7 +11708,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G391" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H391" t="n">
         <v>1500</v>
@@ -11737,7 +11737,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H392" t="n">
         <v>8000</v>
@@ -11766,7 +11766,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11795,7 +11795,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93850255012512</v>
+        <v>2.9385027885437</v>
       </c>
       <c r="H394" t="n">
         <v>4000</v>
@@ -11824,7 +11824,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H395" t="n">
         <v>4000</v>
@@ -11853,7 +11853,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H397" t="n">
         <v>3500</v>
@@ -11911,7 +11911,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H398" t="n">
         <v>8500</v>
@@ -12056,7 +12056,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.81856393814087</v>
+        <v>2.81856417655945</v>
       </c>
       <c r="H403" t="n">
         <v>4000</v>
@@ -12201,7 +12201,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G408" t="n">
-        <v>2.95349502563477</v>
+        <v>2.95349526405334</v>
       </c>
       <c r="H408" t="n">
         <v>5000</v>
@@ -12230,7 +12230,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>2.96848726272583</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H409" t="n">
         <v>16000</v>
@@ -12259,7 +12259,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.96848726272583</v>
+        <v>2.96848750114441</v>
       </c>
       <c r="H410" t="n">
         <v>3000</v>
@@ -12288,7 +12288,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H411" t="n">
         <v>2000</v>
@@ -12317,7 +12317,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G412" t="n">
-        <v>2.92351031303406</v>
+        <v>2.92351007461548</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.87853288650513</v>
+        <v>2.87853312492371</v>
       </c>
       <c r="H413" t="n">
         <v>500</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.84854865074158</v>
+        <v>2.848548412323</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>2.90851807594299</v>
+        <v>2.90851783752441</v>
       </c>
       <c r="H415" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G417" t="n">
-        <v>2.91866326332092</v>
+        <v>2.91866302490234</v>
       </c>
       <c r="H417" t="n">
         <v>2500</v>
@@ -12578,7 +12578,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G421" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H421" t="n">
         <v>2000</v>
@@ -12607,7 +12607,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H426" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H427" t="n">
         <v>4000</v>
@@ -12781,7 +12781,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G428" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G429" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G430" t="n">
-        <v>2.99670195579529</v>
+        <v>2.99670219421387</v>
       </c>
       <c r="H430" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H435" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>3.29325032234192</v>
+        <v>3.2932505607605</v>
       </c>
       <c r="H445" t="n">
         <v>36000</v>
@@ -13303,7 +13303,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G446" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H446" t="n">
         <v>20000</v>
@@ -13332,7 +13332,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G447" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H447" t="n">
         <v>7500</v>
@@ -13361,7 +13361,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G448" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H448" t="n">
         <v>8000</v>
@@ -13448,7 +13448,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H451" t="n">
         <v>11500</v>
@@ -13564,7 +13564,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>3.15278053283691</v>
+        <v>3.15278029441833</v>
       </c>
       <c r="H455" t="n">
         <v>16000</v>
@@ -14057,7 +14057,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H472" t="n">
         <v>15500</v>
@@ -14579,7 +14579,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G490" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14637,7 +14637,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764296531677</v>
       </c>
       <c r="H492" t="n">
         <v>65000</v>
@@ -14695,7 +14695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>3.27764272689819</v>
+        <v>3.27764296531677</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G495" t="n">
-        <v>3.3712899684906</v>
+        <v>3.37128973007202</v>
       </c>
       <c r="H495" t="n">
         <v>17000</v>
@@ -14753,7 +14753,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>3.26203489303589</v>
+        <v>3.26203513145447</v>
       </c>
       <c r="H496" t="n">
         <v>21000</v>
@@ -14869,7 +14869,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G500" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H500" t="n">
         <v>13000</v>
@@ -14898,7 +14898,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G501" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.21521162986755</v>
+        <v>3.21521139144897</v>
       </c>
       <c r="H502" t="n">
         <v>20500</v>
@@ -14956,7 +14956,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G503" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H503" t="n">
         <v>31000</v>
@@ -14985,7 +14985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G504" t="n">
-        <v>3.23081922531128</v>
+        <v>3.2308189868927</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H507" t="n">
         <v>6000</v>
@@ -15217,7 +15217,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>3.07474136352539</v>
+        <v>3.07474112510681</v>
       </c>
       <c r="H512" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>3.15278053283691</v>
+        <v>3.15278029441833</v>
       </c>
       <c r="H519" t="n">
         <v>4000</v>
@@ -15623,7 +15623,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G526" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H526" t="n">
         <v>15000</v>
@@ -15681,7 +15681,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G528" t="n">
-        <v>2.87183976173401</v>
+        <v>2.87183952331543</v>
       </c>
       <c r="H528" t="n">
         <v>17500</v>
@@ -15739,7 +15739,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G530" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H530" t="n">
         <v>4000</v>
@@ -15797,7 +15797,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697661399841</v>
       </c>
       <c r="H532" t="n">
         <v>1309000</v>
@@ -16000,7 +16000,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62211465835571</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H539" t="n">
         <v>3000</v>
@@ -16087,7 +16087,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G542" t="n">
-        <v>2.62211465835571</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H542" t="n">
         <v>6000</v>
@@ -16116,7 +16116,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H543" t="n">
         <v>75500</v>
@@ -16145,7 +16145,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>2.63772249221802</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H544" t="n">
         <v>5000</v>
@@ -16261,7 +16261,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H548" t="n">
         <v>20000</v>
@@ -16348,7 +16348,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H551" t="n">
         <v>9000</v>
@@ -16551,7 +16551,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H558" t="n">
         <v>1000</v>
@@ -16696,7 +16696,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16812,7 +16812,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697661399841</v>
       </c>
       <c r="H567" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H569" t="n">
         <v>11000</v>
@@ -16899,7 +16899,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G572" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H572" t="n">
         <v>5500</v>
@@ -17073,7 +17073,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G576" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H576" t="n">
         <v>4000</v>
@@ -17189,7 +17189,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H580" t="n">
         <v>32000</v>
@@ -17218,7 +17218,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H581" t="n">
         <v>10500</v>
@@ -17276,7 +17276,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H583" t="n">
         <v>1000</v>
@@ -17305,7 +17305,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>2.88744759559631</v>
+        <v>2.88744735717773</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.77819275856018</v>
+        <v>2.7781925201416</v>
       </c>
       <c r="H586" t="n">
         <v>5000</v>
@@ -17421,7 +17421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71576142311096</v>
+        <v>2.71576118469238</v>
       </c>
       <c r="H588" t="n">
         <v>25500</v>
@@ -17479,7 +17479,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>2.66893792152405</v>
+        <v>2.66893815994263</v>
       </c>
       <c r="H590" t="n">
         <v>2000</v>
@@ -17595,7 +17595,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>2.54407501220703</v>
+        <v>2.54407525062561</v>
       </c>
       <c r="H594" t="n">
         <v>5500</v>
@@ -17624,7 +17624,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H595" t="n">
         <v>13500</v>
@@ -17682,7 +17682,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H597" t="n">
         <v>41000</v>
@@ -17711,7 +17711,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G598" t="n">
-        <v>2.5908989906311</v>
+        <v>2.59089827537537</v>
       </c>
       <c r="H598" t="n">
         <v>6000</v>
@@ -17740,7 +17740,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G599" t="n">
-        <v>2.62211465835571</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H599" t="n">
         <v>13500</v>
@@ -17769,7 +17769,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.60650658607483</v>
+        <v>2.60650634765625</v>
       </c>
       <c r="H600" t="n">
         <v>12500</v>
@@ -17798,7 +17798,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G601" t="n">
-        <v>2.5908989906311</v>
+        <v>2.59089827537537</v>
       </c>
       <c r="H601" t="n">
         <v>6500</v>
@@ -17827,7 +17827,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G602" t="n">
-        <v>2.60650658607483</v>
+        <v>2.60650634765625</v>
       </c>
       <c r="H602" t="n">
         <v>6000</v>
@@ -17856,7 +17856,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H603" t="n">
         <v>17500</v>
@@ -17885,7 +17885,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63772249221802</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H604" t="n">
         <v>500</v>
@@ -17972,7 +17972,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74697709083557</v>
+        <v>2.74697661399841</v>
       </c>
       <c r="H607" t="n">
         <v>35500</v>
@@ -18030,7 +18030,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63772249221802</v>
+        <v>2.63772225379944</v>
       </c>
       <c r="H609" t="n">
         <v>47000</v>
@@ -18059,7 +18059,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H610" t="n">
         <v>20500</v>
@@ -18088,7 +18088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H611" t="n">
         <v>27500</v>
@@ -18117,7 +18117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H612" t="n">
         <v>6000</v>
@@ -18146,7 +18146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H613" t="n">
         <v>3000</v>
@@ -18175,7 +18175,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.512859582901</v>
+        <v>2.51285982131958</v>
       </c>
       <c r="H614" t="n">
         <v>20000</v>
@@ -18233,7 +18233,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H616" t="n">
         <v>22500</v>
@@ -18262,7 +18262,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.5752911567688</v>
+        <v>2.57529091835022</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>2.62211465835571</v>
+        <v>2.62211418151855</v>
       </c>
       <c r="H618" t="n">
         <v>1000</v>
@@ -18320,7 +18320,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.4972517490387</v>
+        <v>2.49725198745728</v>
       </c>
       <c r="H619" t="n">
         <v>3000</v>
@@ -18349,7 +18349,7 @@
         <v>3</v>
       </c>
       <c r="G620" t="n">
-        <v>2.34117364883423</v>
+        <v>2.34117341041565</v>
       </c>
       <c r="H620" t="n">
         <v>7500</v>
@@ -18378,7 +18378,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>2.45042848587036</v>
+        <v>2.4504280090332</v>
       </c>
       <c r="H621" t="n">
         <v>7000</v>
@@ -18436,7 +18436,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>2.23191857337952</v>
+        <v>2.2319188117981</v>
       </c>
       <c r="H623" t="n">
         <v>16000</v>
@@ -18465,7 +18465,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G624" t="n">
-        <v>2.21631097793579</v>
+        <v>2.21631121635437</v>
       </c>
       <c r="H624" t="n">
         <v>3000</v>
@@ -18552,7 +18552,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H627" t="n">
         <v>2000</v>
@@ -18610,7 +18610,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.00660419464111</v>
+        <v>2.00660443305969</v>
       </c>
       <c r="H629" t="n">
         <v>18500</v>
@@ -18639,7 +18639,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.99015641212463</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G631" t="n">
-        <v>1.95726180076599</v>
+        <v>1.95726144313812</v>
       </c>
       <c r="H631" t="n">
         <v>14000</v>
@@ -18842,7 +18842,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.99015641212463</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H637" t="n">
         <v>2000</v>
@@ -18871,7 +18871,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -18900,7 +18900,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H639" t="n">
         <v>10000</v>
@@ -18929,7 +18929,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H640" t="n">
         <v>7000</v>
@@ -18958,7 +18958,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H641" t="n">
         <v>18000</v>
@@ -19016,7 +19016,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>2.45068860054016</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H643" t="n">
         <v>18000</v>
@@ -19074,7 +19074,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H645" t="n">
         <v>14000</v>
@@ -19103,7 +19103,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H646" t="n">
         <v>3000</v>
@@ -19161,7 +19161,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G648" t="n">
-        <v>2.45068860054016</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H648" t="n">
         <v>6000</v>
@@ -19277,7 +19277,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H652" t="n">
         <v>6000</v>
@@ -19364,7 +19364,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>2.45068860054016</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H655" t="n">
         <v>8000</v>
@@ -19393,7 +19393,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G656" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H656" t="n">
         <v>16000</v>
@@ -19422,7 +19422,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19480,7 +19480,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H659" t="n">
         <v>1500</v>
@@ -19538,7 +19538,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.61516451835632</v>
+        <v>2.6151647567749</v>
       </c>
       <c r="H661" t="n">
         <v>23500</v>
@@ -19567,7 +19567,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H662" t="n">
         <v>8500</v>
@@ -19625,7 +19625,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H664" t="n">
         <v>1000</v>
@@ -19654,7 +19654,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H665" t="n">
         <v>2000</v>
@@ -19683,7 +19683,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>2.45068860054016</v>
+        <v>2.45068883895874</v>
       </c>
       <c r="H666" t="n">
         <v>44000</v>
@@ -19741,7 +19741,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G668" t="n">
-        <v>2.33555579185486</v>
+        <v>2.33555603027344</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>2.38489890098572</v>
+        <v>2.38489866256714</v>
       </c>
       <c r="H669" t="n">
         <v>76500</v>
@@ -19828,7 +19828,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G671" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H671" t="n">
         <v>31000</v>
@@ -19857,7 +19857,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G672" t="n">
-        <v>2.07239437103271</v>
+        <v>2.07239460945129</v>
       </c>
       <c r="H672" t="n">
         <v>11560</v>
@@ -19886,7 +19886,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H673" t="n">
         <v>7000</v>
@@ -19915,7 +19915,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G674" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H674" t="n">
         <v>2530</v>
@@ -19944,7 +19944,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H675" t="n">
         <v>13631</v>
@@ -19973,7 +19973,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H676" t="n">
         <v>5030</v>
@@ -20002,7 +20002,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G677" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H677" t="n">
         <v>1635</v>
@@ -20031,7 +20031,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G678" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H678" t="n">
         <v>7225</v>
@@ -20060,7 +20060,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H679" t="n">
         <v>12145</v>
@@ -20089,7 +20089,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H680" t="n">
         <v>8410</v>
@@ -20118,7 +20118,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H681" t="n">
         <v>21760</v>
@@ -20147,7 +20147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.38489890098572</v>
+        <v>2.38489866256714</v>
       </c>
       <c r="H682" t="n">
         <v>21900</v>
@@ -20176,7 +20176,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H683" t="n">
         <v>19301</v>
@@ -20234,7 +20234,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G685" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H685" t="n">
         <v>13500</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H686" t="n">
         <v>2000</v>
@@ -20292,7 +20292,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H687" t="n">
         <v>3000</v>
@@ -20321,7 +20321,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G688" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H688" t="n">
         <v>2025</v>
@@ -20350,7 +20350,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G689" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H689" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G690" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H691" t="n">
         <v>14460</v>
@@ -20437,7 +20437,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G692" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H692" t="n">
         <v>12500</v>
@@ -20582,7 +20582,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G697" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H697" t="n">
         <v>13340</v>
@@ -20640,7 +20640,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G699" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H699" t="n">
         <v>2600</v>
@@ -20669,7 +20669,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H700" t="n">
         <v>11550</v>
@@ -20698,7 +20698,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G701" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H701" t="n">
         <v>1600</v>
@@ -20727,7 +20727,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H702" t="n">
         <v>1010</v>
@@ -20814,7 +20814,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G705" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H705" t="n">
         <v>4500</v>
@@ -20843,7 +20843,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H706" t="n">
         <v>500</v>
@@ -20872,7 +20872,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H707" t="n">
         <v>3875</v>
@@ -21162,7 +21162,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H717" t="n">
         <v>1920</v>
@@ -21191,7 +21191,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H718" t="n">
         <v>4000</v>
@@ -21220,7 +21220,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G719" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H719" t="n">
         <v>1000</v>
@@ -21307,7 +21307,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G722" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H722" t="n">
         <v>8900</v>
@@ -21336,7 +21336,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H723" t="n">
         <v>800</v>
@@ -21365,7 +21365,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G724" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21394,7 +21394,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G725" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H725" t="n">
         <v>9500</v>
@@ -21423,7 +21423,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H726" t="n">
         <v>1500</v>
@@ -21452,7 +21452,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H727" t="n">
         <v>588</v>
@@ -21481,7 +21481,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G728" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H728" t="n">
         <v>3100</v>
@@ -21510,7 +21510,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G729" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G730" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G731" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H731" t="n">
         <v>8000</v>
@@ -21597,7 +21597,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G732" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H732" t="n">
         <v>10280</v>
@@ -21713,7 +21713,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H736" t="n">
         <v>3700</v>
@@ -21742,7 +21742,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H737" t="n">
         <v>10300</v>
@@ -21771,7 +21771,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G738" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21800,7 +21800,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H739" t="n">
         <v>7950</v>
@@ -21829,7 +21829,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G740" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -21887,7 +21887,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H742" t="n">
         <v>878</v>
@@ -21916,7 +21916,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -21945,7 +21945,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H745" t="n">
         <v>4960</v>
@@ -22003,7 +22003,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H746" t="n">
         <v>520</v>
@@ -22032,7 +22032,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H747" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H750" t="n">
         <v>17333</v>
@@ -22148,7 +22148,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G751" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H751" t="n">
         <v>14535</v>
@@ -22177,7 +22177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G752" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22206,7 +22206,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G753" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H753" t="n">
         <v>64103</v>
@@ -22235,7 +22235,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H754" t="n">
         <v>14100</v>
@@ -22264,7 +22264,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G755" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H755" t="n">
         <v>5477</v>
@@ -22322,7 +22322,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H757" t="n">
         <v>3679</v>
@@ -22351,7 +22351,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H758" t="n">
         <v>2966</v>
@@ -22380,7 +22380,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G759" t="n">
-        <v>2.1381847858429</v>
+        <v>2.13818502426147</v>
       </c>
       <c r="H759" t="n">
         <v>3500</v>
@@ -22409,7 +22409,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H760" t="n">
         <v>210</v>
@@ -22438,7 +22438,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H761" t="n">
         <v>2170</v>
@@ -22467,7 +22467,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G762" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H762" t="n">
         <v>5110</v>
@@ -22496,7 +22496,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22525,7 +22525,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10528993606567</v>
+        <v>2.10528969764709</v>
       </c>
       <c r="H764" t="n">
         <v>10600</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.00660419464111</v>
+        <v>2.00660443305969</v>
       </c>
       <c r="H766" t="n">
         <v>7000</v>
@@ -22612,7 +22612,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>1.99015641212463</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H767" t="n">
         <v>11020</v>
@@ -22641,7 +22641,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H768" t="n">
         <v>7167</v>
@@ -22670,7 +22670,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>1.97370934486389</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H769" t="n">
         <v>2120</v>
@@ -22728,7 +22728,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H771" t="n">
         <v>5351</v>
@@ -22786,7 +22786,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>2.00660419464111</v>
+        <v>2.00660443305969</v>
       </c>
       <c r="H773" t="n">
         <v>10000</v>
@@ -22815,7 +22815,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>1.95726180076599</v>
+        <v>1.95726144313812</v>
       </c>
       <c r="H774" t="n">
         <v>10000</v>
@@ -22873,7 +22873,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.80923342704773</v>
+        <v>1.80923366546631</v>
       </c>
       <c r="H776" t="n">
         <v>9400</v>
@@ -22960,7 +22960,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G779" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H779" t="n">
         <v>23341</v>
@@ -22989,7 +22989,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>1.90791881084442</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H780" t="n">
         <v>5771</v>
@@ -23018,7 +23018,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G781" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H781" t="n">
         <v>12683</v>
@@ -23047,7 +23047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G782" t="n">
-        <v>1.94081389904022</v>
+        <v>1.94081366062164</v>
       </c>
       <c r="H782" t="n">
         <v>2000</v>
@@ -23076,7 +23076,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90791881084442</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H783" t="n">
         <v>5208</v>
@@ -23105,7 +23105,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G784" t="n">
-        <v>1.79278600215912</v>
+        <v>1.79278576374054</v>
       </c>
       <c r="H784" t="n">
         <v>9450</v>
@@ -23134,7 +23134,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>1.79278600215912</v>
+        <v>1.79278576374054</v>
       </c>
       <c r="H785" t="n">
         <v>6000</v>
@@ -23192,7 +23192,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G787" t="n">
-        <v>1.80923342704773</v>
+        <v>1.80923366546631</v>
       </c>
       <c r="H787" t="n">
         <v>1000</v>
@@ -23221,7 +23221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502384185791</v>
       </c>
       <c r="H788" t="n">
         <v>4000</v>
@@ -23250,7 +23250,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G789" t="n">
-        <v>1.87502360343933</v>
+        <v>1.87502384185791</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G790" t="n">
-        <v>1.89147114753723</v>
+        <v>1.89147126674652</v>
       </c>
       <c r="H790" t="n">
         <v>2551</v>
@@ -23308,7 +23308,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>1.90791881084442</v>
+        <v>1.90791893005371</v>
       </c>
       <c r="H791" t="n">
         <v>8501</v>
@@ -23366,7 +23366,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.02305173873901</v>
+        <v>2.02305197715759</v>
       </c>
       <c r="H793" t="n">
         <v>8769</v>
@@ -23395,7 +23395,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>1.99015641212463</v>
+        <v>1.9901567697525</v>
       </c>
       <c r="H794" t="n">
         <v>5000</v>
@@ -23424,7 +23424,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>1.97370934486389</v>
+        <v>1.9737092256546</v>
       </c>
       <c r="H795" t="n">
         <v>5168</v>
@@ -23511,7 +23511,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H798" t="n">
         <v>20346</v>
@@ -23569,7 +23569,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G800" t="n">
-        <v>2.07239437103271</v>
+        <v>2.07239460945129</v>
       </c>
       <c r="H800" t="n">
         <v>5199</v>
@@ -23598,7 +23598,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H801" t="n">
         <v>18700</v>
@@ -23627,7 +23627,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>2.17108035087585</v>
+        <v>2.17108011245728</v>
       </c>
       <c r="H802" t="n">
         <v>15886</v>
@@ -23656,7 +23656,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G803" t="n">
-        <v>2.18752789497375</v>
+        <v>2.18752765655518</v>
       </c>
       <c r="H803" t="n">
         <v>39306</v>
@@ -23685,7 +23685,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G804" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H804" t="n">
         <v>6170</v>
@@ -23743,7 +23743,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G806" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H806" t="n">
         <v>4149</v>
@@ -23801,7 +23801,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20397543907166</v>
+        <v>2.20397520065308</v>
       </c>
       <c r="H808" t="n">
         <v>8250</v>
@@ -23830,7 +23830,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.1546323299408</v>
+        <v>2.15463256835938</v>
       </c>
       <c r="H809" t="n">
         <v>3200</v>
@@ -23859,7 +23859,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H810" t="n">
         <v>9326</v>
@@ -24004,7 +24004,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H815" t="n">
         <v>4017</v>
@@ -24120,7 +24120,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>2.38489890098572</v>
+        <v>2.38489866256714</v>
       </c>
       <c r="H819" t="n">
         <v>48040</v>
@@ -24207,7 +24207,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H822" t="n">
         <v>2000</v>
@@ -24236,7 +24236,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G823" t="n">
-        <v>2.22042298316956</v>
+        <v>2.22042274475098</v>
       </c>
       <c r="H823" t="n">
         <v>4050</v>
@@ -24294,7 +24294,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>2.25331807136536</v>
+        <v>2.25331783294678</v>
       </c>
       <c r="H825" t="n">
         <v>6850</v>
@@ -24323,7 +24323,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G826" t="n">
-        <v>2.23687028884888</v>
+        <v>2.23687052726746</v>
       </c>
       <c r="H826" t="n">
         <v>4285</v>
@@ -24381,7 +24381,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>2.51647925376892</v>
+        <v>2.51647901535034</v>
       </c>
       <c r="H828" t="n">
         <v>256671</v>
@@ -24410,7 +24410,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H829" t="n">
         <v>292926</v>
@@ -24497,7 +24497,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G832" t="n">
-        <v>2.77964043617249</v>
+        <v>2.77964067459106</v>
       </c>
       <c r="H832" t="n">
         <v>51937</v>
@@ -24526,7 +24526,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H833" t="n">
         <v>25716</v>
@@ -24700,7 +24700,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H839" t="n">
         <v>12621</v>
@@ -24758,7 +24758,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>2.48358416557312</v>
+        <v>2.48358392715454</v>
       </c>
       <c r="H841" t="n">
         <v>18272</v>
@@ -24874,7 +24874,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50003170967102</v>
+        <v>2.50003147125244</v>
       </c>
       <c r="H845" t="n">
         <v>10361</v>
@@ -24903,7 +24903,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5822696685791</v>
+        <v>2.58226943016052</v>
       </c>
       <c r="H846" t="n">
         <v>14130</v>
@@ -25222,7 +25222,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G857" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H857" t="n">
         <v>36588</v>
@@ -25280,7 +25280,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G859" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H859" t="n">
         <v>14827</v>
@@ -25309,7 +25309,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G860" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H860" t="n">
         <v>9138</v>
@@ -25396,7 +25396,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G863" t="n">
-        <v>2.68095469474792</v>
+        <v>2.68095517158508</v>
       </c>
       <c r="H863" t="n">
         <v>4900</v>
@@ -25425,7 +25425,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G864" t="n">
-        <v>2.68095469474792</v>
+        <v>2.68095517158508</v>
       </c>
       <c r="H864" t="n">
         <v>1600</v>
@@ -25454,7 +25454,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>2.73029780387878</v>
+        <v>2.73029756546021</v>
       </c>
       <c r="H865" t="n">
         <v>12720</v>
@@ -25512,7 +25512,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H867" t="n">
         <v>11963</v>
@@ -25541,7 +25541,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>2.71385025978088</v>
+        <v>2.7138500213623</v>
       </c>
       <c r="H868" t="n">
         <v>12942</v>
@@ -25570,7 +25570,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="n">
-        <v>2.82898306846619</v>
+        <v>2.82898330688477</v>
       </c>
       <c r="H869" t="n">
         <v>30735</v>
@@ -25599,7 +25599,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>2.86187815666199</v>
+        <v>2.86187839508057</v>
       </c>
       <c r="H870" t="n">
         <v>110702</v>
@@ -25657,7 +25657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G872" t="n">
-        <v>2.86187815666199</v>
+        <v>2.86187839508057</v>
       </c>
       <c r="H872" t="n">
         <v>56730</v>
@@ -25686,7 +25686,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H873" t="n">
         <v>27201</v>
@@ -25744,7 +25744,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H875" t="n">
         <v>19182</v>
@@ -25773,7 +25773,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H876" t="n">
         <v>20608</v>
@@ -25918,7 +25918,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H881" t="n">
         <v>26805</v>
@@ -25947,7 +25947,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>2.94411635398865</v>
+        <v>2.94411611557007</v>
       </c>
       <c r="H882" t="n">
         <v>21945</v>
@@ -26034,7 +26034,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.94411635398865</v>
+        <v>2.94411611557007</v>
       </c>
       <c r="H885" t="n">
         <v>3081</v>
@@ -26092,7 +26092,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.94411635398865</v>
+        <v>2.94411611557007</v>
       </c>
       <c r="H887" t="n">
         <v>13106</v>
@@ -26121,7 +26121,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>2.91122102737427</v>
+        <v>2.91122126579285</v>
       </c>
       <c r="H888" t="n">
         <v>9185</v>
@@ -26208,7 +26208,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G891" t="n">
-        <v>3.02635431289673</v>
+        <v>3.02635407447815</v>
       </c>
       <c r="H891" t="n">
         <v>20227</v>
@@ -26237,7 +26237,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G892" t="n">
-        <v>3.0016827583313</v>
+        <v>3.00168251991272</v>
       </c>
       <c r="H892" t="n">
         <v>9588</v>
@@ -26266,7 +26266,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G893" t="n">
-        <v>3.02635431289673</v>
+        <v>3.02635407447815</v>
       </c>
       <c r="H893" t="n">
         <v>6123</v>
@@ -26295,7 +26295,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>3.0181303024292</v>
+        <v>3.01813006401062</v>
       </c>
       <c r="H894" t="n">
         <v>4722</v>
@@ -26556,7 +26556,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G903" t="n">
-        <v>3.04280185699463</v>
+        <v>3.04280161857605</v>
       </c>
       <c r="H903" t="n">
         <v>10299</v>
@@ -26585,7 +26585,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H904" t="n">
         <v>35002</v>
@@ -26614,7 +26614,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G905" t="n">
-        <v>3.15793442726135</v>
+        <v>3.15793466567993</v>
       </c>
       <c r="H905" t="n">
         <v>9395</v>
@@ -26643,7 +26643,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H906" t="n">
         <v>18842</v>
@@ -26672,7 +26672,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G907" t="n">
-        <v>3.12503933906555</v>
+        <v>3.12503957748413</v>
       </c>
       <c r="H907" t="n">
         <v>5477</v>
@@ -26730,7 +26730,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>3.15793442726135</v>
+        <v>3.15793466567993</v>
       </c>
       <c r="H909" t="n">
         <v>1061</v>
@@ -26875,7 +26875,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.22372484207153</v>
+        <v>3.22372508049011</v>
       </c>
       <c r="H914" t="n">
         <v>32683</v>
@@ -26933,7 +26933,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G916" t="n">
-        <v>3.1661581993103</v>
+        <v>3.16615843772888</v>
       </c>
       <c r="H916" t="n">
         <v>23119</v>
@@ -26991,7 +26991,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>3.1168155670166</v>
+        <v>3.11681580543518</v>
       </c>
       <c r="H918" t="n">
         <v>36796</v>
@@ -27107,7 +27107,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G922" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H922" t="n">
         <v>18275</v>
@@ -27136,7 +27136,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>3.17438220977783</v>
+        <v>3.17438244819641</v>
       </c>
       <c r="H923" t="n">
         <v>16638</v>
@@ -27165,7 +27165,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G924" t="n">
-        <v>3.1322820186615</v>
+        <v>3.13228178024292</v>
       </c>
       <c r="H924" t="n">
         <v>4945</v>
@@ -27339,7 +27339,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>3.1491219997406</v>
+        <v>3.14912176132202</v>
       </c>
       <c r="H930" t="n">
         <v>4469</v>
@@ -27397,7 +27397,7 @@
         <v>4</v>
       </c>
       <c r="G932" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H932" t="n">
         <v>46107</v>
@@ -27455,7 +27455,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H934" t="n">
         <v>17505</v>
@@ -27484,7 +27484,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H935" t="n">
         <v>4667</v>
@@ -27513,7 +27513,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H936" t="n">
         <v>10328</v>
@@ -27629,7 +27629,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H940" t="n">
         <v>4174</v>
@@ -27658,7 +27658,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H941" t="n">
         <v>13248</v>
@@ -27687,7 +27687,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H942" t="n">
         <v>56586</v>
@@ -27832,7 +27832,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>3.53644680976868</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H947" t="n">
         <v>5552</v>
@@ -27890,7 +27890,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H949" t="n">
         <v>4151</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H953" t="n">
         <v>4381</v>
@@ -28064,7 +28064,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>3.57012724876404</v>
+        <v>3.57012748718262</v>
       </c>
       <c r="H955" t="n">
         <v>3840</v>
@@ -28180,7 +28180,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>3.4438259601593</v>
+        <v>3.44382619857788</v>
       </c>
       <c r="H959" t="n">
         <v>19778</v>
@@ -28325,7 +28325,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G964" t="n">
-        <v>3.41014575958252</v>
+        <v>3.41014552116394</v>
       </c>
       <c r="H964" t="n">
         <v>9510</v>
@@ -28412,7 +28412,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>3.22490286827087</v>
+        <v>3.22490310668945</v>
       </c>
       <c r="H967" t="n">
         <v>12089</v>
@@ -28441,7 +28441,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G968" t="n">
-        <v>3.26700353622437</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H968" t="n">
         <v>13367</v>
@@ -28470,7 +28470,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G969" t="n">
-        <v>3.30068373680115</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H969" t="n">
         <v>1754</v>
@@ -28499,7 +28499,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>3.32594418525696</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H970" t="n">
         <v>650</v>
@@ -28528,7 +28528,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>3.30068373680115</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H971" t="n">
         <v>3678</v>
@@ -28557,7 +28557,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>3.31752419471741</v>
+        <v>3.31752443313599</v>
       </c>
       <c r="H972" t="n">
         <v>4735</v>
@@ -28586,7 +28586,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H973" t="n">
         <v>150</v>
@@ -28615,7 +28615,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G974" t="n">
-        <v>3.28384399414062</v>
+        <v>3.28384375572205</v>
       </c>
       <c r="H974" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>3.26700353622437</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H975" t="n">
         <v>750</v>
@@ -28673,7 +28673,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>3.30068373680115</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H976" t="n">
         <v>1030</v>
@@ -28731,7 +28731,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.33436417579651</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H978" t="n">
         <v>24159</v>
@@ -28760,7 +28760,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G979" t="n">
-        <v>3.41014575958252</v>
+        <v>3.41014552116394</v>
       </c>
       <c r="H979" t="n">
         <v>7866</v>
@@ -28789,7 +28789,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>3.40172553062439</v>
+        <v>3.40172529220581</v>
       </c>
       <c r="H980" t="n">
         <v>8597</v>
@@ -28818,7 +28818,7 @@
         <v>4</v>
       </c>
       <c r="G981" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H981" t="n">
         <v>410</v>
@@ -28876,7 +28876,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>3.33436417579651</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H983" t="n">
         <v>3909</v>
@@ -28905,7 +28905,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G984" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H984" t="n">
         <v>10480</v>
@@ -28963,7 +28963,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.41014575958252</v>
+        <v>3.41014552116394</v>
       </c>
       <c r="H986" t="n">
         <v>1700</v>
@@ -29050,7 +29050,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>3.35120463371277</v>
+        <v>3.35120439529419</v>
       </c>
       <c r="H989" t="n">
         <v>4795</v>
@@ -29195,7 +29195,7 @@
         <v>4</v>
       </c>
       <c r="G994" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H994" t="n">
         <v>9158</v>
@@ -29340,7 +29340,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.58696794509888</v>
+        <v>3.5869677066803</v>
       </c>
       <c r="H999" t="n">
         <v>24870</v>
@@ -29369,7 +29369,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1000" t="n">
         <v>56572</v>
@@ -29398,7 +29398,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.02481365203857</v>
+        <v>4.02481412887573</v>
       </c>
       <c r="H1001" t="n">
         <v>96367</v>
@@ -29427,7 +29427,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.15953493118286</v>
+        <v>4.15953540802002</v>
       </c>
       <c r="H1002" t="n">
         <v>111881</v>
@@ -29485,7 +29485,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1004" t="n">
         <v>78322</v>
@@ -29514,7 +29514,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.05007410049438</v>
+        <v>4.05007362365723</v>
       </c>
       <c r="H1005" t="n">
         <v>28674</v>
@@ -29543,7 +29543,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.10059452056885</v>
+        <v>4.10059404373169</v>
       </c>
       <c r="H1006" t="n">
         <v>23823</v>
@@ -29572,7 +29572,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.99113321304321</v>
+        <v>3.99113297462463</v>
       </c>
       <c r="H1007" t="n">
         <v>22534</v>
@@ -29601,7 +29601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.76379013061523</v>
+        <v>3.76378965377808</v>
       </c>
       <c r="H1008" t="n">
         <v>79946</v>
@@ -29630,7 +29630,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1009" t="n">
         <v>18829</v>
@@ -29659,7 +29659,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1010" t="n">
         <v>35109</v>
@@ -29775,7 +29775,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1014" t="n">
         <v>7495</v>
@@ -29804,7 +29804,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.85641098022461</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1015" t="n">
         <v>10368</v>
@@ -29833,7 +29833,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.83957099914551</v>
+        <v>3.83957123756409</v>
       </c>
       <c r="H1016" t="n">
         <v>27929</v>
@@ -29862,7 +29862,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1017" t="n">
         <v>43128</v>
@@ -29920,7 +29920,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1019" t="n">
         <v>2641</v>
@@ -29949,7 +29949,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.80589079856873</v>
+        <v>3.8058910369873</v>
       </c>
       <c r="H1020" t="n">
         <v>5690</v>
@@ -29978,7 +29978,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.7974705696106</v>
+        <v>3.79747104644775</v>
       </c>
       <c r="H1021" t="n">
         <v>5537</v>
@@ -30036,7 +30036,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.9490327835083</v>
+        <v>3.94903254508972</v>
       </c>
       <c r="H1023" t="n">
         <v>8504</v>
@@ -30065,7 +30065,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1024" t="n">
         <v>24153</v>
@@ -30094,7 +30094,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849361419678</v>
       </c>
       <c r="H1025" t="n">
         <v>31402</v>
@@ -30152,7 +30152,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.13427448272705</v>
+        <v>4.13427495956421</v>
       </c>
       <c r="H1027" t="n">
         <v>10172</v>
@@ -30210,7 +30210,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.06691408157349</v>
+        <v>4.06691455841064</v>
       </c>
       <c r="H1029" t="n">
         <v>29092</v>
@@ -30268,7 +30268,7 @@
         <v>4.75</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.99955344200134</v>
+        <v>3.99955296516418</v>
       </c>
       <c r="H1031" t="n">
         <v>4755</v>
@@ -30355,7 +30355,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1034" t="n">
         <v>2631</v>
@@ -30384,7 +30384,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.03323364257812</v>
+        <v>4.03323411941528</v>
       </c>
       <c r="H1035" t="n">
         <v>10516</v>
@@ -30413,7 +30413,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.05849456787109</v>
+        <v>4.05849361419678</v>
       </c>
       <c r="H1036" t="n">
         <v>12669</v>
@@ -30442,7 +30442,7 @@
         <v>4.75</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.99955344200134</v>
+        <v>3.99955296516418</v>
       </c>
       <c r="H1037" t="n">
         <v>9609</v>
@@ -30471,7 +30471,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.9658727645874</v>
+        <v>3.96587300300598</v>
       </c>
       <c r="H1038" t="n">
         <v>10631</v>
@@ -30529,7 +30529,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1040" t="n">
         <v>27791</v>
@@ -30558,7 +30558,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.8648316860199</v>
+        <v>3.86483120918274</v>
       </c>
       <c r="H1041" t="n">
         <v>2683</v>
@@ -30645,7 +30645,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1044" t="n">
         <v>8102</v>
@@ -30674,7 +30674,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.68800926208496</v>
+        <v>3.68800950050354</v>
       </c>
       <c r="H1045" t="n">
         <v>6158</v>
@@ -30732,7 +30732,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1047" t="n">
         <v>3054</v>
@@ -30761,7 +30761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1048" t="n">
         <v>5003</v>
@@ -30819,7 +30819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1050" t="n">
         <v>21037</v>
@@ -30848,7 +30848,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.85641098022461</v>
+        <v>3.85641121864319</v>
       </c>
       <c r="H1051" t="n">
         <v>38739</v>
@@ -30877,7 +30877,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.97429251670837</v>
+        <v>3.97429275512695</v>
       </c>
       <c r="H1052" t="n">
         <v>48655</v>
@@ -30906,7 +30906,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.89009165763855</v>
+        <v>3.89009189605713</v>
       </c>
       <c r="H1053" t="n">
         <v>34250</v>
@@ -30964,7 +30964,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.67116928100586</v>
+        <v>3.67116904258728</v>
       </c>
       <c r="H1055" t="n">
         <v>24782</v>
@@ -30993,7 +30993,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.72168970108032</v>
+        <v>3.72168946266174</v>
       </c>
       <c r="H1056" t="n">
         <v>4318</v>
@@ -31051,7 +31051,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67958903312683</v>
+        <v>3.67958879470825</v>
       </c>
       <c r="H1058" t="n">
         <v>2298</v>
@@ -31080,7 +31080,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70484972000122</v>
+        <v>3.70484948158264</v>
       </c>
       <c r="H1059" t="n">
         <v>3348</v>
@@ -31167,7 +31167,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1062" t="n">
         <v>6225</v>
@@ -31283,7 +31283,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1066" t="n">
         <v>38758</v>
@@ -31312,7 +31312,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.58696794509888</v>
+        <v>3.5869677066803</v>
       </c>
       <c r="H1067" t="n">
         <v>9893</v>
@@ -31399,7 +31399,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.66274881362915</v>
+        <v>3.66274857521057</v>
       </c>
       <c r="H1070" t="n">
         <v>5888</v>
@@ -31428,7 +31428,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1071" t="n">
         <v>5768</v>
@@ -31486,7 +31486,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1073" t="n">
         <v>64565</v>
@@ -31660,7 +31660,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1079" t="n">
         <v>74698</v>
@@ -31747,7 +31747,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.71326947212219</v>
+        <v>3.71326971054077</v>
       </c>
       <c r="H1082" t="n">
         <v>5435</v>
@@ -31776,7 +31776,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1083" t="n">
         <v>17149</v>
@@ -31805,7 +31805,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.78063035011292</v>
+        <v>3.78063011169434</v>
       </c>
       <c r="H1084" t="n">
         <v>3484</v>
@@ -31834,7 +31834,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.67958903312683</v>
+        <v>3.67958879470825</v>
       </c>
       <c r="H1085" t="n">
         <v>11959</v>
@@ -31863,7 +31863,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.73853015899658</v>
+        <v>3.738529920578</v>
       </c>
       <c r="H1086" t="n">
         <v>12229</v>
@@ -31921,7 +31921,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.69642925262451</v>
+        <v>3.69642877578735</v>
       </c>
       <c r="H1088" t="n">
         <v>3360</v>
@@ -32153,7 +32153,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1096" t="n">
         <v>7457</v>
@@ -32182,7 +32182,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.53644680976868</v>
+        <v>3.53644704818726</v>
       </c>
       <c r="H1097" t="n">
         <v>8056</v>
@@ -32269,7 +32269,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.40172553062439</v>
+        <v>3.40172529220581</v>
       </c>
       <c r="H1100" t="n">
         <v>6138</v>
@@ -32356,7 +32356,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46066641807556</v>
+        <v>3.46066617965698</v>
       </c>
       <c r="H1103" t="n">
         <v>1375</v>
@@ -32472,7 +32472,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.54486703872681</v>
+        <v>3.54486727714539</v>
       </c>
       <c r="H1107" t="n">
         <v>9024</v>
@@ -32501,7 +32501,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1108" t="n">
         <v>34399</v>
@@ -32588,7 +32588,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H1111" t="n">
         <v>9772</v>
@@ -32617,7 +32617,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1112" t="n">
         <v>4545</v>
@@ -32646,7 +32646,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1113" t="n">
         <v>300</v>
@@ -32675,7 +32675,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.40172553062439</v>
+        <v>3.40172529220581</v>
       </c>
       <c r="H1114" t="n">
         <v>9295</v>
@@ -32820,7 +32820,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1119" t="n">
         <v>13064</v>
@@ -32849,7 +32849,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.51960706710815</v>
+        <v>3.51960682868958</v>
       </c>
       <c r="H1120" t="n">
         <v>15675</v>
@@ -32878,7 +32878,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.41856575012207</v>
+        <v>3.41856551170349</v>
       </c>
       <c r="H1121" t="n">
         <v>26861</v>
@@ -32936,7 +32936,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.26700353622437</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1123" t="n">
         <v>12666</v>
@@ -32965,7 +32965,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.30068373680115</v>
+        <v>3.30068397521973</v>
       </c>
       <c r="H1124" t="n">
         <v>10488</v>
@@ -32994,7 +32994,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1125" t="n">
         <v>5070</v>
@@ -33052,7 +33052,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.11544156074524</v>
+        <v>3.11544179916382</v>
       </c>
       <c r="H1127" t="n">
         <v>16752</v>
@@ -33110,7 +33110,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.86283850669861</v>
+        <v>2.86283826828003</v>
       </c>
       <c r="H1129" t="n">
         <v>14846</v>
@@ -33197,7 +33197,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.84599828720093</v>
+        <v>2.84599804878235</v>
       </c>
       <c r="H1132" t="n">
         <v>8787</v>
@@ -33226,7 +33226,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.81231760978699</v>
+        <v>2.81231737136841</v>
       </c>
       <c r="H1133" t="n">
         <v>28149</v>
@@ -33255,7 +33255,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80389761924744</v>
+        <v>2.80389714241028</v>
       </c>
       <c r="H1134" t="n">
         <v>22070</v>
@@ -33313,7 +33313,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1136" t="n">
         <v>66796</v>
@@ -33342,7 +33342,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1137" t="n">
         <v>80725</v>
@@ -33371,7 +33371,7 @@
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1138" t="n">
         <v>8053</v>
@@ -33400,7 +33400,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.43540596961975</v>
+        <v>3.43540573120117</v>
       </c>
       <c r="H1139" t="n">
         <v>5055</v>
@@ -33487,7 +33487,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1142" t="n">
         <v>11790</v>
@@ -33516,7 +33516,7 @@
         <v>4</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1143" t="n">
         <v>1920</v>
@@ -33545,7 +33545,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.33436417579651</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1144" t="n">
         <v>5530</v>
@@ -33574,7 +33574,7 @@
         <v>4</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1145" t="n">
         <v>5210</v>
@@ -33603,7 +33603,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.32594418525696</v>
+        <v>3.32594442367554</v>
       </c>
       <c r="H1146" t="n">
         <v>2889</v>
@@ -33632,7 +33632,7 @@
         <v>4</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1147" t="n">
         <v>2050</v>
@@ -33661,7 +33661,7 @@
         <v>4</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.36804461479187</v>
+        <v>3.36804485321045</v>
       </c>
       <c r="H1148" t="n">
         <v>1680</v>
@@ -33690,7 +33690,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.35962462425232</v>
+        <v>3.3596248626709</v>
       </c>
       <c r="H1149" t="n">
         <v>4800</v>
@@ -33719,7 +33719,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.33436417579651</v>
+        <v>3.33436465263367</v>
       </c>
       <c r="H1150" t="n">
         <v>6812</v>
@@ -33806,7 +33806,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.22490286827087</v>
+        <v>3.22490310668945</v>
       </c>
       <c r="H1153" t="n">
         <v>3850</v>
@@ -33980,7 +33980,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1159" t="n">
         <v>265</v>
@@ -34009,7 +34009,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.26700353622437</v>
+        <v>3.26700377464294</v>
       </c>
       <c r="H1160" t="n">
         <v>1350</v>
@@ -34038,7 +34038,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1161" t="n">
         <v>320</v>
@@ -34067,7 +34067,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1162" t="n">
         <v>400</v>
@@ -34125,7 +34125,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.20806264877319</v>
+        <v>3.20806288719177</v>
       </c>
       <c r="H1164" t="n">
         <v>1200</v>
@@ -34154,7 +34154,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1165" t="n">
         <v>169</v>
@@ -34183,7 +34183,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.2754237651825</v>
+        <v>3.27542400360107</v>
       </c>
       <c r="H1166" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.28384399414062</v>
+        <v>3.28384375572205</v>
       </c>
       <c r="H1168" t="n">
         <v>3031</v>
@@ -34328,7 +34328,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.17438220977783</v>
+        <v>3.17438244819641</v>
       </c>
       <c r="H1171" t="n">
         <v>1224</v>
@@ -34415,7 +34415,7 @@
         <v>3.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.15754199028015</v>
+        <v>3.15754222869873</v>
       </c>
       <c r="H1174" t="n">
         <v>2264</v>
@@ -34444,7 +34444,7 @@
         <v>3.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.15754199028015</v>
+        <v>3.15754222869873</v>
       </c>
       <c r="H1175" t="n">
         <v>2738</v>
@@ -34473,7 +34473,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.16596221923828</v>
+        <v>3.16596245765686</v>
       </c>
       <c r="H1176" t="n">
         <v>2842</v>
@@ -34560,7 +34560,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41084337234497</v>
+        <v>3.41084361076355</v>
       </c>
       <c r="H1179" t="n">
         <v>122</v>
@@ -34589,7 +34589,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.40209770202637</v>
+        <v>3.40209794044495</v>
       </c>
       <c r="H1180" t="n">
         <v>1022</v>
@@ -34705,7 +34705,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1184" t="n">
         <v>1051</v>
@@ -34734,7 +34734,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1185" t="n">
         <v>1629</v>
@@ -34821,7 +34821,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1188" t="n">
         <v>437</v>
@@ -34850,7 +34850,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1189" t="n">
         <v>0</v>
@@ -34879,7 +34879,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1190" t="n">
         <v>0</v>
@@ -34908,7 +34908,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.35836863517761</v>
+        <v>3.35836887359619</v>
       </c>
       <c r="H1192" t="n">
         <v>2500</v>
@@ -35082,7 +35082,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1197" t="n">
         <v>4630</v>
@@ -35111,7 +35111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1198" t="n">
         <v>2600</v>
@@ -35140,7 +35140,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.27091145515442</v>
+        <v>3.27091121673584</v>
       </c>
       <c r="H1199" t="n">
         <v>1010</v>
@@ -35169,7 +35169,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1200" t="n">
         <v>4965</v>
@@ -35198,7 +35198,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1201" t="n">
         <v>5289</v>
@@ -35227,7 +35227,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1202" t="n">
         <v>3125</v>
@@ -35256,7 +35256,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1203" t="n">
         <v>1800</v>
@@ -35285,7 +35285,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1204" t="n">
         <v>9575</v>
@@ -35314,7 +35314,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1205" t="n">
         <v>3220</v>
@@ -35372,7 +35372,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1207" t="n">
         <v>8591</v>
@@ -35401,7 +35401,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1208" t="n">
         <v>3650</v>
@@ -35633,7 +35633,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.85111498832703</v>
+        <v>2.85111522674561</v>
       </c>
       <c r="H1216" t="n">
         <v>19487</v>
@@ -35662,7 +35662,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.85111498832703</v>
+        <v>2.85111522674561</v>
       </c>
       <c r="H1217" t="n">
         <v>7777</v>
@@ -35691,7 +35691,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.75491189956665</v>
+        <v>2.75491213798523</v>
       </c>
       <c r="H1218" t="n">
         <v>11057</v>
@@ -35865,7 +35865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1224" t="n">
         <v>4675</v>
@@ -35894,7 +35894,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1225" t="n">
         <v>4501</v>
@@ -35981,7 +35981,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1228" t="n">
         <v>8827</v>
@@ -36010,7 +36010,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1229" t="n">
         <v>6115</v>
@@ -36039,7 +36039,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1230" t="n">
         <v>2300</v>
@@ -36068,7 +36068,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.69369173049927</v>
+        <v>2.69369149208069</v>
       </c>
       <c r="H1231" t="n">
         <v>2550</v>
@@ -36213,7 +36213,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1236" t="n">
         <v>212</v>
@@ -36300,7 +36300,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.07850480079651</v>
+        <v>3.07850456237793</v>
       </c>
       <c r="H1239" t="n">
         <v>5505</v>
@@ -36416,7 +36416,7 @@
         <v>3.5</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1243" t="n">
         <v>2327</v>
@@ -36619,7 +36619,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1250" t="n">
         <v>1625</v>
@@ -36648,7 +36648,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1251" t="n">
         <v>132</v>
@@ -36677,7 +36677,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1252" t="n">
         <v>650</v>
@@ -36706,7 +36706,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1253" t="n">
         <v>0</v>
@@ -36822,7 +36822,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1257" t="n">
         <v>364</v>
@@ -36851,7 +36851,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1258" t="n">
         <v>948</v>
@@ -36880,7 +36880,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1259" t="n">
         <v>0</v>
@@ -36967,7 +36967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1262" t="n">
         <v>500</v>
@@ -36996,7 +36996,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1263" t="n">
         <v>588</v>
@@ -37025,7 +37025,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1264" t="n">
         <v>397</v>
@@ -37054,7 +37054,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1265" t="n">
         <v>762</v>
@@ -37083,7 +37083,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1266" t="n">
         <v>400</v>
@@ -37112,7 +37112,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.85111498832703</v>
+        <v>2.85111522674561</v>
       </c>
       <c r="H1267" t="n">
         <v>423</v>
@@ -37257,7 +37257,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.67620015144348</v>
+        <v>2.6761999130249</v>
       </c>
       <c r="H1272" t="n">
         <v>600</v>
@@ -37576,7 +37576,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1283" t="n">
         <v>2421</v>
@@ -37605,7 +37605,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.43131899833679</v>
+        <v>2.43131923675537</v>
       </c>
       <c r="H1284" t="n">
         <v>7210</v>
@@ -37663,7 +37663,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.46630215644836</v>
+        <v>2.46630191802979</v>
       </c>
       <c r="H1286" t="n">
         <v>5150</v>
@@ -37692,7 +37692,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1287" t="n">
         <v>7150</v>
@@ -37721,7 +37721,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.57999682426453</v>
+        <v>2.57999706268311</v>
       </c>
       <c r="H1288" t="n">
         <v>2742</v>
@@ -37750,7 +37750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.54501414299011</v>
+        <v>2.54501390457153</v>
       </c>
       <c r="H1289" t="n">
         <v>597</v>
@@ -37779,7 +37779,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.57999682426453</v>
+        <v>2.57999706268311</v>
       </c>
       <c r="H1290" t="n">
         <v>5450</v>
@@ -37808,7 +37808,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.77240347862244</v>
+        <v>2.77240371704102</v>
       </c>
       <c r="H1291" t="n">
         <v>4200</v>
@@ -37866,7 +37866,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.69369173049927</v>
+        <v>2.69369149208069</v>
       </c>
       <c r="H1293" t="n">
         <v>825</v>
@@ -37895,7 +37895,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.6587085723877</v>
+        <v>2.65870881080627</v>
       </c>
       <c r="H1294" t="n">
         <v>1467</v>
@@ -37982,7 +37982,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.55375957489014</v>
+        <v>2.55375981330872</v>
       </c>
       <c r="H1297" t="n">
         <v>565</v>
@@ -38011,7 +38011,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.57999682426453</v>
+        <v>2.57999706268311</v>
       </c>
       <c r="H1298" t="n">
         <v>9217</v>
@@ -38069,7 +38069,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1300" t="n">
         <v>4238</v>
@@ -38098,7 +38098,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.60623407363892</v>
+        <v>2.6062343120575</v>
       </c>
       <c r="H1301" t="n">
         <v>1823</v>
@@ -38243,7 +38243,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1306" t="n">
         <v>8457</v>
@@ -38330,7 +38330,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.77240347862244</v>
+        <v>2.77240371704102</v>
       </c>
       <c r="H1309" t="n">
         <v>4364</v>
@@ -38388,7 +38388,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.85111498832703</v>
+        <v>2.85111522674561</v>
       </c>
       <c r="H1311" t="n">
         <v>750</v>
@@ -38417,7 +38417,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.83362364768982</v>
+        <v>2.8336238861084</v>
       </c>
       <c r="H1312" t="n">
         <v>1050</v>
@@ -38504,7 +38504,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1315" t="n">
         <v>6616</v>
@@ -38533,7 +38533,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.80738639831543</v>
+        <v>2.80738663673401</v>
       </c>
       <c r="H1316" t="n">
         <v>3648</v>
@@ -38591,7 +38591,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1318" t="n">
         <v>5551</v>
@@ -38620,7 +38620,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1319" t="n">
         <v>10275</v>
@@ -38649,7 +38649,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1320" t="n">
         <v>2763</v>
@@ -38765,7 +38765,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1324" t="n">
         <v>500</v>
@@ -38794,7 +38794,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1325" t="n">
         <v>6498</v>
@@ -38823,7 +38823,7 @@
         <v>3.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1326" t="n">
         <v>5429</v>
@@ -39055,7 +39055,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1334" t="n">
         <v>10567</v>
@@ -39084,7 +39084,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1335" t="n">
         <v>3359</v>
@@ -39113,7 +39113,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1336" t="n">
         <v>1510</v>
@@ -39229,7 +39229,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1340" t="n">
         <v>6322</v>
@@ -39258,7 +39258,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1341" t="n">
         <v>11551</v>
@@ -39287,7 +39287,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1342" t="n">
         <v>1846</v>
@@ -39316,7 +39316,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1343" t="n">
         <v>5050</v>
@@ -39345,7 +39345,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1344" t="n">
         <v>940</v>
@@ -39403,7 +39403,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1346" t="n">
         <v>5826</v>
@@ -39432,7 +39432,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1347" t="n">
         <v>1291</v>
@@ -39461,7 +39461,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1348" t="n">
         <v>5413</v>
@@ -39490,7 +39490,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1349" t="n">
         <v>61323</v>
@@ -39519,7 +39519,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1350" t="n">
         <v>5239</v>
@@ -39577,7 +39577,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1352" t="n">
         <v>1660</v>
@@ -39722,7 +39722,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1357" t="n">
         <v>855</v>
@@ -39751,7 +39751,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1358" t="n">
         <v>0</v>
@@ -39780,7 +39780,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1359" t="n">
         <v>0</v>
@@ -39838,7 +39838,7 @@
         <v>3.5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.06101322174072</v>
+        <v>3.0610134601593</v>
       </c>
       <c r="H1361" t="n">
         <v>22818</v>
@@ -39867,7 +39867,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1362" t="n">
         <v>16893</v>
@@ -39896,7 +39896,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.09599637985229</v>
+        <v>3.09599614143372</v>
       </c>
       <c r="H1363" t="n">
         <v>19094</v>
@@ -40041,7 +40041,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.27091145515442</v>
+        <v>3.27091121673584</v>
       </c>
       <c r="H1368" t="n">
         <v>10067</v>
@@ -40128,7 +40128,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.29714846611023</v>
+        <v>3.29714870452881</v>
       </c>
       <c r="H1371" t="n">
         <v>4031</v>
@@ -40186,7 +40186,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.24467420578003</v>
+        <v>3.24467396736145</v>
       </c>
       <c r="H1373" t="n">
         <v>4880</v>
@@ -40215,7 +40215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1374" t="n">
         <v>9425</v>
@@ -40302,7 +40302,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23592829704285</v>
+        <v>3.23592853546143</v>
       </c>
       <c r="H1377" t="n">
         <v>1800</v>
@@ -40331,7 +40331,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.16596221923828</v>
+        <v>3.16596245765686</v>
       </c>
       <c r="H1378" t="n">
         <v>1950</v>
@@ -40360,7 +40360,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1379" t="n">
         <v>13793</v>
@@ -40476,7 +40476,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.1572163105011</v>
+        <v>3.15721654891968</v>
       </c>
       <c r="H1383" t="n">
         <v>2020</v>
@@ -40505,7 +40505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.1572163105011</v>
+        <v>3.15721654891968</v>
       </c>
       <c r="H1384" t="n">
         <v>300</v>
@@ -40534,7 +40534,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.1572163105011</v>
+        <v>3.15721654891968</v>
       </c>
       <c r="H1385" t="n">
         <v>200</v>
@@ -40563,7 +40563,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.1484706401825</v>
+        <v>3.14847087860107</v>
       </c>
       <c r="H1386" t="n">
         <v>1215</v>
@@ -40592,7 +40592,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1387" t="n">
         <v>1000</v>
@@ -40621,7 +40621,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.11348795890808</v>
+        <v>3.1134877204895</v>
       </c>
       <c r="H1388" t="n">
         <v>0</v>
@@ -40650,7 +40650,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.17470812797546</v>
+        <v>3.17470836639404</v>
       </c>
       <c r="H1389" t="n">
         <v>942</v>
@@ -40708,7 +40708,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1391" t="n">
         <v>442</v>
@@ -40737,7 +40737,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.13972496986389</v>
+        <v>3.13972473144531</v>
       </c>
       <c r="H1392" t="n">
         <v>950</v>
@@ -40853,7 +40853,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.99979305267334</v>
+        <v>2.99979329109192</v>
       </c>
       <c r="H1396" t="n">
         <v>200</v>
@@ -40882,7 +40882,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1397" t="n">
         <v>597</v>
@@ -40911,7 +40911,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1398" t="n">
         <v>400</v>
@@ -41027,7 +41027,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1402" t="n">
         <v>233</v>
@@ -41056,7 +41056,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1403" t="n">
         <v>625</v>
@@ -41085,7 +41085,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1404" t="n">
         <v>5552</v>
@@ -41114,7 +41114,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1405" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1405" t="n">
         <v>4985</v>
@@ -41201,7 +41201,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1408" t="n">
         <v>141</v>
@@ -41230,7 +41230,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1409" t="n">
         <v>7666</v>
@@ -41346,7 +41346,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1413" t="n">
         <v>1559</v>
@@ -41375,7 +41375,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1414" t="n">
         <v>5019</v>
@@ -41404,7 +41404,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.97355604171753</v>
+        <v>2.97355580329895</v>
       </c>
       <c r="H1415" t="n">
         <v>7825</v>
@@ -41462,7 +41462,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.96481037139893</v>
+        <v>2.96481013298035</v>
       </c>
       <c r="H1417" t="n">
         <v>2002</v>
@@ -41491,7 +41491,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1418" t="n">
         <v>14401</v>
@@ -41607,7 +41607,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.00853872299194</v>
+        <v>3.00853896141052</v>
       </c>
       <c r="H1422" t="n">
         <v>3025</v>
@@ -41636,7 +41636,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.92108130455017</v>
+        <v>2.92108106613159</v>
       </c>
       <c r="H1423" t="n">
         <v>3547</v>
@@ -41665,7 +41665,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.93857288360596</v>
+        <v>2.93857264518738</v>
       </c>
       <c r="H1424" t="n">
         <v>6125</v>
@@ -41694,7 +41694,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.90358972549438</v>
+        <v>2.90358948707581</v>
       </c>
       <c r="H1425" t="n">
         <v>3463</v>
@@ -41723,7 +41723,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92982697486877</v>
+        <v>2.9298267364502</v>
       </c>
       <c r="H1426" t="n">
         <v>2150</v>
@@ -41897,7 +41897,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.73742055892944</v>
+        <v>2.73742032051086</v>
       </c>
       <c r="H1432" t="n">
         <v>7490</v>
@@ -42042,7 +42042,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1437" t="n">
         <v>3539</v>
@@ -42448,7 +42448,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1451" t="n">
         <v>5102</v>
@@ -42506,7 +42506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1453" t="n">
         <v>8150</v>
@@ -42622,7 +42622,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1457" t="n">
         <v>2600</v>
@@ -42651,7 +42651,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1458" t="n">
         <v>6595</v>
@@ -42680,7 +42680,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1459" t="n">
         <v>4900</v>
@@ -42709,7 +42709,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1460" t="n">
         <v>0</v>
@@ -42738,7 +42738,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1461" t="n">
         <v>957</v>
@@ -42796,7 +42796,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1463" t="n">
         <v>3565</v>
@@ -42854,7 +42854,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1465" t="n">
         <v>1000</v>
@@ -42912,7 +42912,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1467" t="n">
         <v>3295</v>
@@ -42941,7 +42941,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1468" t="n">
         <v>2753</v>
@@ -42970,7 +42970,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1469" t="n">
         <v>7000</v>
@@ -43057,7 +43057,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1472" t="n">
         <v>1042</v>
@@ -43144,7 +43144,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1475" t="n">
         <v>8292</v>
@@ -43173,7 +43173,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1476" t="n">
         <v>7332</v>
@@ -43231,7 +43231,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1478" t="n">
         <v>252613</v>
@@ -43376,7 +43376,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1483" t="n">
         <v>18307</v>
@@ -43434,7 +43434,7 @@
         <v>3.25</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1485" t="n">
         <v>11067</v>
@@ -43898,7 +43898,7 @@
         <v>3.25</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1501" t="n">
         <v>16390</v>
@@ -44188,7 +44188,7 @@
         <v>3.25</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1511" t="n">
         <v>200</v>
@@ -44275,7 +44275,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1514" t="n">
         <v>4539</v>
@@ -44304,7 +44304,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1515" t="n">
         <v>11432</v>
@@ -44333,7 +44333,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1516" t="n">
         <v>12387</v>
@@ -44478,7 +44478,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1521" t="n">
         <v>1669</v>
@@ -44594,7 +44594,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1525" t="n">
         <v>4558</v>
@@ -44623,7 +44623,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1526" t="n">
         <v>1820</v>
@@ -44652,7 +44652,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1527" t="n">
         <v>150</v>
@@ -45029,7 +45029,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1540" t="n">
         <v>50</v>
@@ -45348,7 +45348,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1551" t="n">
         <v>10350</v>
@@ -45377,7 +45377,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1552" t="n">
         <v>3808</v>
@@ -45406,7 +45406,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1553" t="n">
         <v>50</v>
@@ -45435,7 +45435,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1554" t="n">
         <v>18555</v>
@@ -45464,7 +45464,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1555" t="n">
         <v>1118</v>
@@ -45493,7 +45493,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1556" t="n">
         <v>1873</v>
@@ -45609,7 +45609,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1560" t="n">
         <v>2650</v>
@@ -45667,7 +45667,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1562" t="n">
         <v>6000</v>
@@ -45696,7 +45696,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1563" t="n">
         <v>1789</v>
@@ -45725,7 +45725,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1564" t="n">
         <v>2600</v>
@@ -45754,7 +45754,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1565" t="n">
         <v>8722</v>
@@ -45783,7 +45783,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1566" t="n">
         <v>6062</v>
@@ -45812,7 +45812,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1567" t="n">
         <v>25683</v>
@@ -45870,7 +45870,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1569" t="n">
         <v>14198</v>
@@ -45899,7 +45899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1570" t="n">
         <v>5400</v>
@@ -45986,7 +45986,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1573" t="n">
         <v>3411</v>
@@ -46015,7 +46015,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1574" t="n">
         <v>10144</v>
@@ -46073,7 +46073,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1576" t="n">
         <v>6055</v>
@@ -46189,7 +46189,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1580" t="n">
         <v>8200</v>
@@ -46247,7 +46247,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1582" t="n">
         <v>21214</v>
@@ -46595,7 +46595,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1594" t="n">
         <v>24870</v>
@@ -46624,7 +46624,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1595" t="n">
         <v>18412</v>
@@ -46769,7 +46769,7 @@
         <v>3.25</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1600" t="n">
         <v>4085</v>
@@ -46972,7 +46972,7 @@
         <v>3.25</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1607" t="n">
         <v>1951</v>
@@ -47030,7 +47030,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1609" t="n">
         <v>2751</v>
@@ -47059,7 +47059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1610" t="n">
         <v>1618</v>
@@ -47175,7 +47175,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1614" t="n">
         <v>10351</v>
@@ -47320,7 +47320,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1619" t="n">
         <v>1735</v>
@@ -47465,7 +47465,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.9026505947113</v>
+        <v>2.90265083312988</v>
       </c>
       <c r="H1624" t="n">
         <v>1361</v>
@@ -47610,7 +47610,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1629" t="n">
         <v>7874</v>
@@ -47784,7 +47784,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1635" t="n">
         <v>10171</v>
@@ -47813,7 +47813,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1636" t="n">
         <v>6601</v>
@@ -47871,7 +47871,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1638" t="n">
         <v>2344</v>
@@ -47900,7 +47900,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1639" t="n">
         <v>4700</v>
@@ -47958,7 +47958,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1641" t="n">
         <v>1566</v>
@@ -47987,7 +47987,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1642" t="n">
         <v>9227</v>
@@ -48016,7 +48016,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1643" t="n">
         <v>7310</v>
@@ -48045,7 +48045,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1644" t="n">
         <v>1000</v>
@@ -48132,7 +48132,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1647" t="n">
         <v>6041</v>
@@ -48161,7 +48161,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1648" t="n">
         <v>1964</v>
@@ -48248,7 +48248,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1651" t="n">
         <v>200</v>
@@ -48364,7 +48364,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1655" t="n">
         <v>5050</v>
@@ -48683,7 +48683,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1666" t="n">
         <v>2600</v>
@@ -48944,7 +48944,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.49975919723511</v>
+        <v>2.49975895881653</v>
       </c>
       <c r="H1675" t="n">
         <v>6817</v>
@@ -48973,7 +48973,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1676" t="n">
         <v>5212</v>
@@ -49060,7 +49060,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1679" t="n">
         <v>5506</v>
@@ -49263,7 +49263,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1686" t="n">
         <v>19737</v>
@@ -49292,7 +49292,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1687" t="n">
         <v>2100</v>
@@ -49350,7 +49350,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1689" t="n">
         <v>10000</v>
@@ -49437,7 +49437,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1692" t="n">
         <v>7400</v>
@@ -49669,7 +49669,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1700" t="n">
         <v>17055</v>
@@ -49727,7 +49727,7 @@
         <v>3.25</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1702" t="n">
         <v>23657</v>
@@ -49756,7 +49756,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1703" t="n">
         <v>6507</v>
@@ -49814,7 +49814,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1705" t="n">
         <v>39</v>
@@ -49843,7 +49843,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1706" t="n">
         <v>6965</v>
@@ -49872,7 +49872,7 @@
         <v>3.25</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1707" t="n">
         <v>14247</v>
@@ -50133,7 +50133,7 @@
         <v>3.25</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1716" t="n">
         <v>12714</v>
@@ -50162,7 +50162,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1717" t="n">
         <v>8150</v>
@@ -50539,7 +50539,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.049156665802</v>
+        <v>3.04915642738342</v>
       </c>
       <c r="H1730" t="n">
         <v>2212</v>
@@ -50684,7 +50684,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1735" t="n">
         <v>1964</v>
@@ -50713,7 +50713,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1736" t="n">
         <v>5543</v>
@@ -50800,7 +50800,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.95759034156799</v>
+        <v>2.95759057998657</v>
       </c>
       <c r="H1739" t="n">
         <v>5500</v>
@@ -50829,7 +50829,7 @@
         <v>3.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.97590374946594</v>
+        <v>2.97590351104736</v>
       </c>
       <c r="H1740" t="n">
         <v>2956</v>
@@ -51902,7 +51902,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1777" t="n">
         <v>500</v>
@@ -52076,7 +52076,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.92096400260925</v>
+        <v>2.92096376419067</v>
       </c>
       <c r="H1783" t="n">
         <v>695</v>
@@ -52656,7 +52656,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1803" t="n">
         <v>1000</v>
@@ -52743,7 +52743,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.77445769309998</v>
+        <v>2.77445793151855</v>
       </c>
       <c r="H1806" t="n">
         <v>1500</v>
@@ -52801,7 +52801,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1808" t="n">
         <v>708</v>
@@ -52830,7 +52830,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.82939743995667</v>
+        <v>2.82939767837524</v>
       </c>
       <c r="H1809" t="n">
         <v>0</v>
@@ -53033,7 +53033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1816" t="n">
         <v>4470</v>
@@ -53062,7 +53062,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1817" t="n">
         <v>4905</v>
@@ -53091,7 +53091,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1818" t="n">
         <v>5181</v>
@@ -53149,7 +53149,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1820" t="n">
         <v>5370</v>
@@ -53178,7 +53178,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1821" t="n">
         <v>0</v>
@@ -53207,7 +53207,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1822" t="n">
         <v>0</v>
@@ -53294,7 +53294,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1825" t="n">
         <v>2500</v>
@@ -53352,7 +53352,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1827" t="n">
         <v>6300</v>
@@ -53468,7 +53468,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1831" t="n">
         <v>2764</v>
@@ -53497,7 +53497,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1832" t="n">
         <v>7985</v>
@@ -53526,7 +53526,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.6554217338562</v>
+        <v>2.65542197227478</v>
       </c>
       <c r="H1833" t="n">
         <v>13237</v>
@@ -53642,7 +53642,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1837" t="n">
         <v>3566</v>
@@ -53671,7 +53671,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1838" t="n">
         <v>4827</v>
@@ -53729,7 +53729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1840" t="n">
         <v>4580</v>
@@ -53758,7 +53758,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1841" t="n">
         <v>1250</v>
@@ -53874,7 +53874,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1845" t="n">
         <v>4344</v>
@@ -53961,7 +53961,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1848" t="n">
         <v>1420</v>
@@ -53990,7 +53990,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1849" t="n">
         <v>2250</v>
@@ -54077,7 +54077,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.64626502990723</v>
+        <v>2.64626526832581</v>
       </c>
       <c r="H1852" t="n">
         <v>9811</v>
@@ -54251,7 +54251,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1858" t="n">
         <v>32665</v>
@@ -54309,7 +54309,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1860" t="n">
         <v>5060</v>
@@ -54570,7 +54570,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53638577461243</v>
+        <v>2.53638553619385</v>
       </c>
       <c r="H1869" t="n">
         <v>995</v>
@@ -54686,7 +54686,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.5546989440918</v>
+        <v>2.55469870567322</v>
       </c>
       <c r="H1873" t="n">
         <v>1966</v>
@@ -54802,7 +54802,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1877" t="n">
         <v>84</v>
@@ -54831,7 +54831,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1878" t="n">
         <v>856</v>
@@ -54947,7 +54947,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1882" t="n">
         <v>4480</v>
@@ -54976,7 +54976,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1883" t="n">
         <v>0</v>
@@ -55063,7 +55063,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1886" t="n">
         <v>1550</v>
@@ -55121,7 +55121,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1888" t="n">
         <v>2000</v>
@@ -55150,7 +55150,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.60963845252991</v>
+        <v>2.60963869094849</v>
       </c>
       <c r="H1889" t="n">
         <v>1694</v>
@@ -55208,7 +55208,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1891" t="n">
         <v>5040</v>
@@ -55266,7 +55266,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1893" t="n">
         <v>255</v>
@@ -55295,7 +55295,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1894" t="n">
         <v>2350</v>
@@ -55324,7 +55324,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1895" t="n">
         <v>3524</v>
@@ -55353,7 +55353,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1896" t="n">
         <v>7241</v>
@@ -55382,7 +55382,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1897" t="n">
         <v>0</v>
@@ -55411,7 +55411,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.59132504463196</v>
+        <v>2.59132528305054</v>
       </c>
       <c r="H1898" t="n">
         <v>9000</v>
@@ -55469,7 +55469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1900" t="n">
         <v>4150</v>
@@ -55614,7 +55614,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.79277110099792</v>
+        <v>2.79277086257935</v>
       </c>
       <c r="H1905" t="n">
         <v>4525</v>
@@ -55643,7 +55643,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1906" t="n">
         <v>4000</v>
@@ -55759,7 +55759,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.72867465019226</v>
+        <v>2.72867488861084</v>
       </c>
       <c r="H1910" t="n">
         <v>1000</v>
@@ -55875,7 +55875,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.30746984481812</v>
+        <v>2.30747008323669</v>
       </c>
       <c r="H1914" t="n">
         <v>52544</v>
@@ -55962,7 +55962,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1917" t="n">
         <v>13522</v>
@@ -55991,7 +55991,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.50891590118408</v>
+        <v>2.5089156627655</v>
       </c>
       <c r="H1918" t="n">
         <v>5361</v>
@@ -56426,7 +56426,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1933" t="n">
         <v>1893</v>
@@ -56455,7 +56455,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.60048174858093</v>
+        <v>2.60048198699951</v>
       </c>
       <c r="H1934" t="n">
         <v>1786</v>
@@ -56542,7 +56542,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1937" t="n">
         <v>7603</v>
@@ -56571,7 +56571,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78361439704895</v>
+        <v>2.78361463546753</v>
       </c>
       <c r="H1938" t="n">
         <v>3411</v>
@@ -67234,7 +67234,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="D2306" t="n">
-        <v>5.46000003814697</v>
+        <v>5.48000001907349</v>
       </c>
       <c r="E2306" t="n">
         <v>5.28000020980835</v>
@@ -67249,6 +67249,35 @@
         <v>4119</v>
       </c>
       <c r="I2306" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2307" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2307" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="H2307" t="n">
+        <v>7316</v>
+      </c>
+      <c r="I2307" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.91417598724365</v>
+        <v>2.91417622566223</v>
       </c>
       <c r="H2" t="n">
         <v>507500</v>
@@ -485,7 +485,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78459334373474</v>
+        <v>2.7845938205719</v>
       </c>
       <c r="H4" t="n">
         <v>65500</v>
@@ -514,7 +514,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>2.87242126464844</v>
+        <v>2.8724217414856</v>
       </c>
       <c r="H5" t="n">
         <v>117500</v>
@@ -543,7 +543,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8652229309082</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H6" t="n">
         <v>89500</v>
@@ -572,7 +572,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83930587768555</v>
+        <v>2.83930611610413</v>
       </c>
       <c r="H7" t="n">
         <v>35500</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H11" t="n">
         <v>24000</v>
@@ -717,7 +717,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G12" t="n">
-        <v>2.87242126464844</v>
+        <v>2.8724217414856</v>
       </c>
       <c r="H12" t="n">
         <v>41000</v>
@@ -775,7 +775,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G14" t="n">
-        <v>2.87818121910095</v>
+        <v>2.87818074226379</v>
       </c>
       <c r="H14" t="n">
         <v>11000</v>
@@ -862,7 +862,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94873189926147</v>
+        <v>2.9487316608429</v>
       </c>
       <c r="H17" t="n">
         <v>16000</v>
@@ -891,7 +891,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94009280204773</v>
+        <v>2.94009304046631</v>
       </c>
       <c r="H18" t="n">
         <v>3000</v>
@@ -978,7 +978,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8652229309082</v>
+        <v>2.86522269248962</v>
       </c>
       <c r="H21" t="n">
         <v>7500</v>
@@ -1007,7 +1007,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H22" t="n">
         <v>19000</v>
@@ -1065,7 +1065,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9012176990509</v>
+        <v>2.90121817588806</v>
       </c>
       <c r="H24" t="n">
         <v>38500</v>
@@ -1094,7 +1094,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91561579704285</v>
+        <v>2.91561627388</v>
       </c>
       <c r="H25" t="n">
         <v>12500</v>
@@ -1181,7 +1181,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89113903045654</v>
+        <v>2.89113879203796</v>
       </c>
       <c r="H28" t="n">
         <v>6000</v>
@@ -1210,7 +1210,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.91561579704285</v>
+        <v>2.91561627388</v>
       </c>
       <c r="H29" t="n">
         <v>8500</v>
@@ -1239,7 +1239,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G30" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H30" t="n">
         <v>4500</v>
@@ -1268,7 +1268,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93433380126953</v>
+        <v>2.93433356285095</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>2.89113903045654</v>
+        <v>2.89113879203796</v>
       </c>
       <c r="H33" t="n">
         <v>15500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H39" t="n">
         <v>5500</v>
@@ -1558,7 +1558,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H41" t="n">
         <v>30500</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H42" t="n">
         <v>9000</v>
@@ -1616,7 +1616,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1645,7 +1645,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79179215431213</v>
+        <v>2.79179239273071</v>
       </c>
       <c r="H44" t="n">
         <v>4500</v>
@@ -1674,7 +1674,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>2.81338930130005</v>
+        <v>2.81338953971863</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87818121910095</v>
+        <v>2.87818074226379</v>
       </c>
       <c r="H46" t="n">
         <v>500</v>
@@ -1761,7 +1761,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H48" t="n">
         <v>1500</v>
@@ -1790,7 +1790,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G49" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H49" t="n">
         <v>3000</v>
@@ -1964,7 +1964,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482911109924</v>
       </c>
       <c r="H55" t="n">
         <v>1500</v>
@@ -2080,7 +2080,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72412109375</v>
+        <v>2.72412085533142</v>
       </c>
       <c r="H59" t="n">
         <v>8000</v>
@@ -2225,7 +2225,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2283,7 +2283,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G66" t="n">
-        <v>2.69532465934753</v>
+        <v>2.69532489776611</v>
       </c>
       <c r="H66" t="n">
         <v>11000</v>
@@ -2341,7 +2341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>2.77163457870483</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H68" t="n">
         <v>3000</v>
@@ -2370,7 +2370,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>2.77163457870483</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.77163457870483</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H74" t="n">
         <v>11500</v>
@@ -2544,7 +2544,7 @@
         <v>3.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>3.75</v>
       </c>
       <c r="G76" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H76" t="n">
         <v>1000</v>
@@ -2602,7 +2602,7 @@
         <v>3.75</v>
       </c>
       <c r="G77" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H77" t="n">
         <v>7500</v>
@@ -2718,7 +2718,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G81" t="n">
-        <v>2.65069079399109</v>
+        <v>2.65069055557251</v>
       </c>
       <c r="H81" t="n">
         <v>5000</v>
@@ -2776,7 +2776,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>2.67804741859436</v>
+        <v>2.67804718017578</v>
       </c>
       <c r="H83" t="n">
         <v>4000</v>
@@ -2805,7 +2805,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.68524622917175</v>
+        <v>2.68524646759033</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2834,7 +2834,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>2.69244527816772</v>
+        <v>2.69244503974915</v>
       </c>
       <c r="H85" t="n">
         <v>500</v>
@@ -2863,7 +2863,7 @@
         <v>3.75</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69964408874512</v>
+        <v>2.6996443271637</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2921,7 +2921,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.69244527816772</v>
+        <v>2.69244503974915</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -2950,7 +2950,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59885740280151</v>
+        <v>2.59885764122009</v>
       </c>
       <c r="H89" t="n">
         <v>5000</v>
@@ -2979,7 +2979,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>2.59885740280151</v>
+        <v>2.59885764122009</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H91" t="n">
         <v>6500</v>
@@ -3269,7 +3269,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3298,7 +3298,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.60605669021606</v>
+        <v>2.60605645179749</v>
       </c>
       <c r="H101" t="n">
         <v>500</v>
@@ -3385,7 +3385,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H104" t="n">
         <v>10500</v>
@@ -3414,7 +3414,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.67084789276123</v>
+        <v>2.67084813117981</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.55566310882568</v>
+        <v>2.55566334724426</v>
       </c>
       <c r="H112" t="n">
         <v>24000</v>
@@ -3733,7 +3733,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.57006144523621</v>
+        <v>2.57006168365479</v>
       </c>
       <c r="H116" t="n">
         <v>11000</v>
@@ -3762,7 +3762,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>2.57006144523621</v>
+        <v>2.57006168365479</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H125" t="n">
         <v>5500</v>
@@ -4023,7 +4023,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.5916588306427</v>
+        <v>2.59165859222412</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.58445930480957</v>
+        <v>2.58445954322815</v>
       </c>
       <c r="H127" t="n">
         <v>22500</v>
@@ -4139,7 +4139,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>2.6276535987854</v>
+        <v>2.62765383720398</v>
       </c>
       <c r="H130" t="n">
         <v>2500</v>
@@ -4197,7 +4197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H132" t="n">
         <v>31000</v>
@@ -4226,7 +4226,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77163457870483</v>
+        <v>2.77163481712341</v>
       </c>
       <c r="H133" t="n">
         <v>45500</v>
@@ -4255,7 +4255,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H134" t="n">
         <v>17500</v>
@@ -4284,7 +4284,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4835,7 +4835,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H154" t="n">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.80763006210327</v>
+        <v>2.80762982368469</v>
       </c>
       <c r="H158" t="n">
         <v>1000</v>
@@ -4980,7 +4980,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.82202839851379</v>
+        <v>2.82202816009521</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H166" t="n">
         <v>20000</v>
@@ -5241,7 +5241,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>2.84362554550171</v>
+        <v>2.84362578392029</v>
       </c>
       <c r="H168" t="n">
         <v>8500</v>
@@ -5415,7 +5415,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>2.8260600566864</v>
+        <v>2.82605981826782</v>
       </c>
       <c r="H174" t="n">
         <v>5000</v>
@@ -5618,7 +5618,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G181" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H181" t="n">
         <v>1000</v>
@@ -5647,7 +5647,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G182" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H182" t="n">
         <v>2000</v>
@@ -5676,7 +5676,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H183" t="n">
         <v>1500</v>
@@ -5705,7 +5705,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>2.63865566253662</v>
+        <v>2.63865542411804</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66114377975464</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H185" t="n">
         <v>500</v>
@@ -5763,7 +5763,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G186" t="n">
-        <v>2.70612072944641</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5792,7 +5792,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.9010214805603</v>
+        <v>2.90102124214172</v>
       </c>
       <c r="H187" t="n">
         <v>2000</v>
@@ -5850,7 +5850,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H189" t="n">
         <v>9000</v>
@@ -5879,7 +5879,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H190" t="n">
         <v>9500</v>
@@ -5908,7 +5908,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.80357146263123</v>
+        <v>2.80357122421265</v>
       </c>
       <c r="H191" t="n">
         <v>2500</v>
@@ -6082,7 +6082,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.78108310699463</v>
+        <v>2.78108286857605</v>
       </c>
       <c r="H197" t="n">
         <v>11500</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.78108310699463</v>
+        <v>2.78108286857605</v>
       </c>
       <c r="H212" t="n">
         <v>3000</v>
@@ -6546,7 +6546,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G213" t="n">
-        <v>2.89352560043335</v>
+        <v>2.89352536201477</v>
       </c>
       <c r="H213" t="n">
         <v>18000</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.78108310699463</v>
+        <v>2.78108286857605</v>
       </c>
       <c r="H216" t="n">
         <v>5500</v>
@@ -6807,7 +6807,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H222" t="n">
         <v>10000</v>
@@ -6836,7 +6836,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>2.70612072944641</v>
+        <v>2.70612096786499</v>
       </c>
       <c r="H223" t="n">
         <v>5500</v>
@@ -6894,7 +6894,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.58618211746216</v>
+        <v>2.58618235588074</v>
       </c>
       <c r="H225" t="n">
         <v>6500</v>
@@ -6981,7 +6981,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>2.60867071151733</v>
+        <v>2.60867094993591</v>
       </c>
       <c r="H228" t="n">
         <v>1500</v>
@@ -7039,7 +7039,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.66114377975464</v>
+        <v>2.66114401817322</v>
       </c>
       <c r="H230" t="n">
         <v>1500</v>
@@ -7271,7 +7271,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>2.88602900505066</v>
+        <v>2.88602924346924</v>
       </c>
       <c r="H238" t="n">
         <v>500</v>
@@ -7300,7 +7300,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>2.8260600566864</v>
+        <v>2.82605981826782</v>
       </c>
       <c r="H239" t="n">
         <v>4000</v>
@@ -7532,7 +7532,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G247" t="n">
-        <v>2.76609063148499</v>
+        <v>2.76609039306641</v>
       </c>
       <c r="H247" t="n">
         <v>5000</v>
@@ -7764,7 +7764,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G255" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G256" t="n">
-        <v>2.87853312492371</v>
+        <v>2.87853288650513</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.69862484931946</v>
+        <v>2.69862461090088</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.32381582260132</v>
+        <v>2.3238160610199</v>
       </c>
       <c r="H276" t="n">
         <v>4000</v>
@@ -8431,7 +8431,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.2638463973999</v>
+        <v>2.26384663581848</v>
       </c>
       <c r="H278" t="n">
         <v>5500</v>
@@ -8460,7 +8460,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>2.2638463973999</v>
+        <v>2.26384663581848</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.27883863449097</v>
+        <v>2.27883887290955</v>
       </c>
       <c r="H280" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G282" t="n">
-        <v>2.16639614105225</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8576,7 +8576,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>2.24135804176331</v>
+        <v>2.24135780334473</v>
       </c>
       <c r="H283" t="n">
         <v>70000</v>
@@ -8634,7 +8634,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.16639614105225</v>
+        <v>2.16639637947083</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G286" t="n">
-        <v>2.10642647743225</v>
+        <v>2.10642623901367</v>
       </c>
       <c r="H286" t="n">
         <v>15500</v>
@@ -8692,7 +8692,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G287" t="n">
-        <v>2.19638085365295</v>
+        <v>2.19638061523438</v>
       </c>
       <c r="H287" t="n">
         <v>3000</v>
@@ -8982,7 +8982,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03146481513977</v>
+        <v>2.03146457672119</v>
       </c>
       <c r="H297" t="n">
         <v>14000</v>
@@ -9011,7 +9011,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.07644200325012</v>
+        <v>2.07644152641296</v>
       </c>
       <c r="H298" t="n">
         <v>7500</v>
@@ -9127,7 +9127,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10642647743225</v>
+        <v>2.10642623901367</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.14390754699707</v>
+        <v>2.14390778541565</v>
       </c>
       <c r="H303" t="n">
         <v>2500</v>
@@ -9359,7 +9359,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.3987774848938</v>
+        <v>2.39877796173096</v>
       </c>
       <c r="H310" t="n">
         <v>18500</v>
@@ -9388,7 +9388,7 @@
         <v>3.25</v>
       </c>
       <c r="G311" t="n">
-        <v>2.43625855445862</v>
+        <v>2.43625831604004</v>
       </c>
       <c r="H311" t="n">
         <v>27000</v>
@@ -9446,7 +9446,7 @@
         <v>3.200000